--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5283BC68-0D19-45AE-B2A9-CE59501C6B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701D4624-A200-4269-A505-39D628B6F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -784,7 +784,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -805,18 +805,18 @@
         <v>866</v>
       </c>
       <c r="H2">
-        <v>4296</v>
+        <v>4441</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.2087</v>
+        <v>0.21579999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -837,18 +837,18 @@
         <v>278</v>
       </c>
       <c r="H3">
-        <v>599</v>
+        <v>669</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.1981</v>
+        <v>0.22120000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -869,18 +869,18 @@
         <v>1610</v>
       </c>
       <c r="H4">
-        <v>3458</v>
+        <v>4059</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.17810000000000001</v>
+        <v>0.20910000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -901,18 +901,18 @@
         <v>2269</v>
       </c>
       <c r="H5">
-        <v>4950</v>
+        <v>5837</v>
       </c>
       <c r="I5">
         <v>27456</v>
       </c>
       <c r="J5" s="1">
-        <v>0.18029999999999999</v>
+        <v>0.21260000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -933,18 +933,18 @@
         <v>116</v>
       </c>
       <c r="H6">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.1759</v>
+        <v>0.19439999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -965,18 +965,18 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>0.20319999999999999</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -997,18 +997,18 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8">
         <v>48</v>
       </c>
       <c r="J8" s="1">
-        <v>0.25</v>
+        <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1029,18 +1029,18 @@
         <v>78</v>
       </c>
       <c r="H9">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.18</v>
+        <v>0.22950000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1061,18 +1061,18 @@
         <v>290</v>
       </c>
       <c r="H10">
-        <v>636</v>
+        <v>770</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.17910000000000001</v>
+        <v>0.21679999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1093,18 +1093,18 @@
         <v>212</v>
       </c>
       <c r="H11">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.185</v>
+        <v>0.21010000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1125,18 +1125,18 @@
         <v>52</v>
       </c>
       <c r="H12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.1779</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1157,18 +1157,18 @@
         <v>58</v>
       </c>
       <c r="H13">
-        <v>5264</v>
+        <v>5878</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.2059</v>
+        <v>0.22989999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1189,18 +1189,18 @@
         <v>55</v>
       </c>
       <c r="H14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.21049999999999999</v>
+        <v>0.22370000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1221,18 +1221,18 @@
         <v>55</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15">
         <v>57</v>
       </c>
       <c r="J15" s="1">
-        <v>0.2281</v>
+        <v>0.24560000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1253,18 +1253,18 @@
         <v>133</v>
       </c>
       <c r="H16">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.2044</v>
+        <v>0.2135</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1317,18 +1317,18 @@
         <v>43</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I18">
         <v>90</v>
       </c>
       <c r="J18" s="1">
-        <v>0.2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1349,18 +1349,18 @@
         <v>621</v>
       </c>
       <c r="H19">
-        <v>23782</v>
+        <v>25779</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.20269999999999999</v>
+        <v>0.21970000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1381,18 +1381,18 @@
         <v>98</v>
       </c>
       <c r="H20">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.18940000000000001</v>
+        <v>0.2109</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1413,18 +1413,18 @@
         <v>43</v>
       </c>
       <c r="H21">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.1744</v>
+        <v>0.20930000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1445,18 +1445,18 @@
         <v>116</v>
       </c>
       <c r="H22">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.17580000000000001</v>
+        <v>0.19420000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1534,11 +1534,19 @@
       <c r="F26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="H26">
+        <v>41</v>
+      </c>
+      <c r="I26">
+        <v>137</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.29930000000000001</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1559,18 +1567,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.2041</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1591,18 +1599,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>0.19500000000000001</v>
+        <v>0.22339999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1623,18 +1631,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.20200000000000001</v>
+        <v>0.2288</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1655,18 +1663,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>886</v>
+        <v>980</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.1855</v>
+        <v>0.20519999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1698,7 +1706,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1730,7 +1738,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1751,18 +1759,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.2213</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1783,18 +1791,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.47460000000000002</v>
+        <v>0.50849999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1815,18 +1823,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>9.8199999999999996E-2</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1847,18 +1855,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.1358</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1890,7 +1898,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1911,18 +1919,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.1103</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1951,7 +1959,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1983,7 +1991,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2004,18 +2012,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.3468</v>
+        <v>0.36459999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2036,18 +2044,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.17</v>
+        <v>0.20250000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2079,7 +2087,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2100,18 +2108,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.17749999999999999</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2143,7 +2151,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2172,7 +2180,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2193,18 +2201,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>1595806</v>
+        <v>1799113</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.19239999999999999</v>
+        <v>0.21690000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2225,18 +2233,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>257951</v>
+        <v>284027</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.18720000000000001</v>
+        <v>0.20610000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2257,18 +2265,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>2921</v>
+        <v>3274</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.18809999999999999</v>
+        <v>0.21079999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2289,18 +2297,18 @@
         <v>691098</v>
       </c>
       <c r="H50">
-        <v>570532</v>
+        <v>578317</v>
       </c>
       <c r="I50">
         <v>2764392</v>
       </c>
       <c r="J50" s="1">
-        <v>0.2064</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2321,18 +2329,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>212171</v>
+        <v>227572</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.30690000000000001</v>
+        <v>0.32919999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2353,18 +2361,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.19420000000000001</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2385,18 +2393,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.28539999999999999</v>
+        <v>0.31940000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2417,18 +2425,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>384</v>
+        <v>424</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.1731</v>
+        <v>0.19120000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2449,18 +2457,18 @@
         <v>649</v>
       </c>
       <c r="H55">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I55">
         <v>649</v>
       </c>
       <c r="J55" s="1">
-        <v>0.11559999999999999</v>
+        <v>0.15409999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2481,18 +2489,18 @@
         <v>331</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I56">
         <v>331</v>
       </c>
       <c r="J56" s="1">
-        <v>4.8300000000000003E-2</v>
+        <v>7.5499999999999998E-2</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2521,7 +2529,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2542,18 +2550,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.18859999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2574,18 +2582,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.18790000000000001</v>
+        <v>0.21809999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2606,7 +2614,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2627,18 +2635,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>1710</v>
+        <v>1860</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.19470000000000001</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2659,18 +2667,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>0.23050000000000001</v>
+        <v>0.23569999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2691,18 +2699,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1317</v>
+        <v>1667</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.17150000000000001</v>
+        <v>0.21709999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2723,18 +2731,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>1640</v>
+        <v>1938</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.1832</v>
+        <v>0.2165</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2755,18 +2763,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="I65">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="J65" s="1">
-        <v>0.1757</v>
+        <v>0.19139999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2787,18 +2795,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I66">
         <v>240</v>
       </c>
       <c r="J66" s="1">
-        <v>0.1958</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2819,18 +2827,18 @@
         <v>25</v>
       </c>
       <c r="H67">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I67">
         <v>300</v>
       </c>
       <c r="J67" s="1">
-        <v>0.2167</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2851,18 +2859,18 @@
         <v>3</v>
       </c>
       <c r="H68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2883,18 +2891,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I69">
         <v>876</v>
       </c>
       <c r="J69" s="1">
-        <v>0.17810000000000001</v>
+        <v>0.18379999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2915,18 +2923,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.21940000000000001</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2947,18 +2955,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>619</v>
+        <v>719</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>0.18890000000000001</v>
+        <v>0.2195</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2979,18 +2987,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>938</v>
+        <v>1036</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.18360000000000001</v>
+        <v>0.20269999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3011,18 +3019,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3054,7 +3062,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3075,18 +3083,18 @@
         <v>52</v>
       </c>
       <c r="H75">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I75">
         <v>208</v>
       </c>
       <c r="J75" s="1">
-        <v>0.22120000000000001</v>
+        <v>0.22600000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3107,18 +3115,18 @@
         <v>47</v>
       </c>
       <c r="H76">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I76">
         <v>52</v>
       </c>
       <c r="J76" s="1">
-        <v>0.65380000000000005</v>
+        <v>0.67310000000000003</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3150,7 +3158,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3182,7 +3190,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3203,18 +3211,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>0.21029999999999999</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3235,18 +3243,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>778</v>
+        <v>1722</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>0.22589999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3267,18 +3275,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>189</v>
+        <v>418</v>
       </c>
       <c r="I81">
         <v>948</v>
       </c>
       <c r="J81" s="1">
-        <v>0.19939999999999999</v>
+        <v>0.44090000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3299,18 +3307,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="I82">
-        <v>1644</v>
+        <v>1632</v>
       </c>
       <c r="J82" s="1">
-        <v>0.17519999999999999</v>
+        <v>0.18870000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3331,7 +3339,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3352,18 +3360,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>0.1724</v>
+        <v>0.18099999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3395,7 +3403,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3416,18 +3424,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1407</v>
+        <v>1520</v>
       </c>
       <c r="I86">
         <v>7032</v>
       </c>
       <c r="J86" s="1">
-        <v>0.2001</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3448,18 +3456,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.1779</v>
+        <v>0.19139999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3480,18 +3488,18 @@
         <v>493</v>
       </c>
       <c r="H88">
-        <v>1021</v>
+        <v>1139</v>
       </c>
       <c r="I88">
         <v>5916</v>
       </c>
       <c r="J88" s="1">
-        <v>0.1726</v>
+        <v>0.1925</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3523,7 +3531,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3555,7 +3563,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3576,18 +3584,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="I91">
         <v>1932</v>
       </c>
       <c r="J91" s="1">
-        <v>0.19620000000000001</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3608,18 +3616,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="I92">
         <v>1128</v>
       </c>
       <c r="J92" s="1">
-        <v>0.19769999999999999</v>
+        <v>0.2172</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3640,18 +3648,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.18329999999999999</v>
+        <v>0.18790000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3672,7 +3680,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3693,18 +3701,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.17960000000000001</v>
+        <v>0.19070000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3725,7 +3733,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3746,18 +3754,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.26669999999999999</v>
+        <v>0.29499999999999998</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3778,18 +3786,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I98">
         <v>60</v>
       </c>
       <c r="J98" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3821,7 +3829,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3853,7 +3861,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3870,22 +3878,11 @@
       <c r="F101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G101">
-        <v>33</v>
-      </c>
-      <c r="H101">
-        <v>4</v>
-      </c>
-      <c r="I101">
-        <v>33</v>
-      </c>
-      <c r="J101" s="1">
-        <v>0.1212</v>
-      </c>
+      <c r="J101" s="1"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3917,7 +3914,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3949,7 +3946,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3970,18 +3967,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.18060000000000001</v>
+        <v>0.19170000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4002,18 +3999,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4034,18 +4031,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I106">
         <v>552</v>
       </c>
       <c r="J106" s="1">
-        <v>0.183</v>
+        <v>0.18840000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4066,7 +4063,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4087,18 +4084,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I108">
         <v>611</v>
       </c>
       <c r="J108" s="1">
-        <v>0.1817</v>
+        <v>0.18659999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4119,7 +4116,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4151,7 +4148,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4183,7 +4180,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4215,7 +4212,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4247,7 +4244,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4311,7 +4308,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4343,7 +4340,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4375,7 +4372,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4407,7 +4404,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4439,7 +4436,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4471,7 +4468,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4503,7 +4500,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4535,7 +4532,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4567,7 +4564,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4599,7 +4596,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4631,7 +4628,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4663,7 +4660,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4695,7 +4692,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4727,7 +4724,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4759,7 +4756,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4791,7 +4788,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4823,7 +4820,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4855,7 +4852,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4887,7 +4884,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4907,7 +4904,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4928,7 +4925,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4949,7 +4946,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4970,18 +4967,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.1646</v>
+        <v>0.17480000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5002,18 +4999,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>1339</v>
+        <v>1641</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>0.19070000000000001</v>
+        <v>0.23380000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5034,18 +5031,18 @@
         <v>383</v>
       </c>
       <c r="H139">
-        <v>1880</v>
+        <v>1949</v>
       </c>
       <c r="I139">
         <v>9144</v>
       </c>
       <c r="J139" s="1">
-        <v>0.2056</v>
+        <v>0.21310000000000001</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5077,7 +5074,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5109,7 +5106,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5130,18 +5127,18 @@
         <v>22</v>
       </c>
       <c r="H142">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I142">
         <v>264</v>
       </c>
       <c r="J142" s="1">
-        <v>0.18179999999999999</v>
+        <v>0.21590000000000001</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5173,7 +5170,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5194,18 +5191,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>2022</v>
+        <v>2426</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>0.18759999999999999</v>
+        <v>0.22509999999999999</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5226,18 +5223,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.1905</v>
+        <v>0.2354</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5258,18 +5255,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>0.2054</v>
+        <v>0.21429999999999999</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5290,18 +5287,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.18329999999999999</v>
+        <v>0.19719999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5322,18 +5319,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.16830000000000001</v>
+        <v>0.17949999999999999</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5365,7 +5362,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5397,7 +5394,7 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5429,7 +5426,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5450,18 +5447,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>1054</v>
+        <v>1171</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.22209999999999999</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5493,7 +5490,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5525,7 +5522,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5589,7 +5586,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5621,7 +5618,7 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5653,7 +5650,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5674,18 +5671,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.17480000000000001</v>
+        <v>0.18290000000000001</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5717,7 +5714,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5738,18 +5735,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.1822</v>
+        <v>0.1963</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5770,18 +5767,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.1759</v>
+        <v>0.1835</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5802,18 +5799,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>1881</v>
+        <v>1977</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.20250000000000001</v>
+        <v>0.21290000000000001</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5834,18 +5831,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>0.18379999999999999</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5866,18 +5863,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1279</v>
+        <v>1529</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.18060000000000001</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5898,18 +5895,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>2329</v>
+        <v>2724</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.20130000000000001</v>
+        <v>0.23549999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5930,18 +5927,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.1719</v>
+        <v>0.18840000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5962,18 +5959,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>0.19869999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6005,7 +6002,7 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6037,7 +6034,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6058,18 +6055,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.1497</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6090,18 +6087,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.18790000000000001</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6133,7 +6130,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6154,18 +6151,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>2216</v>
+        <v>2463</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.2024</v>
+        <v>0.22489999999999999</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6197,7 +6194,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6226,7 +6223,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6247,18 +6244,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>0.19589999999999999</v>
+        <v>0.20269999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6279,18 +6276,18 @@
         <v>37</v>
       </c>
       <c r="H178">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I178">
         <v>37</v>
       </c>
       <c r="J178" s="1">
-        <v>0.18920000000000001</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6322,7 +6319,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6354,7 +6351,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6375,18 +6372,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.17249999999999999</v>
+        <v>0.19409999999999999</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6407,18 +6404,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.18290000000000001</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6450,7 +6447,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6471,18 +6468,18 @@
         <v>9</v>
       </c>
       <c r="H184">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I184">
         <v>108</v>
       </c>
       <c r="J184" s="1">
-        <v>0.1759</v>
+        <v>0.1852</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6503,18 +6500,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.17230000000000001</v>
+        <v>0.1903</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6535,7 +6532,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6567,7 +6564,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6588,18 +6585,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>0.1898</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6620,18 +6617,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>0.1759</v>
+        <v>0.19439999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6652,18 +6649,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>0.185</v>
+        <v>0.20480000000000001</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6684,18 +6681,18 @@
         <v>59</v>
       </c>
       <c r="H191">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I191">
         <v>59</v>
       </c>
       <c r="J191" s="1">
-        <v>0.30509999999999998</v>
+        <v>0.40679999999999999</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6716,18 +6713,18 @@
         <v>9</v>
       </c>
       <c r="H192">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I192">
         <v>18</v>
       </c>
       <c r="J192" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6759,7 +6756,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6780,18 +6777,18 @@
         <v>9</v>
       </c>
       <c r="H194">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I194">
         <v>9</v>
       </c>
       <c r="J194" s="1">
-        <v>0.88890000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6823,7 +6820,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6855,7 +6852,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6887,7 +6884,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6919,7 +6916,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6951,7 +6948,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7004,18 +7001,18 @@
         <v>45</v>
       </c>
       <c r="H201">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I201">
         <v>45</v>
       </c>
       <c r="J201" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7036,18 +7033,18 @@
         <v>9</v>
       </c>
       <c r="H202">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I202">
         <v>36</v>
       </c>
       <c r="J202" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7079,7 +7076,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7100,18 +7097,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>436963</v>
+        <v>489890</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.19270000000000001</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7132,18 +7129,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>50174</v>
+        <v>59020</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.13669999999999999</v>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7164,18 +7161,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>844</v>
+        <v>906</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>0.2021</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7196,18 +7193,18 @@
         <v>188993</v>
       </c>
       <c r="H207">
-        <v>186162</v>
+        <v>189146</v>
       </c>
       <c r="I207">
         <v>755972</v>
       </c>
       <c r="J207" s="1">
-        <v>0.24629999999999999</v>
+        <v>0.25019999999999998</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7228,7 +7225,7 @@
         <v>188993</v>
       </c>
       <c r="H208">
-        <v>49156</v>
+        <v>49159</v>
       </c>
       <c r="I208">
         <v>188993</v>
@@ -7239,7 +7236,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7260,18 +7257,18 @@
         <v>98</v>
       </c>
       <c r="H209">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I209">
         <v>392</v>
       </c>
       <c r="J209" s="1">
-        <v>0.20150000000000001</v>
+        <v>0.21679999999999999</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7303,7 +7300,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7324,18 +7321,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>0.15679999999999999</v>
+        <v>0.1734</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7356,18 +7353,18 @@
         <v>133</v>
       </c>
       <c r="H212">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I212">
         <v>133</v>
       </c>
       <c r="J212" s="1">
-        <v>0.39100000000000001</v>
+        <v>0.40600000000000003</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7399,7 +7396,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7420,18 +7417,18 @@
         <v>5482</v>
       </c>
       <c r="H214">
-        <v>3664</v>
+        <v>4252</v>
       </c>
       <c r="I214">
         <v>10964</v>
       </c>
       <c r="J214" s="1">
-        <v>0.3342</v>
+        <v>0.38779999999999998</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7452,7 +7449,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7473,18 +7470,18 @@
         <v>263</v>
       </c>
       <c r="H216">
-        <v>1292</v>
+        <v>1317</v>
       </c>
       <c r="I216">
         <v>6312</v>
       </c>
       <c r="J216" s="1">
-        <v>0.20469999999999999</v>
+        <v>0.2087</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7505,18 +7502,18 @@
         <v>40</v>
       </c>
       <c r="H217">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I217">
         <v>480</v>
       </c>
       <c r="J217" s="1">
-        <v>0.18329999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7537,18 +7534,18 @@
         <v>408</v>
       </c>
       <c r="H218">
-        <v>827</v>
+        <v>1059</v>
       </c>
       <c r="I218">
         <v>4896</v>
       </c>
       <c r="J218" s="1">
-        <v>0.16889999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7569,18 +7566,18 @@
         <v>550</v>
       </c>
       <c r="H219">
-        <v>1232</v>
+        <v>1520</v>
       </c>
       <c r="I219">
         <v>6600</v>
       </c>
       <c r="J219" s="1">
-        <v>0.1867</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7601,18 +7598,18 @@
         <v>76</v>
       </c>
       <c r="H220">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="I220">
         <v>912</v>
       </c>
       <c r="J220" s="1">
-        <v>0.1678</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7633,18 +7630,18 @@
         <v>6</v>
       </c>
       <c r="H221">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I221">
         <v>144</v>
       </c>
       <c r="J221" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7665,18 +7662,18 @@
         <v>19</v>
       </c>
       <c r="H222">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I222">
         <v>228</v>
       </c>
       <c r="J222" s="1">
-        <v>0.1842</v>
+        <v>0.20180000000000001</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7697,18 +7694,18 @@
         <v>1</v>
       </c>
       <c r="H223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I223">
         <v>12</v>
       </c>
       <c r="J223" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7740,7 +7737,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7761,18 +7758,18 @@
         <v>31</v>
       </c>
       <c r="H225">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I225">
         <v>372</v>
       </c>
       <c r="J225" s="1">
-        <v>0.18010000000000001</v>
+        <v>0.18820000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7793,18 +7790,18 @@
         <v>175</v>
       </c>
       <c r="H226">
-        <v>395</v>
+        <v>473</v>
       </c>
       <c r="I226">
         <v>2100</v>
       </c>
       <c r="J226" s="1">
-        <v>0.18809999999999999</v>
+        <v>0.22520000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7825,18 +7822,18 @@
         <v>9</v>
       </c>
       <c r="H227">
-        <v>989</v>
+        <v>1100</v>
       </c>
       <c r="I227">
         <v>3285</v>
       </c>
       <c r="J227" s="1">
-        <v>0.30109999999999998</v>
+        <v>0.33489999999999998</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7857,18 +7854,18 @@
         <v>9</v>
       </c>
       <c r="H228">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I228">
         <v>36</v>
       </c>
       <c r="J228" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7900,7 +7897,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7921,18 +7918,18 @@
         <v>34</v>
       </c>
       <c r="H230">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I230">
         <v>132</v>
       </c>
       <c r="J230" s="1">
-        <v>0.35610000000000003</v>
+        <v>0.38640000000000002</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7961,7 +7958,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8014,18 +8011,18 @@
         <v>3654</v>
       </c>
       <c r="H233">
-        <v>7239</v>
+        <v>7942</v>
       </c>
       <c r="I233">
         <v>43848</v>
       </c>
       <c r="J233" s="1">
-        <v>0.1651</v>
+        <v>0.18110000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8045,7 +8042,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8065,7 +8062,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8085,7 +8082,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8126,7 +8123,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8147,7 +8144,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8176,7 +8173,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8197,18 +8194,18 @@
         <v>486</v>
       </c>
       <c r="H241">
-        <v>1949</v>
+        <v>2477</v>
       </c>
       <c r="I241">
         <v>11664</v>
       </c>
       <c r="J241" s="1">
-        <v>0.1671</v>
+        <v>0.21240000000000001</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8229,18 +8226,18 @@
         <v>25</v>
       </c>
       <c r="H242">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I242">
         <v>300</v>
       </c>
       <c r="J242" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8261,18 +8258,18 @@
         <v>68</v>
       </c>
       <c r="H243">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="I243">
         <v>816</v>
       </c>
       <c r="J243" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8293,18 +8290,18 @@
         <v>729</v>
       </c>
       <c r="H244">
-        <v>1463</v>
+        <v>1892</v>
       </c>
       <c r="I244">
         <v>8772</v>
       </c>
       <c r="J244" s="1">
-        <v>0.1668</v>
+        <v>0.2157</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8325,18 +8322,18 @@
         <v>854</v>
       </c>
       <c r="H245">
-        <v>1842</v>
+        <v>2472</v>
       </c>
       <c r="I245">
         <v>11040</v>
       </c>
       <c r="J245" s="1">
-        <v>0.1668</v>
+        <v>0.22389999999999999</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8357,18 +8354,18 @@
         <v>121</v>
       </c>
       <c r="H246">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="I246">
         <v>1452</v>
       </c>
       <c r="J246" s="1">
-        <v>0.16739999999999999</v>
+        <v>0.20319999999999999</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8389,18 +8386,18 @@
         <v>27</v>
       </c>
       <c r="H247">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="I247">
         <v>648</v>
       </c>
       <c r="J247" s="1">
-        <v>0.1744</v>
+        <v>0.22070000000000001</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8421,7 +8418,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8442,18 +8439,18 @@
         <v>2</v>
       </c>
       <c r="H249">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I249">
         <v>24</v>
       </c>
       <c r="J249" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8474,18 +8471,18 @@
         <v>30</v>
       </c>
       <c r="H250">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I250">
         <v>360</v>
       </c>
       <c r="J250" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8506,18 +8503,18 @@
         <v>51</v>
       </c>
       <c r="H251">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="I251">
         <v>624</v>
       </c>
       <c r="J251" s="1">
-        <v>0.17150000000000001</v>
+        <v>0.21149999999999999</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8538,18 +8535,18 @@
         <v>337</v>
       </c>
       <c r="H252">
-        <v>677</v>
+        <v>919</v>
       </c>
       <c r="I252">
         <v>4044</v>
       </c>
       <c r="J252" s="1">
-        <v>0.16739999999999999</v>
+        <v>0.2273</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8570,18 +8567,18 @@
         <v>50</v>
       </c>
       <c r="H253">
-        <v>3516</v>
+        <v>4415</v>
       </c>
       <c r="I253">
         <v>18972</v>
       </c>
       <c r="J253" s="1">
-        <v>0.18529999999999999</v>
+        <v>0.23269999999999999</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8602,18 +8599,18 @@
         <v>58</v>
       </c>
       <c r="H254">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I254">
         <v>232</v>
       </c>
       <c r="J254" s="1">
-        <v>0.1767</v>
+        <v>0.2026</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8645,7 +8642,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8666,18 +8663,18 @@
         <v>56</v>
       </c>
       <c r="H256">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I256">
         <v>228</v>
       </c>
       <c r="J256" s="1">
-        <v>0.114</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8709,7 +8706,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8730,18 +8727,18 @@
         <v>4610</v>
       </c>
       <c r="H258">
-        <v>9590</v>
+        <v>11350</v>
       </c>
       <c r="I258">
         <v>55320</v>
       </c>
       <c r="J258" s="1">
-        <v>0.1734</v>
+        <v>0.20519999999999999</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8762,18 +8759,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I259">
         <v>468</v>
       </c>
       <c r="J259" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.19439999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8805,7 +8802,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8826,18 +8823,18 @@
         <v>90</v>
       </c>
       <c r="H261">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="I261">
         <v>1080</v>
       </c>
       <c r="J261" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8858,18 +8855,18 @@
         <v>27</v>
       </c>
       <c r="H262">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I262">
         <v>192</v>
       </c>
       <c r="J262" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2031</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8890,18 +8887,18 @@
         <v>121</v>
       </c>
       <c r="H263">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="I263">
         <v>1428</v>
       </c>
       <c r="J263" s="1">
-        <v>0.16739999999999999</v>
+        <v>0.20380000000000001</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8933,7 +8930,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8954,18 +8951,18 @@
         <v>351</v>
       </c>
       <c r="H265">
-        <v>824</v>
+        <v>885</v>
       </c>
       <c r="I265">
         <v>4291</v>
       </c>
       <c r="J265" s="1">
-        <v>0.192</v>
+        <v>0.20619999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8986,18 +8983,18 @@
         <v>35</v>
       </c>
       <c r="H266">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I266">
         <v>420</v>
       </c>
       <c r="J266" s="1">
-        <v>0.19289999999999999</v>
+        <v>0.21429999999999999</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9018,18 +9015,18 @@
         <v>232</v>
       </c>
       <c r="H267">
-        <v>533</v>
+        <v>583</v>
       </c>
       <c r="I267">
         <v>2784</v>
       </c>
       <c r="J267" s="1">
-        <v>0.1915</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9050,18 +9047,18 @@
         <v>66</v>
       </c>
       <c r="H268">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="I268">
         <v>792</v>
       </c>
       <c r="J268" s="1">
-        <v>0.19320000000000001</v>
+        <v>0.21840000000000001</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9082,18 +9079,18 @@
         <v>84</v>
       </c>
       <c r="H269">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="I269">
         <v>1008</v>
       </c>
       <c r="J269" s="1">
-        <v>0.1875</v>
+        <v>0.21029999999999999</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9114,7 +9111,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9135,18 +9132,18 @@
         <v>33</v>
       </c>
       <c r="H271">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I271">
         <v>384</v>
       </c>
       <c r="J271" s="1">
-        <v>0.19009999999999999</v>
+        <v>0.2135</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9178,7 +9175,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9199,7 +9196,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9220,7 +9217,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9241,18 +9238,18 @@
         <v>51</v>
       </c>
       <c r="H275">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I275">
         <v>276</v>
       </c>
       <c r="J275" s="1">
-        <v>0.1812</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9273,18 +9270,18 @@
         <v>445</v>
       </c>
       <c r="H276">
-        <v>1009</v>
+        <v>1120</v>
       </c>
       <c r="I276">
         <v>5340</v>
       </c>
       <c r="J276" s="1">
-        <v>0.189</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9305,18 +9302,18 @@
         <v>17</v>
       </c>
       <c r="H277">
-        <v>972</v>
+        <v>1081</v>
       </c>
       <c r="I277">
         <v>5110</v>
       </c>
       <c r="J277" s="1">
-        <v>0.19020000000000001</v>
+        <v>0.21149999999999999</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9348,7 +9345,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9380,7 +9377,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9412,7 +9409,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9433,18 +9430,18 @@
         <v>34</v>
       </c>
       <c r="H281">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I281">
         <v>34</v>
       </c>
       <c r="J281" s="1">
-        <v>5.8799999999999998E-2</v>
+        <v>0.23530000000000001</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9476,7 +9473,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9508,7 +9505,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9529,18 +9526,18 @@
         <v>12</v>
       </c>
       <c r="H284">
-        <v>1092</v>
+        <v>1176</v>
       </c>
       <c r="I284">
         <v>5904</v>
       </c>
       <c r="J284" s="1">
-        <v>0.185</v>
+        <v>0.19919999999999999</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9561,18 +9558,18 @@
         <v>33</v>
       </c>
       <c r="H285">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I285">
         <v>396</v>
       </c>
       <c r="J285" s="1">
-        <v>0.18690000000000001</v>
+        <v>0.21210000000000001</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9593,18 +9590,18 @@
         <v>23</v>
       </c>
       <c r="H286">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I286">
         <v>276</v>
       </c>
       <c r="J286" s="1">
-        <v>0.1812</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9625,18 +9622,18 @@
         <v>79</v>
       </c>
       <c r="H287">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="I287">
         <v>948</v>
       </c>
       <c r="J287" s="1">
-        <v>0.18779999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9657,7 +9654,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9678,18 +9675,18 @@
         <v>21</v>
       </c>
       <c r="H289">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I289">
         <v>264</v>
       </c>
       <c r="J289" s="1">
-        <v>0.18559999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9710,18 +9707,18 @@
         <v>22</v>
       </c>
       <c r="H290">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I290">
         <v>44</v>
       </c>
       <c r="J290" s="1">
-        <v>0.29549999999999998</v>
+        <v>0.31819999999999998</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9753,7 +9750,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9785,7 +9782,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9817,7 +9814,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9849,7 +9846,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9881,7 +9878,7 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9913,7 +9910,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9945,7 +9942,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9977,7 +9974,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10009,7 +10006,7 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10041,7 +10038,7 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10073,7 +10070,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10105,7 +10102,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10137,7 +10134,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10158,7 +10155,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10179,7 +10176,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10211,7 +10208,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10243,7 +10240,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10275,7 +10272,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10307,7 +10304,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10339,7 +10336,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10371,7 +10368,7 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10403,7 +10400,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10435,7 +10432,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10467,7 +10464,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10499,7 +10496,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10531,7 +10528,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10563,7 +10560,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10595,7 +10592,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10627,7 +10624,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10659,7 +10656,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10679,7 +10676,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10700,7 +10697,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10718,7 +10715,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10739,18 +10736,18 @@
         <v>96</v>
       </c>
       <c r="H324">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="I324">
         <v>2304</v>
       </c>
       <c r="J324" s="1">
-        <v>0.20619999999999999</v>
+        <v>0.2135</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10771,18 +10768,18 @@
         <v>17</v>
       </c>
       <c r="H325">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I325">
         <v>204</v>
       </c>
       <c r="J325" s="1">
-        <v>0.19120000000000001</v>
+        <v>0.23039999999999999</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10803,18 +10800,18 @@
         <v>109</v>
       </c>
       <c r="H326">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="I326">
         <v>1308</v>
       </c>
       <c r="J326" s="1">
-        <v>0.1835</v>
+        <v>0.21560000000000001</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10835,18 +10832,18 @@
         <v>8</v>
       </c>
       <c r="H327">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I327">
         <v>96</v>
       </c>
       <c r="J327" s="1">
-        <v>0.17710000000000001</v>
+        <v>0.21879999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10878,7 +10875,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10910,7 +10907,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10931,18 +10928,18 @@
         <v>17</v>
       </c>
       <c r="H330">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I330">
         <v>204</v>
       </c>
       <c r="J330" s="1">
-        <v>0.18629999999999999</v>
+        <v>0.22059999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10963,18 +10960,18 @@
         <v>7</v>
       </c>
       <c r="H331">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I331">
         <v>84</v>
       </c>
       <c r="J331" s="1">
-        <v>0.17860000000000001</v>
+        <v>0.22620000000000001</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -10995,18 +10992,18 @@
         <v>200</v>
       </c>
       <c r="H332">
-        <v>489</v>
+        <v>559</v>
       </c>
       <c r="I332">
         <v>2400</v>
       </c>
       <c r="J332" s="1">
-        <v>0.20380000000000001</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11027,18 +11024,18 @@
         <v>14</v>
       </c>
       <c r="H333">
-        <v>938</v>
+        <v>1022</v>
       </c>
       <c r="I333">
         <v>5110</v>
       </c>
       <c r="J333" s="1">
-        <v>0.18360000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11070,7 +11067,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11102,7 +11099,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11134,7 +11131,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11166,7 +11163,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11187,18 +11184,18 @@
         <v>10</v>
       </c>
       <c r="H338">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I338">
         <v>120</v>
       </c>
       <c r="J338" s="1">
-        <v>0.18329999999999999</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11230,7 +11227,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11250,7 +11247,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11271,7 +11268,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11292,7 +11289,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11313,18 +11310,18 @@
         <v>392</v>
       </c>
       <c r="H343">
-        <v>1940</v>
+        <v>1986</v>
       </c>
       <c r="I343">
         <v>9408</v>
       </c>
       <c r="J343" s="1">
-        <v>0.20619999999999999</v>
+        <v>0.21110000000000001</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11345,18 +11342,18 @@
         <v>39</v>
       </c>
       <c r="H344">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I344">
         <v>468</v>
       </c>
       <c r="J344" s="1">
-        <v>0.2009</v>
+        <v>0.21790000000000001</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11377,18 +11374,18 @@
         <v>778</v>
       </c>
       <c r="H345">
-        <v>1720</v>
+        <v>2038</v>
       </c>
       <c r="I345">
         <v>9336</v>
       </c>
       <c r="J345" s="1">
-        <v>0.1842</v>
+        <v>0.21829999999999999</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11409,18 +11406,18 @@
         <v>16</v>
       </c>
       <c r="H346">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I346">
         <v>192</v>
       </c>
       <c r="J346" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11441,18 +11438,18 @@
         <v>26</v>
       </c>
       <c r="H347">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I347">
         <v>312</v>
       </c>
       <c r="J347" s="1">
-        <v>0.1923</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11473,18 +11470,18 @@
         <v>24</v>
       </c>
       <c r="H348">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I348">
         <v>576</v>
       </c>
       <c r="J348" s="1">
-        <v>0.2049</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11505,18 +11502,18 @@
         <v>7</v>
       </c>
       <c r="H349">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I349">
         <v>84</v>
       </c>
       <c r="J349" s="1">
-        <v>0.22620000000000001</v>
+        <v>0.23810000000000001</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11548,7 +11545,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11569,18 +11566,18 @@
         <v>925</v>
       </c>
       <c r="H351">
-        <v>2009</v>
+        <v>2299</v>
       </c>
       <c r="I351">
         <v>11100</v>
       </c>
       <c r="J351" s="1">
-        <v>0.18099999999999999</v>
+        <v>0.20710000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11601,18 +11598,18 @@
         <v>45</v>
       </c>
       <c r="H352">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="I352">
         <v>540</v>
       </c>
       <c r="J352" s="1">
-        <v>0.18329999999999999</v>
+        <v>0.24260000000000001</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11633,18 +11630,18 @@
         <v>26</v>
       </c>
       <c r="H353">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I353">
         <v>420</v>
       </c>
       <c r="J353" s="1">
-        <v>0.18099999999999999</v>
+        <v>0.19289999999999999</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11665,18 +11662,18 @@
         <v>145</v>
       </c>
       <c r="H354">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="I354">
         <v>1740</v>
       </c>
       <c r="J354" s="1">
-        <v>0.223</v>
+        <v>0.2379</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11697,18 +11694,18 @@
         <v>105</v>
       </c>
       <c r="H355">
-        <v>6294</v>
+        <v>6868</v>
       </c>
       <c r="I355">
         <v>38325</v>
       </c>
       <c r="J355" s="1">
-        <v>0.16420000000000001</v>
+        <v>0.1792</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11740,7 +11737,7 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11758,21 +11755,21 @@
         <v>43</v>
       </c>
       <c r="G357">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H357">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I357">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="J357" s="1">
-        <v>0.54549999999999998</v>
+        <v>0.75380000000000003</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11804,7 +11801,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11836,7 +11833,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11868,7 +11865,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11889,18 +11886,18 @@
         <v>10</v>
       </c>
       <c r="H361">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I361">
         <v>20</v>
       </c>
       <c r="J361" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11921,18 +11918,18 @@
         <v>3536</v>
       </c>
       <c r="H362">
-        <v>8632</v>
+        <v>9484</v>
       </c>
       <c r="I362">
         <v>42432</v>
       </c>
       <c r="J362" s="1">
-        <v>0.2034</v>
+        <v>0.2235</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11953,18 +11950,18 @@
         <v>33</v>
       </c>
       <c r="H363">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I363">
         <v>396</v>
       </c>
       <c r="J363" s="1">
-        <v>0.20200000000000001</v>
+        <v>0.21970000000000001</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11985,18 +11982,18 @@
         <v>11</v>
       </c>
       <c r="H364">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I364">
         <v>132</v>
       </c>
       <c r="J364" s="1">
-        <v>0.17419999999999999</v>
+        <v>0.18940000000000001</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12017,18 +12014,18 @@
         <v>24</v>
       </c>
       <c r="H365">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I365">
         <v>288</v>
       </c>
       <c r="J365" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12060,7 +12057,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12084,15 +12081,15 @@
         <v>8</v>
       </c>
       <c r="I367">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J367" s="1">
-        <v>0.125</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12107,7 +12104,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12128,18 +12125,18 @@
         <v>278</v>
       </c>
       <c r="H369">
-        <v>1325</v>
+        <v>1404</v>
       </c>
       <c r="I369">
         <v>6672</v>
       </c>
       <c r="J369" s="1">
-        <v>0.1986</v>
+        <v>0.2104</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12160,18 +12157,18 @@
         <v>129</v>
       </c>
       <c r="H370">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="I370">
         <v>1548</v>
       </c>
       <c r="J370" s="1">
-        <v>0.18540000000000001</v>
+        <v>0.22159999999999999</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12192,18 +12189,18 @@
         <v>533</v>
       </c>
       <c r="H371">
-        <v>1145</v>
+        <v>1390</v>
       </c>
       <c r="I371">
         <v>6636</v>
       </c>
       <c r="J371" s="1">
-        <v>0.17249999999999999</v>
+        <v>0.20949999999999999</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12224,18 +12221,18 @@
         <v>315</v>
       </c>
       <c r="H372">
-        <v>704</v>
+        <v>833</v>
       </c>
       <c r="I372">
         <v>3780</v>
       </c>
       <c r="J372" s="1">
-        <v>0.1862</v>
+        <v>0.22040000000000001</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12256,18 +12253,18 @@
         <v>20</v>
       </c>
       <c r="H373">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I373">
         <v>240</v>
       </c>
       <c r="J373" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12288,18 +12285,18 @@
         <v>19</v>
       </c>
       <c r="H374">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I374">
         <v>228</v>
       </c>
       <c r="J374" s="1">
-        <v>0.1711</v>
+        <v>0.2281</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12320,18 +12317,18 @@
         <v>19</v>
       </c>
       <c r="H375">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I375">
         <v>456</v>
       </c>
       <c r="J375" s="1">
-        <v>0.18859999999999999</v>
+        <v>0.2039</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12352,18 +12349,18 @@
         <v>86</v>
       </c>
       <c r="H376">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="I376">
         <v>1032</v>
       </c>
       <c r="J376" s="1">
-        <v>0.18410000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12384,7 +12381,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12416,7 +12413,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12437,18 +12434,18 @@
         <v>32</v>
       </c>
       <c r="H379">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="I379">
         <v>384</v>
       </c>
       <c r="J379" s="1">
-        <v>0.1615</v>
+        <v>0.19270000000000001</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12469,18 +12466,18 @@
         <v>615</v>
       </c>
       <c r="H380">
-        <v>1408</v>
+        <v>1611</v>
       </c>
       <c r="I380">
         <v>7380</v>
       </c>
       <c r="J380" s="1">
-        <v>0.1908</v>
+        <v>0.21829999999999999</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12501,18 +12498,18 @@
         <v>172</v>
       </c>
       <c r="H381">
-        <v>3157</v>
+        <v>3493</v>
       </c>
       <c r="I381">
         <v>17695</v>
       </c>
       <c r="J381" s="1">
-        <v>0.1784</v>
+        <v>0.19739999999999999</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12544,7 +12541,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12576,7 +12573,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12597,18 +12594,18 @@
         <v>48</v>
       </c>
       <c r="H384">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I384">
         <v>192</v>
       </c>
       <c r="J384" s="1">
-        <v>0.25519999999999998</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12640,7 +12637,7 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12661,7 +12658,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12682,18 +12679,18 @@
         <v>13</v>
       </c>
       <c r="H387">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I387">
         <v>26</v>
       </c>
       <c r="J387" s="1">
-        <v>0.42309999999999998</v>
+        <v>0.57689999999999997</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12714,18 +12711,18 @@
         <v>50</v>
       </c>
       <c r="H388">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="I388">
         <v>600</v>
       </c>
       <c r="J388" s="1">
-        <v>0.1767</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12746,18 +12743,18 @@
         <v>48</v>
       </c>
       <c r="H389">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I389">
         <v>576</v>
       </c>
       <c r="J389" s="1">
-        <v>0.1736</v>
+        <v>0.20660000000000001</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12778,18 +12775,18 @@
         <v>17</v>
       </c>
       <c r="H390">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I390">
         <v>204</v>
       </c>
       <c r="J390" s="1">
-        <v>0.1618</v>
+        <v>0.1961</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12810,18 +12807,18 @@
         <v>25</v>
       </c>
       <c r="H391">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I391">
         <v>300</v>
       </c>
       <c r="J391" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>
@@ -12842,18 +12839,21 @@
         <v>62</v>
       </c>
       <c r="H392">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="I392">
         <v>744</v>
       </c>
       <c r="J392" s="1">
-        <v>0.17879999999999999</v>
+        <v>0.22040000000000001</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A393" s="3">
-        <v>46090</v>
+        <v>46097</v>
+      </c>
+      <c r="B393" s="2">
+        <v>2026</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>23</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701D4624-A200-4269-A505-39D628B6F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA6D89E-313D-4277-8324-7D69F09A9DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="113">
   <si>
     <t>Tahun</t>
   </si>
@@ -737,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045E82A1-AFA5-46B1-A9F4-12F5B515B637}">
-  <dimension ref="A1:J393"/>
+  <dimension ref="A1:J392"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
@@ -784,7 +784,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -801,22 +801,19 @@
       <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2">
-        <v>866</v>
-      </c>
       <c r="H2">
-        <v>4441</v>
+        <v>5114</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.21579999999999999</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -833,22 +830,19 @@
       <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G3">
-        <v>278</v>
-      </c>
       <c r="H3">
-        <v>669</v>
+        <v>702</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.22120000000000001</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -865,22 +859,19 @@
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4">
-        <v>1610</v>
-      </c>
       <c r="H4">
-        <v>4059</v>
+        <v>4253</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.20910000000000001</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -897,22 +888,19 @@
       <c r="F5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G5">
-        <v>2269</v>
-      </c>
       <c r="H5">
-        <v>5837</v>
+        <v>6088</v>
       </c>
       <c r="I5">
         <v>27456</v>
       </c>
       <c r="J5" s="1">
-        <v>0.21260000000000001</v>
+        <v>0.22170000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -929,22 +917,19 @@
       <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G6">
-        <v>116</v>
-      </c>
       <c r="H6">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.21149999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -961,22 +946,19 @@
       <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
       <c r="H7">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>0.214</v>
+        <v>0.24279999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -993,9 +975,6 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
       <c r="H8">
         <v>13</v>
       </c>
@@ -1008,7 +987,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1025,22 +1004,19 @@
       <c r="F9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G9">
-        <v>78</v>
-      </c>
       <c r="H9">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.22950000000000001</v>
+        <v>0.2379</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1057,22 +1033,19 @@
       <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10">
-        <v>290</v>
-      </c>
       <c r="H10">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.21679999999999999</v>
+        <v>0.21959999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1089,22 +1062,19 @@
       <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G11">
-        <v>212</v>
-      </c>
       <c r="H11">
-        <v>527</v>
+        <v>581</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.21010000000000001</v>
+        <v>0.23169999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1121,22 +1091,19 @@
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G12">
-        <v>52</v>
-      </c>
       <c r="H12">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>0.1779</v>
+        <v>0.19389999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1153,22 +1120,19 @@
       <c r="F13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G13">
-        <v>58</v>
-      </c>
       <c r="H13">
-        <v>5878</v>
+        <v>6500</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.22989999999999999</v>
+        <v>0.25430000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1185,22 +1149,19 @@
       <c r="F14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G14">
-        <v>55</v>
-      </c>
       <c r="H14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.22370000000000001</v>
+        <v>0.2281</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1217,9 +1178,6 @@
       <c r="F15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G15">
-        <v>55</v>
-      </c>
       <c r="H15">
         <v>14</v>
       </c>
@@ -1232,7 +1190,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1249,22 +1207,19 @@
       <c r="F16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G16">
-        <v>133</v>
-      </c>
       <c r="H16">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.2135</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1281,9 +1236,6 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17">
-        <v>6</v>
-      </c>
       <c r="H17">
         <v>6</v>
       </c>
@@ -1296,7 +1248,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1313,9 +1265,6 @@
       <c r="F18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G18">
-        <v>43</v>
-      </c>
       <c r="H18">
         <v>15</v>
       </c>
@@ -1328,7 +1277,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1345,22 +1294,19 @@
       <c r="F19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G19">
-        <v>621</v>
-      </c>
       <c r="H19">
-        <v>25779</v>
+        <v>28515</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.21970000000000001</v>
+        <v>0.24299999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1377,22 +1323,19 @@
       <c r="F20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G20">
-        <v>98</v>
-      </c>
       <c r="H20">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.2109</v>
+        <v>0.23300000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1409,22 +1352,19 @@
       <c r="F21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G21">
-        <v>43</v>
-      </c>
       <c r="H21">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.20930000000000001</v>
+        <v>0.22289999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1441,22 +1381,19 @@
       <c r="F22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G22">
-        <v>116</v>
-      </c>
       <c r="H22">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.19420000000000001</v>
+        <v>0.21049999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1476,7 +1413,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1496,7 +1433,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1517,7 +1454,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1546,7 +1483,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1567,18 +1504,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.2097</v>
+        <v>0.24149999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1599,18 +1536,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>0.22339999999999999</v>
+        <v>0.23580000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1631,18 +1568,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.2288</v>
+        <v>0.24010000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1663,18 +1600,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>980</v>
+        <v>1081</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.20519999999999999</v>
+        <v>0.2263</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1695,18 +1632,18 @@
         <v>398</v>
       </c>
       <c r="H31">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="I31">
         <v>398</v>
       </c>
       <c r="J31" s="1">
-        <v>0.27889999999999998</v>
+        <v>0.3543</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1727,18 +1664,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.27339999999999998</v>
+        <v>0.32029999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1759,18 +1696,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>0.2213</v>
+        <v>0.23769999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1791,18 +1728,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.50849999999999995</v>
+        <v>0.52539999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1823,18 +1760,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>9.8199999999999996E-2</v>
+        <v>0.1227</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1855,18 +1792,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>0.1358</v>
+        <v>0.15090000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1898,7 +1835,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1919,18 +1856,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>0.1103</v>
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1950,16 +1887,19 @@
       <c r="G39">
         <v>10</v>
       </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
       <c r="I39">
         <v>20</v>
       </c>
       <c r="J39" s="1">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1991,7 +1931,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2012,18 +1952,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.36459999999999998</v>
+        <v>0.39750000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2044,18 +1984,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.20250000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2076,18 +2016,18 @@
         <v>244</v>
       </c>
       <c r="H43">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I43">
         <v>244</v>
       </c>
       <c r="J43" s="1">
-        <v>0.26640000000000003</v>
+        <v>0.2828</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2108,18 +2048,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.1993</v>
+        <v>0.2319</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2151,7 +2091,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2169,7 +2109,10 @@
         <v>43</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
       </c>
       <c r="I46">
         <v>3</v>
@@ -2180,7 +2123,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2201,18 +2144,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>1799113</v>
+        <v>1960522</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.21690000000000001</v>
+        <v>0.23630000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2233,18 +2176,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>284027</v>
+        <v>300338.3</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.20610000000000001</v>
+        <v>0.21790000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2265,18 +2208,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>3274</v>
+        <v>3570</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.21079999999999999</v>
+        <v>0.22989999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2297,18 +2240,18 @@
         <v>691098</v>
       </c>
       <c r="H50">
-        <v>578317</v>
+        <v>613993</v>
       </c>
       <c r="I50">
         <v>2764392</v>
       </c>
       <c r="J50" s="1">
-        <v>0.2092</v>
+        <v>0.22209999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2329,18 +2272,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>227572</v>
+        <v>238343</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.32919999999999999</v>
+        <v>0.3448</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2361,18 +2304,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.21740000000000001</v>
+        <v>0.22750000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2393,18 +2336,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.31940000000000002</v>
+        <v>0.33529999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2425,18 +2368,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.19120000000000001</v>
+        <v>0.20469999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2457,18 +2400,18 @@
         <v>649</v>
       </c>
       <c r="H55">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="I55">
         <v>649</v>
       </c>
       <c r="J55" s="1">
-        <v>0.15409999999999999</v>
+        <v>0.19719999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2489,18 +2432,18 @@
         <v>331</v>
       </c>
       <c r="H56">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I56">
         <v>331</v>
       </c>
       <c r="J56" s="1">
-        <v>7.5499999999999998E-2</v>
+        <v>9.06E-2</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2520,6 +2463,9 @@
       <c r="G57">
         <v>2234</v>
       </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
       <c r="I57">
         <v>4468</v>
       </c>
@@ -2529,7 +2475,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2550,18 +2496,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.22950000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2582,18 +2528,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.21809999999999999</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2610,11 +2556,22 @@
       <c r="F60" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J60" s="1"/>
+      <c r="G60">
+        <v>691280</v>
+      </c>
+      <c r="H60">
+        <v>1895603</v>
+      </c>
+      <c r="I60">
+        <v>8295360</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.22850000000000001</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2635,18 +2592,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>1860</v>
+        <v>2033</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.2117</v>
+        <v>0.23139999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2667,18 +2624,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>0.23569999999999999</v>
+        <v>0.24929999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2699,18 +2656,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1667</v>
+        <v>1820</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.21709999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2731,18 +2688,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>1938</v>
+        <v>2126</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.2165</v>
+        <v>0.23749999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2763,18 +2720,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="I65">
         <v>1092</v>
       </c>
       <c r="J65" s="1">
-        <v>0.19139999999999999</v>
+        <v>0.20880000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2795,18 +2752,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I66">
         <v>240</v>
       </c>
       <c r="J66" s="1">
-        <v>0.2167</v>
+        <v>0.23749999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2827,18 +2784,18 @@
         <v>25</v>
       </c>
       <c r="H67">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I67">
         <v>300</v>
       </c>
       <c r="J67" s="1">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2870,7 +2827,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2891,18 +2848,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="I69">
         <v>876</v>
       </c>
       <c r="J69" s="1">
-        <v>0.18379999999999999</v>
+        <v>0.22489999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2923,18 +2880,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.223</v>
+        <v>0.2374</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2955,18 +2912,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>719</v>
+        <v>786</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>0.2195</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2987,18 +2944,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>1036</v>
+        <v>1134</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.20269999999999999</v>
+        <v>0.22189999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3019,18 +2976,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.2</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3062,7 +3019,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3083,18 +3040,18 @@
         <v>52</v>
       </c>
       <c r="H75">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I75">
         <v>208</v>
       </c>
       <c r="J75" s="1">
-        <v>0.22600000000000001</v>
+        <v>0.2452</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3126,7 +3083,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3158,7 +3115,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3190,7 +3147,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3211,18 +3168,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>0.216</v>
+        <v>0.22620000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3243,18 +3200,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>1722</v>
+        <v>830</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>0.5</v>
+        <v>0.24099999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3275,18 +3232,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="I81">
         <v>948</v>
       </c>
       <c r="J81" s="1">
-        <v>0.44090000000000001</v>
+        <v>0.21310000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3307,18 +3264,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="I82">
         <v>1632</v>
       </c>
       <c r="J82" s="1">
-        <v>0.18870000000000001</v>
+        <v>0.20649999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3339,7 +3296,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3360,18 +3317,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>0.18099999999999999</v>
+        <v>0.2213</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3403,7 +3360,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3424,18 +3381,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1520</v>
+        <v>1668</v>
       </c>
       <c r="I86">
         <v>7032</v>
       </c>
       <c r="J86" s="1">
-        <v>0.2162</v>
+        <v>0.23719999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3456,18 +3413,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.19139999999999999</v>
+        <v>0.19819999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3488,18 +3445,18 @@
         <v>493</v>
       </c>
       <c r="H88">
-        <v>1139</v>
+        <v>1311</v>
       </c>
       <c r="I88">
-        <v>5916</v>
+        <v>6916</v>
       </c>
       <c r="J88" s="1">
-        <v>0.1925</v>
+        <v>0.18959999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3531,7 +3488,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3552,18 +3509,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>1684</v>
+        <v>2127</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>0.18740000000000001</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3584,18 +3541,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="I91">
         <v>1932</v>
       </c>
       <c r="J91" s="1">
-        <v>0.21740000000000001</v>
+        <v>0.23139999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3616,18 +3573,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="I92">
         <v>1128</v>
       </c>
       <c r="J92" s="1">
-        <v>0.2172</v>
+        <v>0.2394</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3648,18 +3605,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.18790000000000001</v>
+        <v>0.20910000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3680,7 +3637,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3701,18 +3658,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.19070000000000001</v>
+        <v>0.2019</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3733,7 +3690,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3754,18 +3711,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.29499999999999998</v>
+        <v>0.32969999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3786,18 +3743,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I98">
         <v>60</v>
       </c>
       <c r="J98" s="1">
-        <v>0.2</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3818,18 +3775,18 @@
         <v>14</v>
       </c>
       <c r="H99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I99">
         <v>15</v>
       </c>
       <c r="J99" s="1">
-        <v>0.4</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3861,7 +3818,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3882,7 +3839,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3903,18 +3860,18 @@
         <v>8</v>
       </c>
       <c r="H102">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I102">
         <v>18</v>
       </c>
       <c r="J102" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3946,7 +3903,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3967,18 +3924,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.19170000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4010,7 +3967,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4031,18 +3988,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I106">
         <v>552</v>
       </c>
       <c r="J106" s="1">
-        <v>0.18840000000000001</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4063,7 +4020,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4084,18 +4041,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I108">
         <v>611</v>
       </c>
       <c r="J108" s="1">
-        <v>0.18659999999999999</v>
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4116,7 +4073,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4137,18 +4094,18 @@
         <v>16</v>
       </c>
       <c r="H110">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I110">
         <v>192</v>
       </c>
       <c r="J110" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.19789999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4169,18 +4126,18 @@
         <v>458</v>
       </c>
       <c r="H111">
-        <v>2098</v>
+        <v>2729</v>
       </c>
       <c r="I111">
         <v>10992</v>
       </c>
       <c r="J111" s="1">
-        <v>0.19089999999999999</v>
+        <v>0.24829999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4201,18 +4158,18 @@
         <v>5</v>
       </c>
       <c r="H112">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I112">
         <v>60</v>
       </c>
       <c r="J112" s="1">
-        <v>0.2167</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4233,18 +4190,18 @@
         <v>43</v>
       </c>
       <c r="H113">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="I113">
         <v>516</v>
       </c>
       <c r="J113" s="1">
-        <v>0.17829999999999999</v>
+        <v>0.21510000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4265,18 +4222,18 @@
         <v>665</v>
       </c>
       <c r="H114">
-        <v>1362</v>
+        <v>1689</v>
       </c>
       <c r="I114">
         <v>7992</v>
       </c>
       <c r="J114" s="1">
-        <v>0.1704</v>
+        <v>0.21129999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4297,18 +4254,18 @@
         <v>1043</v>
       </c>
       <c r="H115">
-        <v>2153</v>
+        <v>2703</v>
       </c>
       <c r="I115">
         <v>12264</v>
       </c>
       <c r="J115" s="1">
-        <v>0.17560000000000001</v>
+        <v>0.22040000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4329,18 +4286,18 @@
         <v>71</v>
       </c>
       <c r="H116">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="I116">
         <v>852</v>
       </c>
       <c r="J116" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.21360000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4361,18 +4318,18 @@
         <v>22</v>
       </c>
       <c r="H117">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="I117">
         <v>528</v>
       </c>
       <c r="J117" s="1">
-        <v>0.1799</v>
+        <v>0.2462</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4404,7 +4361,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4436,7 +4393,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4457,18 +4414,18 @@
         <v>81</v>
       </c>
       <c r="H120">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I120">
         <v>972</v>
       </c>
       <c r="J120" s="1">
-        <v>0.1842</v>
+        <v>0.20880000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4489,18 +4446,18 @@
         <v>52</v>
       </c>
       <c r="H121">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I121">
         <v>624</v>
       </c>
       <c r="J121" s="1">
-        <v>0.1731</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4521,18 +4478,18 @@
         <v>44</v>
       </c>
       <c r="H122">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="I122">
         <v>528</v>
       </c>
       <c r="J122" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.21210000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4553,18 +4510,18 @@
         <v>11</v>
       </c>
       <c r="H123">
-        <v>864</v>
+        <v>1111</v>
       </c>
       <c r="I123">
         <v>4046</v>
       </c>
       <c r="J123" s="1">
-        <v>0.2135</v>
+        <v>0.27460000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4596,7 +4553,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4628,7 +4585,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4660,7 +4617,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4692,7 +4649,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4713,18 +4670,18 @@
         <v>2</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I128">
         <v>4</v>
       </c>
       <c r="J128" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4756,7 +4713,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4777,18 +4734,18 @@
         <v>188</v>
       </c>
       <c r="H130">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="I130">
         <v>2256</v>
       </c>
       <c r="J130" s="1">
-        <v>0.1724</v>
+        <v>0.20349999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4809,18 +4766,18 @@
         <v>43</v>
       </c>
       <c r="H131">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="I131">
         <v>516</v>
       </c>
       <c r="J131" s="1">
-        <v>0.1764</v>
+        <v>0.2248</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4841,18 +4798,18 @@
         <v>14</v>
       </c>
       <c r="H132">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I132">
         <v>168</v>
       </c>
       <c r="J132" s="1">
-        <v>0.19639999999999999</v>
+        <v>0.21429999999999999</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4873,18 +4830,18 @@
         <v>52</v>
       </c>
       <c r="H133">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I133">
         <v>624</v>
       </c>
       <c r="J133" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.18590000000000001</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4904,7 +4861,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4925,7 +4882,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4946,7 +4903,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4967,18 +4924,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.17480000000000001</v>
+        <v>0.1951</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -4999,18 +4956,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>1641</v>
+        <v>1669</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>0.23380000000000001</v>
+        <v>0.23769999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5031,18 +4988,18 @@
         <v>383</v>
       </c>
       <c r="H139">
-        <v>1949</v>
+        <v>2270</v>
       </c>
       <c r="I139">
         <v>9144</v>
       </c>
       <c r="J139" s="1">
-        <v>0.21310000000000001</v>
+        <v>0.24829999999999999</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5074,7 +5031,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5106,7 +5063,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5138,7 +5095,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5170,7 +5127,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5191,18 +5148,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>2426</v>
+        <v>2555</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>0.22509999999999999</v>
+        <v>0.23710000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5223,18 +5180,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.2354</v>
+        <v>0.23880000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5255,18 +5212,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>0.21429999999999999</v>
+        <v>0.22020000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5287,18 +5244,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.19719999999999999</v>
+        <v>0.20280000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5319,18 +5276,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.17949999999999999</v>
+        <v>0.1971</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5362,7 +5319,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5383,18 +5340,18 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I150">
         <v>48</v>
       </c>
       <c r="J150" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.20830000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5426,7 +5383,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5447,18 +5404,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>1171</v>
+        <v>1271</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.26790000000000003</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5490,7 +5447,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5522,7 +5479,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5543,18 +5500,18 @@
         <v>45</v>
       </c>
       <c r="H155">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I155">
         <v>180</v>
       </c>
       <c r="J155" s="1">
-        <v>0.2389</v>
+        <v>0.24440000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5575,18 +5532,18 @@
         <v>45</v>
       </c>
       <c r="H156">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I156">
         <v>45</v>
       </c>
       <c r="J156" s="1">
-        <v>0.15559999999999999</v>
+        <v>0.17780000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5607,18 +5564,18 @@
         <v>9</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I157">
         <v>18</v>
       </c>
       <c r="J157" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5650,7 +5607,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5671,18 +5628,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.18290000000000001</v>
+        <v>0.20930000000000001</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5703,18 +5660,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>0.1736</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5735,18 +5692,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.1963</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5767,18 +5724,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.1835</v>
+        <v>0.1948</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5799,18 +5756,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>1977</v>
+        <v>2215</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.21290000000000001</v>
+        <v>0.23849999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5842,7 +5799,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5863,18 +5820,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1529</v>
+        <v>1597</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.216</v>
+        <v>0.22559999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5895,18 +5852,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>2724</v>
+        <v>2758</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.23549999999999999</v>
+        <v>0.2384</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5927,18 +5884,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.18840000000000001</v>
+        <v>0.19789999999999999</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5959,18 +5916,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.23719999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6002,7 +5959,7 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6034,7 +5991,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6055,18 +6012,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.189</v>
+        <v>0.19370000000000001</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6087,18 +6044,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.2145</v>
+        <v>0.21629999999999999</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6130,7 +6087,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6151,18 +6108,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>2463</v>
+        <v>2702</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.22489999999999999</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6194,7 +6151,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6214,6 +6171,9 @@
       <c r="G176">
         <v>57</v>
       </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
       <c r="I176">
         <v>57</v>
       </c>
@@ -6223,7 +6183,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6255,7 +6215,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6287,7 +6247,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6319,7 +6279,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6351,7 +6311,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6372,18 +6332,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.19409999999999999</v>
+        <v>0.20930000000000001</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6404,18 +6364,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6447,7 +6407,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6479,7 +6439,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6500,18 +6460,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.1903</v>
+        <v>0.19789999999999999</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6532,7 +6492,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6564,7 +6524,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6585,18 +6545,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.23150000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6617,18 +6577,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6649,18 +6609,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>0.20480000000000001</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6692,7 +6652,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6724,7 +6684,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6756,7 +6716,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6788,7 +6748,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6820,7 +6780,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6852,7 +6812,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6884,7 +6844,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6916,7 +6876,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6948,7 +6908,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6980,7 +6940,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7012,7 +6972,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7033,18 +6993,18 @@
         <v>9</v>
       </c>
       <c r="H202">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I202">
         <v>36</v>
       </c>
       <c r="J202" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7076,7 +7036,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7097,18 +7057,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>489890</v>
+        <v>540052</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.216</v>
+        <v>0.23810000000000001</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7129,18 +7089,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>59020</v>
+        <v>62810</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.1608</v>
+        <v>0.1711</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7161,18 +7121,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>906</v>
+        <v>976</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>0.217</v>
+        <v>0.23369999999999999</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7204,7 +7164,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7236,7 +7196,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7257,18 +7217,18 @@
         <v>98</v>
       </c>
       <c r="H209">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I209">
         <v>392</v>
       </c>
       <c r="J209" s="1">
-        <v>0.21679999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7300,7 +7260,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7321,18 +7281,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>0.1734</v>
+        <v>0.18820000000000001</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7353,18 +7313,18 @@
         <v>133</v>
       </c>
       <c r="H212">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I212">
         <v>133</v>
       </c>
       <c r="J212" s="1">
-        <v>0.40600000000000003</v>
+        <v>0.43609999999999999</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7396,7 +7356,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7417,39 +7377,50 @@
         <v>5482</v>
       </c>
       <c r="H214">
-        <v>4252</v>
+        <v>4731</v>
       </c>
       <c r="I214">
         <v>10964</v>
       </c>
       <c r="J214" s="1">
-        <v>0.38779999999999998</v>
+        <v>0.43149999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E215" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J215" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="G215">
+        <v>263</v>
+      </c>
+      <c r="H215">
+        <v>1472</v>
+      </c>
+      <c r="I215">
+        <v>6312</v>
+      </c>
+      <c r="J215" s="1">
+        <v>0.23319999999999999</v>
+      </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7461,27 +7432,27 @@
         <v>24</v>
       </c>
       <c r="E216" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G216">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="H216">
-        <v>1317</v>
+        <v>102</v>
       </c>
       <c r="I216">
-        <v>6312</v>
+        <v>480</v>
       </c>
       <c r="J216" s="1">
-        <v>0.2087</v>
+        <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7493,27 +7464,27 @@
         <v>24</v>
       </c>
       <c r="E217" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G217">
-        <v>40</v>
+        <v>408</v>
       </c>
       <c r="H217">
-        <v>96</v>
+        <v>1109</v>
       </c>
       <c r="I217">
-        <v>480</v>
+        <v>4896</v>
       </c>
       <c r="J217" s="1">
-        <v>0.2</v>
+        <v>0.22650000000000001</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7525,27 +7496,27 @@
         <v>24</v>
       </c>
       <c r="E218" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G218">
-        <v>408</v>
+        <v>550</v>
       </c>
       <c r="H218">
-        <v>1059</v>
+        <v>1526</v>
       </c>
       <c r="I218">
-        <v>4896</v>
+        <v>6600</v>
       </c>
       <c r="J218" s="1">
-        <v>0.21629999999999999</v>
+        <v>0.23119999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7557,27 +7528,27 @@
         <v>24</v>
       </c>
       <c r="E219" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G219">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="H219">
-        <v>1520</v>
+        <v>192</v>
       </c>
       <c r="I219">
-        <v>6600</v>
+        <v>912</v>
       </c>
       <c r="J219" s="1">
-        <v>0.2303</v>
+        <v>0.21049999999999999</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7589,27 +7560,27 @@
         <v>24</v>
       </c>
       <c r="E220" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G220">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="H220">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="I220">
-        <v>912</v>
+        <v>144</v>
       </c>
       <c r="J220" s="1">
-        <v>0.193</v>
+        <v>0.2361</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7621,27 +7592,27 @@
         <v>24</v>
       </c>
       <c r="E221" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G221">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H221">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I221">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="J221" s="1">
-        <v>0.2014</v>
+        <v>0.21490000000000001</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7653,27 +7624,27 @@
         <v>24</v>
       </c>
       <c r="E222" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G222">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H222">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="I222">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="J222" s="1">
-        <v>0.20180000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7685,19 +7656,19 @@
         <v>24</v>
       </c>
       <c r="E223" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G223">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H223">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I223">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J223" s="1">
         <v>0.25</v>
@@ -7705,7 +7676,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7717,27 +7688,27 @@
         <v>24</v>
       </c>
       <c r="E224" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G224">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H224">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="I224">
-        <v>48</v>
+        <v>372</v>
       </c>
       <c r="J224" s="1">
-        <v>0.25</v>
+        <v>0.2016</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7749,27 +7720,27 @@
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G225">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="H225">
-        <v>70</v>
+        <v>494</v>
       </c>
       <c r="I225">
-        <v>372</v>
+        <v>2100</v>
       </c>
       <c r="J225" s="1">
-        <v>0.18820000000000001</v>
+        <v>0.23519999999999999</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7778,30 +7749,30 @@
         <v>17</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E226" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G226">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="H226">
-        <v>473</v>
+        <v>1209</v>
       </c>
       <c r="I226">
-        <v>2100</v>
+        <v>3285</v>
       </c>
       <c r="J226" s="1">
-        <v>0.22520000000000001</v>
+        <v>0.36799999999999999</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7816,24 +7787,24 @@
         <v>40</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G227">
         <v>9</v>
       </c>
       <c r="H227">
-        <v>1100</v>
+        <v>12</v>
       </c>
       <c r="I227">
-        <v>3285</v>
+        <v>36</v>
       </c>
       <c r="J227" s="1">
-        <v>0.33489999999999998</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7848,24 +7819,24 @@
         <v>40</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G228">
         <v>9</v>
       </c>
       <c r="H228">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I228">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J228" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7877,27 +7848,27 @@
         <v>25</v>
       </c>
       <c r="E229" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G229">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H229">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="I229">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="J229" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.40910000000000002</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7909,27 +7880,27 @@
         <v>25</v>
       </c>
       <c r="E230" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G230">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H230">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I230">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="J230" s="1">
-        <v>0.38640000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7941,24 +7912,27 @@
         <v>25</v>
       </c>
       <c r="E231" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G231">
+        <v>9</v>
+      </c>
+      <c r="H231">
         <v>2</v>
       </c>
       <c r="I231">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J231" s="1">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7970,27 +7944,27 @@
         <v>25</v>
       </c>
       <c r="E232" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G232">
-        <v>9</v>
+        <v>3654</v>
       </c>
       <c r="H232">
-        <v>2</v>
+        <v>8749</v>
       </c>
       <c r="I232">
-        <v>18</v>
+        <v>43848</v>
       </c>
       <c r="J232" s="1">
-        <v>0.1111</v>
+        <v>0.19950000000000001</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8002,27 +7976,16 @@
         <v>25</v>
       </c>
       <c r="E233" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G233">
-        <v>3654</v>
-      </c>
-      <c r="H233">
-        <v>7942</v>
-      </c>
-      <c r="I233">
-        <v>43848</v>
-      </c>
-      <c r="J233" s="1">
-        <v>0.18110000000000001</v>
-      </c>
+      <c r="J233" s="1"/>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8034,7 +7997,7 @@
         <v>25</v>
       </c>
       <c r="E234" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>30</v>
@@ -8042,7 +8005,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8054,7 +8017,7 @@
         <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>30</v>
@@ -8062,7 +8025,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8071,10 +8034,10 @@
         <v>17</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E236" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>30</v>
@@ -8082,7 +8045,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8091,10 +8054,10 @@
         <v>17</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E237" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>30</v>
@@ -8102,7 +8065,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8117,13 +8080,13 @@
         <v>53</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="J238" s="1"/>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8135,45 +8098,59 @@
         <v>25</v>
       </c>
       <c r="E239" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J239" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="G239">
+        <v>33</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>33</v>
+      </c>
+      <c r="J239" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E240" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G240">
-        <v>33</v>
+        <v>486</v>
+      </c>
+      <c r="H240">
+        <v>2809</v>
       </c>
       <c r="I240">
-        <v>33</v>
+        <v>11664</v>
       </c>
       <c r="J240" s="1">
-        <v>0</v>
+        <v>0.24079999999999999</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8185,27 +8162,27 @@
         <v>24</v>
       </c>
       <c r="E241" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G241">
-        <v>486</v>
+        <v>25</v>
       </c>
       <c r="H241">
-        <v>2477</v>
+        <v>75</v>
       </c>
       <c r="I241">
-        <v>11664</v>
+        <v>300</v>
       </c>
       <c r="J241" s="1">
-        <v>0.21240000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8217,27 +8194,27 @@
         <v>24</v>
       </c>
       <c r="E242" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G242">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="H242">
-        <v>75</v>
+        <v>183</v>
       </c>
       <c r="I242">
-        <v>300</v>
+        <v>816</v>
       </c>
       <c r="J242" s="1">
-        <v>0.25</v>
+        <v>0.2243</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8249,27 +8226,27 @@
         <v>24</v>
       </c>
       <c r="E243" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G243">
-        <v>68</v>
+        <v>729</v>
       </c>
       <c r="H243">
-        <v>168</v>
+        <v>2045</v>
       </c>
       <c r="I243">
-        <v>816</v>
+        <v>8772</v>
       </c>
       <c r="J243" s="1">
-        <v>0.2059</v>
+        <v>0.2331</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8281,27 +8258,27 @@
         <v>24</v>
       </c>
       <c r="E244" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G244">
-        <v>729</v>
+        <v>854</v>
       </c>
       <c r="H244">
-        <v>1892</v>
+        <v>2561</v>
       </c>
       <c r="I244">
-        <v>8772</v>
+        <v>11040</v>
       </c>
       <c r="J244" s="1">
-        <v>0.2157</v>
+        <v>0.23200000000000001</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8313,27 +8290,27 @@
         <v>24</v>
       </c>
       <c r="E245" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G245">
-        <v>854</v>
+        <v>121</v>
       </c>
       <c r="H245">
-        <v>2472</v>
+        <v>316</v>
       </c>
       <c r="I245">
-        <v>11040</v>
+        <v>1452</v>
       </c>
       <c r="J245" s="1">
-        <v>0.22389999999999999</v>
+        <v>0.21759999999999999</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8345,27 +8322,27 @@
         <v>24</v>
       </c>
       <c r="E246" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G246">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="H246">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="I246">
-        <v>1452</v>
+        <v>648</v>
       </c>
       <c r="J246" s="1">
-        <v>0.20319999999999999</v>
+        <v>0.24690000000000001</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8377,27 +8354,16 @@
         <v>24</v>
       </c>
       <c r="E247" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G247">
-        <v>27</v>
-      </c>
-      <c r="H247">
-        <v>143</v>
-      </c>
-      <c r="I247">
-        <v>648</v>
-      </c>
-      <c r="J247" s="1">
-        <v>0.22070000000000001</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="J247" s="1"/>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8409,16 +8375,27 @@
         <v>24</v>
       </c>
       <c r="E248" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J248" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="G248">
+        <v>2</v>
+      </c>
+      <c r="H248">
+        <v>6</v>
+      </c>
+      <c r="I248">
+        <v>24</v>
+      </c>
+      <c r="J248" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8430,27 +8407,27 @@
         <v>24</v>
       </c>
       <c r="E249" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G249">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H249">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="I249">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="J249" s="1">
-        <v>0.25</v>
+        <v>0.2361</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8462,27 +8439,27 @@
         <v>24</v>
       </c>
       <c r="E250" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G250">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="H250">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="I250">
-        <v>360</v>
+        <v>624</v>
       </c>
       <c r="J250" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8494,27 +8471,27 @@
         <v>24</v>
       </c>
       <c r="E251" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G251">
-        <v>51</v>
+        <v>337</v>
       </c>
       <c r="H251">
-        <v>132</v>
+        <v>969</v>
       </c>
       <c r="I251">
-        <v>624</v>
+        <v>4044</v>
       </c>
       <c r="J251" s="1">
-        <v>0.21149999999999999</v>
+        <v>0.23960000000000001</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8523,30 +8500,30 @@
         <v>18</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E252" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G252">
-        <v>337</v>
+        <v>50</v>
       </c>
       <c r="H252">
-        <v>919</v>
+        <v>4828</v>
       </c>
       <c r="I252">
-        <v>4044</v>
+        <v>18972</v>
       </c>
       <c r="J252" s="1">
-        <v>0.2273</v>
+        <v>0.2545</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8561,24 +8538,24 @@
         <v>40</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G253">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H253">
-        <v>4415</v>
+        <v>48</v>
       </c>
       <c r="I253">
-        <v>18972</v>
+        <v>232</v>
       </c>
       <c r="J253" s="1">
-        <v>0.23269999999999999</v>
+        <v>0.2069</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8593,24 +8570,24 @@
         <v>40</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G254">
         <v>58</v>
       </c>
       <c r="H254">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I254">
-        <v>232</v>
+        <v>58</v>
       </c>
       <c r="J254" s="1">
-        <v>0.2026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8622,27 +8599,27 @@
         <v>25</v>
       </c>
       <c r="E255" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G255">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I255">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="J255" s="1">
-        <v>0</v>
+        <v>0.1842</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8654,27 +8631,27 @@
         <v>25</v>
       </c>
       <c r="E256" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G256">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="H256">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I256">
-        <v>228</v>
+        <v>6</v>
       </c>
       <c r="J256" s="1">
-        <v>0.16669999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8686,27 +8663,27 @@
         <v>25</v>
       </c>
       <c r="E257" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G257">
-        <v>3</v>
+        <v>4610</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>12442</v>
       </c>
       <c r="I257">
-        <v>6</v>
+        <v>55320</v>
       </c>
       <c r="J257" s="1">
-        <v>0</v>
+        <v>0.22489999999999999</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8718,27 +8695,27 @@
         <v>25</v>
       </c>
       <c r="E258" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G258">
-        <v>4610</v>
+        <v>44</v>
       </c>
       <c r="H258">
-        <v>11350</v>
+        <v>95</v>
       </c>
       <c r="I258">
-        <v>55320</v>
+        <v>468</v>
       </c>
       <c r="J258" s="1">
-        <v>0.20519999999999999</v>
+        <v>0.20300000000000001</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8753,24 +8730,24 @@
         <v>53</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G259">
         <v>44</v>
       </c>
       <c r="H259">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="I259">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="J259" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.12820000000000001</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8782,27 +8759,27 @@
         <v>25</v>
       </c>
       <c r="E260" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G260">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="H260">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="I260">
-        <v>78</v>
+        <v>1080</v>
       </c>
       <c r="J260" s="1">
-        <v>0.1026</v>
+        <v>0.22040000000000001</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8814,27 +8791,27 @@
         <v>25</v>
       </c>
       <c r="E261" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G261">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="H261">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="I261">
-        <v>1080</v>
+        <v>192</v>
       </c>
       <c r="J261" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.21879999999999999</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8846,27 +8823,27 @@
         <v>25</v>
       </c>
       <c r="E262" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G262">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="H262">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="I262">
-        <v>192</v>
+        <v>1428</v>
       </c>
       <c r="J262" s="1">
-        <v>0.2031</v>
+        <v>0.2185</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8878,59 +8855,59 @@
         <v>25</v>
       </c>
       <c r="E263" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G263">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="H263">
-        <v>291</v>
+        <v>3</v>
       </c>
       <c r="I263">
-        <v>1428</v>
+        <v>24</v>
       </c>
       <c r="J263" s="1">
-        <v>0.20380000000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E264" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G264">
-        <v>12</v>
+        <v>351</v>
       </c>
       <c r="H264">
-        <v>3</v>
+        <v>997</v>
       </c>
       <c r="I264">
-        <v>24</v>
+        <v>4291</v>
       </c>
       <c r="J264" s="1">
-        <v>0.125</v>
+        <v>0.23230000000000001</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8942,27 +8919,27 @@
         <v>24</v>
       </c>
       <c r="E265" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G265">
-        <v>351</v>
+        <v>35</v>
       </c>
       <c r="H265">
-        <v>885</v>
+        <v>96</v>
       </c>
       <c r="I265">
-        <v>4291</v>
+        <v>420</v>
       </c>
       <c r="J265" s="1">
-        <v>0.20619999999999999</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8974,27 +8951,27 @@
         <v>24</v>
       </c>
       <c r="E266" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G266">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H266">
-        <v>90</v>
+        <v>656</v>
       </c>
       <c r="I266">
-        <v>420</v>
+        <v>2784</v>
       </c>
       <c r="J266" s="1">
-        <v>0.21429999999999999</v>
+        <v>0.2356</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9006,27 +8983,27 @@
         <v>24</v>
       </c>
       <c r="E267" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G267">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="H267">
-        <v>583</v>
+        <v>185</v>
       </c>
       <c r="I267">
-        <v>2784</v>
+        <v>792</v>
       </c>
       <c r="J267" s="1">
-        <v>0.2094</v>
+        <v>0.2336</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9038,27 +9015,27 @@
         <v>24</v>
       </c>
       <c r="E268" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G268">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H268">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="I268">
-        <v>792</v>
+        <v>1008</v>
       </c>
       <c r="J268" s="1">
-        <v>0.21840000000000001</v>
+        <v>0.22720000000000001</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9070,27 +9047,16 @@
         <v>24</v>
       </c>
       <c r="E269" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G269">
-        <v>84</v>
-      </c>
-      <c r="H269">
-        <v>212</v>
-      </c>
-      <c r="I269">
-        <v>1008</v>
-      </c>
-      <c r="J269" s="1">
-        <v>0.21029999999999999</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="J269" s="1"/>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9102,16 +9068,27 @@
         <v>24</v>
       </c>
       <c r="E270" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J270" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="G270">
+        <v>33</v>
+      </c>
+      <c r="H270">
+        <v>88</v>
+      </c>
+      <c r="I270">
+        <v>384</v>
+      </c>
+      <c r="J270" s="1">
+        <v>0.22919999999999999</v>
+      </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9123,27 +9100,27 @@
         <v>24</v>
       </c>
       <c r="E271" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G271">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H271">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="I271">
-        <v>384</v>
+        <v>36</v>
       </c>
       <c r="J271" s="1">
-        <v>0.2135</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9155,27 +9132,16 @@
         <v>24</v>
       </c>
       <c r="E272" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G272">
-        <v>3</v>
-      </c>
-      <c r="H272">
-        <v>8</v>
-      </c>
-      <c r="I272">
-        <v>36</v>
-      </c>
-      <c r="J272" s="1">
-        <v>0.22220000000000001</v>
-      </c>
+      <c r="J272" s="1"/>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9187,7 +9153,7 @@
         <v>24</v>
       </c>
       <c r="E273" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>30</v>
@@ -9196,7 +9162,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9208,16 +9174,27 @@
         <v>24</v>
       </c>
       <c r="E274" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J274" s="1"/>
+      <c r="G274">
+        <v>51</v>
+      </c>
+      <c r="H274">
+        <v>58</v>
+      </c>
+      <c r="I274">
+        <v>276</v>
+      </c>
+      <c r="J274" s="1">
+        <v>0.21010000000000001</v>
+      </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9229,27 +9206,27 @@
         <v>24</v>
       </c>
       <c r="E275" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G275">
-        <v>51</v>
+        <v>445</v>
       </c>
       <c r="H275">
-        <v>55</v>
+        <v>1244</v>
       </c>
       <c r="I275">
-        <v>276</v>
+        <v>5340</v>
       </c>
       <c r="J275" s="1">
-        <v>0.1993</v>
+        <v>0.23300000000000001</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9258,30 +9235,30 @@
         <v>19</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E276" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G276">
-        <v>445</v>
+        <v>17</v>
       </c>
       <c r="H276">
-        <v>1120</v>
+        <v>1186</v>
       </c>
       <c r="I276">
-        <v>5340</v>
+        <v>5110</v>
       </c>
       <c r="J276" s="1">
-        <v>0.2097</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9296,24 +9273,24 @@
         <v>40</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G277">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H277">
-        <v>1081</v>
+        <v>11</v>
       </c>
       <c r="I277">
-        <v>5110</v>
+        <v>44</v>
       </c>
       <c r="J277" s="1">
-        <v>0.21149999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9328,24 +9305,24 @@
         <v>40</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G278">
         <v>11</v>
       </c>
       <c r="H278">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I278">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="J278" s="1">
-        <v>0.2273</v>
+        <v>0.63639999999999997</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9357,27 +9334,27 @@
         <v>25</v>
       </c>
       <c r="E279" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G279">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H279">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I279">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="J279" s="1">
-        <v>0.54549999999999998</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9392,24 +9369,24 @@
         <v>44</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G280">
         <v>34</v>
       </c>
       <c r="H280">
+        <v>10</v>
+      </c>
+      <c r="I280">
         <v>34</v>
       </c>
-      <c r="I280">
-        <v>136</v>
-      </c>
       <c r="J280" s="1">
-        <v>0.25</v>
+        <v>0.29409999999999997</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9421,27 +9398,27 @@
         <v>25</v>
       </c>
       <c r="E281" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G281">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H281">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I281">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J281" s="1">
-        <v>0.23530000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9453,27 +9430,27 @@
         <v>25</v>
       </c>
       <c r="E282" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G282">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H282">
+        <v>2</v>
+      </c>
+      <c r="I282">
         <v>4</v>
       </c>
-      <c r="I282">
-        <v>12</v>
-      </c>
       <c r="J282" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9485,27 +9462,27 @@
         <v>25</v>
       </c>
       <c r="E283" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G283">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H283">
-        <v>2</v>
+        <v>1236</v>
       </c>
       <c r="I283">
-        <v>4</v>
+        <v>5904</v>
       </c>
       <c r="J283" s="1">
-        <v>0.5</v>
+        <v>0.20930000000000001</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9517,27 +9494,27 @@
         <v>25</v>
       </c>
       <c r="E284" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G284">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H284">
-        <v>1176</v>
+        <v>91</v>
       </c>
       <c r="I284">
-        <v>5904</v>
+        <v>396</v>
       </c>
       <c r="J284" s="1">
-        <v>0.19919999999999999</v>
+        <v>0.2298</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9549,27 +9526,27 @@
         <v>25</v>
       </c>
       <c r="E285" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G285">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H285">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="I285">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="J285" s="1">
-        <v>0.21210000000000001</v>
+        <v>0.21010000000000001</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9581,27 +9558,27 @@
         <v>25</v>
       </c>
       <c r="E286" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G286">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H286">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="I286">
-        <v>276</v>
+        <v>948</v>
       </c>
       <c r="J286" s="1">
-        <v>0.1993</v>
+        <v>0.22889999999999999</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9610,30 +9587,19 @@
         <v>19</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E287" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G287">
-        <v>79</v>
-      </c>
-      <c r="H287">
-        <v>200</v>
-      </c>
-      <c r="I287">
-        <v>948</v>
-      </c>
-      <c r="J287" s="1">
-        <v>0.21099999999999999</v>
-      </c>
+      <c r="J287" s="1"/>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9642,19 +9608,30 @@
         <v>19</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E288" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J288" s="1"/>
+      <c r="G288">
+        <v>21</v>
+      </c>
+      <c r="H288">
+        <v>59</v>
+      </c>
+      <c r="I288">
+        <v>264</v>
+      </c>
+      <c r="J288" s="1">
+        <v>0.2235</v>
+      </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9669,56 +9646,56 @@
         <v>53</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G289">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H289">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="I289">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="J289" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.31819999999999998</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E290" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G290">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="H290">
-        <v>14</v>
+        <v>433</v>
       </c>
       <c r="I290">
-        <v>44</v>
+        <v>1968</v>
       </c>
       <c r="J290" s="1">
-        <v>0.31819999999999998</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9730,27 +9707,27 @@
         <v>24</v>
       </c>
       <c r="E291" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G291">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="H291">
-        <v>376</v>
+        <v>792</v>
       </c>
       <c r="I291">
-        <v>1968</v>
+        <v>4128</v>
       </c>
       <c r="J291" s="1">
-        <v>0.19109999999999999</v>
+        <v>0.19189999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9762,27 +9739,27 @@
         <v>24</v>
       </c>
       <c r="E292" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G292">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="H292">
-        <v>743</v>
+        <v>196</v>
       </c>
       <c r="I292">
-        <v>4128</v>
+        <v>888</v>
       </c>
       <c r="J292" s="1">
-        <v>0.18</v>
+        <v>0.22070000000000001</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9794,27 +9771,27 @@
         <v>24</v>
       </c>
       <c r="E293" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G293">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="H293">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="I293">
-        <v>888</v>
+        <v>1320</v>
       </c>
       <c r="J293" s="1">
-        <v>0.17910000000000001</v>
+        <v>0.18410000000000001</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9826,27 +9803,27 @@
         <v>24</v>
       </c>
       <c r="E294" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G294">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="H294">
-        <v>233</v>
+        <v>418</v>
       </c>
       <c r="I294">
-        <v>1320</v>
+        <v>1920</v>
       </c>
       <c r="J294" s="1">
-        <v>0.17649999999999999</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9858,27 +9835,27 @@
         <v>24</v>
       </c>
       <c r="E295" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G295">
-        <v>160</v>
+        <v>311</v>
       </c>
       <c r="H295">
-        <v>377</v>
+        <v>741</v>
       </c>
       <c r="I295">
-        <v>1920</v>
+        <v>3732</v>
       </c>
       <c r="J295" s="1">
-        <v>0.19639999999999999</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9890,27 +9867,27 @@
         <v>24</v>
       </c>
       <c r="E296" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G296">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="H296">
-        <v>668</v>
+        <v>615</v>
       </c>
       <c r="I296">
-        <v>3732</v>
+        <v>3432</v>
       </c>
       <c r="J296" s="1">
-        <v>0.17899999999999999</v>
+        <v>0.1792</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9922,27 +9899,27 @@
         <v>24</v>
       </c>
       <c r="E297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G297">
-        <v>286</v>
+        <v>12</v>
       </c>
       <c r="H297">
-        <v>583</v>
+        <v>36</v>
       </c>
       <c r="I297">
-        <v>3432</v>
+        <v>144</v>
       </c>
       <c r="J297" s="1">
-        <v>0.1699</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9954,27 +9931,27 @@
         <v>24</v>
       </c>
       <c r="E298" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G298">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="H298">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="I298">
-        <v>144</v>
+        <v>1020</v>
       </c>
       <c r="J298" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.19020000000000001</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -9986,27 +9963,27 @@
         <v>24</v>
       </c>
       <c r="E299" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G299">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="H299">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="I299">
-        <v>1020</v>
+        <v>528</v>
       </c>
       <c r="J299" s="1">
-        <v>0.17349999999999999</v>
+        <v>0.23480000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10018,27 +9995,27 @@
         <v>24</v>
       </c>
       <c r="E300" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G300">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H300">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="I300">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="J300" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.24110000000000001</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10050,27 +10027,27 @@
         <v>24</v>
       </c>
       <c r="E301" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G301">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="H301">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="I301">
-        <v>564</v>
+        <v>1092</v>
       </c>
       <c r="J301" s="1">
-        <v>0.21990000000000001</v>
+        <v>0.18679999999999999</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10082,27 +10059,27 @@
         <v>24</v>
       </c>
       <c r="E302" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G302">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="H302">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="I302">
-        <v>1092</v>
+        <v>384</v>
       </c>
       <c r="J302" s="1">
-        <v>0.1777</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10114,27 +10091,16 @@
         <v>24</v>
       </c>
       <c r="E303" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G303">
-        <v>13</v>
-      </c>
-      <c r="H303">
-        <v>74</v>
-      </c>
-      <c r="I303">
-        <v>384</v>
-      </c>
-      <c r="J303" s="1">
-        <v>0.19270000000000001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J303" s="1"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10146,7 +10112,7 @@
         <v>24</v>
       </c>
       <c r="E304" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>30</v>
@@ -10155,7 +10121,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10167,16 +10133,27 @@
         <v>24</v>
       </c>
       <c r="E305" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J305" s="1"/>
+      <c r="G305">
+        <v>17</v>
+      </c>
+      <c r="H305">
+        <v>46</v>
+      </c>
+      <c r="I305">
+        <v>204</v>
+      </c>
+      <c r="J305" s="1">
+        <v>0.22550000000000001</v>
+      </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10188,27 +10165,27 @@
         <v>24</v>
       </c>
       <c r="E306" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G306">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H306">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="I306">
-        <v>204</v>
+        <v>564</v>
       </c>
       <c r="J306" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10220,27 +10197,27 @@
         <v>24</v>
       </c>
       <c r="E307" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G307">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="H307">
-        <v>102</v>
+        <v>549</v>
       </c>
       <c r="I307">
-        <v>564</v>
+        <v>2724</v>
       </c>
       <c r="J307" s="1">
-        <v>0.18090000000000001</v>
+        <v>0.20150000000000001</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10249,30 +10226,30 @@
         <v>20</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E308" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G308">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c r="H308">
-        <v>481</v>
+        <v>1073</v>
       </c>
       <c r="I308">
-        <v>2724</v>
+        <v>5842</v>
       </c>
       <c r="J308" s="1">
-        <v>0.17660000000000001</v>
+        <v>0.1837</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10287,24 +10264,24 @@
         <v>40</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G309">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H309">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="I309">
-        <v>5842</v>
+        <v>156</v>
       </c>
       <c r="J309" s="1">
-        <v>0.1678</v>
+        <v>0.1603</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10319,24 +10296,24 @@
         <v>40</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G310">
         <v>39</v>
       </c>
       <c r="H310">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I310">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="J310" s="1">
-        <v>0.1603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10348,27 +10325,27 @@
         <v>25</v>
       </c>
       <c r="E311" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G311">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I311">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="J311" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10383,24 +10360,24 @@
         <v>44</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G312">
         <v>44</v>
       </c>
       <c r="H312">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I312">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="J312" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10412,27 +10389,27 @@
         <v>25</v>
       </c>
       <c r="E313" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G313">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="H313">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I313">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="J313" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10444,27 +10421,27 @@
         <v>25</v>
       </c>
       <c r="E314" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G314">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H314">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I314">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J314" s="1">
-        <v>0.5</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10476,27 +10453,27 @@
         <v>25</v>
       </c>
       <c r="E315" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G315">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="H315">
-        <v>5</v>
+        <v>218</v>
       </c>
       <c r="I315">
-        <v>18</v>
+        <v>1044</v>
       </c>
       <c r="J315" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.20880000000000001</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10508,27 +10485,27 @@
         <v>25</v>
       </c>
       <c r="E316" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G316">
-        <v>87</v>
+        <v>228</v>
       </c>
       <c r="H316">
-        <v>183</v>
+        <v>544</v>
       </c>
       <c r="I316">
-        <v>1044</v>
+        <v>2736</v>
       </c>
       <c r="J316" s="1">
-        <v>0.17530000000000001</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10540,27 +10517,27 @@
         <v>25</v>
       </c>
       <c r="E317" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G317">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="H317">
-        <v>497</v>
+        <v>59</v>
       </c>
       <c r="I317">
-        <v>2736</v>
+        <v>300</v>
       </c>
       <c r="J317" s="1">
-        <v>0.1817</v>
+        <v>0.19670000000000001</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10572,27 +10549,27 @@
         <v>25</v>
       </c>
       <c r="E318" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G318">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="H318">
-        <v>46</v>
+        <v>417</v>
       </c>
       <c r="I318">
-        <v>300</v>
+        <v>2196</v>
       </c>
       <c r="J318" s="1">
-        <v>0.15329999999999999</v>
+        <v>0.18990000000000001</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10601,30 +10578,30 @@
         <v>20</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E319" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G319">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="H319">
-        <v>390</v>
+        <v>8</v>
       </c>
       <c r="I319">
-        <v>2196</v>
+        <v>36</v>
       </c>
       <c r="J319" s="1">
-        <v>0.17760000000000001</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10633,30 +10610,19 @@
         <v>20</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E320" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G320">
-        <v>3</v>
-      </c>
-      <c r="H320">
-        <v>8</v>
-      </c>
-      <c r="I320">
-        <v>36</v>
-      </c>
-      <c r="J320" s="1">
-        <v>0.22220000000000001</v>
-      </c>
+      <c r="J320" s="1"/>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10671,12 +10637,12 @@
         <v>53</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10685,37 +10651,48 @@
         <v>20</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E322" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J322" s="1"/>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="E323" t="s">
+        <v>27</v>
+      </c>
       <c r="F323" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J323" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="G323">
+        <v>96</v>
+      </c>
+      <c r="H323">
+        <v>552</v>
+      </c>
+      <c r="I323">
+        <v>2304</v>
+      </c>
+      <c r="J323" s="1">
+        <v>0.23960000000000001</v>
+      </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10727,27 +10704,27 @@
         <v>24</v>
       </c>
       <c r="E324" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G324">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="H324">
-        <v>492</v>
+        <v>50</v>
       </c>
       <c r="I324">
-        <v>2304</v>
+        <v>204</v>
       </c>
       <c r="J324" s="1">
-        <v>0.2135</v>
+        <v>0.24510000000000001</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10759,27 +10736,27 @@
         <v>24</v>
       </c>
       <c r="E325" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G325">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H325">
-        <v>47</v>
+        <v>303</v>
       </c>
       <c r="I325">
-        <v>204</v>
+        <v>1308</v>
       </c>
       <c r="J325" s="1">
-        <v>0.23039999999999999</v>
+        <v>0.23169999999999999</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10791,27 +10768,27 @@
         <v>24</v>
       </c>
       <c r="E326" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G326">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="H326">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="I326">
-        <v>1308</v>
+        <v>96</v>
       </c>
       <c r="J326" s="1">
-        <v>0.21560000000000001</v>
+        <v>0.23960000000000001</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10823,27 +10800,27 @@
         <v>24</v>
       </c>
       <c r="E327" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G327">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H327">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="I327">
-        <v>96</v>
+        <v>408</v>
       </c>
       <c r="J327" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10855,27 +10832,27 @@
         <v>24</v>
       </c>
       <c r="E328" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G328">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="H328">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="I328">
-        <v>408</v>
+        <v>120</v>
       </c>
       <c r="J328" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10887,27 +10864,27 @@
         <v>24</v>
       </c>
       <c r="E329" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G329">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H329">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I329">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="J329" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.24510000000000001</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10919,27 +10896,27 @@
         <v>24</v>
       </c>
       <c r="E330" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G330">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H330">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I330">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="J330" s="1">
-        <v>0.22059999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10951,27 +10928,27 @@
         <v>24</v>
       </c>
       <c r="E331" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G331">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="H331">
-        <v>19</v>
+        <v>580</v>
       </c>
       <c r="I331">
-        <v>84</v>
+        <v>2400</v>
       </c>
       <c r="J331" s="1">
-        <v>0.22620000000000001</v>
+        <v>0.2417</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -10980,30 +10957,30 @@
         <v>21</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E332" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G332">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H332">
-        <v>559</v>
+        <v>1134</v>
       </c>
       <c r="I332">
-        <v>2400</v>
+        <v>5110</v>
       </c>
       <c r="J332" s="1">
-        <v>0.2329</v>
+        <v>0.22189999999999999</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11018,24 +10995,24 @@
         <v>40</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G333">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H333">
-        <v>1022</v>
+        <v>0</v>
       </c>
       <c r="I333">
-        <v>5110</v>
+        <v>76</v>
       </c>
       <c r="J333" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11050,7 +11027,7 @@
         <v>40</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G334">
         <v>19</v>
@@ -11059,7 +11036,7 @@
         <v>0</v>
       </c>
       <c r="I334">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J334" s="1">
         <v>0</v>
@@ -11067,7 +11044,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11079,19 +11056,19 @@
         <v>25</v>
       </c>
       <c r="E335" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G335">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H335">
         <v>0</v>
       </c>
       <c r="I335">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J335" s="1">
         <v>0</v>
@@ -11099,7 +11076,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11111,19 +11088,19 @@
         <v>25</v>
       </c>
       <c r="E336" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G336">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H336">
         <v>0</v>
       </c>
       <c r="I336">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J336" s="1">
         <v>0</v>
@@ -11131,7 +11108,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11143,27 +11120,27 @@
         <v>25</v>
       </c>
       <c r="E337" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G337">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I337">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="J337" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11175,27 +11152,27 @@
         <v>25</v>
       </c>
       <c r="E338" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G338">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H338">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I338">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="J338" s="1">
-        <v>0.2167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11207,27 +11184,16 @@
         <v>25</v>
       </c>
       <c r="E339" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G339">
-        <v>1</v>
-      </c>
-      <c r="H339">
-        <v>0</v>
-      </c>
-      <c r="I339">
-        <v>1</v>
-      </c>
-      <c r="J339" s="1">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J339" s="1"/>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11239,7 +11205,7 @@
         <v>25</v>
       </c>
       <c r="E340" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>30</v>
@@ -11247,7 +11213,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11259,7 +11225,7 @@
         <v>25</v>
       </c>
       <c r="E341" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>30</v>
@@ -11268,28 +11234,39 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E342" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J342" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="G342">
+        <v>392</v>
+      </c>
+      <c r="H342">
+        <v>2272</v>
+      </c>
+      <c r="I342">
+        <v>9408</v>
+      </c>
+      <c r="J342" s="1">
+        <v>0.24149999999999999</v>
+      </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11301,27 +11278,27 @@
         <v>24</v>
       </c>
       <c r="E343" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G343">
-        <v>392</v>
+        <v>39</v>
       </c>
       <c r="H343">
-        <v>1986</v>
+        <v>110</v>
       </c>
       <c r="I343">
-        <v>9408</v>
+        <v>468</v>
       </c>
       <c r="J343" s="1">
-        <v>0.21110000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11333,27 +11310,27 @@
         <v>24</v>
       </c>
       <c r="E344" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G344">
-        <v>39</v>
+        <v>778</v>
       </c>
       <c r="H344">
-        <v>102</v>
+        <v>2134</v>
       </c>
       <c r="I344">
-        <v>468</v>
+        <v>9336</v>
       </c>
       <c r="J344" s="1">
-        <v>0.21790000000000001</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11365,27 +11342,27 @@
         <v>24</v>
       </c>
       <c r="E345" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G345">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="H345">
-        <v>2038</v>
+        <v>45</v>
       </c>
       <c r="I345">
-        <v>9336</v>
+        <v>192</v>
       </c>
       <c r="J345" s="1">
-        <v>0.21829999999999999</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11397,27 +11374,27 @@
         <v>24</v>
       </c>
       <c r="E346" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G346">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H346">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="I346">
-        <v>192</v>
+        <v>312</v>
       </c>
       <c r="J346" s="1">
-        <v>0.2344</v>
+        <v>0.22120000000000001</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11429,27 +11406,27 @@
         <v>24</v>
       </c>
       <c r="E347" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G347">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H347">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="I347">
-        <v>312</v>
+        <v>576</v>
       </c>
       <c r="J347" s="1">
-        <v>0.2051</v>
+        <v>0.22570000000000001</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11461,27 +11438,27 @@
         <v>24</v>
       </c>
       <c r="E348" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G348">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H348">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="I348">
-        <v>576</v>
+        <v>84</v>
       </c>
       <c r="J348" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.23810000000000001</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11493,27 +11470,27 @@
         <v>24</v>
       </c>
       <c r="E349" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G349">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H349">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I349">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="J349" s="1">
-        <v>0.23810000000000001</v>
+        <v>0.20369999999999999</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11525,27 +11502,27 @@
         <v>24</v>
       </c>
       <c r="E350" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G350">
-        <v>9</v>
+        <v>925</v>
       </c>
       <c r="H350">
-        <v>21</v>
+        <v>2488</v>
       </c>
       <c r="I350">
-        <v>108</v>
+        <v>11100</v>
       </c>
       <c r="J350" s="1">
-        <v>0.19439999999999999</v>
+        <v>0.22409999999999999</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11557,27 +11534,27 @@
         <v>24</v>
       </c>
       <c r="E351" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G351">
-        <v>925</v>
+        <v>45</v>
       </c>
       <c r="H351">
-        <v>2299</v>
+        <v>121</v>
       </c>
       <c r="I351">
-        <v>11100</v>
+        <v>540</v>
       </c>
       <c r="J351" s="1">
-        <v>0.20710000000000001</v>
+        <v>0.22409999999999999</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11589,27 +11566,27 @@
         <v>24</v>
       </c>
       <c r="E352" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G352">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H352">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="I352">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="J352" s="1">
-        <v>0.24260000000000001</v>
+        <v>0.20949999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11621,27 +11598,27 @@
         <v>24</v>
       </c>
       <c r="E353" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G353">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H353">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="I353">
-        <v>420</v>
+        <v>1740</v>
       </c>
       <c r="J353" s="1">
-        <v>0.19289999999999999</v>
+        <v>0.24249999999999999</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11650,30 +11627,30 @@
         <v>22</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E354" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G354">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="H354">
-        <v>414</v>
+        <v>7540</v>
       </c>
       <c r="I354">
-        <v>1740</v>
+        <v>38325</v>
       </c>
       <c r="J354" s="1">
-        <v>0.2379</v>
+        <v>0.19670000000000001</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11688,24 +11665,24 @@
         <v>40</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G355">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="H355">
-        <v>6868</v>
+        <v>64</v>
       </c>
       <c r="I355">
-        <v>38325</v>
+        <v>260</v>
       </c>
       <c r="J355" s="1">
-        <v>0.1792</v>
+        <v>0.2462</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11720,24 +11697,24 @@
         <v>40</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G356">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H356">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="I356">
-        <v>352</v>
+        <v>65</v>
       </c>
       <c r="J356" s="1">
-        <v>0.13639999999999999</v>
+        <v>0.98460000000000003</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11749,27 +11726,27 @@
         <v>25</v>
       </c>
       <c r="E357" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G357">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="H357">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I357">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="J357" s="1">
-        <v>0.75380000000000003</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11784,24 +11761,24 @@
         <v>44</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G358">
         <v>33</v>
       </c>
       <c r="H358">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I358">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="J358" s="1">
-        <v>0.2424</v>
+        <v>0.42420000000000002</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11813,27 +11790,27 @@
         <v>25</v>
       </c>
       <c r="E359" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G359">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H359">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I359">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J359" s="1">
-        <v>0.42420000000000002</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11845,27 +11822,27 @@
         <v>25</v>
       </c>
       <c r="E360" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G360">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H360">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I360">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J360" s="1">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11877,27 +11854,27 @@
         <v>25</v>
       </c>
       <c r="E361" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G361">
-        <v>10</v>
+        <v>3536</v>
       </c>
       <c r="H361">
-        <v>7</v>
+        <v>9688</v>
       </c>
       <c r="I361">
-        <v>20</v>
+        <v>42432</v>
       </c>
       <c r="J361" s="1">
-        <v>0.35</v>
+        <v>0.2283</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11909,27 +11886,27 @@
         <v>25</v>
       </c>
       <c r="E362" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G362">
-        <v>3536</v>
+        <v>33</v>
       </c>
       <c r="H362">
-        <v>9484</v>
+        <v>92</v>
       </c>
       <c r="I362">
-        <v>42432</v>
+        <v>396</v>
       </c>
       <c r="J362" s="1">
-        <v>0.2235</v>
+        <v>0.23230000000000001</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11941,27 +11918,27 @@
         <v>25</v>
       </c>
       <c r="E363" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G363">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H363">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="I363">
-        <v>396</v>
+        <v>132</v>
       </c>
       <c r="J363" s="1">
-        <v>0.21970000000000001</v>
+        <v>0.19700000000000001</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11973,27 +11950,27 @@
         <v>25</v>
       </c>
       <c r="E364" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G364">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H364">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="I364">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="J364" s="1">
-        <v>0.18940000000000001</v>
+        <v>0.21879999999999999</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12002,30 +11979,30 @@
         <v>22</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E365" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G365">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H365">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="I365">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="J365" s="1">
-        <v>0.2049</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12034,10 +12011,10 @@
         <v>22</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E366" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>30</v>
@@ -12046,18 +12023,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>0.25</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12068,43 +12045,43 @@
       <c r="D367" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E367" t="s">
-        <v>53</v>
-      </c>
-      <c r="F367" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G367">
-        <v>4</v>
-      </c>
-      <c r="H367">
-        <v>8</v>
-      </c>
-      <c r="I367">
-        <v>48</v>
-      </c>
-      <c r="J367" s="1">
-        <v>0.16669999999999999</v>
-      </c>
+      <c r="J367" s="1"/>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J368" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="E368" t="s">
+        <v>27</v>
+      </c>
+      <c r="F368" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G368">
+        <v>278</v>
+      </c>
+      <c r="H368">
+        <v>1535</v>
+      </c>
+      <c r="I368">
+        <v>6672</v>
+      </c>
+      <c r="J368" s="1">
+        <v>0.2301</v>
+      </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12116,27 +12093,27 @@
         <v>24</v>
       </c>
       <c r="E369" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G369">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="H369">
-        <v>1404</v>
+        <v>352</v>
       </c>
       <c r="I369">
-        <v>6672</v>
+        <v>1548</v>
       </c>
       <c r="J369" s="1">
-        <v>0.2104</v>
+        <v>0.22739999999999999</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12148,27 +12125,27 @@
         <v>24</v>
       </c>
       <c r="E370" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F370" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G370">
-        <v>129</v>
+        <v>553</v>
       </c>
       <c r="H370">
-        <v>343</v>
+        <v>1466</v>
       </c>
       <c r="I370">
-        <v>1548</v>
+        <v>6636</v>
       </c>
       <c r="J370" s="1">
-        <v>0.22159999999999999</v>
+        <v>0.22090000000000001</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12180,27 +12157,27 @@
         <v>24</v>
       </c>
       <c r="E371" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F371" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G371">
-        <v>533</v>
+        <v>315</v>
       </c>
       <c r="H371">
-        <v>1390</v>
+        <v>867</v>
       </c>
       <c r="I371">
-        <v>6636</v>
+        <v>3780</v>
       </c>
       <c r="J371" s="1">
-        <v>0.20949999999999999</v>
+        <v>0.22939999999999999</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12212,27 +12189,27 @@
         <v>24</v>
       </c>
       <c r="E372" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G372">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="H372">
-        <v>833</v>
+        <v>53</v>
       </c>
       <c r="I372">
-        <v>3780</v>
+        <v>240</v>
       </c>
       <c r="J372" s="1">
-        <v>0.22040000000000001</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12241,30 +12218,30 @@
         <v>23</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E373" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F373" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G373">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H373">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I373">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="J373" s="1">
-        <v>0.2167</v>
+        <v>0.23250000000000001</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12273,30 +12250,30 @@
         <v>23</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E374" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G374">
         <v>19</v>
       </c>
       <c r="H374">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="I374">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="J374" s="1">
-        <v>0.2281</v>
+        <v>0.22370000000000001</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12308,27 +12285,27 @@
         <v>24</v>
       </c>
       <c r="E375" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G375">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="H375">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="I375">
-        <v>456</v>
+        <v>1032</v>
       </c>
       <c r="J375" s="1">
-        <v>0.2039</v>
+        <v>0.22770000000000001</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12340,27 +12317,16 @@
         <v>24</v>
       </c>
       <c r="E376" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G376">
-        <v>86</v>
-      </c>
-      <c r="H376">
-        <v>227</v>
-      </c>
-      <c r="I376">
-        <v>1032</v>
-      </c>
-      <c r="J376" s="1">
-        <v>0.22</v>
-      </c>
+      <c r="J376" s="1"/>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12372,16 +12338,27 @@
         <v>24</v>
       </c>
       <c r="E377" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F377" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J377" s="1"/>
+      <c r="G377">
+        <v>2</v>
+      </c>
+      <c r="H377">
+        <v>4</v>
+      </c>
+      <c r="I377">
+        <v>24</v>
+      </c>
+      <c r="J377" s="1">
+        <v>0.16669999999999999</v>
+      </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12393,27 +12370,27 @@
         <v>24</v>
       </c>
       <c r="E378" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G378">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H378">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="I378">
-        <v>24</v>
+        <v>384</v>
       </c>
       <c r="J378" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.1953</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12425,27 +12402,27 @@
         <v>24</v>
       </c>
       <c r="E379" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F379" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G379">
-        <v>32</v>
+        <v>615</v>
       </c>
       <c r="H379">
-        <v>74</v>
+        <v>1679</v>
       </c>
       <c r="I379">
-        <v>384</v>
+        <v>7380</v>
       </c>
       <c r="J379" s="1">
-        <v>0.19270000000000001</v>
+        <v>0.22750000000000001</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12454,30 +12431,30 @@
         <v>23</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E380" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G380">
-        <v>615</v>
+        <v>172</v>
       </c>
       <c r="H380">
-        <v>1611</v>
+        <v>3909</v>
       </c>
       <c r="I380">
-        <v>7380</v>
+        <v>17695</v>
       </c>
       <c r="J380" s="1">
-        <v>0.21829999999999999</v>
+        <v>0.22090000000000001</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12492,24 +12469,24 @@
         <v>40</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G381">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H381">
-        <v>3493</v>
+        <v>155</v>
       </c>
       <c r="I381">
-        <v>17695</v>
+        <v>700</v>
       </c>
       <c r="J381" s="1">
-        <v>0.19739999999999999</v>
+        <v>0.22140000000000001</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12524,24 +12501,24 @@
         <v>40</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G382">
         <v>175</v>
       </c>
       <c r="H382">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I382">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="J382" s="1">
-        <v>0.21709999999999999</v>
+        <v>0.88570000000000004</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12553,27 +12530,27 @@
         <v>25</v>
       </c>
       <c r="E383" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G383">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="H383">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="I383">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="J383" s="1">
-        <v>0.86860000000000004</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12588,24 +12565,24 @@
         <v>44</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G384">
         <v>48</v>
       </c>
       <c r="H384">
+        <v>41</v>
+      </c>
+      <c r="I384">
         <v>48</v>
       </c>
-      <c r="I384">
-        <v>192</v>
-      </c>
       <c r="J384" s="1">
-        <v>0.25</v>
+        <v>0.85419999999999996</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12617,27 +12594,16 @@
         <v>25</v>
       </c>
       <c r="E385" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G385">
-        <v>48</v>
-      </c>
-      <c r="H385">
-        <v>41</v>
-      </c>
-      <c r="I385">
-        <v>48</v>
-      </c>
-      <c r="J385" s="1">
-        <v>0.85419999999999996</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="J385" s="1"/>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12649,16 +12615,27 @@
         <v>25</v>
       </c>
       <c r="E386" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F386" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J386" s="1"/>
+      <c r="G386">
+        <v>13</v>
+      </c>
+      <c r="H386">
+        <v>14</v>
+      </c>
+      <c r="I386">
+        <v>26</v>
+      </c>
+      <c r="J386" s="1">
+        <v>0.53849999999999998</v>
+      </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12670,27 +12647,27 @@
         <v>25</v>
       </c>
       <c r="E387" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G387">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H387">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="I387">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="J387" s="1">
-        <v>0.57689999999999997</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12702,27 +12679,27 @@
         <v>25</v>
       </c>
       <c r="E388" t="s">
+        <v>49</v>
+      </c>
+      <c r="F388" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G388">
         <v>48</v>
-      </c>
-      <c r="F388" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G388">
-        <v>50</v>
       </c>
       <c r="H388">
         <v>126</v>
       </c>
       <c r="I388">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="J388" s="1">
-        <v>0.21</v>
+        <v>0.21879999999999999</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12734,27 +12711,27 @@
         <v>25</v>
       </c>
       <c r="E389" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F389" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G389">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H389">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="I389">
-        <v>576</v>
+        <v>204</v>
       </c>
       <c r="J389" s="1">
-        <v>0.20660000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12763,30 +12740,30 @@
         <v>23</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E390" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F390" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G390">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H390">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="I390">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="J390" s="1">
-        <v>0.1961</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12795,30 +12772,30 @@
         <v>23</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E391" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F391" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G391">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="H391">
-        <v>63</v>
+        <v>170</v>
       </c>
       <c r="I391">
-        <v>300</v>
+        <v>744</v>
       </c>
       <c r="J391" s="1">
-        <v>0.21</v>
+        <v>0.22850000000000001</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>
@@ -12833,52 +12810,9 @@
         <v>53</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G392">
-        <v>62</v>
-      </c>
-      <c r="H392">
-        <v>164</v>
-      </c>
-      <c r="I392">
-        <v>744</v>
-      </c>
-      <c r="J392" s="1">
-        <v>0.22040000000000001</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A393" s="3">
-        <v>46097</v>
-      </c>
-      <c r="B393" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C393" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D393" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E393" t="s">
-        <v>53</v>
-      </c>
-      <c r="F393" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G393">
-        <v>16</v>
-      </c>
-      <c r="H393">
-        <v>16</v>
-      </c>
-      <c r="I393">
-        <v>744</v>
-      </c>
-      <c r="J393" s="1">
-        <v>2.1499999999999998E-2</v>
-      </c>
+      <c r="J392" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA6D89E-313D-4277-8324-7D69F09A9DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530F489F-7CD4-4771-AA8B-AD5B6C12184C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -784,7 +784,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -802,18 +802,18 @@
         <v>28</v>
       </c>
       <c r="H2">
-        <v>5114</v>
+        <v>5146</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.2485</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -831,18 +831,18 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>702</v>
+        <v>746</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.2321</v>
+        <v>0.2467</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -860,18 +860,18 @@
         <v>30</v>
       </c>
       <c r="H4">
-        <v>4253</v>
+        <v>4798</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.219</v>
+        <v>0.24709999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -889,18 +889,18 @@
         <v>30</v>
       </c>
       <c r="H5">
-        <v>6088</v>
+        <v>6779</v>
       </c>
       <c r="I5">
         <v>27456</v>
       </c>
       <c r="J5" s="1">
-        <v>0.22170000000000001</v>
+        <v>0.24690000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -918,18 +918,18 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.21149999999999999</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -947,18 +947,18 @@
         <v>28</v>
       </c>
       <c r="H7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>0.24279999999999999</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1005,18 +1005,18 @@
         <v>30</v>
       </c>
       <c r="H9">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.2379</v>
+        <v>0.24529999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1034,18 +1034,18 @@
         <v>30</v>
       </c>
       <c r="H10">
-        <v>780</v>
+        <v>877</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.21959999999999999</v>
+        <v>0.24690000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1063,18 +1063,18 @@
         <v>30</v>
       </c>
       <c r="H11">
-        <v>581</v>
+        <v>619</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.23169999999999999</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1092,18 +1092,18 @@
         <v>30</v>
       </c>
       <c r="H12">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>0.19389999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1121,18 +1121,18 @@
         <v>41</v>
       </c>
       <c r="H13">
-        <v>6500</v>
+        <v>7125</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.25430000000000003</v>
+        <v>0.2787</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1150,18 +1150,18 @@
         <v>42</v>
       </c>
       <c r="H14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.2281</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1179,18 +1179,18 @@
         <v>43</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I15">
         <v>57</v>
       </c>
       <c r="J15" s="1">
-        <v>0.24560000000000001</v>
+        <v>0.31580000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1208,18 +1208,18 @@
         <v>42</v>
       </c>
       <c r="H16">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.219</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1295,18 +1295,18 @@
         <v>30</v>
       </c>
       <c r="H19">
-        <v>28515</v>
+        <v>32458</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.24299999999999999</v>
+        <v>0.27660000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1324,18 +1324,18 @@
         <v>30</v>
       </c>
       <c r="H20">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.23300000000000001</v>
+        <v>0.24940000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1353,18 +1353,18 @@
         <v>30</v>
       </c>
       <c r="H21">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.22289999999999999</v>
+        <v>0.24610000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1382,18 +1382,18 @@
         <v>30</v>
       </c>
       <c r="H22">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.21049999999999999</v>
+        <v>0.24510000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1504,18 +1504,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.24149999999999999</v>
+        <v>0.24859999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1536,18 +1536,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>0.23580000000000001</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1568,18 +1568,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.24010000000000001</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1600,18 +1600,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>1081</v>
+        <v>1160</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.2263</v>
+        <v>0.2429</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1632,18 +1632,18 @@
         <v>398</v>
       </c>
       <c r="H31">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I31">
         <v>398</v>
       </c>
       <c r="J31" s="1">
-        <v>0.3543</v>
+        <v>0.38440000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1664,18 +1664,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.32029999999999997</v>
+        <v>0.33589999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1696,18 +1696,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>0.23769999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1728,18 +1728,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.52539999999999998</v>
+        <v>0.55930000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1760,18 +1760,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>0.1227</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1792,18 +1792,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>0.15090000000000001</v>
+        <v>0.1585</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1856,18 +1856,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>0.13100000000000001</v>
+        <v>0.1517</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1920,18 +1920,18 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I40">
         <v>60</v>
       </c>
       <c r="J40" s="1">
-        <v>0.23330000000000001</v>
+        <v>0.26669999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -1984,18 +1984,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.23499999999999999</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2048,18 +2048,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.2319</v>
+        <v>0.24279999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2109,21 +2109,21 @@
         <v>43</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>3</v>
       </c>
       <c r="J46" s="1">
-        <v>0</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2144,18 +2144,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>1960522</v>
+        <v>2054630</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.23630000000000001</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2176,18 +2176,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>300338.3</v>
+        <v>323916</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.21790000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2208,18 +2208,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>3570</v>
+        <v>3804</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.22989999999999999</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2240,18 +2240,18 @@
         <v>691098</v>
       </c>
       <c r="H50">
-        <v>613993</v>
+        <v>666836</v>
       </c>
       <c r="I50">
         <v>2764392</v>
       </c>
       <c r="J50" s="1">
-        <v>0.22209999999999999</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2272,18 +2272,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>238343</v>
+        <v>252369</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.3448</v>
+        <v>0.36509999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2304,18 +2304,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.22750000000000001</v>
+        <v>0.23480000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2336,18 +2336,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.33529999999999999</v>
+        <v>0.35730000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2368,18 +2368,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.20469999999999999</v>
+        <v>0.21060000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2400,18 +2400,18 @@
         <v>649</v>
       </c>
       <c r="H55">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="I55">
         <v>649</v>
       </c>
       <c r="J55" s="1">
-        <v>0.19719999999999999</v>
+        <v>0.2404</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2496,18 +2496,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.22950000000000001</v>
+        <v>0.24440000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2528,18 +2528,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.23400000000000001</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2560,18 +2560,18 @@
         <v>691280</v>
       </c>
       <c r="H60">
-        <v>1895603</v>
+        <v>2062506</v>
       </c>
       <c r="I60">
         <v>8295360</v>
       </c>
       <c r="J60" s="1">
-        <v>0.22850000000000001</v>
+        <v>0.24859999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2592,18 +2592,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>2033</v>
+        <v>2190</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.23139999999999999</v>
+        <v>0.24929999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2624,18 +2624,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>0.24929999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2656,18 +2656,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1820</v>
+        <v>1917</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.23699999999999999</v>
+        <v>0.24959999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2688,18 +2688,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>2126</v>
+        <v>2231</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.23749999999999999</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2720,18 +2720,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="I65">
         <v>1092</v>
       </c>
       <c r="J65" s="1">
-        <v>0.20880000000000001</v>
+        <v>0.24629999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2752,18 +2752,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I66">
         <v>240</v>
       </c>
       <c r="J66" s="1">
-        <v>0.23749999999999999</v>
+        <v>0.25829999999999997</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2816,18 +2816,18 @@
         <v>3</v>
       </c>
       <c r="H68">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2848,18 +2848,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="I69">
         <v>876</v>
       </c>
       <c r="J69" s="1">
-        <v>0.22489999999999999</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2880,18 +2880,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.2374</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2912,18 +2912,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>786</v>
+        <v>819</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>0.2399</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2944,18 +2944,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>1134</v>
+        <v>1232</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.22189999999999999</v>
+        <v>0.24110000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3040,18 +3040,18 @@
         <v>52</v>
       </c>
       <c r="H75">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I75">
         <v>208</v>
       </c>
       <c r="J75" s="1">
-        <v>0.2452</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3168,18 +3168,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>0.22620000000000001</v>
+        <v>0.24959999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3200,18 +3200,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>830</v>
+        <v>866</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>0.24099999999999999</v>
+        <v>0.2515</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3232,18 +3232,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="I81">
         <v>948</v>
       </c>
       <c r="J81" s="1">
-        <v>0.21310000000000001</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3264,18 +3264,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>337</v>
+        <v>398</v>
       </c>
       <c r="I82">
         <v>1632</v>
       </c>
       <c r="J82" s="1">
-        <v>0.20649999999999999</v>
+        <v>0.24390000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3317,18 +3317,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>0.2213</v>
+        <v>0.24709999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3381,18 +3381,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1668</v>
+        <v>1742</v>
       </c>
       <c r="I86">
         <v>7032</v>
       </c>
       <c r="J86" s="1">
-        <v>0.23719999999999999</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3413,18 +3413,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.19819999999999999</v>
+        <v>0.2455</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3445,18 +3445,18 @@
         <v>493</v>
       </c>
       <c r="H88">
-        <v>1311</v>
+        <v>1470</v>
       </c>
       <c r="I88">
-        <v>6916</v>
+        <v>5916</v>
       </c>
       <c r="J88" s="1">
-        <v>0.18959999999999999</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3509,18 +3509,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>2127</v>
+        <v>2225</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>0.2366</v>
+        <v>0.24759999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3541,18 +3541,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="I91">
         <v>1932</v>
       </c>
       <c r="J91" s="1">
-        <v>0.23139999999999999</v>
+        <v>0.24740000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3573,18 +3573,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="I92">
         <v>1128</v>
       </c>
       <c r="J92" s="1">
-        <v>0.2394</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3605,18 +3605,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.20910000000000001</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3658,18 +3658,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.2019</v>
+        <v>0.24260000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3711,18 +3711,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.32969999999999999</v>
+        <v>0.35980000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3743,18 +3743,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98">
         <v>60</v>
       </c>
       <c r="J98" s="1">
-        <v>0.2167</v>
+        <v>0.23330000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3775,18 +3775,18 @@
         <v>14</v>
       </c>
       <c r="H99">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I99">
         <v>15</v>
       </c>
       <c r="J99" s="1">
-        <v>0.4667</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3924,18 +3924,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.2</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -3956,18 +3956,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -3988,18 +3988,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="I106">
         <v>552</v>
       </c>
       <c r="J106" s="1">
-        <v>0.1993</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4041,18 +4041,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I108">
         <v>611</v>
       </c>
       <c r="J108" s="1">
-        <v>0.19800000000000001</v>
+        <v>0.23569999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4094,18 +4094,18 @@
         <v>16</v>
       </c>
       <c r="H110">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I110">
         <v>192</v>
       </c>
       <c r="J110" s="1">
-        <v>0.19789999999999999</v>
+        <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4126,18 +4126,18 @@
         <v>458</v>
       </c>
       <c r="H111">
-        <v>2729</v>
+        <v>2735</v>
       </c>
       <c r="I111">
         <v>10992</v>
       </c>
       <c r="J111" s="1">
-        <v>0.24829999999999999</v>
+        <v>0.24879999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4190,18 +4190,18 @@
         <v>43</v>
       </c>
       <c r="H113">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I113">
         <v>516</v>
       </c>
       <c r="J113" s="1">
-        <v>0.21510000000000001</v>
+        <v>0.2364</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4222,18 +4222,18 @@
         <v>665</v>
       </c>
       <c r="H114">
-        <v>1689</v>
+        <v>1908</v>
       </c>
       <c r="I114">
         <v>7992</v>
       </c>
       <c r="J114" s="1">
-        <v>0.21129999999999999</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4254,18 +4254,18 @@
         <v>1043</v>
       </c>
       <c r="H115">
-        <v>2703</v>
+        <v>2995</v>
       </c>
       <c r="I115">
         <v>12264</v>
       </c>
       <c r="J115" s="1">
-        <v>0.22040000000000001</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4286,18 +4286,18 @@
         <v>71</v>
       </c>
       <c r="H116">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="I116">
         <v>852</v>
       </c>
       <c r="J116" s="1">
-        <v>0.21360000000000001</v>
+        <v>0.24410000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4329,7 +4329,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4350,18 +4350,18 @@
         <v>5</v>
       </c>
       <c r="H118">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I118">
         <v>60</v>
       </c>
       <c r="J118" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4414,18 +4414,18 @@
         <v>81</v>
       </c>
       <c r="H120">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="I120">
         <v>972</v>
       </c>
       <c r="J120" s="1">
-        <v>0.20880000000000001</v>
+        <v>0.24279999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4446,18 +4446,18 @@
         <v>52</v>
       </c>
       <c r="H121">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I121">
         <v>624</v>
       </c>
       <c r="J121" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.2356</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4478,18 +4478,18 @@
         <v>44</v>
       </c>
       <c r="H122">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="I122">
         <v>528</v>
       </c>
       <c r="J122" s="1">
-        <v>0.21210000000000001</v>
+        <v>0.25380000000000003</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4510,18 +4510,18 @@
         <v>11</v>
       </c>
       <c r="H123">
-        <v>1111</v>
+        <v>1221</v>
       </c>
       <c r="I123">
         <v>4046</v>
       </c>
       <c r="J123" s="1">
-        <v>0.27460000000000001</v>
+        <v>0.30180000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4606,18 +4606,18 @@
         <v>45</v>
       </c>
       <c r="H126">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I126">
         <v>180</v>
       </c>
       <c r="J126" s="1">
-        <v>0.24440000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4649,7 +4649,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4734,18 +4734,18 @@
         <v>188</v>
       </c>
       <c r="H130">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="I130">
         <v>2256</v>
       </c>
       <c r="J130" s="1">
-        <v>0.20349999999999999</v>
+        <v>0.22919999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4766,18 +4766,18 @@
         <v>43</v>
       </c>
       <c r="H131">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I131">
         <v>516</v>
       </c>
       <c r="J131" s="1">
-        <v>0.2248</v>
+        <v>0.2422</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4798,18 +4798,18 @@
         <v>14</v>
       </c>
       <c r="H132">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I132">
         <v>168</v>
       </c>
       <c r="J132" s="1">
-        <v>0.21429999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4830,18 +4830,18 @@
         <v>52</v>
       </c>
       <c r="H133">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="I133">
         <v>624</v>
       </c>
       <c r="J133" s="1">
-        <v>0.18590000000000001</v>
+        <v>0.21959999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4861,7 +4861,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4924,18 +4924,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.1951</v>
+        <v>0.24390000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -4956,18 +4956,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>1669</v>
+        <v>1757</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>0.23769999999999999</v>
+        <v>0.25030000000000002</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5084,18 +5084,18 @@
         <v>22</v>
       </c>
       <c r="H142">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I142">
         <v>264</v>
       </c>
       <c r="J142" s="1">
-        <v>0.21590000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5116,18 +5116,18 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I143">
         <v>12</v>
       </c>
       <c r="J143" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5148,18 +5148,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>2555</v>
+        <v>2725</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>0.23710000000000001</v>
+        <v>0.25290000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5180,18 +5180,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.23880000000000001</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5212,18 +5212,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>0.22020000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5244,18 +5244,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.20280000000000001</v>
+        <v>0.23749999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5276,18 +5276,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.1971</v>
+        <v>0.2452</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5340,18 +5340,18 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I150">
         <v>48</v>
       </c>
       <c r="J150" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5404,18 +5404,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>1271</v>
+        <v>1390</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.26790000000000003</v>
+        <v>0.29289999999999999</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5532,18 +5532,18 @@
         <v>45</v>
       </c>
       <c r="H156">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I156">
         <v>45</v>
       </c>
       <c r="J156" s="1">
-        <v>0.17780000000000001</v>
+        <v>0.31109999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5564,18 +5564,18 @@
         <v>9</v>
       </c>
       <c r="H157">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I157">
         <v>18</v>
       </c>
       <c r="J157" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5596,18 +5596,18 @@
         <v>1</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158">
         <v>2</v>
       </c>
       <c r="J158" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5628,18 +5628,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.20930000000000001</v>
+        <v>0.24590000000000001</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5660,18 +5660,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>0.2014</v>
+        <v>0.22919999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5692,18 +5692,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.2006</v>
+        <v>0.2359</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5724,18 +5724,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>381</v>
+        <v>483</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.1948</v>
+        <v>0.24690000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5756,18 +5756,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>2215</v>
+        <v>2299</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.23849999999999999</v>
+        <v>0.2475</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5788,18 +5788,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>0.2094</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5820,18 +5820,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1597</v>
+        <v>1750</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.22559999999999999</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5852,18 +5852,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>2758</v>
+        <v>2900</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.2384</v>
+        <v>0.25069999999999998</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5884,18 +5884,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.19789999999999999</v>
+        <v>0.22739999999999999</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5916,18 +5916,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>0.23719999999999999</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -5948,18 +5948,18 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I169">
         <v>84</v>
       </c>
       <c r="J169" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.23810000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -5980,18 +5980,18 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I170">
         <v>12</v>
       </c>
       <c r="J170" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6012,18 +6012,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.19370000000000001</v>
+        <v>0.22070000000000001</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6044,18 +6044,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.21629999999999999</v>
+        <v>0.2394</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6076,18 +6076,18 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I173">
         <v>84</v>
       </c>
       <c r="J173" s="1">
-        <v>0.17860000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6108,18 +6108,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>2702</v>
+        <v>2982</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.27229999999999999</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6140,18 +6140,18 @@
         <v>57</v>
       </c>
       <c r="H175">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I175">
         <v>228</v>
       </c>
       <c r="J175" s="1">
-        <v>0.1404</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6204,18 +6204,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>0.20269999999999999</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6236,18 +6236,18 @@
         <v>37</v>
       </c>
       <c r="H178">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I178">
         <v>37</v>
       </c>
       <c r="J178" s="1">
-        <v>0.2162</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6311,7 +6311,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6332,18 +6332,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.20930000000000001</v>
+        <v>0.2397</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6364,18 +6364,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.21299999999999999</v>
+        <v>0.2361</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6428,18 +6428,18 @@
         <v>9</v>
       </c>
       <c r="H184">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I184">
         <v>108</v>
       </c>
       <c r="J184" s="1">
-        <v>0.1852</v>
+        <v>0.23150000000000001</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6460,18 +6460,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.19789999999999999</v>
+        <v>0.2263</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6545,18 +6545,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>0.23150000000000001</v>
+        <v>0.24540000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6577,18 +6577,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6609,18 +6609,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>0.2218</v>
+        <v>0.23019999999999999</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6641,18 +6641,18 @@
         <v>59</v>
       </c>
       <c r="H191">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I191">
         <v>59</v>
       </c>
       <c r="J191" s="1">
-        <v>0.40679999999999999</v>
+        <v>0.67800000000000005</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6748,7 +6748,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6812,7 +6812,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6833,18 +6833,18 @@
         <v>9</v>
       </c>
       <c r="H197">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I197">
         <v>9</v>
       </c>
       <c r="J197" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6897,18 +6897,18 @@
         <v>59</v>
       </c>
       <c r="H199">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I199">
         <v>59</v>
       </c>
       <c r="J199" s="1">
-        <v>0.49149999999999999</v>
+        <v>0.69489999999999996</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7036,7 +7036,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7057,18 +7057,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>540052</v>
+        <v>558947</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.23810000000000001</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7089,18 +7089,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>62810</v>
+        <v>66845</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.1711</v>
+        <v>0.18210000000000001</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7121,18 +7121,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>976</v>
+        <v>1029</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>0.23369999999999999</v>
+        <v>0.24640000000000001</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7324,7 +7324,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7356,7 +7356,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7409,18 +7409,18 @@
         <v>263</v>
       </c>
       <c r="H215">
-        <v>1472</v>
+        <v>1551</v>
       </c>
       <c r="I215">
         <v>6312</v>
       </c>
       <c r="J215" s="1">
-        <v>0.23319999999999999</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7441,18 +7441,18 @@
         <v>40</v>
       </c>
       <c r="H216">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I216">
         <v>480</v>
       </c>
       <c r="J216" s="1">
-        <v>0.21249999999999999</v>
+        <v>0.23960000000000001</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7473,18 +7473,18 @@
         <v>408</v>
       </c>
       <c r="H217">
-        <v>1109</v>
+        <v>1219</v>
       </c>
       <c r="I217">
         <v>4896</v>
       </c>
       <c r="J217" s="1">
-        <v>0.22650000000000001</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7505,18 +7505,18 @@
         <v>550</v>
       </c>
       <c r="H218">
-        <v>1526</v>
+        <v>1589</v>
       </c>
       <c r="I218">
         <v>6600</v>
       </c>
       <c r="J218" s="1">
-        <v>0.23119999999999999</v>
+        <v>0.24079999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7537,18 +7537,18 @@
         <v>76</v>
       </c>
       <c r="H219">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="I219">
         <v>912</v>
       </c>
       <c r="J219" s="1">
-        <v>0.21049999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7569,18 +7569,18 @@
         <v>6</v>
       </c>
       <c r="H220">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I220">
         <v>144</v>
       </c>
       <c r="J220" s="1">
-        <v>0.2361</v>
+        <v>0.24310000000000001</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7601,18 +7601,18 @@
         <v>19</v>
       </c>
       <c r="H221">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I221">
         <v>228</v>
       </c>
       <c r="J221" s="1">
-        <v>0.21490000000000001</v>
+        <v>0.23250000000000001</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7644,7 +7644,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7697,18 +7697,18 @@
         <v>31</v>
       </c>
       <c r="H224">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I224">
         <v>372</v>
       </c>
       <c r="J224" s="1">
-        <v>0.2016</v>
+        <v>0.2419</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7729,18 +7729,18 @@
         <v>175</v>
       </c>
       <c r="H225">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I225">
         <v>2100</v>
       </c>
       <c r="J225" s="1">
-        <v>0.23519999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7761,18 +7761,18 @@
         <v>9</v>
       </c>
       <c r="H226">
-        <v>1209</v>
+        <v>1313</v>
       </c>
       <c r="I226">
         <v>3285</v>
       </c>
       <c r="J226" s="1">
-        <v>0.36799999999999999</v>
+        <v>0.3997</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7857,18 +7857,18 @@
         <v>34</v>
       </c>
       <c r="H229">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I229">
         <v>132</v>
       </c>
       <c r="J229" s="1">
-        <v>0.40910000000000002</v>
+        <v>0.42420000000000002</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7900,7 +7900,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7932,7 +7932,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7953,18 +7953,18 @@
         <v>3654</v>
       </c>
       <c r="H232">
-        <v>8749</v>
+        <v>9391</v>
       </c>
       <c r="I232">
         <v>43848</v>
       </c>
       <c r="J232" s="1">
-        <v>0.19950000000000001</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8005,7 +8005,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8118,7 +8118,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8139,18 +8139,18 @@
         <v>486</v>
       </c>
       <c r="H240">
-        <v>2809</v>
+        <v>2917</v>
       </c>
       <c r="I240">
         <v>11664</v>
       </c>
       <c r="J240" s="1">
-        <v>0.24079999999999999</v>
+        <v>0.25009999999999999</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8203,18 +8203,18 @@
         <v>68</v>
       </c>
       <c r="H242">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="I242">
         <v>816</v>
       </c>
       <c r="J242" s="1">
-        <v>0.2243</v>
+        <v>0.24879999999999999</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8235,18 +8235,18 @@
         <v>729</v>
       </c>
       <c r="H243">
-        <v>2045</v>
+        <v>2186</v>
       </c>
       <c r="I243">
         <v>8772</v>
       </c>
       <c r="J243" s="1">
-        <v>0.2331</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8267,18 +8267,18 @@
         <v>854</v>
       </c>
       <c r="H244">
-        <v>2561</v>
+        <v>2740</v>
       </c>
       <c r="I244">
         <v>11040</v>
       </c>
       <c r="J244" s="1">
-        <v>0.23200000000000001</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8299,18 +8299,18 @@
         <v>121</v>
       </c>
       <c r="H245">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="I245">
         <v>1452</v>
       </c>
       <c r="J245" s="1">
-        <v>0.21759999999999999</v>
+        <v>0.2452</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8331,18 +8331,18 @@
         <v>27</v>
       </c>
       <c r="H246">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I246">
         <v>648</v>
       </c>
       <c r="J246" s="1">
-        <v>0.24690000000000001</v>
+        <v>0.26079999999999998</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8395,7 +8395,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8416,18 +8416,18 @@
         <v>30</v>
       </c>
       <c r="H249">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I249">
         <v>360</v>
       </c>
       <c r="J249" s="1">
-        <v>0.2361</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8448,18 +8448,18 @@
         <v>51</v>
       </c>
       <c r="H250">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I250">
         <v>624</v>
       </c>
       <c r="J250" s="1">
-        <v>0.23400000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8480,18 +8480,18 @@
         <v>337</v>
       </c>
       <c r="H251">
-        <v>969</v>
+        <v>1008</v>
       </c>
       <c r="I251">
         <v>4044</v>
       </c>
       <c r="J251" s="1">
-        <v>0.23960000000000001</v>
+        <v>0.24929999999999999</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8512,18 +8512,18 @@
         <v>50</v>
       </c>
       <c r="H252">
-        <v>4828</v>
+        <v>5240</v>
       </c>
       <c r="I252">
         <v>18972</v>
       </c>
       <c r="J252" s="1">
-        <v>0.2545</v>
+        <v>0.2762</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8544,18 +8544,18 @@
         <v>58</v>
       </c>
       <c r="H253">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I253">
         <v>232</v>
       </c>
       <c r="J253" s="1">
-        <v>0.2069</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8587,7 +8587,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8608,18 +8608,18 @@
         <v>56</v>
       </c>
       <c r="H255">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I255">
         <v>228</v>
       </c>
       <c r="J255" s="1">
-        <v>0.1842</v>
+        <v>0.22370000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8651,7 +8651,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8672,18 +8672,18 @@
         <v>4610</v>
       </c>
       <c r="H257">
-        <v>12442</v>
+        <v>14246</v>
       </c>
       <c r="I257">
         <v>55320</v>
       </c>
       <c r="J257" s="1">
-        <v>0.22489999999999999</v>
+        <v>0.25750000000000001</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8704,18 +8704,18 @@
         <v>44</v>
       </c>
       <c r="H258">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="I258">
         <v>468</v>
       </c>
       <c r="J258" s="1">
-        <v>0.20300000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8736,18 +8736,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I259">
         <v>78</v>
       </c>
       <c r="J259" s="1">
-        <v>0.12820000000000001</v>
+        <v>0.17949999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8768,18 +8768,18 @@
         <v>90</v>
       </c>
       <c r="H260">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="I260">
         <v>1080</v>
       </c>
       <c r="J260" s="1">
-        <v>0.22040000000000001</v>
+        <v>0.24349999999999999</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8800,18 +8800,18 @@
         <v>27</v>
       </c>
       <c r="H261">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I261">
         <v>192</v>
       </c>
       <c r="J261" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.24479999999999999</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8832,18 +8832,18 @@
         <v>121</v>
       </c>
       <c r="H262">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="I262">
         <v>1428</v>
       </c>
       <c r="J262" s="1">
-        <v>0.2185</v>
+        <v>0.24790000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8875,7 +8875,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8896,18 +8896,18 @@
         <v>351</v>
       </c>
       <c r="H264">
-        <v>997</v>
+        <v>1063</v>
       </c>
       <c r="I264">
         <v>4291</v>
       </c>
       <c r="J264" s="1">
-        <v>0.23230000000000001</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8928,18 +8928,18 @@
         <v>35</v>
       </c>
       <c r="H265">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I265">
         <v>420</v>
       </c>
       <c r="J265" s="1">
-        <v>0.2286</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8960,18 +8960,18 @@
         <v>232</v>
       </c>
       <c r="H266">
-        <v>656</v>
+        <v>696</v>
       </c>
       <c r="I266">
         <v>2784</v>
       </c>
       <c r="J266" s="1">
-        <v>0.2356</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -8992,18 +8992,18 @@
         <v>66</v>
       </c>
       <c r="H267">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="I267">
         <v>792</v>
       </c>
       <c r="J267" s="1">
-        <v>0.2336</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9024,18 +9024,18 @@
         <v>84</v>
       </c>
       <c r="H268">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="I268">
         <v>1008</v>
       </c>
       <c r="J268" s="1">
-        <v>0.22720000000000001</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9056,7 +9056,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9077,18 +9077,18 @@
         <v>33</v>
       </c>
       <c r="H270">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I270">
         <v>384</v>
       </c>
       <c r="J270" s="1">
-        <v>0.22919999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9109,18 +9109,18 @@
         <v>3</v>
       </c>
       <c r="H271">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I271">
         <v>36</v>
       </c>
       <c r="J271" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9141,7 +9141,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9162,7 +9162,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9183,18 +9183,18 @@
         <v>51</v>
       </c>
       <c r="H274">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I274">
         <v>276</v>
       </c>
       <c r="J274" s="1">
-        <v>0.21010000000000001</v>
+        <v>0.24640000000000001</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9215,18 +9215,18 @@
         <v>445</v>
       </c>
       <c r="H275">
-        <v>1244</v>
+        <v>1334</v>
       </c>
       <c r="I275">
         <v>5340</v>
       </c>
       <c r="J275" s="1">
-        <v>0.23300000000000001</v>
+        <v>0.24979999999999999</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9247,18 +9247,18 @@
         <v>17</v>
       </c>
       <c r="H276">
-        <v>1186</v>
+        <v>1293</v>
       </c>
       <c r="I276">
         <v>5110</v>
       </c>
       <c r="J276" s="1">
-        <v>0.2321</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9290,7 +9290,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9311,18 +9311,18 @@
         <v>11</v>
       </c>
       <c r="H278">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I278">
         <v>11</v>
       </c>
       <c r="J278" s="1">
-        <v>0.63639999999999997</v>
+        <v>0.72729999999999995</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9375,18 +9375,18 @@
         <v>34</v>
       </c>
       <c r="H280">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I280">
         <v>34</v>
       </c>
       <c r="J280" s="1">
-        <v>0.29409999999999997</v>
+        <v>0.38240000000000002</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9407,18 +9407,18 @@
         <v>6</v>
       </c>
       <c r="H281">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I281">
         <v>12</v>
       </c>
       <c r="J281" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9471,18 +9471,18 @@
         <v>12</v>
       </c>
       <c r="H283">
-        <v>1236</v>
+        <v>1477</v>
       </c>
       <c r="I283">
         <v>5904</v>
       </c>
       <c r="J283" s="1">
-        <v>0.20930000000000001</v>
+        <v>0.25019999999999998</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9503,18 +9503,18 @@
         <v>33</v>
       </c>
       <c r="H284">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I284">
         <v>396</v>
       </c>
       <c r="J284" s="1">
-        <v>0.2298</v>
+        <v>0.2475</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9535,18 +9535,18 @@
         <v>23</v>
       </c>
       <c r="H285">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I285">
         <v>276</v>
       </c>
       <c r="J285" s="1">
-        <v>0.21010000000000001</v>
+        <v>0.24640000000000001</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9567,18 +9567,18 @@
         <v>79</v>
       </c>
       <c r="H286">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="I286">
         <v>948</v>
       </c>
       <c r="J286" s="1">
-        <v>0.22889999999999999</v>
+        <v>0.24790000000000001</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9620,18 +9620,18 @@
         <v>21</v>
       </c>
       <c r="H288">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I288">
         <v>264</v>
       </c>
       <c r="J288" s="1">
-        <v>0.2235</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9652,18 +9652,18 @@
         <v>22</v>
       </c>
       <c r="H289">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I289">
         <v>44</v>
       </c>
       <c r="J289" s="1">
-        <v>0.31819999999999998</v>
+        <v>0.34089999999999998</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9684,18 +9684,18 @@
         <v>82</v>
       </c>
       <c r="H290">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="I290">
         <v>1968</v>
       </c>
       <c r="J290" s="1">
-        <v>0.22</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9716,18 +9716,18 @@
         <v>173</v>
       </c>
       <c r="H291">
-        <v>792</v>
+        <v>948</v>
       </c>
       <c r="I291">
         <v>4128</v>
       </c>
       <c r="J291" s="1">
-        <v>0.19189999999999999</v>
+        <v>0.22969999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9748,18 +9748,18 @@
         <v>74</v>
       </c>
       <c r="H292">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="I292">
         <v>888</v>
       </c>
       <c r="J292" s="1">
-        <v>0.22070000000000001</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9780,18 +9780,18 @@
         <v>110</v>
       </c>
       <c r="H293">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="I293">
         <v>1320</v>
       </c>
       <c r="J293" s="1">
-        <v>0.18410000000000001</v>
+        <v>0.22270000000000001</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9812,18 +9812,18 @@
         <v>160</v>
       </c>
       <c r="H294">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="I294">
         <v>1920</v>
       </c>
       <c r="J294" s="1">
-        <v>0.2177</v>
+        <v>0.23799999999999999</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9844,18 +9844,18 @@
         <v>311</v>
       </c>
       <c r="H295">
-        <v>741</v>
+        <v>864</v>
       </c>
       <c r="I295">
         <v>3732</v>
       </c>
       <c r="J295" s="1">
-        <v>0.1986</v>
+        <v>0.23150000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9876,18 +9876,18 @@
         <v>286</v>
       </c>
       <c r="H296">
-        <v>615</v>
+        <v>757</v>
       </c>
       <c r="I296">
         <v>3432</v>
       </c>
       <c r="J296" s="1">
-        <v>0.1792</v>
+        <v>0.22059999999999999</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9940,18 +9940,18 @@
         <v>85</v>
       </c>
       <c r="H298">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="I298">
         <v>1020</v>
       </c>
       <c r="J298" s="1">
-        <v>0.19020000000000001</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10004,18 +10004,18 @@
         <v>47</v>
       </c>
       <c r="H300">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I300">
         <v>564</v>
       </c>
       <c r="J300" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10036,18 +10036,18 @@
         <v>91</v>
       </c>
       <c r="H301">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="I301">
         <v>1092</v>
       </c>
       <c r="J301" s="1">
-        <v>0.18679999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10068,18 +10068,18 @@
         <v>13</v>
       </c>
       <c r="H302">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I302">
         <v>384</v>
       </c>
       <c r="J302" s="1">
-        <v>0.224</v>
+        <v>0.23960000000000001</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10100,7 +10100,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10121,7 +10121,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10153,7 +10153,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10174,18 +10174,18 @@
         <v>48</v>
       </c>
       <c r="H306">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="I306">
         <v>564</v>
       </c>
       <c r="J306" s="1">
-        <v>0.21629999999999999</v>
+        <v>0.24110000000000001</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10206,18 +10206,18 @@
         <v>227</v>
       </c>
       <c r="H307">
-        <v>549</v>
+        <v>638</v>
       </c>
       <c r="I307">
         <v>2724</v>
       </c>
       <c r="J307" s="1">
-        <v>0.20150000000000001</v>
+        <v>0.23419999999999999</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10238,18 +10238,18 @@
         <v>16</v>
       </c>
       <c r="H308">
-        <v>1073</v>
+        <v>1156</v>
       </c>
       <c r="I308">
         <v>5842</v>
       </c>
       <c r="J308" s="1">
-        <v>0.1837</v>
+        <v>0.19789999999999999</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10270,18 +10270,18 @@
         <v>39</v>
       </c>
       <c r="H309">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I309">
         <v>156</v>
       </c>
       <c r="J309" s="1">
-        <v>0.1603</v>
+        <v>0.30769999999999997</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10334,18 +10334,18 @@
         <v>44</v>
       </c>
       <c r="H311">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I311">
         <v>180</v>
       </c>
       <c r="J311" s="1">
-        <v>0.25</v>
+        <v>0.26669999999999999</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10409,7 +10409,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10462,18 +10462,18 @@
         <v>87</v>
       </c>
       <c r="H315">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="I315">
         <v>1044</v>
       </c>
       <c r="J315" s="1">
-        <v>0.20880000000000001</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10494,18 +10494,18 @@
         <v>228</v>
       </c>
       <c r="H316">
-        <v>544</v>
+        <v>646</v>
       </c>
       <c r="I316">
         <v>2736</v>
       </c>
       <c r="J316" s="1">
-        <v>0.1988</v>
+        <v>0.2361</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10526,18 +10526,18 @@
         <v>22</v>
       </c>
       <c r="H317">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I317">
         <v>300</v>
       </c>
       <c r="J317" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.22670000000000001</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10558,18 +10558,18 @@
         <v>184</v>
       </c>
       <c r="H318">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="I318">
         <v>2196</v>
       </c>
       <c r="J318" s="1">
-        <v>0.18990000000000001</v>
+        <v>0.20219999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10601,7 +10601,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10660,7 +10660,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10681,18 +10681,18 @@
         <v>96</v>
       </c>
       <c r="H323">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="I323">
         <v>2304</v>
       </c>
       <c r="J323" s="1">
-        <v>0.23960000000000001</v>
+        <v>0.24779999999999999</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10713,18 +10713,18 @@
         <v>17</v>
       </c>
       <c r="H324">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I324">
         <v>204</v>
       </c>
       <c r="J324" s="1">
-        <v>0.24510000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10745,18 +10745,18 @@
         <v>109</v>
       </c>
       <c r="H325">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="I325">
         <v>1308</v>
       </c>
       <c r="J325" s="1">
-        <v>0.23169999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10777,18 +10777,18 @@
         <v>8</v>
       </c>
       <c r="H326">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I326">
         <v>96</v>
       </c>
       <c r="J326" s="1">
-        <v>0.23960000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10809,18 +10809,18 @@
         <v>34</v>
       </c>
       <c r="H327">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="I327">
         <v>408</v>
       </c>
       <c r="J327" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.24260000000000001</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10841,18 +10841,18 @@
         <v>5</v>
       </c>
       <c r="H328">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I328">
         <v>120</v>
       </c>
       <c r="J328" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10873,18 +10873,18 @@
         <v>17</v>
       </c>
       <c r="H329">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I329">
         <v>204</v>
       </c>
       <c r="J329" s="1">
-        <v>0.24510000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10905,18 +10905,18 @@
         <v>7</v>
       </c>
       <c r="H330">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I330">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="J330" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10937,18 +10937,18 @@
         <v>200</v>
       </c>
       <c r="H331">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="I331">
         <v>2400</v>
       </c>
       <c r="J331" s="1">
-        <v>0.2417</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -10969,18 +10969,18 @@
         <v>14</v>
       </c>
       <c r="H332">
-        <v>1134</v>
+        <v>1232</v>
       </c>
       <c r="I332">
         <v>5110</v>
       </c>
       <c r="J332" s="1">
-        <v>0.22189999999999999</v>
+        <v>0.24110000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11012,7 +11012,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11044,7 +11044,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11076,7 +11076,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11108,7 +11108,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11193,7 +11193,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11213,7 +11213,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11234,7 +11234,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11255,18 +11255,18 @@
         <v>392</v>
       </c>
       <c r="H342">
-        <v>2272</v>
+        <v>2348</v>
       </c>
       <c r="I342">
         <v>9408</v>
       </c>
       <c r="J342" s="1">
-        <v>0.24149999999999999</v>
+        <v>0.24959999999999999</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11287,18 +11287,18 @@
         <v>39</v>
       </c>
       <c r="H343">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I343">
         <v>468</v>
       </c>
       <c r="J343" s="1">
-        <v>0.23499999999999999</v>
+        <v>0.24790000000000001</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11319,18 +11319,18 @@
         <v>778</v>
       </c>
       <c r="H344">
-        <v>2134</v>
+        <v>2321</v>
       </c>
       <c r="I344">
         <v>9336</v>
       </c>
       <c r="J344" s="1">
-        <v>0.2286</v>
+        <v>0.24859999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11351,18 +11351,18 @@
         <v>16</v>
       </c>
       <c r="H345">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I345">
         <v>192</v>
       </c>
       <c r="J345" s="1">
-        <v>0.2344</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11383,18 +11383,18 @@
         <v>26</v>
       </c>
       <c r="H346">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I346">
         <v>312</v>
       </c>
       <c r="J346" s="1">
-        <v>0.22120000000000001</v>
+        <v>0.24679999999999999</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11415,18 +11415,18 @@
         <v>24</v>
       </c>
       <c r="H347">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I347">
         <v>576</v>
       </c>
       <c r="J347" s="1">
-        <v>0.22570000000000001</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11458,7 +11458,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11479,18 +11479,18 @@
         <v>9</v>
       </c>
       <c r="H349">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I349">
         <v>108</v>
       </c>
       <c r="J349" s="1">
-        <v>0.20369999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11511,18 +11511,18 @@
         <v>925</v>
       </c>
       <c r="H350">
-        <v>2488</v>
+        <v>2726</v>
       </c>
       <c r="I350">
         <v>11100</v>
       </c>
       <c r="J350" s="1">
-        <v>0.22409999999999999</v>
+        <v>0.24560000000000001</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11543,18 +11543,18 @@
         <v>45</v>
       </c>
       <c r="H351">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I351">
         <v>540</v>
       </c>
       <c r="J351" s="1">
-        <v>0.22409999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11575,18 +11575,18 @@
         <v>26</v>
       </c>
       <c r="H352">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="I352">
         <v>420</v>
       </c>
       <c r="J352" s="1">
-        <v>0.20949999999999999</v>
+        <v>0.2429</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11607,18 +11607,18 @@
         <v>145</v>
       </c>
       <c r="H353">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="I353">
         <v>1740</v>
       </c>
       <c r="J353" s="1">
-        <v>0.24249999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11639,18 +11639,18 @@
         <v>105</v>
       </c>
       <c r="H354">
-        <v>7540</v>
+        <v>8353</v>
       </c>
       <c r="I354">
         <v>38325</v>
       </c>
       <c r="J354" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11671,18 +11671,18 @@
         <v>65</v>
       </c>
       <c r="H355">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I355">
         <v>260</v>
       </c>
       <c r="J355" s="1">
-        <v>0.2462</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11703,18 +11703,18 @@
         <v>65</v>
       </c>
       <c r="H356">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I356">
         <v>65</v>
       </c>
       <c r="J356" s="1">
-        <v>0.98460000000000003</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11735,18 +11735,18 @@
         <v>33</v>
       </c>
       <c r="H357">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I357">
         <v>132</v>
       </c>
       <c r="J357" s="1">
-        <v>0.2424</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11778,7 +11778,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11810,7 +11810,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11831,18 +11831,18 @@
         <v>10</v>
       </c>
       <c r="H360">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I360">
         <v>20</v>
       </c>
       <c r="J360" s="1">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11863,18 +11863,18 @@
         <v>3536</v>
       </c>
       <c r="H361">
-        <v>9688</v>
+        <v>10458</v>
       </c>
       <c r="I361">
         <v>42432</v>
       </c>
       <c r="J361" s="1">
-        <v>0.2283</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11895,18 +11895,18 @@
         <v>33</v>
       </c>
       <c r="H362">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I362">
         <v>396</v>
       </c>
       <c r="J362" s="1">
-        <v>0.23230000000000001</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11927,18 +11927,18 @@
         <v>11</v>
       </c>
       <c r="H363">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I363">
         <v>132</v>
       </c>
       <c r="J363" s="1">
-        <v>0.19700000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11959,18 +11959,18 @@
         <v>24</v>
       </c>
       <c r="H364">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I364">
         <v>288</v>
       </c>
       <c r="J364" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12002,7 +12002,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12023,18 +12023,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12070,18 +12070,18 @@
         <v>278</v>
       </c>
       <c r="H368">
-        <v>1535</v>
+        <v>1654</v>
       </c>
       <c r="I368">
         <v>6672</v>
       </c>
       <c r="J368" s="1">
-        <v>0.2301</v>
+        <v>0.24790000000000001</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12102,18 +12102,18 @@
         <v>129</v>
       </c>
       <c r="H369">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="I369">
         <v>1548</v>
       </c>
       <c r="J369" s="1">
-        <v>0.22739999999999999</v>
+        <v>0.2429</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12134,18 +12134,18 @@
         <v>553</v>
       </c>
       <c r="H370">
-        <v>1466</v>
+        <v>1631</v>
       </c>
       <c r="I370">
         <v>6636</v>
       </c>
       <c r="J370" s="1">
-        <v>0.22090000000000001</v>
+        <v>0.24579999999999999</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12166,18 +12166,18 @@
         <v>315</v>
       </c>
       <c r="H371">
-        <v>867</v>
+        <v>940</v>
       </c>
       <c r="I371">
         <v>3780</v>
       </c>
       <c r="J371" s="1">
-        <v>0.22939999999999999</v>
+        <v>0.2487</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12198,18 +12198,18 @@
         <v>20</v>
       </c>
       <c r="H372">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I372">
         <v>240</v>
       </c>
       <c r="J372" s="1">
-        <v>0.2208</v>
+        <v>0.23330000000000001</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12230,18 +12230,18 @@
         <v>19</v>
       </c>
       <c r="H373">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I373">
         <v>228</v>
       </c>
       <c r="J373" s="1">
-        <v>0.23250000000000001</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12262,18 +12262,18 @@
         <v>19</v>
       </c>
       <c r="H374">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I374">
         <v>456</v>
       </c>
       <c r="J374" s="1">
-        <v>0.22370000000000001</v>
+        <v>0.23250000000000001</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12294,18 +12294,18 @@
         <v>86</v>
       </c>
       <c r="H375">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="I375">
         <v>1032</v>
       </c>
       <c r="J375" s="1">
-        <v>0.22770000000000001</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12347,18 +12347,18 @@
         <v>2</v>
       </c>
       <c r="H377">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I377">
         <v>24</v>
       </c>
       <c r="J377" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12379,18 +12379,18 @@
         <v>32</v>
       </c>
       <c r="H378">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I378">
         <v>384</v>
       </c>
       <c r="J378" s="1">
-        <v>0.1953</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12411,18 +12411,18 @@
         <v>615</v>
       </c>
       <c r="H379">
-        <v>1679</v>
+        <v>1797</v>
       </c>
       <c r="I379">
         <v>7380</v>
       </c>
       <c r="J379" s="1">
-        <v>0.22750000000000001</v>
+        <v>0.24349999999999999</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12443,18 +12443,18 @@
         <v>172</v>
       </c>
       <c r="H380">
-        <v>3909</v>
+        <v>4381</v>
       </c>
       <c r="I380">
         <v>17695</v>
       </c>
       <c r="J380" s="1">
-        <v>0.22090000000000001</v>
+        <v>0.24759999999999999</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12475,18 +12475,18 @@
         <v>175</v>
       </c>
       <c r="H381">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I381">
         <v>700</v>
       </c>
       <c r="J381" s="1">
-        <v>0.22140000000000001</v>
+        <v>0.23569999999999999</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12507,18 +12507,18 @@
         <v>175</v>
       </c>
       <c r="H382">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I382">
         <v>175</v>
       </c>
       <c r="J382" s="1">
-        <v>0.88570000000000004</v>
+        <v>0.94289999999999996</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12550,7 +12550,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12603,7 +12603,7 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12635,7 +12635,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12656,18 +12656,18 @@
         <v>50</v>
       </c>
       <c r="H387">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I387">
         <v>600</v>
       </c>
       <c r="J387" s="1">
-        <v>0.22</v>
+        <v>0.23669999999999999</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12688,18 +12688,18 @@
         <v>48</v>
       </c>
       <c r="H388">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I388">
         <v>576</v>
       </c>
       <c r="J388" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.23960000000000001</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12720,18 +12720,18 @@
         <v>17</v>
       </c>
       <c r="H389">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I389">
         <v>204</v>
       </c>
       <c r="J389" s="1">
-        <v>0.20100000000000001</v>
+        <v>0.22550000000000001</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12752,18 +12752,18 @@
         <v>25</v>
       </c>
       <c r="H390">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I390">
         <v>300</v>
       </c>
       <c r="J390" s="1">
-        <v>0.21</v>
+        <v>0.2233</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12784,18 +12784,18 @@
         <v>62</v>
       </c>
       <c r="H391">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I391">
         <v>744</v>
       </c>
       <c r="J391" s="1">
-        <v>0.22850000000000001</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530F489F-7CD4-4771-AA8B-AD5B6C12184C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113C4718-5338-41FB-9940-0470BBE29917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -784,7 +784,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -802,18 +802,18 @@
         <v>28</v>
       </c>
       <c r="H2">
-        <v>5146</v>
+        <v>5155</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.25</v>
+        <v>0.2505</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -831,18 +831,18 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.2467</v>
+        <v>0.25169999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -860,18 +860,18 @@
         <v>30</v>
       </c>
       <c r="H4">
-        <v>4798</v>
+        <v>4869</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.24709999999999999</v>
+        <v>0.25080000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -889,18 +889,18 @@
         <v>30</v>
       </c>
       <c r="H5">
-        <v>6779</v>
+        <v>6855</v>
       </c>
       <c r="I5">
         <v>27456</v>
       </c>
       <c r="J5" s="1">
-        <v>0.24690000000000001</v>
+        <v>0.24970000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -918,18 +918,18 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1005,18 +1005,18 @@
         <v>30</v>
       </c>
       <c r="H9">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.24529999999999999</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1034,18 +1034,18 @@
         <v>30</v>
       </c>
       <c r="H10">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.24690000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1063,18 +1063,18 @@
         <v>30</v>
       </c>
       <c r="H11">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.25040000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1121,18 +1121,18 @@
         <v>41</v>
       </c>
       <c r="H13">
-        <v>7125</v>
+        <v>7309</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.2787</v>
+        <v>0.28589999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1150,18 +1150,18 @@
         <v>42</v>
       </c>
       <c r="H14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.2412</v>
+        <v>0.25440000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1208,18 +1208,18 @@
         <v>42</v>
       </c>
       <c r="H16">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.2208</v>
+        <v>0.2281</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1266,18 +1266,18 @@
         <v>46</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I18">
         <v>90</v>
       </c>
       <c r="J18" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.18890000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1295,18 +1295,18 @@
         <v>30</v>
       </c>
       <c r="H19">
-        <v>32458</v>
+        <v>32954</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.27660000000000001</v>
+        <v>0.28079999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1324,18 +1324,18 @@
         <v>30</v>
       </c>
       <c r="H20">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.24940000000000001</v>
+        <v>0.25190000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1353,18 +1353,18 @@
         <v>30</v>
       </c>
       <c r="H21">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.24610000000000001</v>
+        <v>0.25190000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1382,18 +1382,18 @@
         <v>30</v>
       </c>
       <c r="H22">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.24510000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1472,18 +1472,18 @@
         <v>43</v>
       </c>
       <c r="H26">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I26">
         <v>137</v>
       </c>
       <c r="J26" s="1">
-        <v>0.29930000000000001</v>
+        <v>0.32119999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1504,18 +1504,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.24859999999999999</v>
+        <v>0.24929999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1568,18 +1568,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.2472</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1600,18 +1600,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.2429</v>
+        <v>0.2487</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1664,18 +1664,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.33589999999999998</v>
+        <v>0.36720000000000003</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1760,18 +1760,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>0.1288</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1792,18 +1792,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>0.1585</v>
+        <v>0.1736</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1824,18 +1824,18 @@
         <v>72</v>
       </c>
       <c r="H37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I37">
         <v>72</v>
       </c>
       <c r="J37" s="1">
-        <v>0.15279999999999999</v>
+        <v>0.18060000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1920,18 +1920,18 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40">
         <v>60</v>
       </c>
       <c r="J40" s="1">
-        <v>0.26669999999999999</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -1952,18 +1952,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.39750000000000002</v>
+        <v>0.41270000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -1984,18 +1984,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.24</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2016,18 +2016,18 @@
         <v>244</v>
       </c>
       <c r="H43">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I43">
         <v>244</v>
       </c>
       <c r="J43" s="1">
-        <v>0.2828</v>
+        <v>0.30330000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2048,18 +2048,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.24279999999999999</v>
+        <v>0.24640000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2080,18 +2080,18 @@
         <v>61</v>
       </c>
       <c r="H45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I45">
         <v>61</v>
       </c>
       <c r="J45" s="1">
-        <v>0.13109999999999999</v>
+        <v>0.16389999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2144,18 +2144,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>2054630</v>
+        <v>2069563</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.2477</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2176,18 +2176,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>323916</v>
+        <v>329748</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.23499999999999999</v>
+        <v>0.23930000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2208,18 +2208,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>3804</v>
+        <v>3828</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.245</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2240,18 +2240,18 @@
         <v>691098</v>
       </c>
       <c r="H50">
-        <v>666836</v>
+        <v>684554</v>
       </c>
       <c r="I50">
         <v>2764392</v>
       </c>
       <c r="J50" s="1">
-        <v>0.2412</v>
+        <v>0.24759999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2272,18 +2272,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>252369</v>
+        <v>258483</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.36509999999999998</v>
+        <v>0.37390000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2304,18 +2304,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.23480000000000001</v>
+        <v>0.24060000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2336,18 +2336,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.35730000000000001</v>
+        <v>0.36130000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2368,18 +2368,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.21060000000000001</v>
+        <v>0.21820000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2400,18 +2400,18 @@
         <v>649</v>
       </c>
       <c r="H55">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I55">
         <v>649</v>
       </c>
       <c r="J55" s="1">
-        <v>0.2404</v>
+        <v>0.24809999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2496,18 +2496,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.24440000000000001</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2528,18 +2528,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.2447</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2560,18 +2560,18 @@
         <v>691280</v>
       </c>
       <c r="H60">
-        <v>2062506</v>
+        <v>2074158</v>
       </c>
       <c r="I60">
         <v>8295360</v>
       </c>
       <c r="J60" s="1">
-        <v>0.24859999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2592,18 +2592,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>2190</v>
+        <v>2196</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.24929999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2656,18 +2656,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1917</v>
+        <v>1936</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.24959999999999999</v>
+        <v>0.25209999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2688,18 +2688,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.2492</v>
+        <v>0.24979999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2720,18 +2720,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I65">
         <v>1092</v>
       </c>
       <c r="J65" s="1">
-        <v>0.24629999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2880,18 +2880,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.2482</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2944,18 +2944,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>1232</v>
+        <v>1260</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.24660000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -2976,18 +2976,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.2167</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3232,18 +3232,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I81">
         <v>948</v>
       </c>
       <c r="J81" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.25109999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3264,18 +3264,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I82">
         <v>1632</v>
       </c>
       <c r="J82" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.24629999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3381,18 +3381,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1742</v>
+        <v>1758</v>
       </c>
       <c r="I86">
         <v>7032</v>
       </c>
       <c r="J86" s="1">
-        <v>0.2477</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3413,18 +3413,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.2455</v>
+        <v>0.25679999999999997</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3445,18 +3445,18 @@
         <v>493</v>
       </c>
       <c r="H88">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="I88">
         <v>5916</v>
       </c>
       <c r="J88" s="1">
-        <v>0.2485</v>
+        <v>0.25440000000000002</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3477,18 +3477,18 @@
         <v>2</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I89">
         <v>24</v>
       </c>
       <c r="J89" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3509,18 +3509,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>2225</v>
+        <v>2248</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>0.24759999999999999</v>
+        <v>0.25009999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3541,18 +3541,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I91">
         <v>1932</v>
       </c>
       <c r="J91" s="1">
-        <v>0.24740000000000001</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3570,21 +3570,21 @@
         <v>28</v>
       </c>
       <c r="G92">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H92">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I92">
         <v>1128</v>
       </c>
       <c r="J92" s="1">
-        <v>0.2482</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3605,18 +3605,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.253</v>
+        <v>0.26669999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3658,18 +3658,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.24260000000000001</v>
+        <v>0.25190000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3722,7 +3722,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3807,18 +3807,18 @@
         <v>33</v>
       </c>
       <c r="H100">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I100">
         <v>132</v>
       </c>
       <c r="J100" s="1">
-        <v>0.2273</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3835,11 +3835,22 @@
       <c r="F101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J101" s="1"/>
+      <c r="G101">
+        <v>33</v>
+      </c>
+      <c r="H101">
+        <v>8</v>
+      </c>
+      <c r="I101">
+        <v>33</v>
+      </c>
+      <c r="J101" s="1">
+        <v>0.2424</v>
+      </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3860,18 +3871,18 @@
         <v>8</v>
       </c>
       <c r="H102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I102">
         <v>18</v>
       </c>
       <c r="J102" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.27779999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3889,7 +3900,7 @@
         <v>46</v>
       </c>
       <c r="G103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3903,7 +3914,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3924,18 +3935,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.2472</v>
+        <v>0.25829999999999997</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -3956,18 +3967,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.26390000000000002</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -3988,18 +3999,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I106">
         <v>552</v>
       </c>
       <c r="J106" s="1">
-        <v>0.2409</v>
+        <v>0.25359999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4020,7 +4031,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4038,21 +4049,21 @@
         <v>30</v>
       </c>
       <c r="G108">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H108">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="I108">
         <v>611</v>
       </c>
       <c r="J108" s="1">
-        <v>0.23569999999999999</v>
+        <v>0.2586</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4073,7 +4084,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4105,7 +4116,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4137,7 +4148,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4169,7 +4180,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4201,7 +4212,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4233,7 +4244,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4265,7 +4276,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4297,7 +4308,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4329,7 +4340,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4361,7 +4372,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4393,7 +4404,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4425,7 +4436,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4457,7 +4468,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4489,7 +4500,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4521,7 +4532,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4553,7 +4564,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4585,7 +4596,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4617,7 +4628,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4649,7 +4660,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4681,7 +4692,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4713,7 +4724,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4745,7 +4756,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4777,7 +4788,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4809,7 +4820,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4841,7 +4852,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4861,7 +4872,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4882,7 +4893,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4903,7 +4914,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4924,18 +4935,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.24590000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -4967,7 +4978,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -4999,7 +5010,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5020,18 +5031,18 @@
         <v>1</v>
       </c>
       <c r="H140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I140">
         <v>12</v>
       </c>
       <c r="J140" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5052,18 +5063,18 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I141">
         <v>12</v>
       </c>
       <c r="J141" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5095,7 +5106,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5127,7 +5138,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5159,7 +5170,7 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5180,18 +5191,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.252</v>
+        <v>0.25259999999999999</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5223,7 +5234,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5244,18 +5255,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.23749999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5276,18 +5287,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.2452</v>
+        <v>0.24840000000000001</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5319,7 +5330,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5351,7 +5362,7 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5383,7 +5394,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5404,18 +5415,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>1390</v>
+        <v>1426</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.29289999999999999</v>
+        <v>0.30049999999999999</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5447,7 +5458,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5479,7 +5490,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5500,18 +5511,18 @@
         <v>45</v>
       </c>
       <c r="H155">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I155">
         <v>180</v>
       </c>
       <c r="J155" s="1">
-        <v>0.24440000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5543,7 +5554,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5575,7 +5586,7 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5607,7 +5618,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5628,18 +5639,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.24590000000000001</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5660,18 +5671,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>0.22919999999999999</v>
+        <v>0.24310000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5692,18 +5703,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.2359</v>
+        <v>0.25140000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5724,18 +5735,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.24690000000000001</v>
+        <v>0.25559999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5756,18 +5767,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>2299</v>
+        <v>2305</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.2475</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5788,18 +5799,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>0.25</v>
+        <v>0.25640000000000002</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5820,18 +5831,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1750</v>
+        <v>1763</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.2472</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5852,18 +5863,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>2900</v>
+        <v>2929</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.25069999999999998</v>
+        <v>0.25319999999999998</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5884,18 +5895,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.22739999999999999</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5927,7 +5938,7 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -5948,18 +5959,18 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I169">
         <v>84</v>
       </c>
       <c r="J169" s="1">
-        <v>0.23810000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -5991,7 +6002,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6012,18 +6023,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.22070000000000001</v>
+        <v>0.22919999999999999</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6044,18 +6055,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.2394</v>
+        <v>0.2429</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6076,18 +6087,18 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I173">
         <v>84</v>
       </c>
       <c r="J173" s="1">
-        <v>0.25</v>
+        <v>0.26190000000000002</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6108,18 +6119,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>2982</v>
+        <v>3062</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.27229999999999999</v>
+        <v>0.27960000000000002</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6140,18 +6151,18 @@
         <v>57</v>
       </c>
       <c r="H175">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I175">
         <v>228</v>
       </c>
       <c r="J175" s="1">
-        <v>0.1535</v>
+        <v>0.17979999999999999</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6183,7 +6194,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6204,18 +6215,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>0.2162</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6247,7 +6258,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6279,7 +6290,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6311,7 +6322,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6332,18 +6343,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.2397</v>
+        <v>0.2422</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6364,18 +6375,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.2361</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6407,7 +6418,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6439,7 +6450,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6460,18 +6471,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.2263</v>
+        <v>0.24529999999999999</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6492,7 +6503,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6524,7 +6535,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6556,7 +6567,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6588,7 +6599,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6620,7 +6631,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6652,7 +6663,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6684,7 +6695,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6716,7 +6727,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6748,7 +6759,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6780,7 +6791,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6812,7 +6823,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6844,7 +6855,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6876,7 +6887,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6908,7 +6919,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6940,7 +6951,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -6961,18 +6972,18 @@
         <v>45</v>
       </c>
       <c r="H201">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I201">
         <v>45</v>
       </c>
       <c r="J201" s="1">
-        <v>0.55559999999999998</v>
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7004,7 +7015,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7036,7 +7047,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7057,18 +7068,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>558947</v>
+        <v>566979</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.2465</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7089,18 +7100,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>66845</v>
+        <v>68414</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.18210000000000001</v>
+        <v>0.18640000000000001</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7132,7 +7143,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7164,7 +7175,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7196,7 +7207,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7228,7 +7239,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7260,7 +7271,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7281,18 +7292,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>0.18820000000000001</v>
+        <v>0.1956</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7324,7 +7335,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7356,7 +7367,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7388,7 +7399,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7420,7 +7431,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7441,18 +7452,18 @@
         <v>40</v>
       </c>
       <c r="H216">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I216">
         <v>480</v>
       </c>
       <c r="J216" s="1">
-        <v>0.23960000000000001</v>
+        <v>0.24579999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7484,7 +7495,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7505,18 +7516,18 @@
         <v>550</v>
       </c>
       <c r="H218">
-        <v>1589</v>
+        <v>1606</v>
       </c>
       <c r="I218">
         <v>6600</v>
       </c>
       <c r="J218" s="1">
-        <v>0.24079999999999999</v>
+        <v>0.24329999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7537,18 +7548,18 @@
         <v>76</v>
       </c>
       <c r="H219">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I219">
         <v>912</v>
       </c>
       <c r="J219" s="1">
-        <v>0.23899999999999999</v>
+        <v>0.24560000000000001</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7580,7 +7591,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7601,18 +7612,18 @@
         <v>19</v>
       </c>
       <c r="H221">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I221">
         <v>228</v>
       </c>
       <c r="J221" s="1">
-        <v>0.23250000000000001</v>
+        <v>0.24560000000000001</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7644,7 +7655,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7676,7 +7687,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7708,7 +7719,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7740,7 +7751,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7761,18 +7772,18 @@
         <v>9</v>
       </c>
       <c r="H226">
-        <v>1313</v>
+        <v>1350</v>
       </c>
       <c r="I226">
         <v>3285</v>
       </c>
       <c r="J226" s="1">
-        <v>0.3997</v>
+        <v>0.41099999999999998</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7804,7 +7815,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7836,7 +7847,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7868,7 +7879,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7900,7 +7911,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7932,7 +7943,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7953,18 +7964,18 @@
         <v>3654</v>
       </c>
       <c r="H232">
-        <v>9391</v>
+        <v>9547</v>
       </c>
       <c r="I232">
         <v>43848</v>
       </c>
       <c r="J232" s="1">
-        <v>0.2142</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -7985,7 +7996,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8005,7 +8016,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8025,7 +8036,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8045,7 +8056,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8065,7 +8076,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8086,7 +8097,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8118,7 +8129,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8139,18 +8150,18 @@
         <v>486</v>
       </c>
       <c r="H240">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="I240">
         <v>11664</v>
       </c>
       <c r="J240" s="1">
-        <v>0.25009999999999999</v>
+        <v>0.25040000000000001</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8171,18 +8182,18 @@
         <v>25</v>
       </c>
       <c r="H241">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I241">
         <v>300</v>
       </c>
       <c r="J241" s="1">
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8203,18 +8214,18 @@
         <v>68</v>
       </c>
       <c r="H242">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I242">
         <v>816</v>
       </c>
       <c r="J242" s="1">
-        <v>0.24879999999999999</v>
+        <v>0.25119999999999998</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8235,18 +8246,18 @@
         <v>729</v>
       </c>
       <c r="H243">
-        <v>2186</v>
+        <v>2197</v>
       </c>
       <c r="I243">
         <v>8772</v>
       </c>
       <c r="J243" s="1">
-        <v>0.2492</v>
+        <v>0.2505</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8267,18 +8278,18 @@
         <v>854</v>
       </c>
       <c r="H244">
-        <v>2740</v>
+        <v>2762</v>
       </c>
       <c r="I244">
         <v>11040</v>
       </c>
       <c r="J244" s="1">
-        <v>0.2482</v>
+        <v>0.25019999999999998</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8299,18 +8310,18 @@
         <v>121</v>
       </c>
       <c r="H245">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I245">
         <v>1452</v>
       </c>
       <c r="J245" s="1">
-        <v>0.2452</v>
+        <v>0.25069999999999998</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8342,7 +8353,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8363,7 +8374,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8395,7 +8406,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8427,7 +8438,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8448,18 +8459,18 @@
         <v>51</v>
       </c>
       <c r="H250">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I250">
         <v>624</v>
       </c>
       <c r="J250" s="1">
-        <v>0.25</v>
+        <v>0.25800000000000001</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8480,18 +8491,18 @@
         <v>337</v>
       </c>
       <c r="H251">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="I251">
         <v>4044</v>
       </c>
       <c r="J251" s="1">
-        <v>0.24929999999999999</v>
+        <v>0.25119999999999998</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8512,18 +8523,18 @@
         <v>50</v>
       </c>
       <c r="H252">
-        <v>5240</v>
+        <v>5362</v>
       </c>
       <c r="I252">
         <v>18972</v>
       </c>
       <c r="J252" s="1">
-        <v>0.2762</v>
+        <v>0.28260000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8555,7 +8566,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8587,7 +8598,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8608,18 +8619,18 @@
         <v>56</v>
       </c>
       <c r="H255">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I255">
         <v>228</v>
       </c>
       <c r="J255" s="1">
-        <v>0.22370000000000001</v>
+        <v>0.23680000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8651,7 +8662,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8672,18 +8683,18 @@
         <v>4610</v>
       </c>
       <c r="H257">
-        <v>14246</v>
+        <v>14378</v>
       </c>
       <c r="I257">
         <v>55320</v>
       </c>
       <c r="J257" s="1">
-        <v>0.25750000000000001</v>
+        <v>0.25990000000000002</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8715,7 +8726,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8736,18 +8747,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I259">
         <v>78</v>
       </c>
       <c r="J259" s="1">
-        <v>0.17949999999999999</v>
+        <v>0.1923</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8768,18 +8779,18 @@
         <v>90</v>
       </c>
       <c r="H260">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="I260">
         <v>1080</v>
       </c>
       <c r="J260" s="1">
-        <v>0.24349999999999999</v>
+        <v>0.25090000000000001</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8800,18 +8811,18 @@
         <v>27</v>
       </c>
       <c r="H261">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I261">
         <v>192</v>
       </c>
       <c r="J261" s="1">
-        <v>0.24479999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8832,18 +8843,18 @@
         <v>121</v>
       </c>
       <c r="H262">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="I262">
         <v>1428</v>
       </c>
       <c r="J262" s="1">
-        <v>0.24790000000000001</v>
+        <v>0.25140000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8875,7 +8886,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8896,18 +8907,18 @@
         <v>351</v>
       </c>
       <c r="H264">
-        <v>1063</v>
+        <v>1080</v>
       </c>
       <c r="I264">
         <v>4291</v>
       </c>
       <c r="J264" s="1">
-        <v>0.2477</v>
+        <v>0.25169999999999998</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8939,7 +8950,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8971,7 +8982,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9003,7 +9014,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9024,18 +9035,18 @@
         <v>84</v>
       </c>
       <c r="H268">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I268">
         <v>1008</v>
       </c>
       <c r="J268" s="1">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9056,7 +9067,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9088,7 +9099,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9120,7 +9131,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9141,7 +9152,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9162,7 +9173,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9183,18 +9194,18 @@
         <v>51</v>
       </c>
       <c r="H274">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I274">
         <v>276</v>
       </c>
       <c r="J274" s="1">
-        <v>0.24640000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9215,18 +9226,18 @@
         <v>445</v>
       </c>
       <c r="H275">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="I275">
         <v>5340</v>
       </c>
       <c r="J275" s="1">
-        <v>0.24979999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9247,18 +9258,18 @@
         <v>17</v>
       </c>
       <c r="H276">
-        <v>1293</v>
+        <v>1323</v>
       </c>
       <c r="I276">
         <v>5110</v>
       </c>
       <c r="J276" s="1">
-        <v>0.253</v>
+        <v>0.25890000000000002</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9290,7 +9301,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9322,7 +9333,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9354,7 +9365,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9375,18 +9386,18 @@
         <v>34</v>
       </c>
       <c r="H280">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I280">
         <v>34</v>
       </c>
       <c r="J280" s="1">
-        <v>0.38240000000000002</v>
+        <v>0.55879999999999996</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9407,18 +9418,18 @@
         <v>6</v>
       </c>
       <c r="H281">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I281">
         <v>12</v>
       </c>
       <c r="J281" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9450,7 +9461,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9471,18 +9482,18 @@
         <v>12</v>
       </c>
       <c r="H283">
-        <v>1477</v>
+        <v>1488</v>
       </c>
       <c r="I283">
         <v>5904</v>
       </c>
       <c r="J283" s="1">
-        <v>0.25019999999999998</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9503,18 +9514,18 @@
         <v>33</v>
       </c>
       <c r="H284">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I284">
         <v>396</v>
       </c>
       <c r="J284" s="1">
-        <v>0.2475</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9535,18 +9546,18 @@
         <v>23</v>
       </c>
       <c r="H285">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I285">
         <v>276</v>
       </c>
       <c r="J285" s="1">
-        <v>0.24640000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9567,18 +9578,18 @@
         <v>79</v>
       </c>
       <c r="H286">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I286">
         <v>948</v>
       </c>
       <c r="J286" s="1">
-        <v>0.24790000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9599,7 +9610,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9620,18 +9631,18 @@
         <v>21</v>
       </c>
       <c r="H288">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I288">
         <v>264</v>
       </c>
       <c r="J288" s="1">
-        <v>0.2424</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9652,18 +9663,18 @@
         <v>22</v>
       </c>
       <c r="H289">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I289">
         <v>44</v>
       </c>
       <c r="J289" s="1">
-        <v>0.34089999999999998</v>
+        <v>0.38640000000000002</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9684,18 +9695,18 @@
         <v>82</v>
       </c>
       <c r="H290">
-        <v>474</v>
+        <v>681</v>
       </c>
       <c r="I290">
         <v>1968</v>
       </c>
       <c r="J290" s="1">
-        <v>0.2409</v>
+        <v>0.34599999999999997</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9716,18 +9727,18 @@
         <v>173</v>
       </c>
       <c r="H291">
-        <v>948</v>
+        <v>1029</v>
       </c>
       <c r="I291">
         <v>4128</v>
       </c>
       <c r="J291" s="1">
-        <v>0.22969999999999999</v>
+        <v>0.24929999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9748,18 +9759,18 @@
         <v>74</v>
       </c>
       <c r="H292">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I292">
         <v>888</v>
       </c>
       <c r="J292" s="1">
-        <v>0.2432</v>
+        <v>0.24660000000000001</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9780,18 +9791,18 @@
         <v>110</v>
       </c>
       <c r="H293">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="I293">
         <v>1320</v>
       </c>
       <c r="J293" s="1">
-        <v>0.22270000000000001</v>
+        <v>0.2356</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9812,18 +9823,18 @@
         <v>160</v>
       </c>
       <c r="H294">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="I294">
         <v>1920</v>
       </c>
       <c r="J294" s="1">
-        <v>0.23799999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9844,18 +9855,18 @@
         <v>311</v>
       </c>
       <c r="H295">
-        <v>864</v>
+        <v>911</v>
       </c>
       <c r="I295">
         <v>3732</v>
       </c>
       <c r="J295" s="1">
-        <v>0.23150000000000001</v>
+        <v>0.24410000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9876,18 +9887,18 @@
         <v>286</v>
       </c>
       <c r="H296">
-        <v>757</v>
+        <v>826</v>
       </c>
       <c r="I296">
         <v>3432</v>
       </c>
       <c r="J296" s="1">
-        <v>0.22059999999999999</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9919,7 +9930,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9951,7 +9962,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -9983,7 +9994,7 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10015,7 +10026,7 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10036,18 +10047,18 @@
         <v>91</v>
       </c>
       <c r="H301">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="I301">
         <v>1092</v>
       </c>
       <c r="J301" s="1">
-        <v>0.20599999999999999</v>
+        <v>0.23719999999999999</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10068,18 +10079,18 @@
         <v>13</v>
       </c>
       <c r="H302">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I302">
         <v>384</v>
       </c>
       <c r="J302" s="1">
-        <v>0.23960000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10100,7 +10111,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10121,7 +10132,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10142,18 +10153,18 @@
         <v>17</v>
       </c>
       <c r="H305">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I305">
         <v>204</v>
       </c>
       <c r="J305" s="1">
-        <v>0.22550000000000001</v>
+        <v>0.23530000000000001</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10174,18 +10185,18 @@
         <v>48</v>
       </c>
       <c r="H306">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I306">
         <v>564</v>
       </c>
       <c r="J306" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10217,7 +10228,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10238,18 +10249,18 @@
         <v>16</v>
       </c>
       <c r="H308">
-        <v>1156</v>
+        <v>1352</v>
       </c>
       <c r="I308">
         <v>5842</v>
       </c>
       <c r="J308" s="1">
-        <v>0.19789999999999999</v>
+        <v>0.23139999999999999</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10281,7 +10292,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10302,18 +10313,18 @@
         <v>39</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I310">
         <v>39</v>
       </c>
       <c r="J310" s="1">
-        <v>0</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10345,7 +10356,7 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10366,18 +10377,18 @@
         <v>44</v>
       </c>
       <c r="H312">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I312">
         <v>45</v>
       </c>
       <c r="J312" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.4889</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10409,7 +10420,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10441,7 +10452,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10462,18 +10473,18 @@
         <v>87</v>
       </c>
       <c r="H315">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I315">
         <v>1044</v>
       </c>
       <c r="J315" s="1">
-        <v>0.2366</v>
+        <v>0.23849999999999999</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10494,18 +10505,18 @@
         <v>228</v>
       </c>
       <c r="H316">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="I316">
         <v>2736</v>
       </c>
       <c r="J316" s="1">
-        <v>0.2361</v>
+        <v>0.24049999999999999</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10526,18 +10537,18 @@
         <v>22</v>
       </c>
       <c r="H317">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I317">
         <v>300</v>
       </c>
       <c r="J317" s="1">
-        <v>0.22670000000000001</v>
+        <v>0.23669999999999999</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10558,18 +10569,18 @@
         <v>184</v>
       </c>
       <c r="H318">
-        <v>444</v>
+        <v>519</v>
       </c>
       <c r="I318">
         <v>2196</v>
       </c>
       <c r="J318" s="1">
-        <v>0.20219999999999999</v>
+        <v>0.23630000000000001</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10601,7 +10612,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10622,7 +10633,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10642,7 +10653,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10660,7 +10671,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10681,18 +10692,18 @@
         <v>96</v>
       </c>
       <c r="H323">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I323">
         <v>2304</v>
       </c>
       <c r="J323" s="1">
-        <v>0.24779999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10724,7 +10735,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10756,7 +10767,7 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10788,7 +10799,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10809,18 +10820,18 @@
         <v>34</v>
       </c>
       <c r="H327">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I327">
         <v>408</v>
       </c>
       <c r="J327" s="1">
-        <v>0.24260000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10852,7 +10863,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10884,7 +10895,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10916,7 +10927,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10948,7 +10959,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -10969,18 +10980,18 @@
         <v>14</v>
       </c>
       <c r="H332">
-        <v>1232</v>
+        <v>1260</v>
       </c>
       <c r="I332">
         <v>5110</v>
       </c>
       <c r="J332" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.24660000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11001,18 +11012,18 @@
         <v>19</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I333">
         <v>76</v>
       </c>
       <c r="J333" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11044,7 +11055,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11065,18 +11076,18 @@
         <v>5</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I335">
         <v>20</v>
       </c>
       <c r="J335" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11108,7 +11119,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11140,7 +11151,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11172,7 +11183,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11193,7 +11204,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11213,7 +11224,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11234,7 +11245,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11255,18 +11266,18 @@
         <v>392</v>
       </c>
       <c r="H342">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="I342">
         <v>9408</v>
       </c>
       <c r="J342" s="1">
-        <v>0.24959999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11287,18 +11298,18 @@
         <v>39</v>
       </c>
       <c r="H343">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I343">
         <v>468</v>
       </c>
       <c r="J343" s="1">
-        <v>0.24790000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11319,18 +11330,18 @@
         <v>778</v>
       </c>
       <c r="H344">
-        <v>2321</v>
+        <v>2334</v>
       </c>
       <c r="I344">
         <v>9336</v>
       </c>
       <c r="J344" s="1">
-        <v>0.24859999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11362,7 +11373,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11383,18 +11394,18 @@
         <v>26</v>
       </c>
       <c r="H346">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I346">
         <v>312</v>
       </c>
       <c r="J346" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11415,18 +11426,18 @@
         <v>24</v>
       </c>
       <c r="H347">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I347">
         <v>576</v>
       </c>
       <c r="J347" s="1">
-        <v>0.2465</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11447,18 +11458,18 @@
         <v>7</v>
       </c>
       <c r="H348">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I348">
         <v>84</v>
       </c>
       <c r="J348" s="1">
-        <v>0.23810000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11479,18 +11490,18 @@
         <v>9</v>
       </c>
       <c r="H349">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I349">
         <v>108</v>
       </c>
       <c r="J349" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11511,18 +11522,18 @@
         <v>925</v>
       </c>
       <c r="H350">
-        <v>2726</v>
+        <v>2775</v>
       </c>
       <c r="I350">
         <v>11100</v>
       </c>
       <c r="J350" s="1">
-        <v>0.24560000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11554,7 +11565,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11572,21 +11583,21 @@
         <v>30</v>
       </c>
       <c r="G352">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H352">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I352">
         <v>420</v>
       </c>
       <c r="J352" s="1">
-        <v>0.2429</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11618,7 +11629,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11639,18 +11650,18 @@
         <v>105</v>
       </c>
       <c r="H354">
-        <v>8353</v>
+        <v>8572</v>
       </c>
       <c r="I354">
         <v>38325</v>
       </c>
       <c r="J354" s="1">
-        <v>0.218</v>
+        <v>0.22370000000000001</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11682,7 +11693,7 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11714,7 +11725,7 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11746,7 +11757,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11778,7 +11789,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11810,7 +11821,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11842,7 +11853,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11863,18 +11874,18 @@
         <v>3536</v>
       </c>
       <c r="H361">
-        <v>10458</v>
+        <v>10608</v>
       </c>
       <c r="I361">
         <v>42432</v>
       </c>
       <c r="J361" s="1">
-        <v>0.2465</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11895,18 +11906,18 @@
         <v>33</v>
       </c>
       <c r="H362">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I362">
         <v>396</v>
       </c>
       <c r="J362" s="1">
-        <v>0.2424</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11938,7 +11949,7 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11959,18 +11970,18 @@
         <v>24</v>
       </c>
       <c r="H364">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I364">
         <v>288</v>
       </c>
       <c r="J364" s="1">
-        <v>0.2465</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12002,7 +12013,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12023,18 +12034,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12049,7 +12060,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12081,7 +12092,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12113,7 +12124,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12145,7 +12156,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12177,7 +12188,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12209,7 +12220,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12241,7 +12252,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12273,7 +12284,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12305,7 +12316,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12326,7 +12337,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12358,7 +12369,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12390,7 +12401,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12422,7 +12433,7 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12454,7 +12465,7 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12486,7 +12497,7 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12518,7 +12529,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12550,7 +12561,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12582,7 +12593,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12603,7 +12614,7 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12635,7 +12646,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12667,7 +12678,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12699,7 +12710,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12731,7 +12742,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12763,7 +12774,7 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12795,7 +12806,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DC2731-AF0C-4669-93BC-E401506CA317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE4C072-1DE0-4CEF-9903-CD711381BCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Divre I SU</t>
-  </si>
-  <si>
-    <t>Divre II SB</t>
   </si>
   <si>
     <t>Divre III Pg</t>
@@ -316,6 +313,9 @@
   </si>
   <si>
     <t>Perawatan Detail Peralatan HSCB 1 Tahunan</t>
+  </si>
+  <si>
+    <t>Divre II Pd</t>
   </si>
 </sst>
 </file>
@@ -733,13 +733,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G2">
         <v>59</v>
@@ -765,13 +765,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
         <v>47</v>
@@ -797,13 +797,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>59</v>
@@ -829,13 +829,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>398</v>
@@ -861,13 +861,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="G6">
         <v>398</v>
@@ -893,13 +893,13 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>64</v>
@@ -925,13 +925,13 @@
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8">
         <v>61</v>
@@ -957,13 +957,13 @@
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9">
         <v>59</v>
@@ -989,13 +989,13 @@
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10">
         <v>161</v>
@@ -1021,13 +1021,13 @@
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11">
         <v>265</v>
@@ -1053,13 +1053,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12">
         <v>72</v>
@@ -1085,13 +1085,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13">
         <v>289</v>
@@ -1117,13 +1117,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1149,13 +1149,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -1181,13 +1181,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16">
         <v>395</v>
@@ -1213,13 +1213,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18">
         <v>245</v>
@@ -1277,13 +1277,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19">
         <v>69</v>
@@ -1309,13 +1309,13 @@
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20">
         <v>61</v>
@@ -1341,13 +1341,13 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21">
         <v>3</v>
@@ -1373,13 +1373,13 @@
         <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22">
         <v>691280</v>
@@ -1405,13 +1405,13 @@
         <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23">
         <v>689046</v>
@@ -1437,13 +1437,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G24">
         <v>647</v>
@@ -1469,13 +1469,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25">
         <v>691098</v>
@@ -1501,13 +1501,13 @@
         <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G26">
         <v>691280</v>
@@ -1533,13 +1533,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27">
         <v>346</v>
@@ -1565,13 +1565,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G28">
         <v>501</v>
@@ -1597,13 +1597,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G29">
         <v>1109</v>
@@ -1629,13 +1629,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G30">
         <v>649</v>
@@ -1661,13 +1661,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31">
         <v>331</v>
@@ -1693,13 +1693,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G32">
         <v>2234</v>
@@ -1725,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G33">
         <v>59</v>
@@ -1757,13 +1757,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34">
         <v>47</v>
@@ -1789,13 +1789,13 @@
         <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35">
         <v>691280</v>
@@ -1821,13 +1821,13 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1885,13 +1885,13 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1949,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2013,13 +2013,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2077,13 +2077,13 @@
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2109,13 +2109,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2141,13 +2141,13 @@
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2173,13 +2173,13 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2205,13 +2205,13 @@
         <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         <v>10</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2269,13 +2269,13 @@
         <v>10</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2429,13 +2429,13 @@
         <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2461,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2525,13 +2525,13 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G58">
         <v>366</v>
@@ -2557,13 +2557,13 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G59">
         <v>244</v>
@@ -2589,13 +2589,13 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60">
         <v>640</v>
@@ -2621,13 +2621,13 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61">
         <v>696</v>
@@ -2653,13 +2653,13 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62">
         <v>90</v>
@@ -2685,13 +2685,13 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G63">
         <v>8</v>
@@ -2717,13 +2717,13 @@
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64">
         <v>25</v>
@@ -2749,13 +2749,13 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2781,13 +2781,13 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66">
         <v>73</v>
@@ -2813,13 +2813,13 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G67">
         <v>139</v>
@@ -2845,13 +2845,13 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G68">
         <v>273</v>
@@ -2877,13 +2877,13 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G69">
         <v>14</v>
@@ -2909,13 +2909,13 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G70">
         <v>30</v>
@@ -2941,13 +2941,13 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G71">
         <v>30</v>
@@ -2973,13 +2973,13 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G72">
         <v>52</v>
@@ -3005,13 +3005,13 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G73">
         <v>47</v>
@@ -3037,13 +3037,13 @@
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -3069,13 +3069,13 @@
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G75">
         <v>17</v>
@@ -3101,13 +3101,13 @@
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G76">
         <v>189</v>
@@ -3133,13 +3133,13 @@
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G77">
         <v>287</v>
@@ -3165,13 +3165,13 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G78">
         <v>74</v>
@@ -3197,13 +3197,13 @@
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G79">
         <v>123</v>
@@ -3229,13 +3229,13 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G80">
         <v>29</v>
@@ -3261,13 +3261,13 @@
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G81">
         <v>15</v>
@@ -3293,13 +3293,13 @@
         <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G82">
         <v>293</v>
@@ -3325,13 +3325,13 @@
         <v>13</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G83">
         <v>37</v>
@@ -3357,13 +3357,13 @@
         <v>13</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G84">
         <v>493</v>
@@ -3389,13 +3389,13 @@
         <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G85">
         <v>749</v>
@@ -3421,13 +3421,13 @@
         <v>13</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G86">
         <v>55</v>
@@ -3453,13 +3453,13 @@
         <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G87">
         <v>45</v>
@@ -3485,13 +3485,13 @@
         <v>13</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E88" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G88">
         <v>177</v>
@@ -3517,13 +3517,13 @@
         <v>13</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G89">
         <v>2</v>
@@ -3549,13 +3549,13 @@
         <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E90" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G90">
         <v>45</v>
@@ -3581,13 +3581,13 @@
         <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E91" t="s">
+        <v>76</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G91">
         <v>3</v>
@@ -3613,13 +3613,13 @@
         <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G92">
         <v>14</v>
@@ -3645,13 +3645,13 @@
         <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G93">
         <v>14</v>
@@ -3677,13 +3677,13 @@
         <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G94">
         <v>33</v>
@@ -3709,13 +3709,13 @@
         <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G95">
         <v>3</v>
@@ -3741,13 +3741,13 @@
         <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G96">
         <v>8</v>
@@ -3773,13 +3773,13 @@
         <v>13</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G97">
         <v>45</v>
@@ -3805,13 +3805,13 @@
         <v>13</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G98">
         <v>30</v>
@@ -3837,13 +3837,13 @@
         <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G99">
         <v>6</v>
@@ -3869,13 +3869,13 @@
         <v>13</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G100">
         <v>50</v>
@@ -3901,13 +3901,13 @@
         <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E101" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G101">
         <v>16</v>
@@ -3933,13 +3933,13 @@
         <v>14</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E102" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G102">
         <v>458</v>
@@ -3965,13 +3965,13 @@
         <v>14</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E103" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G103">
         <v>5</v>
@@ -3997,13 +3997,13 @@
         <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G104">
         <v>43</v>
@@ -4029,13 +4029,13 @@
         <v>14</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G105">
         <v>665</v>
@@ -4061,13 +4061,13 @@
         <v>14</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E106" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G106">
         <v>1043</v>
@@ -4093,13 +4093,13 @@
         <v>14</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E107" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G107">
         <v>71</v>
@@ -4125,13 +4125,13 @@
         <v>14</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G108">
         <v>22</v>
@@ -4157,13 +4157,13 @@
         <v>14</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E109" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G109">
         <v>5</v>
@@ -4189,13 +4189,13 @@
         <v>14</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E110" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -4221,13 +4221,13 @@
         <v>14</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G111">
         <v>81</v>
@@ -4253,13 +4253,13 @@
         <v>14</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E112" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G112">
         <v>52</v>
@@ -4285,13 +4285,13 @@
         <v>14</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G113">
         <v>44</v>
@@ -4317,13 +4317,13 @@
         <v>14</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E114" t="s">
+        <v>76</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G114">
         <v>11</v>
@@ -4349,13 +4349,13 @@
         <v>14</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G115">
         <v>17</v>
@@ -4381,13 +4381,13 @@
         <v>14</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G116">
         <v>17</v>
@@ -4413,13 +4413,13 @@
         <v>14</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G117">
         <v>45</v>
@@ -4445,13 +4445,13 @@
         <v>14</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G118">
         <v>45</v>
@@ -4477,13 +4477,13 @@
         <v>14</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -4509,13 +4509,13 @@
         <v>14</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G120">
         <v>12</v>
@@ -4541,13 +4541,13 @@
         <v>14</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G121">
         <v>188</v>
@@ -4573,13 +4573,13 @@
         <v>14</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G122">
         <v>43</v>
@@ -4605,13 +4605,13 @@
         <v>14</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G123">
         <v>14</v>
@@ -4637,13 +4637,13 @@
         <v>14</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G124">
         <v>52</v>
@@ -4669,13 +4669,13 @@
         <v>15</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E125" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G125">
         <v>41</v>
@@ -4701,13 +4701,13 @@
         <v>15</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G126">
         <v>585</v>
@@ -4733,13 +4733,13 @@
         <v>15</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E127" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G127">
         <v>383</v>
@@ -4765,13 +4765,13 @@
         <v>15</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -4797,13 +4797,13 @@
         <v>15</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -4829,13 +4829,13 @@
         <v>15</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G130">
         <v>22</v>
@@ -4861,13 +4861,13 @@
         <v>15</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E131" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -4893,13 +4893,13 @@
         <v>15</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G132">
         <v>898</v>
@@ -4925,13 +4925,13 @@
         <v>15</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E133" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G133">
         <v>126</v>
@@ -4957,13 +4957,13 @@
         <v>15</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G134">
         <v>14</v>
@@ -4989,13 +4989,13 @@
         <v>15</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G135">
         <v>60</v>
@@ -5021,13 +5021,13 @@
         <v>15</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E136" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G136">
         <v>51</v>
@@ -5053,13 +5053,13 @@
         <v>15</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E137" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G137">
         <v>7</v>
@@ -5085,13 +5085,13 @@
         <v>15</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G138">
         <v>4</v>
@@ -5117,13 +5117,13 @@
         <v>15</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E139" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G139">
         <v>4</v>
@@ -5149,13 +5149,13 @@
         <v>15</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E140" t="s">
+        <v>76</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G140">
         <v>13</v>
@@ -5181,13 +5181,13 @@
         <v>15</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G141">
         <v>29</v>
@@ -5213,13 +5213,13 @@
         <v>15</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G142">
         <v>29</v>
@@ -5245,13 +5245,13 @@
         <v>15</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G143">
         <v>45</v>
@@ -5277,13 +5277,13 @@
         <v>15</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E144" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G144">
         <v>45</v>
@@ -5309,13 +5309,13 @@
         <v>15</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E145" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G145">
         <v>9</v>
@@ -5341,13 +5341,13 @@
         <v>15</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5373,13 +5373,13 @@
         <v>15</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G147">
         <v>42</v>
@@ -5405,13 +5405,13 @@
         <v>15</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G148">
         <v>12</v>
@@ -5437,13 +5437,13 @@
         <v>15</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G149">
         <v>58</v>
@@ -5469,13 +5469,13 @@
         <v>15</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G150">
         <v>64</v>
@@ -5501,13 +5501,13 @@
         <v>16</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E151" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G151">
         <v>387</v>
@@ -5533,13 +5533,13 @@
         <v>16</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E152" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G152">
         <v>39</v>
@@ -5565,13 +5565,13 @@
         <v>16</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E153" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G153">
         <v>590</v>
@@ -5597,13 +5597,13 @@
         <v>16</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E154" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G154">
         <v>964</v>
@@ -5629,13 +5629,13 @@
         <v>16</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E155" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G155">
         <v>96</v>
@@ -5661,13 +5661,13 @@
         <v>16</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E156" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G156">
         <v>13</v>
@@ -5693,13 +5693,13 @@
         <v>16</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E157" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G157">
         <v>7</v>
@@ -5725,13 +5725,13 @@
         <v>16</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E158" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -5757,13 +5757,13 @@
         <v>16</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E159" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G159">
         <v>108</v>
@@ -5789,13 +5789,13 @@
         <v>16</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E160" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G160">
         <v>47</v>
@@ -5821,13 +5821,13 @@
         <v>16</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E161" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G161">
         <v>7</v>
@@ -5853,13 +5853,13 @@
         <v>16</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E162" t="s">
+        <v>76</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G162">
         <v>30</v>
@@ -5885,13 +5885,13 @@
         <v>16</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G163">
         <v>57</v>
@@ -5917,13 +5917,13 @@
         <v>16</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G164">
         <v>57</v>
@@ -5949,13 +5949,13 @@
         <v>16</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G165">
         <v>37</v>
@@ -5981,13 +5981,13 @@
         <v>16</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E166" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G166">
         <v>37</v>
@@ -6013,13 +6013,13 @@
         <v>16</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E167" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G167">
         <v>2</v>
@@ -6045,13 +6045,13 @@
         <v>16</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E168" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G168">
         <v>9</v>
@@ -6077,13 +6077,13 @@
         <v>16</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E169" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G169">
         <v>170</v>
@@ -6109,13 +6109,13 @@
         <v>16</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E170" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G170">
         <v>36</v>
@@ -6141,13 +6141,13 @@
         <v>16</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E171" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G171">
         <v>13</v>
@@ -6173,13 +6173,13 @@
         <v>16</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E172" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G172">
         <v>9</v>
@@ -6205,13 +6205,13 @@
         <v>16</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E173" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G173">
         <v>88</v>
@@ -6237,13 +6237,13 @@
         <v>16</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E174" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G174">
         <v>4</v>
@@ -6269,13 +6269,13 @@
         <v>16</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E175" t="s">
+        <v>30</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E175" t="s">
-        <v>31</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G175">
         <v>9</v>
@@ -6301,13 +6301,13 @@
         <v>16</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G176">
         <v>9</v>
@@ -6333,13 +6333,13 @@
         <v>16</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G177">
         <v>59</v>
@@ -6365,13 +6365,13 @@
         <v>16</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E178" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G178">
         <v>59</v>
@@ -6397,13 +6397,13 @@
         <v>16</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G179">
         <v>9</v>
@@ -6429,13 +6429,13 @@
         <v>16</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E180" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G180">
         <v>9</v>
@@ -6461,13 +6461,13 @@
         <v>16</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E181" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G181">
         <v>9</v>
@@ -6493,13 +6493,13 @@
         <v>16</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G182">
         <v>85</v>
@@ -6525,13 +6525,13 @@
         <v>16</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G183">
         <v>27</v>
@@ -6557,13 +6557,13 @@
         <v>16</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E184" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G184">
         <v>9</v>
@@ -6589,13 +6589,13 @@
         <v>16</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E185" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G185">
         <v>41</v>
@@ -6621,13 +6621,13 @@
         <v>16</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E186" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G186">
         <v>59</v>
@@ -6653,13 +6653,13 @@
         <v>16</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E187" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G187">
         <v>9</v>
@@ -6685,13 +6685,13 @@
         <v>16</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E188" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G188">
         <v>45</v>
@@ -6717,13 +6717,13 @@
         <v>16</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E189" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G189">
         <v>9</v>
@@ -6749,13 +6749,13 @@
         <v>16</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E190" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G190">
         <v>9</v>
@@ -6781,13 +6781,13 @@
         <v>16</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E191" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G191">
         <v>188993</v>
@@ -6813,13 +6813,13 @@
         <v>16</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E192" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G192">
         <v>183511</v>
@@ -6845,13 +6845,13 @@
         <v>16</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E193" t="s">
+        <v>53</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E193" t="s">
-        <v>54</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G193">
         <v>174</v>
@@ -6877,13 +6877,13 @@
         <v>16</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E194" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G194">
         <v>188993</v>
@@ -6909,13 +6909,13 @@
         <v>16</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E195" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G195">
         <v>188993</v>
@@ -6941,13 +6941,13 @@
         <v>16</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E196" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G196">
         <v>98</v>
@@ -6973,13 +6973,13 @@
         <v>16</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E197" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G197">
         <v>127</v>
@@ -7005,13 +7005,13 @@
         <v>16</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E198" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G198">
         <v>271</v>
@@ -7037,13 +7037,13 @@
         <v>16</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E199" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G199">
         <v>133</v>
@@ -7069,13 +7069,13 @@
         <v>16</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E200" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G200">
         <v>67</v>
@@ -7101,13 +7101,13 @@
         <v>16</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E201" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G201">
         <v>5482</v>
@@ -7133,13 +7133,13 @@
         <v>16</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E202" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G202">
         <v>188377</v>
@@ -7165,13 +7165,13 @@
         <v>16</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E203" t="s">
+        <v>62</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E203" t="s">
-        <v>63</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G203">
         <v>9</v>
@@ -7197,13 +7197,13 @@
         <v>17</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E204" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G204">
         <v>263</v>
@@ -7229,13 +7229,13 @@
         <v>17</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E205" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G205">
         <v>40</v>
@@ -7261,13 +7261,13 @@
         <v>17</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E206" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G206">
         <v>408</v>
@@ -7293,13 +7293,13 @@
         <v>17</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E207" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G207">
         <v>550</v>
@@ -7325,13 +7325,13 @@
         <v>17</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E208" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G208">
         <v>76</v>
@@ -7357,13 +7357,13 @@
         <v>17</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E209" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G209">
         <v>6</v>
@@ -7389,13 +7389,13 @@
         <v>17</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E210" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G210">
         <v>19</v>
@@ -7421,13 +7421,13 @@
         <v>17</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E211" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7453,13 +7453,13 @@
         <v>17</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E212" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G212">
         <v>4</v>
@@ -7485,13 +7485,13 @@
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E213" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G213">
         <v>31</v>
@@ -7517,13 +7517,13 @@
         <v>17</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E214" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G214">
         <v>175</v>
@@ -7549,13 +7549,13 @@
         <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E215" t="s">
+        <v>76</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G215">
         <v>9</v>
@@ -7581,13 +7581,13 @@
         <v>17</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E216" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G216">
         <v>9</v>
@@ -7613,13 +7613,13 @@
         <v>17</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G217">
         <v>9</v>
@@ -7645,13 +7645,13 @@
         <v>17</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G218">
         <v>34</v>
@@ -7677,13 +7677,13 @@
         <v>17</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G219">
         <v>2</v>
@@ -7709,13 +7709,13 @@
         <v>17</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E220" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G220">
         <v>9</v>
@@ -7741,13 +7741,13 @@
         <v>17</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E221" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G221">
         <v>3654</v>
@@ -7773,13 +7773,13 @@
         <v>17</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G222">
         <v>33</v>
@@ -7805,13 +7805,13 @@
         <v>18</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E223" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G223">
         <v>486</v>
@@ -7837,13 +7837,13 @@
         <v>18</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G224">
         <v>25</v>
@@ -7869,13 +7869,13 @@
         <v>18</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E225" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G225">
         <v>68</v>
@@ -7901,13 +7901,13 @@
         <v>18</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E226" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G226">
         <v>729</v>
@@ -7933,13 +7933,13 @@
         <v>18</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E227" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G227">
         <v>854</v>
@@ -7965,13 +7965,13 @@
         <v>18</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E228" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G228">
         <v>121</v>
@@ -7997,13 +7997,13 @@
         <v>18</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E229" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G229">
         <v>27</v>
@@ -8029,13 +8029,13 @@
         <v>18</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E230" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G230">
         <v>2</v>
@@ -8061,13 +8061,13 @@
         <v>18</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E231" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G231">
         <v>30</v>
@@ -8093,13 +8093,13 @@
         <v>18</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E232" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G232">
         <v>51</v>
@@ -8125,13 +8125,13 @@
         <v>18</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E233" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G233">
         <v>337</v>
@@ -8157,13 +8157,13 @@
         <v>18</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E234" t="s">
+        <v>76</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G234">
         <v>50</v>
@@ -8189,13 +8189,13 @@
         <v>18</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E235" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G235">
         <v>58</v>
@@ -8221,13 +8221,13 @@
         <v>18</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E236" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G236">
         <v>58</v>
@@ -8253,13 +8253,13 @@
         <v>18</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E237" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G237">
         <v>56</v>
@@ -8285,13 +8285,13 @@
         <v>18</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E238" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G238">
         <v>3</v>
@@ -8317,13 +8317,13 @@
         <v>18</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E239" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G239">
         <v>4610</v>
@@ -8349,13 +8349,13 @@
         <v>18</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E240" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G240">
         <v>44</v>
@@ -8381,13 +8381,13 @@
         <v>18</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E241" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G241">
         <v>44</v>
@@ -8413,13 +8413,13 @@
         <v>18</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E242" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G242">
         <v>90</v>
@@ -8445,13 +8445,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E243" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G243">
         <v>27</v>
@@ -8477,13 +8477,13 @@
         <v>18</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E244" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G244">
         <v>121</v>
@@ -8509,13 +8509,13 @@
         <v>18</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E245" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G245">
         <v>12</v>
@@ -8541,13 +8541,13 @@
         <v>19</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E246" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G246">
         <v>35</v>
@@ -8573,13 +8573,13 @@
         <v>19</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E247" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G247">
         <v>232</v>
@@ -8605,13 +8605,13 @@
         <v>19</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E248" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G248">
         <v>351</v>
@@ -8637,13 +8637,13 @@
         <v>19</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E249" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G249">
         <v>33</v>
@@ -8669,13 +8669,13 @@
         <v>19</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E250" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G250">
         <v>3</v>
@@ -8701,13 +8701,13 @@
         <v>19</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E251" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G251">
         <v>445</v>
@@ -8733,13 +8733,13 @@
         <v>19</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E252" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G252">
         <v>66</v>
@@ -8765,13 +8765,13 @@
         <v>19</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E253" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G253">
         <v>84</v>
@@ -8797,13 +8797,13 @@
         <v>19</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E254" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G254">
         <v>51</v>
@@ -8829,13 +8829,13 @@
         <v>19</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E255" t="s">
+        <v>76</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G255">
         <v>17</v>
@@ -8861,13 +8861,13 @@
         <v>19</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E256" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G256">
         <v>11</v>
@@ -8893,13 +8893,13 @@
         <v>19</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E257" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G257">
         <v>11</v>
@@ -8925,13 +8925,13 @@
         <v>19</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E258" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G258">
         <v>34</v>
@@ -8957,13 +8957,13 @@
         <v>19</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E259" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G259">
         <v>34</v>
@@ -8989,13 +8989,13 @@
         <v>19</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E260" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G260">
         <v>6</v>
@@ -9021,13 +9021,13 @@
         <v>19</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E261" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G261">
         <v>2</v>
@@ -9053,13 +9053,13 @@
         <v>19</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E262" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G262">
         <v>33</v>
@@ -9085,13 +9085,13 @@
         <v>19</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E263" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G263">
         <v>23</v>
@@ -9117,13 +9117,13 @@
         <v>19</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E264" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G264">
         <v>79</v>
@@ -9149,13 +9149,13 @@
         <v>19</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E265" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G265">
         <v>12</v>
@@ -9181,13 +9181,13 @@
         <v>19</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E266" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G266">
         <v>21</v>
@@ -9213,13 +9213,13 @@
         <v>19</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E267" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G267">
         <v>22</v>
@@ -9245,13 +9245,13 @@
         <v>20</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E268" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G268">
         <v>74</v>
@@ -9277,13 +9277,13 @@
         <v>20</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E269" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G269">
         <v>160</v>
@@ -9309,13 +9309,13 @@
         <v>20</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E270" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G270">
         <v>82</v>
@@ -9341,13 +9341,13 @@
         <v>20</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E271" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G271">
         <v>227</v>
@@ -9373,13 +9373,13 @@
         <v>20</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E272" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G272">
         <v>173</v>
@@ -9405,13 +9405,13 @@
         <v>20</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E273" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G273">
         <v>3</v>
@@ -9437,13 +9437,13 @@
         <v>20</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E274" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G274">
         <v>110</v>
@@ -9469,13 +9469,13 @@
         <v>20</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E275" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G275">
         <v>311</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E276" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G276">
         <v>286</v>
@@ -9533,13 +9533,13 @@
         <v>20</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E277" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G277">
         <v>12</v>
@@ -9565,13 +9565,13 @@
         <v>20</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E278" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G278">
         <v>85</v>
@@ -9597,13 +9597,13 @@
         <v>20</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E279" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G279">
         <v>44</v>
@@ -9629,13 +9629,13 @@
         <v>20</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E280" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G280">
         <v>47</v>
@@ -9661,13 +9661,13 @@
         <v>20</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E281" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G281">
         <v>17</v>
@@ -9693,13 +9693,13 @@
         <v>20</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E282" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G282">
         <v>13</v>
@@ -9725,13 +9725,13 @@
         <v>20</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E283" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G283">
         <v>91</v>
@@ -9757,13 +9757,13 @@
         <v>20</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E284" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G284">
         <v>48</v>
@@ -9789,13 +9789,13 @@
         <v>20</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E285" t="s">
+        <v>76</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G285">
         <v>16</v>
@@ -9821,13 +9821,13 @@
         <v>20</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E286" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G286">
         <v>39</v>
@@ -9853,13 +9853,13 @@
         <v>20</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E287" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G287">
         <v>39</v>
@@ -9885,13 +9885,13 @@
         <v>20</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E288" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G288">
         <v>44</v>
@@ -9917,13 +9917,13 @@
         <v>20</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E289" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G289">
         <v>44</v>
@@ -9949,13 +9949,13 @@
         <v>20</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E290" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G290">
         <v>9</v>
@@ -9981,13 +9981,13 @@
         <v>20</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E291" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G291">
         <v>2</v>
@@ -10013,13 +10013,13 @@
         <v>20</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E292" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G292">
         <v>228</v>
@@ -10045,13 +10045,13 @@
         <v>20</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E293" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G293">
         <v>22</v>
@@ -10077,13 +10077,13 @@
         <v>20</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E294" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G294">
         <v>184</v>
@@ -10109,13 +10109,13 @@
         <v>20</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E295" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G295">
         <v>87</v>
@@ -10138,16 +10138,16 @@
         <v>2026</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E296" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G296">
         <v>96</v>
@@ -10170,16 +10170,16 @@
         <v>2026</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E297" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G297">
         <v>17</v>
@@ -10202,16 +10202,16 @@
         <v>2026</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E298" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G298">
         <v>109</v>
@@ -10234,16 +10234,16 @@
         <v>2026</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E299" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G299">
         <v>8</v>
@@ -10266,16 +10266,16 @@
         <v>2026</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E300" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G300">
         <v>34</v>
@@ -10298,16 +10298,16 @@
         <v>2026</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E301" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G301">
         <v>5</v>
@@ -10330,16 +10330,16 @@
         <v>2026</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E302" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G302">
         <v>17</v>
@@ -10362,16 +10362,16 @@
         <v>2026</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E303" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G303">
         <v>7</v>
@@ -10394,16 +10394,16 @@
         <v>2026</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E304" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G304">
         <v>200</v>
@@ -10426,16 +10426,16 @@
         <v>2026</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E305" t="s">
+        <v>76</v>
+      </c>
+      <c r="F305" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G305">
         <v>14</v>
@@ -10458,16 +10458,16 @@
         <v>2026</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E306" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G306">
         <v>19</v>
@@ -10490,16 +10490,16 @@
         <v>2026</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E307" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G307">
         <v>19</v>
@@ -10522,16 +10522,16 @@
         <v>2026</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E308" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G308">
         <v>5</v>
@@ -10554,16 +10554,16 @@
         <v>2026</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E309" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G309">
         <v>2</v>
@@ -10586,16 +10586,16 @@
         <v>2026</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E310" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -10618,16 +10618,16 @@
         <v>2026</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E311" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -10650,16 +10650,16 @@
         <v>2026</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E312" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G312">
         <v>39</v>
@@ -10682,16 +10682,16 @@
         <v>2026</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E313" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G313">
         <v>778</v>
@@ -10714,16 +10714,16 @@
         <v>2026</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E314" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G314">
         <v>392</v>
@@ -10746,16 +10746,16 @@
         <v>2026</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E315" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G315">
         <v>7</v>
@@ -10778,16 +10778,16 @@
         <v>2026</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E316" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G316">
         <v>9</v>
@@ -10810,16 +10810,16 @@
         <v>2026</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E317" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G317">
         <v>145</v>
@@ -10842,16 +10842,16 @@
         <v>2026</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E318" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G318">
         <v>925</v>
@@ -10874,16 +10874,16 @@
         <v>2026</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E319" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G319">
         <v>45</v>
@@ -10906,16 +10906,16 @@
         <v>2026</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E320" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G320">
         <v>24</v>
@@ -10938,16 +10938,16 @@
         <v>2026</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E321" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G321">
         <v>26</v>
@@ -10970,16 +10970,16 @@
         <v>2026</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E322" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G322">
         <v>26</v>
@@ -11002,16 +11002,16 @@
         <v>2026</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E323" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G323">
         <v>4</v>
@@ -11034,16 +11034,16 @@
         <v>2026</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E324" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G324">
         <v>16</v>
@@ -11066,16 +11066,16 @@
         <v>2026</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E325" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G325">
         <v>4</v>
@@ -11098,16 +11098,16 @@
         <v>2026</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E326" t="s">
+        <v>76</v>
+      </c>
+      <c r="F326" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G326">
         <v>105</v>
@@ -11130,16 +11130,16 @@
         <v>2026</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E327" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G327">
         <v>65</v>
@@ -11162,16 +11162,16 @@
         <v>2026</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E328" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G328">
         <v>65</v>
@@ -11194,16 +11194,16 @@
         <v>2026</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E329" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G329">
         <v>33</v>
@@ -11226,16 +11226,16 @@
         <v>2026</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E330" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G330">
         <v>33</v>
@@ -11258,16 +11258,16 @@
         <v>2026</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E331" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G331">
         <v>10</v>
@@ -11290,16 +11290,16 @@
         <v>2026</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E332" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G332">
         <v>6</v>
@@ -11322,16 +11322,16 @@
         <v>2026</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E333" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G333">
         <v>33</v>
@@ -11354,16 +11354,16 @@
         <v>2026</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E334" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G334">
         <v>11</v>
@@ -11386,16 +11386,16 @@
         <v>2026</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E335" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G335">
         <v>24</v>
@@ -11418,16 +11418,16 @@
         <v>2026</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E336" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G336">
         <v>3536</v>
@@ -11450,16 +11450,16 @@
         <v>2026</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E337" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G337">
         <v>278</v>
@@ -11482,16 +11482,16 @@
         <v>2026</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E338" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G338">
         <v>129</v>
@@ -11514,16 +11514,16 @@
         <v>2026</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E339" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G339">
         <v>553</v>
@@ -11546,16 +11546,16 @@
         <v>2026</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E340" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G340">
         <v>315</v>
@@ -11578,16 +11578,16 @@
         <v>2026</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E341" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G341">
         <v>20</v>
@@ -11610,16 +11610,16 @@
         <v>2026</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E342" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G342">
         <v>19</v>
@@ -11642,16 +11642,16 @@
         <v>2026</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E343" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G343">
         <v>19</v>
@@ -11674,16 +11674,16 @@
         <v>2026</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E344" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G344">
         <v>86</v>
@@ -11706,16 +11706,16 @@
         <v>2026</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E345" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G345">
         <v>0</v>
@@ -11736,16 +11736,16 @@
         <v>2026</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E346" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G346">
         <v>2</v>
@@ -11768,16 +11768,16 @@
         <v>2026</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E347" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G347">
         <v>32</v>
@@ -11800,16 +11800,16 @@
         <v>2026</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E348" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G348">
         <v>615</v>
@@ -11832,16 +11832,16 @@
         <v>2026</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E349" t="s">
+        <v>76</v>
+      </c>
+      <c r="F349" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F349" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G349">
         <v>172</v>
@@ -11864,16 +11864,16 @@
         <v>2026</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E350" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G350">
         <v>175</v>
@@ -11896,16 +11896,16 @@
         <v>2026</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E351" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G351">
         <v>175</v>
@@ -11928,16 +11928,16 @@
         <v>2026</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E352" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G352">
         <v>48</v>
@@ -11960,16 +11960,16 @@
         <v>2026</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E353" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G353">
         <v>48</v>
@@ -11992,16 +11992,16 @@
         <v>2026</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E354" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G354">
         <v>0</v>
@@ -12022,16 +12022,16 @@
         <v>2026</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E355" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G355">
         <v>13</v>
@@ -12054,16 +12054,16 @@
         <v>2026</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E356" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G356">
         <v>50</v>
@@ -12086,16 +12086,16 @@
         <v>2026</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E357" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G357">
         <v>48</v>
@@ -12118,16 +12118,16 @@
         <v>2026</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E358" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G358">
         <v>17</v>
@@ -12150,16 +12150,16 @@
         <v>2026</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E359" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G359">
         <v>62</v>
@@ -12182,16 +12182,16 @@
         <v>2026</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E360" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G360">
         <v>25</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE4C072-1DE0-4CEF-9903-CD711381BCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE0CD95-952C-4CB7-A89C-EB0F7D80954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Daop 9 Jr</t>
-  </si>
-  <si>
-    <t>Divre I SU</t>
   </si>
   <si>
     <t>Divre III Pg</t>
@@ -316,6 +313,9 @@
   </si>
   <si>
     <t>Divre II Pd</t>
+  </si>
+  <si>
+    <t>Divre I Su</t>
   </si>
 </sst>
 </file>
@@ -733,13 +733,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G2">
         <v>59</v>
@@ -765,13 +765,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>47</v>
@@ -797,13 +797,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>59</v>
@@ -829,13 +829,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>398</v>
@@ -861,13 +861,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="G6">
         <v>398</v>
@@ -893,13 +893,13 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>64</v>
@@ -925,13 +925,13 @@
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>61</v>
@@ -957,13 +957,13 @@
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>59</v>
@@ -989,13 +989,13 @@
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10">
         <v>161</v>
@@ -1021,13 +1021,13 @@
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11">
         <v>265</v>
@@ -1053,13 +1053,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12">
         <v>72</v>
@@ -1085,13 +1085,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13">
         <v>289</v>
@@ -1117,13 +1117,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1149,13 +1149,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -1181,13 +1181,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16">
         <v>395</v>
@@ -1213,13 +1213,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18">
         <v>245</v>
@@ -1277,13 +1277,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19">
         <v>69</v>
@@ -1309,13 +1309,13 @@
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20">
         <v>61</v>
@@ -1341,13 +1341,13 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <v>3</v>
@@ -1373,13 +1373,13 @@
         <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22">
         <v>691280</v>
@@ -1405,13 +1405,13 @@
         <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23">
         <v>689046</v>
@@ -1437,13 +1437,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G24">
         <v>647</v>
@@ -1469,13 +1469,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25">
         <v>691098</v>
@@ -1501,13 +1501,13 @@
         <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26">
         <v>691280</v>
@@ -1533,13 +1533,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27">
         <v>346</v>
@@ -1565,13 +1565,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28">
         <v>501</v>
@@ -1597,13 +1597,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29">
         <v>1109</v>
@@ -1629,13 +1629,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30">
         <v>649</v>
@@ -1661,13 +1661,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>331</v>
@@ -1693,13 +1693,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G32">
         <v>2234</v>
@@ -1725,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G33">
         <v>59</v>
@@ -1757,13 +1757,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34">
         <v>47</v>
@@ -1789,13 +1789,13 @@
         <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G35">
         <v>691280</v>
@@ -1821,13 +1821,13 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1885,13 +1885,13 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1949,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2013,13 +2013,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2077,13 +2077,13 @@
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2109,13 +2109,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2141,13 +2141,13 @@
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2173,13 +2173,13 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2205,13 +2205,13 @@
         <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         <v>10</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2269,13 +2269,13 @@
         <v>10</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2429,13 +2429,13 @@
         <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2461,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2525,13 +2525,13 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G58">
         <v>366</v>
@@ -2557,13 +2557,13 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G59">
         <v>244</v>
@@ -2589,13 +2589,13 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G60">
         <v>640</v>
@@ -2621,13 +2621,13 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G61">
         <v>696</v>
@@ -2653,13 +2653,13 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G62">
         <v>90</v>
@@ -2685,13 +2685,13 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G63">
         <v>8</v>
@@ -2717,13 +2717,13 @@
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G64">
         <v>25</v>
@@ -2749,13 +2749,13 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2781,13 +2781,13 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G66">
         <v>73</v>
@@ -2813,13 +2813,13 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G67">
         <v>139</v>
@@ -2845,13 +2845,13 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G68">
         <v>273</v>
@@ -2877,13 +2877,13 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E69" t="s">
+        <v>75</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G69">
         <v>14</v>
@@ -2909,13 +2909,13 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G70">
         <v>30</v>
@@ -2941,13 +2941,13 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G71">
         <v>30</v>
@@ -2973,13 +2973,13 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G72">
         <v>52</v>
@@ -3005,13 +3005,13 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G73">
         <v>47</v>
@@ -3037,13 +3037,13 @@
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -3069,13 +3069,13 @@
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G75">
         <v>17</v>
@@ -3101,13 +3101,13 @@
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G76">
         <v>189</v>
@@ -3133,13 +3133,13 @@
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G77">
         <v>287</v>
@@ -3165,13 +3165,13 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G78">
         <v>74</v>
@@ -3197,13 +3197,13 @@
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G79">
         <v>123</v>
@@ -3229,13 +3229,13 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G80">
         <v>29</v>
@@ -3261,13 +3261,13 @@
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G81">
         <v>15</v>
@@ -3293,13 +3293,13 @@
         <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G82">
         <v>293</v>
@@ -3325,13 +3325,13 @@
         <v>13</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G83">
         <v>37</v>
@@ -3357,13 +3357,13 @@
         <v>13</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G84">
         <v>493</v>
@@ -3389,13 +3389,13 @@
         <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G85">
         <v>749</v>
@@ -3421,13 +3421,13 @@
         <v>13</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G86">
         <v>55</v>
@@ -3453,13 +3453,13 @@
         <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G87">
         <v>45</v>
@@ -3485,13 +3485,13 @@
         <v>13</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G88">
         <v>177</v>
@@ -3517,13 +3517,13 @@
         <v>13</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G89">
         <v>2</v>
@@ -3549,13 +3549,13 @@
         <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G90">
         <v>45</v>
@@ -3581,13 +3581,13 @@
         <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E91" t="s">
+        <v>75</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G91">
         <v>3</v>
@@ -3613,13 +3613,13 @@
         <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G92">
         <v>14</v>
@@ -3645,13 +3645,13 @@
         <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G93">
         <v>14</v>
@@ -3677,13 +3677,13 @@
         <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G94">
         <v>33</v>
@@ -3709,13 +3709,13 @@
         <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G95">
         <v>3</v>
@@ -3741,13 +3741,13 @@
         <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G96">
         <v>8</v>
@@ -3773,13 +3773,13 @@
         <v>13</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E97" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G97">
         <v>45</v>
@@ -3805,13 +3805,13 @@
         <v>13</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G98">
         <v>30</v>
@@ -3837,13 +3837,13 @@
         <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G99">
         <v>6</v>
@@ -3869,13 +3869,13 @@
         <v>13</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G100">
         <v>50</v>
@@ -3901,13 +3901,13 @@
         <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G101">
         <v>16</v>
@@ -3933,13 +3933,13 @@
         <v>14</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G102">
         <v>458</v>
@@ -3965,13 +3965,13 @@
         <v>14</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E103" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G103">
         <v>5</v>
@@ -3997,13 +3997,13 @@
         <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G104">
         <v>43</v>
@@ -4029,13 +4029,13 @@
         <v>14</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G105">
         <v>665</v>
@@ -4061,13 +4061,13 @@
         <v>14</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G106">
         <v>1043</v>
@@ -4093,13 +4093,13 @@
         <v>14</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G107">
         <v>71</v>
@@ -4125,13 +4125,13 @@
         <v>14</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G108">
         <v>22</v>
@@ -4157,13 +4157,13 @@
         <v>14</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G109">
         <v>5</v>
@@ -4189,13 +4189,13 @@
         <v>14</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -4221,13 +4221,13 @@
         <v>14</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E111" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G111">
         <v>81</v>
@@ -4253,13 +4253,13 @@
         <v>14</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E112" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G112">
         <v>52</v>
@@ -4285,13 +4285,13 @@
         <v>14</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E113" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G113">
         <v>44</v>
@@ -4317,13 +4317,13 @@
         <v>14</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E114" t="s">
+        <v>75</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G114">
         <v>11</v>
@@ -4349,13 +4349,13 @@
         <v>14</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G115">
         <v>17</v>
@@ -4381,13 +4381,13 @@
         <v>14</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116">
         <v>17</v>
@@ -4413,13 +4413,13 @@
         <v>14</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G117">
         <v>45</v>
@@ -4445,13 +4445,13 @@
         <v>14</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G118">
         <v>45</v>
@@ -4477,13 +4477,13 @@
         <v>14</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -4509,13 +4509,13 @@
         <v>14</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G120">
         <v>12</v>
@@ -4541,13 +4541,13 @@
         <v>14</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E121" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G121">
         <v>188</v>
@@ -4573,13 +4573,13 @@
         <v>14</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G122">
         <v>43</v>
@@ -4605,13 +4605,13 @@
         <v>14</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E123" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G123">
         <v>14</v>
@@ -4637,13 +4637,13 @@
         <v>14</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E124" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G124">
         <v>52</v>
@@ -4669,13 +4669,13 @@
         <v>15</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G125">
         <v>41</v>
@@ -4701,13 +4701,13 @@
         <v>15</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E126" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G126">
         <v>585</v>
@@ -4733,13 +4733,13 @@
         <v>15</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E127" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G127">
         <v>383</v>
@@ -4765,13 +4765,13 @@
         <v>15</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -4797,13 +4797,13 @@
         <v>15</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E129" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -4829,13 +4829,13 @@
         <v>15</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G130">
         <v>22</v>
@@ -4861,13 +4861,13 @@
         <v>15</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -4893,13 +4893,13 @@
         <v>15</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E132" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G132">
         <v>898</v>
@@ -4925,13 +4925,13 @@
         <v>15</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E133" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G133">
         <v>126</v>
@@ -4957,13 +4957,13 @@
         <v>15</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E134" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G134">
         <v>14</v>
@@ -4989,13 +4989,13 @@
         <v>15</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G135">
         <v>60</v>
@@ -5021,13 +5021,13 @@
         <v>15</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E136" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G136">
         <v>51</v>
@@ -5053,13 +5053,13 @@
         <v>15</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E137" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G137">
         <v>7</v>
@@ -5085,13 +5085,13 @@
         <v>15</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E138" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G138">
         <v>4</v>
@@ -5117,13 +5117,13 @@
         <v>15</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E139" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G139">
         <v>4</v>
@@ -5149,13 +5149,13 @@
         <v>15</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E140" t="s">
+        <v>75</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G140">
         <v>13</v>
@@ -5181,13 +5181,13 @@
         <v>15</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E141" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G141">
         <v>29</v>
@@ -5213,13 +5213,13 @@
         <v>15</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G142">
         <v>29</v>
@@ -5245,13 +5245,13 @@
         <v>15</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G143">
         <v>45</v>
@@ -5277,13 +5277,13 @@
         <v>15</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E144" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G144">
         <v>45</v>
@@ -5309,13 +5309,13 @@
         <v>15</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G145">
         <v>9</v>
@@ -5341,13 +5341,13 @@
         <v>15</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E146" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5373,13 +5373,13 @@
         <v>15</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E147" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G147">
         <v>42</v>
@@ -5405,13 +5405,13 @@
         <v>15</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E148" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G148">
         <v>12</v>
@@ -5437,13 +5437,13 @@
         <v>15</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E149" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G149">
         <v>58</v>
@@ -5469,13 +5469,13 @@
         <v>15</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E150" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G150">
         <v>64</v>
@@ -5501,13 +5501,13 @@
         <v>16</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E151" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G151">
         <v>387</v>
@@ -5533,13 +5533,13 @@
         <v>16</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G152">
         <v>39</v>
@@ -5565,13 +5565,13 @@
         <v>16</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E153" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G153">
         <v>590</v>
@@ -5597,13 +5597,13 @@
         <v>16</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E154" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G154">
         <v>964</v>
@@ -5629,13 +5629,13 @@
         <v>16</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E155" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G155">
         <v>96</v>
@@ -5661,13 +5661,13 @@
         <v>16</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E156" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G156">
         <v>13</v>
@@ -5693,13 +5693,13 @@
         <v>16</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E157" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G157">
         <v>7</v>
@@ -5725,13 +5725,13 @@
         <v>16</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E158" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -5757,13 +5757,13 @@
         <v>16</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E159" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G159">
         <v>108</v>
@@ -5789,13 +5789,13 @@
         <v>16</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E160" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G160">
         <v>47</v>
@@ -5821,13 +5821,13 @@
         <v>16</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E161" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G161">
         <v>7</v>
@@ -5853,13 +5853,13 @@
         <v>16</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E162" t="s">
+        <v>75</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G162">
         <v>30</v>
@@ -5885,13 +5885,13 @@
         <v>16</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E163" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G163">
         <v>57</v>
@@ -5917,13 +5917,13 @@
         <v>16</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E164" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G164">
         <v>57</v>
@@ -5949,13 +5949,13 @@
         <v>16</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E165" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G165">
         <v>37</v>
@@ -5981,13 +5981,13 @@
         <v>16</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E166" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G166">
         <v>37</v>
@@ -6013,13 +6013,13 @@
         <v>16</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E167" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G167">
         <v>2</v>
@@ -6045,13 +6045,13 @@
         <v>16</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E168" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G168">
         <v>9</v>
@@ -6077,13 +6077,13 @@
         <v>16</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E169" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G169">
         <v>170</v>
@@ -6109,13 +6109,13 @@
         <v>16</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E170" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G170">
         <v>36</v>
@@ -6141,13 +6141,13 @@
         <v>16</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E171" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G171">
         <v>13</v>
@@ -6173,13 +6173,13 @@
         <v>16</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E172" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G172">
         <v>9</v>
@@ -6205,13 +6205,13 @@
         <v>16</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E173" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G173">
         <v>88</v>
@@ -6237,13 +6237,13 @@
         <v>16</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E174" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G174">
         <v>4</v>
@@ -6269,13 +6269,13 @@
         <v>16</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E175" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E175" t="s">
-        <v>30</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G175">
         <v>9</v>
@@ -6301,13 +6301,13 @@
         <v>16</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E176" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G176">
         <v>9</v>
@@ -6333,13 +6333,13 @@
         <v>16</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E177" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G177">
         <v>59</v>
@@ -6365,13 +6365,13 @@
         <v>16</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E178" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G178">
         <v>59</v>
@@ -6397,13 +6397,13 @@
         <v>16</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E179" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G179">
         <v>9</v>
@@ -6429,13 +6429,13 @@
         <v>16</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G180">
         <v>9</v>
@@ -6461,13 +6461,13 @@
         <v>16</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E181" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G181">
         <v>9</v>
@@ -6493,13 +6493,13 @@
         <v>16</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E182" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G182">
         <v>85</v>
@@ -6525,13 +6525,13 @@
         <v>16</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G183">
         <v>27</v>
@@ -6557,13 +6557,13 @@
         <v>16</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E184" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G184">
         <v>9</v>
@@ -6589,13 +6589,13 @@
         <v>16</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E185" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G185">
         <v>41</v>
@@ -6621,13 +6621,13 @@
         <v>16</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E186" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G186">
         <v>59</v>
@@ -6653,13 +6653,13 @@
         <v>16</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E187" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G187">
         <v>9</v>
@@ -6685,13 +6685,13 @@
         <v>16</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E188" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G188">
         <v>45</v>
@@ -6717,13 +6717,13 @@
         <v>16</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E189" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G189">
         <v>9</v>
@@ -6749,13 +6749,13 @@
         <v>16</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E190" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G190">
         <v>9</v>
@@ -6781,13 +6781,13 @@
         <v>16</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E191" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G191">
         <v>188993</v>
@@ -6813,13 +6813,13 @@
         <v>16</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E192" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G192">
         <v>183511</v>
@@ -6845,13 +6845,13 @@
         <v>16</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E193" t="s">
+        <v>52</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E193" t="s">
-        <v>53</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G193">
         <v>174</v>
@@ -6877,13 +6877,13 @@
         <v>16</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E194" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G194">
         <v>188993</v>
@@ -6909,13 +6909,13 @@
         <v>16</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E195" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G195">
         <v>188993</v>
@@ -6941,13 +6941,13 @@
         <v>16</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E196" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G196">
         <v>98</v>
@@ -6973,13 +6973,13 @@
         <v>16</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E197" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G197">
         <v>127</v>
@@ -7005,13 +7005,13 @@
         <v>16</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E198" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G198">
         <v>271</v>
@@ -7037,13 +7037,13 @@
         <v>16</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E199" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G199">
         <v>133</v>
@@ -7069,13 +7069,13 @@
         <v>16</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E200" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G200">
         <v>67</v>
@@ -7101,13 +7101,13 @@
         <v>16</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E201" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G201">
         <v>5482</v>
@@ -7133,13 +7133,13 @@
         <v>16</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E202" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G202">
         <v>188377</v>
@@ -7165,13 +7165,13 @@
         <v>16</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E203" t="s">
+        <v>61</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E203" t="s">
-        <v>62</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G203">
         <v>9</v>
@@ -7197,13 +7197,13 @@
         <v>17</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E204" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G204">
         <v>263</v>
@@ -7229,13 +7229,13 @@
         <v>17</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G205">
         <v>40</v>
@@ -7261,13 +7261,13 @@
         <v>17</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E206" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G206">
         <v>408</v>
@@ -7293,13 +7293,13 @@
         <v>17</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E207" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G207">
         <v>550</v>
@@ -7325,13 +7325,13 @@
         <v>17</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E208" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G208">
         <v>76</v>
@@ -7357,13 +7357,13 @@
         <v>17</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E209" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G209">
         <v>6</v>
@@ -7389,13 +7389,13 @@
         <v>17</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E210" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G210">
         <v>19</v>
@@ -7421,13 +7421,13 @@
         <v>17</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E211" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7453,13 +7453,13 @@
         <v>17</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E212" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G212">
         <v>4</v>
@@ -7485,13 +7485,13 @@
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E213" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G213">
         <v>31</v>
@@ -7517,13 +7517,13 @@
         <v>17</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E214" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G214">
         <v>175</v>
@@ -7549,13 +7549,13 @@
         <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E215" t="s">
+        <v>75</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G215">
         <v>9</v>
@@ -7581,13 +7581,13 @@
         <v>17</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E216" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G216">
         <v>9</v>
@@ -7613,13 +7613,13 @@
         <v>17</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E217" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G217">
         <v>9</v>
@@ -7645,13 +7645,13 @@
         <v>17</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E218" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G218">
         <v>34</v>
@@ -7677,13 +7677,13 @@
         <v>17</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E219" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G219">
         <v>2</v>
@@ -7709,13 +7709,13 @@
         <v>17</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E220" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G220">
         <v>9</v>
@@ -7741,13 +7741,13 @@
         <v>17</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G221">
         <v>3654</v>
@@ -7773,13 +7773,13 @@
         <v>17</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E222" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G222">
         <v>33</v>
@@ -7805,13 +7805,13 @@
         <v>18</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E223" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G223">
         <v>486</v>
@@ -7837,13 +7837,13 @@
         <v>18</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G224">
         <v>25</v>
@@ -7869,13 +7869,13 @@
         <v>18</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E225" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G225">
         <v>68</v>
@@ -7901,13 +7901,13 @@
         <v>18</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E226" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G226">
         <v>729</v>
@@ -7933,13 +7933,13 @@
         <v>18</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E227" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G227">
         <v>854</v>
@@ -7965,13 +7965,13 @@
         <v>18</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E228" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G228">
         <v>121</v>
@@ -7997,13 +7997,13 @@
         <v>18</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E229" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G229">
         <v>27</v>
@@ -8029,13 +8029,13 @@
         <v>18</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E230" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G230">
         <v>2</v>
@@ -8061,13 +8061,13 @@
         <v>18</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E231" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G231">
         <v>30</v>
@@ -8093,13 +8093,13 @@
         <v>18</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E232" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G232">
         <v>51</v>
@@ -8125,13 +8125,13 @@
         <v>18</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E233" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G233">
         <v>337</v>
@@ -8157,13 +8157,13 @@
         <v>18</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E234" t="s">
+        <v>75</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G234">
         <v>50</v>
@@ -8189,13 +8189,13 @@
         <v>18</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E235" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G235">
         <v>58</v>
@@ -8221,13 +8221,13 @@
         <v>18</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E236" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G236">
         <v>58</v>
@@ -8253,13 +8253,13 @@
         <v>18</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E237" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G237">
         <v>56</v>
@@ -8285,13 +8285,13 @@
         <v>18</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E238" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G238">
         <v>3</v>
@@ -8317,13 +8317,13 @@
         <v>18</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E239" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G239">
         <v>4610</v>
@@ -8349,13 +8349,13 @@
         <v>18</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E240" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G240">
         <v>44</v>
@@ -8381,13 +8381,13 @@
         <v>18</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E241" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G241">
         <v>44</v>
@@ -8413,13 +8413,13 @@
         <v>18</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E242" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G242">
         <v>90</v>
@@ -8445,13 +8445,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E243" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G243">
         <v>27</v>
@@ -8477,13 +8477,13 @@
         <v>18</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E244" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G244">
         <v>121</v>
@@ -8509,13 +8509,13 @@
         <v>18</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E245" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G245">
         <v>12</v>
@@ -8541,13 +8541,13 @@
         <v>19</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E246" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G246">
         <v>35</v>
@@ -8573,13 +8573,13 @@
         <v>19</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E247" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G247">
         <v>232</v>
@@ -8605,13 +8605,13 @@
         <v>19</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E248" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G248">
         <v>351</v>
@@ -8637,13 +8637,13 @@
         <v>19</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E249" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G249">
         <v>33</v>
@@ -8669,13 +8669,13 @@
         <v>19</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E250" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G250">
         <v>3</v>
@@ -8701,13 +8701,13 @@
         <v>19</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E251" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G251">
         <v>445</v>
@@ -8733,13 +8733,13 @@
         <v>19</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E252" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G252">
         <v>66</v>
@@ -8765,13 +8765,13 @@
         <v>19</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E253" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G253">
         <v>84</v>
@@ -8797,13 +8797,13 @@
         <v>19</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E254" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G254">
         <v>51</v>
@@ -8829,13 +8829,13 @@
         <v>19</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E255" t="s">
+        <v>75</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G255">
         <v>17</v>
@@ -8861,13 +8861,13 @@
         <v>19</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E256" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G256">
         <v>11</v>
@@ -8893,13 +8893,13 @@
         <v>19</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E257" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G257">
         <v>11</v>
@@ -8925,13 +8925,13 @@
         <v>19</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E258" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G258">
         <v>34</v>
@@ -8957,13 +8957,13 @@
         <v>19</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E259" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G259">
         <v>34</v>
@@ -8989,13 +8989,13 @@
         <v>19</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E260" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G260">
         <v>6</v>
@@ -9021,13 +9021,13 @@
         <v>19</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E261" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G261">
         <v>2</v>
@@ -9053,13 +9053,13 @@
         <v>19</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E262" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G262">
         <v>33</v>
@@ -9085,13 +9085,13 @@
         <v>19</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E263" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G263">
         <v>23</v>
@@ -9117,13 +9117,13 @@
         <v>19</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E264" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G264">
         <v>79</v>
@@ -9149,13 +9149,13 @@
         <v>19</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E265" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G265">
         <v>12</v>
@@ -9181,13 +9181,13 @@
         <v>19</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E266" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G266">
         <v>21</v>
@@ -9213,13 +9213,13 @@
         <v>19</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E267" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G267">
         <v>22</v>
@@ -9242,16 +9242,16 @@
         <v>2026</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E268" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G268">
         <v>74</v>
@@ -9274,16 +9274,16 @@
         <v>2026</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E269" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G269">
         <v>160</v>
@@ -9306,16 +9306,16 @@
         <v>2026</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E270" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G270">
         <v>82</v>
@@ -9338,16 +9338,16 @@
         <v>2026</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E271" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G271">
         <v>227</v>
@@ -9370,16 +9370,16 @@
         <v>2026</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E272" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G272">
         <v>173</v>
@@ -9402,16 +9402,16 @@
         <v>2026</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E273" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G273">
         <v>3</v>
@@ -9434,16 +9434,16 @@
         <v>2026</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E274" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G274">
         <v>110</v>
@@ -9466,16 +9466,16 @@
         <v>2026</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E275" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G275">
         <v>311</v>
@@ -9498,16 +9498,16 @@
         <v>2026</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E276" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G276">
         <v>286</v>
@@ -9530,16 +9530,16 @@
         <v>2026</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E277" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G277">
         <v>12</v>
@@ -9562,16 +9562,16 @@
         <v>2026</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E278" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G278">
         <v>85</v>
@@ -9594,16 +9594,16 @@
         <v>2026</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E279" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G279">
         <v>44</v>
@@ -9626,16 +9626,16 @@
         <v>2026</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E280" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G280">
         <v>47</v>
@@ -9658,16 +9658,16 @@
         <v>2026</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E281" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G281">
         <v>17</v>
@@ -9690,16 +9690,16 @@
         <v>2026</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E282" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G282">
         <v>13</v>
@@ -9722,16 +9722,16 @@
         <v>2026</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E283" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G283">
         <v>91</v>
@@ -9754,16 +9754,16 @@
         <v>2026</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E284" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G284">
         <v>48</v>
@@ -9786,16 +9786,16 @@
         <v>2026</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E285" t="s">
+        <v>75</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G285">
         <v>16</v>
@@ -9818,16 +9818,16 @@
         <v>2026</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E286" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G286">
         <v>39</v>
@@ -9850,16 +9850,16 @@
         <v>2026</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E287" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G287">
         <v>39</v>
@@ -9882,16 +9882,16 @@
         <v>2026</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E288" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G288">
         <v>44</v>
@@ -9914,16 +9914,16 @@
         <v>2026</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E289" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G289">
         <v>44</v>
@@ -9946,16 +9946,16 @@
         <v>2026</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E290" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G290">
         <v>9</v>
@@ -9978,16 +9978,16 @@
         <v>2026</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E291" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G291">
         <v>2</v>
@@ -10010,16 +10010,16 @@
         <v>2026</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E292" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G292">
         <v>228</v>
@@ -10042,16 +10042,16 @@
         <v>2026</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E293" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G293">
         <v>22</v>
@@ -10074,16 +10074,16 @@
         <v>2026</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E294" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G294">
         <v>184</v>
@@ -10106,16 +10106,16 @@
         <v>2026</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E295" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G295">
         <v>87</v>
@@ -10138,16 +10138,16 @@
         <v>2026</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E296" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G296">
         <v>96</v>
@@ -10170,16 +10170,16 @@
         <v>2026</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E297" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G297">
         <v>17</v>
@@ -10202,16 +10202,16 @@
         <v>2026</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E298" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G298">
         <v>109</v>
@@ -10234,16 +10234,16 @@
         <v>2026</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E299" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G299">
         <v>8</v>
@@ -10266,16 +10266,16 @@
         <v>2026</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E300" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G300">
         <v>34</v>
@@ -10298,16 +10298,16 @@
         <v>2026</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E301" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G301">
         <v>5</v>
@@ -10330,16 +10330,16 @@
         <v>2026</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E302" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G302">
         <v>17</v>
@@ -10362,16 +10362,16 @@
         <v>2026</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E303" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G303">
         <v>7</v>
@@ -10394,16 +10394,16 @@
         <v>2026</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E304" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G304">
         <v>200</v>
@@ -10426,16 +10426,16 @@
         <v>2026</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E305" t="s">
+        <v>75</v>
+      </c>
+      <c r="F305" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G305">
         <v>14</v>
@@ -10458,16 +10458,16 @@
         <v>2026</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E306" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G306">
         <v>19</v>
@@ -10490,16 +10490,16 @@
         <v>2026</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E307" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G307">
         <v>19</v>
@@ -10522,16 +10522,16 @@
         <v>2026</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E308" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G308">
         <v>5</v>
@@ -10554,16 +10554,16 @@
         <v>2026</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E309" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G309">
         <v>2</v>
@@ -10586,16 +10586,16 @@
         <v>2026</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E310" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -10618,16 +10618,16 @@
         <v>2026</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E311" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -10650,16 +10650,16 @@
         <v>2026</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E312" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G312">
         <v>39</v>
@@ -10682,16 +10682,16 @@
         <v>2026</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E313" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G313">
         <v>778</v>
@@ -10714,16 +10714,16 @@
         <v>2026</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E314" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G314">
         <v>392</v>
@@ -10746,16 +10746,16 @@
         <v>2026</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E315" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G315">
         <v>7</v>
@@ -10778,16 +10778,16 @@
         <v>2026</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E316" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G316">
         <v>9</v>
@@ -10810,16 +10810,16 @@
         <v>2026</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E317" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G317">
         <v>145</v>
@@ -10842,16 +10842,16 @@
         <v>2026</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E318" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G318">
         <v>925</v>
@@ -10874,16 +10874,16 @@
         <v>2026</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E319" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G319">
         <v>45</v>
@@ -10906,16 +10906,16 @@
         <v>2026</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E320" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G320">
         <v>24</v>
@@ -10938,16 +10938,16 @@
         <v>2026</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E321" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G321">
         <v>26</v>
@@ -10970,16 +10970,16 @@
         <v>2026</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E322" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G322">
         <v>26</v>
@@ -11002,16 +11002,16 @@
         <v>2026</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E323" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G323">
         <v>4</v>
@@ -11034,16 +11034,16 @@
         <v>2026</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E324" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G324">
         <v>16</v>
@@ -11066,16 +11066,16 @@
         <v>2026</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E325" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G325">
         <v>4</v>
@@ -11098,16 +11098,16 @@
         <v>2026</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E326" t="s">
+        <v>75</v>
+      </c>
+      <c r="F326" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G326">
         <v>105</v>
@@ -11130,16 +11130,16 @@
         <v>2026</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E327" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G327">
         <v>65</v>
@@ -11162,16 +11162,16 @@
         <v>2026</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E328" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G328">
         <v>65</v>
@@ -11194,16 +11194,16 @@
         <v>2026</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E329" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G329">
         <v>33</v>
@@ -11226,16 +11226,16 @@
         <v>2026</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E330" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G330">
         <v>33</v>
@@ -11258,16 +11258,16 @@
         <v>2026</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E331" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G331">
         <v>10</v>
@@ -11290,16 +11290,16 @@
         <v>2026</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E332" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G332">
         <v>6</v>
@@ -11322,16 +11322,16 @@
         <v>2026</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E333" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G333">
         <v>33</v>
@@ -11354,16 +11354,16 @@
         <v>2026</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E334" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G334">
         <v>11</v>
@@ -11386,16 +11386,16 @@
         <v>2026</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E335" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G335">
         <v>24</v>
@@ -11418,16 +11418,16 @@
         <v>2026</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E336" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G336">
         <v>3536</v>
@@ -11450,16 +11450,16 @@
         <v>2026</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E337" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G337">
         <v>278</v>
@@ -11482,16 +11482,16 @@
         <v>2026</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E338" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G338">
         <v>129</v>
@@ -11514,16 +11514,16 @@
         <v>2026</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E339" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G339">
         <v>553</v>
@@ -11546,16 +11546,16 @@
         <v>2026</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E340" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G340">
         <v>315</v>
@@ -11578,16 +11578,16 @@
         <v>2026</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E341" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G341">
         <v>20</v>
@@ -11610,16 +11610,16 @@
         <v>2026</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E342" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G342">
         <v>19</v>
@@ -11642,16 +11642,16 @@
         <v>2026</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E343" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G343">
         <v>19</v>
@@ -11674,16 +11674,16 @@
         <v>2026</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E344" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G344">
         <v>86</v>
@@ -11706,16 +11706,16 @@
         <v>2026</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E345" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G345">
         <v>0</v>
@@ -11736,16 +11736,16 @@
         <v>2026</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E346" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G346">
         <v>2</v>
@@ -11768,16 +11768,16 @@
         <v>2026</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E347" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G347">
         <v>32</v>
@@ -11800,16 +11800,16 @@
         <v>2026</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E348" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G348">
         <v>615</v>
@@ -11832,16 +11832,16 @@
         <v>2026</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E349" t="s">
+        <v>75</v>
+      </c>
+      <c r="F349" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F349" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G349">
         <v>172</v>
@@ -11864,16 +11864,16 @@
         <v>2026</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E350" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G350">
         <v>175</v>
@@ -11896,16 +11896,16 @@
         <v>2026</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E351" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G351">
         <v>175</v>
@@ -11928,16 +11928,16 @@
         <v>2026</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E352" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G352">
         <v>48</v>
@@ -11960,16 +11960,16 @@
         <v>2026</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E353" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G353">
         <v>48</v>
@@ -11992,16 +11992,16 @@
         <v>2026</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E354" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G354">
         <v>0</v>
@@ -12022,16 +12022,16 @@
         <v>2026</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E355" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G355">
         <v>13</v>
@@ -12054,16 +12054,16 @@
         <v>2026</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E356" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G356">
         <v>50</v>
@@ -12086,16 +12086,16 @@
         <v>2026</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E357" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G357">
         <v>48</v>
@@ -12118,16 +12118,16 @@
         <v>2026</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E358" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G358">
         <v>17</v>
@@ -12150,16 +12150,16 @@
         <v>2026</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E359" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G359">
         <v>62</v>
@@ -12182,16 +12182,16 @@
         <v>2026</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E360" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G360">
         <v>25</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE0CD95-952C-4CB7-A89C-EB0F7D80954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D40EBF-A6B0-45C9-B791-9855C029C96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D40EBF-A6B0-45C9-B791-9855C029C96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A328FFF-B586-4581-9D38-A696B5DE5C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
   <sheets>
     <sheet name="Perawatan" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Perawatan!$A$1:$J$392</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -12335,6 +12338,7 @@
       <c r="J392" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J392" xr:uid="{045E82A1-AFA5-46B1-A9F4-12F5B515B637}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\2. Feb\KP\✓ Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\1. Jan\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3583CD-12D7-439D-A29E-9060A85D0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085112EB-D43B-4AB1-809D-1C5DE0FD7057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -787,7 +787,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -808,18 +808,18 @@
         <v>866</v>
       </c>
       <c r="H2">
-        <v>3430</v>
+        <v>1715</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -840,18 +840,18 @@
         <v>278</v>
       </c>
       <c r="H3">
-        <v>506</v>
+        <v>258</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.1673</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -872,18 +872,18 @@
         <v>1610</v>
       </c>
       <c r="H4">
-        <v>3234</v>
+        <v>1609</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.1666</v>
+        <v>8.2900000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -904,18 +904,18 @@
         <v>2269</v>
       </c>
       <c r="H5">
-        <v>4566</v>
+        <v>2278</v>
       </c>
       <c r="I5">
-        <v>27456</v>
+        <v>27444</v>
       </c>
       <c r="J5" s="1">
-        <v>0.1663</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -936,18 +936,18 @@
         <v>116</v>
       </c>
       <c r="H6">
-        <v>234</v>
+        <v>115</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -968,18 +968,18 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>0.16550000000000001</v>
+        <v>8.2699999999999996E-2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -1000,18 +1000,18 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>48</v>
       </c>
       <c r="J8" s="1">
-        <v>0.1875</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1032,18 +1032,18 @@
         <v>78</v>
       </c>
       <c r="H9">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.1663</v>
+        <v>8.3199999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1064,18 +1064,18 @@
         <v>290</v>
       </c>
       <c r="H10">
-        <v>592</v>
+        <v>296</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1096,18 +1096,18 @@
         <v>212</v>
       </c>
       <c r="H11">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.4099999999999994E-2</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1128,18 +1128,18 @@
         <v>52</v>
       </c>
       <c r="H12">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1160,18 +1160,18 @@
         <v>58</v>
       </c>
       <c r="H13">
-        <v>4641</v>
+        <v>2458</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.18149999999999999</v>
+        <v>9.6199999999999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1192,18 +1192,18 @@
         <v>55</v>
       </c>
       <c r="H14">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.1711</v>
+        <v>7.46E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1224,18 +1224,18 @@
         <v>55</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>57</v>
       </c>
       <c r="J15" s="1">
-        <v>0.1754</v>
+        <v>8.77E-2</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1256,18 +1256,18 @@
         <v>133</v>
       </c>
       <c r="H16">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.20799999999999999</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1320,18 +1320,18 @@
         <v>43</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>90</v>
       </c>
       <c r="J18" s="1">
-        <v>0.1444</v>
+        <v>8.8900000000000007E-2</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1352,18 +1352,18 @@
         <v>621</v>
       </c>
       <c r="H19">
-        <v>20841</v>
+        <v>9707</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.17760000000000001</v>
+        <v>8.2699999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1384,18 +1384,18 @@
         <v>98</v>
       </c>
       <c r="H20">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.1673</v>
+        <v>8.7800000000000003E-2</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1416,18 +1416,18 @@
         <v>43</v>
       </c>
       <c r="H21">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.1686</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1448,18 +1448,18 @@
         <v>116</v>
       </c>
       <c r="H22">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1543,7 +1543,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1564,18 +1564,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1596,18 +1596,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1628,18 +1628,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1660,18 +1660,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>774</v>
+        <v>394</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.16209999999999999</v>
+        <v>8.2500000000000004E-2</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1692,18 +1692,18 @@
         <v>398</v>
       </c>
       <c r="H31">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="I31">
         <v>398</v>
       </c>
       <c r="J31" s="1">
-        <v>0.2286</v>
+        <v>0.1457</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1724,18 +1724,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.25779999999999997</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1756,18 +1756,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>0.18029999999999999</v>
+        <v>6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1788,18 +1788,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.40679999999999999</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1820,18 +1820,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>7.3599999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1852,18 +1852,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>4.1500000000000002E-2</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1884,18 +1884,18 @@
         <v>72</v>
       </c>
       <c r="H37">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>72</v>
       </c>
       <c r="J37" s="1">
-        <v>0.15279999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1916,18 +1916,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1977,18 +1977,18 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I40">
         <v>60</v>
       </c>
       <c r="J40" s="1">
-        <v>0.2</v>
+        <v>6.6699999999999995E-2</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2009,18 +2009,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.33160000000000001</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2041,18 +2041,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.125</v>
+        <v>4.2500000000000003E-2</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2073,18 +2073,18 @@
         <v>244</v>
       </c>
       <c r="H43">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I43">
         <v>244</v>
       </c>
       <c r="J43" s="1">
-        <v>0.23769999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2105,18 +2105,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.14860000000000001</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2137,18 +2137,18 @@
         <v>61</v>
       </c>
       <c r="H45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I45">
         <v>61</v>
       </c>
       <c r="J45" s="1">
-        <v>0.1148</v>
+        <v>6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2198,18 +2198,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>1348606</v>
+        <v>671122</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.16259999999999999</v>
+        <v>8.09E-2</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2230,18 +2230,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>211349</v>
+        <v>109448</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.15340000000000001</v>
+        <v>7.9399999999999998E-2</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2262,18 +2262,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>2520</v>
+        <v>1195</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.1623</v>
+        <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2291,21 +2291,21 @@
         <v>27</v>
       </c>
       <c r="G50">
-        <v>691098</v>
+        <v>691280</v>
       </c>
       <c r="H50">
-        <v>548459</v>
+        <v>352697</v>
       </c>
       <c r="I50">
-        <v>2764392</v>
+        <v>2765120</v>
       </c>
       <c r="J50" s="1">
-        <v>0.19839999999999999</v>
+        <v>0.12759999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2326,18 +2326,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>178733</v>
+        <v>91147</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.2586</v>
+        <v>0.13189999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2358,18 +2358,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.15290000000000001</v>
+        <v>6.3799999999999996E-2</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2390,18 +2390,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.2555</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2422,18 +2422,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.1555</v>
+        <v>6.4899999999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2451,21 +2451,21 @@
         <v>44</v>
       </c>
       <c r="G55">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="H55">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="I55">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="J55" s="1">
-        <v>0.114</v>
+        <v>3.27E-2</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2485,19 +2485,16 @@
       <c r="G56">
         <v>331</v>
       </c>
-      <c r="H56">
-        <v>16</v>
-      </c>
       <c r="I56">
         <v>331</v>
       </c>
       <c r="J56" s="1">
-        <v>4.8300000000000003E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2526,7 +2523,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2547,18 +2544,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.1653</v>
+        <v>7.9799999999999996E-2</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2579,18 +2576,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.16839999999999999</v>
+        <v>7.6200000000000004E-2</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2611,7 +2608,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2632,18 +2629,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>1464</v>
+        <v>732</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2664,18 +2661,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>488</v>
+        <v>244</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2696,18 +2693,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1288</v>
+        <v>640</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.16769999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2728,18 +2725,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>1486</v>
+        <v>746</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.16600000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2760,18 +2757,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="I65">
         <v>1104</v>
       </c>
       <c r="J65" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.2400000000000001E-2</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2792,18 +2789,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I66">
         <v>192</v>
       </c>
       <c r="J66" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.11459999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2824,18 +2821,18 @@
         <v>25</v>
       </c>
       <c r="H67">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="I67">
         <v>300</v>
       </c>
       <c r="J67" s="1">
-        <v>0.15670000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2856,18 +2853,18 @@
         <v>3</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2888,18 +2885,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="I69">
         <v>840</v>
       </c>
       <c r="J69" s="1">
-        <v>0.17380000000000001</v>
+        <v>8.6900000000000005E-2</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2920,18 +2917,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2952,18 +2949,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>546</v>
+        <v>273</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2984,18 +2981,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>826</v>
+        <v>434</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.16159999999999999</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3016,18 +3013,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.1167</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3059,7 +3056,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3091,7 +3088,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3112,18 +3109,18 @@
         <v>47</v>
       </c>
       <c r="H76">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I76">
         <v>52</v>
       </c>
       <c r="J76" s="1">
-        <v>0.65380000000000005</v>
+        <v>0.15379999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3155,7 +3152,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3176,18 +3173,18 @@
         <v>17</v>
       </c>
       <c r="H78">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>34</v>
       </c>
       <c r="J78" s="1">
-        <v>0.44119999999999998</v>
+        <v>5.8799999999999998E-2</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3208,18 +3205,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>377</v>
+        <v>189</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>0.16619999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3240,18 +3237,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>580</v>
+        <v>286</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>0.16839999999999999</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3272,18 +3269,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I81">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="J81" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.5500000000000007E-2</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3304,18 +3301,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="I82">
         <v>1644</v>
       </c>
       <c r="J82" s="1">
-        <v>0.1636</v>
+        <v>8.2100000000000006E-2</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3336,7 +3333,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3357,18 +3354,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>0.15229999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3400,7 +3397,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3421,18 +3418,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1172</v>
+        <v>586</v>
       </c>
       <c r="I86">
-        <v>7032</v>
+        <v>7044</v>
       </c>
       <c r="J86" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3199999999999996E-2</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3453,18 +3450,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1100000000000005E-2</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3496,7 +3493,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3517,18 +3514,18 @@
         <v>2</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I89">
         <v>24</v>
       </c>
       <c r="J89" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3549,18 +3546,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>1499</v>
+        <v>749</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>0.1668</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3581,18 +3578,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="I91">
-        <v>1932</v>
+        <v>2124</v>
       </c>
       <c r="J91" s="1">
-        <v>0.1605</v>
+        <v>7.1099999999999997E-2</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3613,18 +3610,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="I92">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="J92" s="1">
-        <v>0.16669999999999999</v>
+        <v>7.7299999999999994E-2</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3645,18 +3642,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.15609999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3677,7 +3674,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3698,18 +3695,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.16300000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3730,7 +3727,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3751,18 +3748,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.23469999999999999</v>
+        <v>0.12970000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3783,18 +3780,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I98">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J98" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3818,15 +3815,15 @@
         <v>6</v>
       </c>
       <c r="I99">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J99" s="1">
-        <v>0.4</v>
+        <v>0.42859999999999998</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3847,18 +3844,18 @@
         <v>33</v>
       </c>
       <c r="H100">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I100">
         <v>132</v>
       </c>
       <c r="J100" s="1">
-        <v>0.20449999999999999</v>
+        <v>6.8199999999999997E-2</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3875,22 +3872,11 @@
       <c r="F101" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G101">
-        <v>33</v>
-      </c>
-      <c r="H101">
-        <v>4</v>
-      </c>
-      <c r="I101">
-        <v>33</v>
-      </c>
-      <c r="J101" s="1">
-        <v>0.1212</v>
-      </c>
+      <c r="J101" s="1"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3914,15 +3900,15 @@
         <v>4</v>
       </c>
       <c r="I102">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J102" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3954,7 +3940,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3975,18 +3961,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.16389999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4007,18 +3993,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>0.15279999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4039,18 +4025,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I106">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="J106" s="1">
-        <v>0.16300000000000001</v>
+        <v>8.5199999999999998E-2</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4071,7 +4057,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4092,18 +4078,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="I108">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="J108" s="1">
-        <v>0.1555</v>
+        <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4124,7 +4110,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4145,18 +4131,18 @@
         <v>16</v>
       </c>
       <c r="H110">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I110">
         <v>192</v>
       </c>
       <c r="J110" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4174,21 +4160,21 @@
         <v>25</v>
       </c>
       <c r="G111">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H111">
-        <v>1280</v>
+        <v>429</v>
       </c>
       <c r="I111">
-        <v>10992</v>
+        <v>11016</v>
       </c>
       <c r="J111" s="1">
-        <v>0.1164</v>
+        <v>3.8899999999999997E-2</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4209,18 +4195,18 @@
         <v>5</v>
       </c>
       <c r="H112">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I112">
         <v>60</v>
       </c>
       <c r="J112" s="1">
-        <v>0.2167</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4241,18 +4227,18 @@
         <v>43</v>
       </c>
       <c r="H113">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I113">
         <v>516</v>
       </c>
       <c r="J113" s="1">
-        <v>0.1221</v>
+        <v>0.1143</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4270,21 +4256,21 @@
         <v>26</v>
       </c>
       <c r="G114">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="H114">
-        <v>1649</v>
+        <v>780</v>
       </c>
       <c r="I114">
-        <v>7992</v>
+        <v>7908</v>
       </c>
       <c r="J114" s="1">
-        <v>0.20630000000000001</v>
+        <v>9.8599999999999993E-2</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4302,21 +4288,21 @@
         <v>26</v>
       </c>
       <c r="G115">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="H115">
-        <v>1114</v>
+        <v>449</v>
       </c>
       <c r="I115">
-        <v>12264</v>
+        <v>12432</v>
       </c>
       <c r="J115" s="1">
-        <v>9.0800000000000006E-2</v>
+        <v>3.61E-2</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4337,18 +4323,18 @@
         <v>71</v>
       </c>
       <c r="H116">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="I116">
         <v>852</v>
       </c>
       <c r="J116" s="1">
-        <v>0.11849999999999999</v>
+        <v>6.8099999999999994E-2</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4369,18 +4355,18 @@
         <v>22</v>
       </c>
       <c r="H117">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="I117">
         <v>528</v>
       </c>
       <c r="J117" s="1">
-        <v>0.1023</v>
+        <v>7.7700000000000005E-2</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4401,18 +4387,18 @@
         <v>5</v>
       </c>
       <c r="H118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I118">
         <v>60</v>
       </c>
       <c r="J118" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4433,18 +4419,18 @@
         <v>1</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>12</v>
       </c>
       <c r="J119" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4465,18 +4451,18 @@
         <v>81</v>
       </c>
       <c r="H120">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="I120">
         <v>972</v>
       </c>
       <c r="J120" s="1">
-        <v>0.12139999999999999</v>
+        <v>5.7599999999999998E-2</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4497,18 +4483,18 @@
         <v>52</v>
       </c>
       <c r="H121">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I121">
         <v>624</v>
       </c>
       <c r="J121" s="1">
-        <v>0.10580000000000001</v>
+        <v>8.8099999999999998E-2</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4529,18 +4515,18 @@
         <v>44</v>
       </c>
       <c r="H122">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I122">
         <v>528</v>
       </c>
       <c r="J122" s="1">
-        <v>8.7099999999999997E-2</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4561,18 +4547,18 @@
         <v>11</v>
       </c>
       <c r="H123">
-        <v>641</v>
+        <v>298</v>
       </c>
       <c r="I123">
         <v>4046</v>
       </c>
       <c r="J123" s="1">
-        <v>0.15840000000000001</v>
+        <v>7.3700000000000002E-2</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4590,21 +4576,21 @@
         <v>27</v>
       </c>
       <c r="G124">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H124">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I124">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J124" s="1">
-        <v>0.23530000000000001</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4622,21 +4608,21 @@
         <v>44</v>
       </c>
       <c r="G125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J125" s="1">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4654,21 +4640,21 @@
         <v>27</v>
       </c>
       <c r="G126">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H126">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I126">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J126" s="1">
-        <v>9.4399999999999998E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4686,21 +4672,21 @@
         <v>44</v>
       </c>
       <c r="G127">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H127">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I127">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J127" s="1">
-        <v>0.31109999999999999</v>
+        <v>2.2700000000000001E-2</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4732,7 +4718,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4753,18 +4739,18 @@
         <v>12</v>
       </c>
       <c r="H129">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I129">
         <v>24</v>
       </c>
       <c r="J129" s="1">
-        <v>0.375</v>
+        <v>4.1700000000000001E-2</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4782,21 +4768,21 @@
         <v>26</v>
       </c>
       <c r="G130">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="H130">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="I130">
-        <v>2256</v>
+        <v>2040</v>
       </c>
       <c r="J130" s="1">
-        <v>0.1547</v>
+        <v>0.14660000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4817,18 +4803,18 @@
         <v>43</v>
       </c>
       <c r="H131">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I131">
         <v>516</v>
       </c>
       <c r="J131" s="1">
-        <v>0.1143</v>
+        <v>7.5600000000000001E-2</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4846,21 +4832,21 @@
         <v>26</v>
       </c>
       <c r="G132">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H132">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I132">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="J132" s="1">
-        <v>0.16070000000000001</v>
+        <v>0.1623</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4881,18 +4867,18 @@
         <v>52</v>
       </c>
       <c r="H133">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I133">
         <v>624</v>
       </c>
       <c r="J133" s="1">
-        <v>0.13780000000000001</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4913,7 +4899,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4934,7 +4920,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4955,7 +4941,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4976,18 +4962,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.1585</v>
+        <v>8.1299999999999997E-2</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5008,18 +4994,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>1171</v>
+        <v>586</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>0.1668</v>
+        <v>8.3500000000000005E-2</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5040,18 +5026,18 @@
         <v>383</v>
       </c>
       <c r="H139">
-        <v>1508</v>
+        <v>762</v>
       </c>
       <c r="I139">
         <v>9144</v>
       </c>
       <c r="J139" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5072,18 +5058,18 @@
         <v>1</v>
       </c>
       <c r="H140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>12</v>
       </c>
       <c r="J140" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5104,18 +5090,18 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141">
         <v>12</v>
       </c>
       <c r="J141" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5136,18 +5122,18 @@
         <v>22</v>
       </c>
       <c r="H142">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I142">
         <v>264</v>
       </c>
       <c r="J142" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5168,18 +5154,18 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143">
         <v>12</v>
       </c>
       <c r="J143" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5200,18 +5186,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>1819</v>
+        <v>909</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>0.16880000000000001</v>
+        <v>8.4400000000000003E-2</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5232,18 +5218,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>253</v>
+        <v>128</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.1673</v>
+        <v>8.4699999999999998E-2</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5264,18 +5250,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>0.16370000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5296,18 +5282,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5328,18 +5314,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.1651</v>
+        <v>8.1699999999999995E-2</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5360,18 +5346,18 @@
         <v>7</v>
       </c>
       <c r="H149">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I149">
         <v>84</v>
       </c>
       <c r="J149" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5392,18 +5378,18 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I150">
         <v>48</v>
       </c>
       <c r="J150" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5435,7 +5421,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5456,18 +5442,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>924</v>
+        <v>483</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.19470000000000001</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5488,18 +5474,18 @@
         <v>29</v>
       </c>
       <c r="H153">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I153">
         <v>112</v>
       </c>
       <c r="J153" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.16070000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5531,7 +5517,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5552,18 +5538,18 @@
         <v>45</v>
       </c>
       <c r="H155">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I155">
         <v>180</v>
       </c>
       <c r="J155" s="1">
-        <v>0.23330000000000001</v>
+        <v>0.21110000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5595,7 +5581,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5616,18 +5602,18 @@
         <v>9</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I157">
         <v>18</v>
       </c>
       <c r="J157" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5659,7 +5645,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5680,18 +5666,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.16259999999999999</v>
+        <v>7.9299999999999995E-2</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5712,18 +5698,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>0.15970000000000001</v>
+        <v>7.6399999999999996E-2</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5744,18 +5730,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.1653</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5776,18 +5762,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>344</v>
+        <v>172</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.1759</v>
+        <v>8.7900000000000006E-2</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5808,18 +5794,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>1539</v>
+        <v>774</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.16569999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5840,18 +5826,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5872,18 +5858,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1185</v>
+        <v>594</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.3900000000000002E-2</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5904,18 +5890,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>1920</v>
+        <v>969</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.16600000000000001</v>
+        <v>8.3799999999999999E-2</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5936,18 +5922,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.1658</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5968,18 +5954,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6000,18 +5986,18 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I169">
         <v>84</v>
       </c>
       <c r="J169" s="1">
-        <v>0.16669999999999999</v>
+        <v>3.5700000000000003E-2</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6032,18 +6018,18 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I170">
         <v>12</v>
       </c>
       <c r="J170" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6064,18 +6050,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.14510000000000001</v>
+        <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6096,18 +6082,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.1600000000000006E-2</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6128,18 +6114,18 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I173">
         <v>84</v>
       </c>
       <c r="J173" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6160,18 +6146,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>1958</v>
+        <v>1058</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.17879999999999999</v>
+        <v>9.6600000000000005E-2</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6192,18 +6178,18 @@
         <v>57</v>
       </c>
       <c r="H175">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I175">
         <v>228</v>
       </c>
       <c r="J175" s="1">
-        <v>0.1404</v>
+        <v>6.1400000000000003E-2</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6232,7 +6218,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6253,18 +6239,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>0.19589999999999999</v>
+        <v>8.1100000000000005E-2</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6296,7 +6282,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6328,7 +6314,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6360,7 +6346,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6381,18 +6367,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>322</v>
+        <v>162</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.1578</v>
+        <v>7.9399999999999998E-2</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6413,18 +6399,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.16439999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6445,18 +6431,18 @@
         <v>13</v>
       </c>
       <c r="H183">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I183">
         <v>156</v>
       </c>
       <c r="J183" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6477,18 +6463,18 @@
         <v>9</v>
       </c>
       <c r="H184">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I184">
         <v>108</v>
       </c>
       <c r="J184" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6509,18 +6495,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.16950000000000001</v>
+        <v>8.43E-2</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6541,7 +6527,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6573,7 +6559,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6594,18 +6580,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6626,18 +6612,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6658,18 +6644,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6690,18 +6676,18 @@
         <v>59</v>
       </c>
       <c r="H191">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I191">
         <v>59</v>
       </c>
       <c r="J191" s="1">
-        <v>0.30509999999999998</v>
+        <v>0.2034</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6733,7 +6719,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6754,18 +6740,18 @@
         <v>9</v>
       </c>
       <c r="H193">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I193">
         <v>36</v>
       </c>
       <c r="J193" s="1">
-        <v>0.25</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6786,18 +6772,18 @@
         <v>9</v>
       </c>
       <c r="H194">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I194">
         <v>9</v>
       </c>
       <c r="J194" s="1">
-        <v>0.66669999999999996</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6817,19 +6803,16 @@
       <c r="G195">
         <v>85</v>
       </c>
-      <c r="H195">
-        <v>19</v>
-      </c>
       <c r="I195">
         <v>85</v>
       </c>
       <c r="J195" s="1">
-        <v>0.2235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6850,18 +6833,18 @@
         <v>27</v>
       </c>
       <c r="H196">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I196">
         <v>27</v>
       </c>
       <c r="J196" s="1">
-        <v>0.77780000000000005</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6893,7 +6876,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6914,18 +6897,18 @@
         <v>41</v>
       </c>
       <c r="H198">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I198">
         <v>41</v>
       </c>
       <c r="J198" s="1">
-        <v>0.78049999999999997</v>
+        <v>0.34150000000000003</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6957,7 +6940,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6977,19 +6960,16 @@
       <c r="G200">
         <v>9</v>
       </c>
-      <c r="H200">
-        <v>9</v>
-      </c>
       <c r="I200">
         <v>36</v>
       </c>
       <c r="J200" s="1">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7010,18 +6990,18 @@
         <v>45</v>
       </c>
       <c r="H201">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I201">
         <v>45</v>
       </c>
       <c r="J201" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7042,18 +7022,18 @@
         <v>9</v>
       </c>
       <c r="H202">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I202">
         <v>36</v>
       </c>
       <c r="J202" s="1">
-        <v>0.1389</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7085,7 +7065,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7106,18 +7086,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>377986</v>
+        <v>188993</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7138,18 +7118,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>42045</v>
+        <v>12453</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.11459999999999999</v>
+        <v>3.39E-2</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7170,18 +7150,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>696</v>
+        <v>348</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7202,18 +7182,18 @@
         <v>188993</v>
       </c>
       <c r="H207">
-        <v>179681</v>
+        <v>69950</v>
       </c>
       <c r="I207">
         <v>755972</v>
       </c>
       <c r="J207" s="1">
-        <v>0.23769999999999999</v>
+        <v>9.2499999999999999E-2</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7234,18 +7214,18 @@
         <v>188993</v>
       </c>
       <c r="H208">
-        <v>49159</v>
+        <v>40025</v>
       </c>
       <c r="I208">
         <v>188993</v>
       </c>
       <c r="J208" s="1">
-        <v>0.2601</v>
+        <v>0.21179999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7266,18 +7246,18 @@
         <v>98</v>
       </c>
       <c r="H209">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="I209">
         <v>392</v>
       </c>
       <c r="J209" s="1">
-        <v>0.19639999999999999</v>
+        <v>7.6499999999999999E-2</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7298,18 +7278,18 @@
         <v>127</v>
       </c>
       <c r="H210">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I210">
         <v>127</v>
       </c>
       <c r="J210" s="1">
-        <v>0.252</v>
+        <v>0.20469999999999999</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7330,18 +7310,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>0.12920000000000001</v>
+        <v>3.5099999999999999E-2</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7362,18 +7342,18 @@
         <v>133</v>
       </c>
       <c r="H212">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I212">
         <v>133</v>
       </c>
       <c r="J212" s="1">
-        <v>0.3609</v>
+        <v>0.15790000000000001</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7394,18 +7374,18 @@
         <v>67</v>
       </c>
       <c r="H213">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I213">
         <v>67</v>
       </c>
       <c r="J213" s="1">
-        <v>0.28360000000000002</v>
+        <v>0.17910000000000001</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7426,18 +7406,18 @@
         <v>5482</v>
       </c>
       <c r="H214">
-        <v>3114</v>
+        <v>370</v>
       </c>
       <c r="I214">
         <v>10964</v>
       </c>
       <c r="J214" s="1">
-        <v>0.28399999999999997</v>
+        <v>3.3700000000000001E-2</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7458,7 +7438,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7479,18 +7459,18 @@
         <v>263</v>
       </c>
       <c r="H216">
-        <v>1052</v>
+        <v>528</v>
       </c>
       <c r="I216">
         <v>6312</v>
       </c>
       <c r="J216" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3699999999999997E-2</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7511,18 +7491,18 @@
         <v>40</v>
       </c>
       <c r="H217">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I217">
         <v>480</v>
       </c>
       <c r="J217" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7543,18 +7523,18 @@
         <v>408</v>
       </c>
       <c r="H218">
-        <v>818</v>
+        <v>390</v>
       </c>
       <c r="I218">
         <v>4896</v>
       </c>
       <c r="J218" s="1">
-        <v>0.1671</v>
+        <v>7.9699999999999993E-2</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7575,18 +7555,18 @@
         <v>550</v>
       </c>
       <c r="H219">
-        <v>1055</v>
+        <v>552</v>
       </c>
       <c r="I219">
         <v>6600</v>
       </c>
       <c r="J219" s="1">
-        <v>0.1598</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7607,18 +7587,18 @@
         <v>76</v>
       </c>
       <c r="H220">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="I220">
         <v>912</v>
       </c>
       <c r="J220" s="1">
-        <v>0.16339999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7639,18 +7619,18 @@
         <v>6</v>
       </c>
       <c r="H221">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I221">
         <v>144</v>
       </c>
       <c r="J221" s="1">
-        <v>0.15970000000000001</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7671,18 +7651,18 @@
         <v>19</v>
       </c>
       <c r="H222">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I222">
         <v>228</v>
       </c>
       <c r="J222" s="1">
-        <v>0.1623</v>
+        <v>7.0199999999999999E-2</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7714,7 +7694,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7735,18 +7715,18 @@
         <v>4</v>
       </c>
       <c r="H224">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I224">
         <v>48</v>
       </c>
       <c r="J224" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7767,18 +7747,18 @@
         <v>31</v>
       </c>
       <c r="H225">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="I225">
         <v>372</v>
       </c>
       <c r="J225" s="1">
-        <v>0.16400000000000001</v>
+        <v>7.5300000000000006E-2</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7799,18 +7779,18 @@
         <v>175</v>
       </c>
       <c r="H226">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="I226">
         <v>2100</v>
       </c>
       <c r="J226" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7831,18 +7811,18 @@
         <v>9</v>
       </c>
       <c r="H227">
-        <v>893</v>
+        <v>487</v>
       </c>
       <c r="I227">
         <v>3285</v>
       </c>
       <c r="J227" s="1">
-        <v>0.27179999999999999</v>
+        <v>0.1482</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7863,18 +7843,18 @@
         <v>9</v>
       </c>
       <c r="H228">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I228">
         <v>36</v>
       </c>
       <c r="J228" s="1">
-        <v>0.27779999999999999</v>
+        <v>2.7799999999999998E-2</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7894,19 +7874,16 @@
       <c r="G229">
         <v>9</v>
       </c>
-      <c r="H229">
-        <v>4</v>
-      </c>
       <c r="I229">
         <v>9</v>
       </c>
       <c r="J229" s="1">
-        <v>0.44440000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7927,18 +7904,18 @@
         <v>34</v>
       </c>
       <c r="H230">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I230">
         <v>132</v>
       </c>
       <c r="J230" s="1">
-        <v>0.31059999999999999</v>
+        <v>6.8199999999999997E-2</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7967,7 +7944,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7999,7 +7976,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8020,18 +7997,18 @@
         <v>3654</v>
       </c>
       <c r="H233">
-        <v>6870</v>
+        <v>2898</v>
       </c>
       <c r="I233">
         <v>43848</v>
       </c>
       <c r="J233" s="1">
-        <v>0.15670000000000001</v>
+        <v>6.6100000000000006E-2</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8052,7 +8029,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8073,7 +8050,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8094,7 +8071,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8115,7 +8092,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8136,7 +8113,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8157,7 +8134,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8186,7 +8163,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8207,18 +8184,18 @@
         <v>486</v>
       </c>
       <c r="H241">
-        <v>1949</v>
+        <v>972</v>
       </c>
       <c r="I241">
         <v>11664</v>
       </c>
       <c r="J241" s="1">
-        <v>0.1671</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8239,18 +8216,18 @@
         <v>25</v>
       </c>
       <c r="H242">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="I242">
         <v>300</v>
       </c>
       <c r="J242" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8271,18 +8248,18 @@
         <v>68</v>
       </c>
       <c r="H243">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="I243">
         <v>816</v>
       </c>
       <c r="J243" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8303,18 +8280,18 @@
         <v>729</v>
       </c>
       <c r="H244">
-        <v>1463</v>
+        <v>731</v>
       </c>
       <c r="I244">
         <v>8772</v>
       </c>
       <c r="J244" s="1">
-        <v>0.1668</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8335,18 +8312,18 @@
         <v>854</v>
       </c>
       <c r="H245">
-        <v>1842</v>
+        <v>922</v>
       </c>
       <c r="I245">
         <v>11040</v>
       </c>
       <c r="J245" s="1">
-        <v>0.1668</v>
+        <v>8.3500000000000005E-2</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8367,18 +8344,18 @@
         <v>121</v>
       </c>
       <c r="H246">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="I246">
         <v>1452</v>
       </c>
       <c r="J246" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8399,18 +8376,18 @@
         <v>27</v>
       </c>
       <c r="H247">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="I247">
         <v>648</v>
       </c>
       <c r="J247" s="1">
-        <v>0.1744</v>
+        <v>8.7999999999999995E-2</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8431,7 +8408,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8452,18 +8429,18 @@
         <v>2</v>
       </c>
       <c r="H249">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I249">
         <v>24</v>
       </c>
       <c r="J249" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8484,18 +8461,18 @@
         <v>30</v>
       </c>
       <c r="H250">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I250">
         <v>360</v>
       </c>
       <c r="J250" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8516,18 +8493,18 @@
         <v>51</v>
       </c>
       <c r="H251">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="I251">
         <v>624</v>
       </c>
       <c r="J251" s="1">
-        <v>0.17150000000000001</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8548,18 +8525,18 @@
         <v>337</v>
       </c>
       <c r="H252">
-        <v>677</v>
+        <v>338</v>
       </c>
       <c r="I252">
         <v>4044</v>
       </c>
       <c r="J252" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8580,18 +8557,18 @@
         <v>50</v>
       </c>
       <c r="H253">
-        <v>3516</v>
+        <v>1859</v>
       </c>
       <c r="I253">
         <v>18972</v>
       </c>
       <c r="J253" s="1">
-        <v>0.18529999999999999</v>
+        <v>9.8000000000000004E-2</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8612,18 +8589,18 @@
         <v>58</v>
       </c>
       <c r="H254">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I254">
         <v>232</v>
       </c>
       <c r="J254" s="1">
-        <v>0.1767</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8655,7 +8632,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8676,18 +8653,18 @@
         <v>56</v>
       </c>
       <c r="H256">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I256">
         <v>228</v>
       </c>
       <c r="J256" s="1">
-        <v>0.114</v>
+        <v>4.3900000000000002E-2</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8719,7 +8696,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8740,18 +8717,18 @@
         <v>4610</v>
       </c>
       <c r="H258">
-        <v>9590</v>
+        <v>4796</v>
       </c>
       <c r="I258">
         <v>55320</v>
       </c>
       <c r="J258" s="1">
-        <v>0.1734</v>
+        <v>8.6699999999999999E-2</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8772,18 +8749,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I259">
         <v>468</v>
       </c>
       <c r="J259" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8804,18 +8781,18 @@
         <v>44</v>
       </c>
       <c r="H260">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I260">
         <v>78</v>
       </c>
       <c r="J260" s="1">
-        <v>0.1026</v>
+        <v>1.2800000000000001E-2</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8836,18 +8813,18 @@
         <v>90</v>
       </c>
       <c r="H261">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I261">
         <v>1080</v>
       </c>
       <c r="J261" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8868,18 +8845,18 @@
         <v>27</v>
       </c>
       <c r="H262">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I262">
         <v>192</v>
       </c>
       <c r="J262" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8900,18 +8877,18 @@
         <v>121</v>
       </c>
       <c r="H263">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="I263">
         <v>1428</v>
       </c>
       <c r="J263" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8932,18 +8909,18 @@
         <v>12</v>
       </c>
       <c r="H264">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I264">
         <v>24</v>
       </c>
       <c r="J264" s="1">
-        <v>0.125</v>
+        <v>4.1700000000000001E-2</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8964,18 +8941,18 @@
         <v>351</v>
       </c>
       <c r="H265">
-        <v>712</v>
+        <v>366</v>
       </c>
       <c r="I265">
         <v>4291</v>
       </c>
       <c r="J265" s="1">
-        <v>0.16589999999999999</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8993,7 +8970,7 @@
         <v>26</v>
       </c>
       <c r="G266">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H266">
         <v>35</v>
@@ -9007,7 +8984,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9028,18 +9005,18 @@
         <v>232</v>
       </c>
       <c r="H267">
-        <v>464</v>
+        <v>232</v>
       </c>
       <c r="I267">
         <v>2784</v>
       </c>
       <c r="J267" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9060,18 +9037,18 @@
         <v>66</v>
       </c>
       <c r="H268">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="I268">
         <v>792</v>
       </c>
       <c r="J268" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9092,18 +9069,18 @@
         <v>84</v>
       </c>
       <c r="H269">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="I269">
         <v>1008</v>
       </c>
       <c r="J269" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9124,7 +9101,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9145,18 +9122,18 @@
         <v>33</v>
       </c>
       <c r="H271">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I271">
         <v>384</v>
       </c>
       <c r="J271" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9177,18 +9154,18 @@
         <v>3</v>
       </c>
       <c r="H272">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I272">
         <v>36</v>
       </c>
       <c r="J272" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9209,7 +9186,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9230,7 +9207,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9251,18 +9228,18 @@
         <v>51</v>
       </c>
       <c r="H275">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I275">
         <v>276</v>
       </c>
       <c r="J275" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9283,18 +9260,18 @@
         <v>445</v>
       </c>
       <c r="H276">
-        <v>890</v>
+        <v>445</v>
       </c>
       <c r="I276">
         <v>5340</v>
       </c>
       <c r="J276" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9315,18 +9292,18 @@
         <v>17</v>
       </c>
       <c r="H277">
-        <v>860</v>
+        <v>465</v>
       </c>
       <c r="I277">
         <v>5110</v>
       </c>
       <c r="J277" s="1">
-        <v>0.16830000000000001</v>
+        <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9358,7 +9335,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9379,18 +9356,18 @@
         <v>11</v>
       </c>
       <c r="H279">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I279">
         <v>11</v>
       </c>
       <c r="J279" s="1">
-        <v>0.45450000000000002</v>
+        <v>9.0899999999999995E-2</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9411,18 +9388,18 @@
         <v>34</v>
       </c>
       <c r="H280">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I280">
         <v>136</v>
       </c>
       <c r="J280" s="1">
-        <v>0.25</v>
+        <v>0.18379999999999999</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9454,7 +9431,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9475,18 +9452,18 @@
         <v>6</v>
       </c>
       <c r="H282">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I282">
         <v>12</v>
       </c>
       <c r="J282" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9518,7 +9495,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9550,7 +9527,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9571,18 +9548,18 @@
         <v>33</v>
       </c>
       <c r="H285">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="I285">
         <v>396</v>
       </c>
       <c r="J285" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9603,18 +9580,18 @@
         <v>23</v>
       </c>
       <c r="H286">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I286">
         <v>276</v>
       </c>
       <c r="J286" s="1">
-        <v>0.16669999999999999</v>
+        <v>7.9699999999999993E-2</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9635,18 +9612,18 @@
         <v>79</v>
       </c>
       <c r="H287">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I287">
         <v>948</v>
       </c>
       <c r="J287" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9667,7 +9644,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9688,18 +9665,18 @@
         <v>21</v>
       </c>
       <c r="H289">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I289">
         <v>264</v>
       </c>
       <c r="J289" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9717,21 +9694,21 @@
         <v>28</v>
       </c>
       <c r="G290">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H290">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I290">
         <v>44</v>
       </c>
       <c r="J290" s="1">
-        <v>0.2727</v>
+        <v>0.15909999999999999</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9752,18 +9729,18 @@
         <v>82</v>
       </c>
       <c r="H291">
-        <v>328</v>
+        <v>164</v>
       </c>
       <c r="I291">
         <v>1968</v>
       </c>
       <c r="J291" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9784,18 +9761,18 @@
         <v>173</v>
       </c>
       <c r="H292">
-        <v>688</v>
+        <v>344</v>
       </c>
       <c r="I292">
         <v>4128</v>
       </c>
       <c r="J292" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9816,18 +9793,18 @@
         <v>74</v>
       </c>
       <c r="H293">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="I293">
         <v>888</v>
       </c>
       <c r="J293" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9848,18 +9825,18 @@
         <v>110</v>
       </c>
       <c r="H294">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="I294">
         <v>1320</v>
       </c>
       <c r="J294" s="1">
-        <v>0.16289999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9880,18 +9857,18 @@
         <v>160</v>
       </c>
       <c r="H295">
-        <v>319</v>
+        <v>160</v>
       </c>
       <c r="I295">
         <v>1920</v>
       </c>
       <c r="J295" s="1">
-        <v>0.1661</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9912,18 +9889,18 @@
         <v>311</v>
       </c>
       <c r="H296">
-        <v>615</v>
+        <v>311</v>
       </c>
       <c r="I296">
         <v>3732</v>
       </c>
       <c r="J296" s="1">
-        <v>0.1648</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9944,18 +9921,18 @@
         <v>286</v>
       </c>
       <c r="H297">
-        <v>572</v>
+        <v>286</v>
       </c>
       <c r="I297">
         <v>3432</v>
       </c>
       <c r="J297" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9976,18 +9953,18 @@
         <v>12</v>
       </c>
       <c r="H298">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I298">
         <v>144</v>
       </c>
       <c r="J298" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10008,18 +9985,18 @@
         <v>85</v>
       </c>
       <c r="H299">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="I299">
         <v>1020</v>
       </c>
       <c r="J299" s="1">
-        <v>0.1676</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10040,18 +10017,18 @@
         <v>44</v>
       </c>
       <c r="H300">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I300">
         <v>528</v>
       </c>
       <c r="J300" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10072,18 +10049,18 @@
         <v>47</v>
       </c>
       <c r="H301">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="I301">
         <v>564</v>
       </c>
       <c r="J301" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10104,18 +10081,18 @@
         <v>91</v>
       </c>
       <c r="H302">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="I302">
         <v>1092</v>
       </c>
       <c r="J302" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10136,18 +10113,18 @@
         <v>13</v>
       </c>
       <c r="H303">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I303">
         <v>384</v>
       </c>
       <c r="J303" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10168,7 +10145,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10189,7 +10166,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10210,18 +10187,18 @@
         <v>17</v>
       </c>
       <c r="H306">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I306">
         <v>204</v>
       </c>
       <c r="J306" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10242,18 +10219,18 @@
         <v>48</v>
       </c>
       <c r="H307">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="I307">
         <v>564</v>
       </c>
       <c r="J307" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.5099999999999995E-2</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10274,18 +10251,18 @@
         <v>227</v>
       </c>
       <c r="H308">
-        <v>449</v>
+        <v>227</v>
       </c>
       <c r="I308">
         <v>2724</v>
       </c>
       <c r="J308" s="1">
-        <v>0.1648</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10306,18 +10283,18 @@
         <v>16</v>
       </c>
       <c r="H309">
-        <v>945</v>
+        <v>344</v>
       </c>
       <c r="I309">
         <v>5842</v>
       </c>
       <c r="J309" s="1">
-        <v>0.1618</v>
+        <v>5.8900000000000001E-2</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10338,18 +10315,18 @@
         <v>39</v>
       </c>
       <c r="H310">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I310">
         <v>156</v>
       </c>
       <c r="J310" s="1">
-        <v>0.25</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10370,18 +10347,18 @@
         <v>39</v>
       </c>
       <c r="H311">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I311">
         <v>39</v>
       </c>
       <c r="J311" s="1">
-        <v>0.25640000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10402,18 +10379,18 @@
         <v>44</v>
       </c>
       <c r="H312">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I312">
         <v>180</v>
       </c>
       <c r="J312" s="1">
-        <v>0.2167</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10434,18 +10411,18 @@
         <v>44</v>
       </c>
       <c r="H313">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I313">
         <v>45</v>
       </c>
       <c r="J313" s="1">
-        <v>0.22220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10466,18 +10443,18 @@
         <v>2</v>
       </c>
       <c r="H314">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I314">
         <v>4</v>
       </c>
       <c r="J314" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10509,7 +10486,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10541,7 +10518,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10562,18 +10539,18 @@
         <v>228</v>
       </c>
       <c r="H317">
-        <v>462</v>
+        <v>228</v>
       </c>
       <c r="I317">
         <v>2736</v>
       </c>
       <c r="J317" s="1">
-        <v>0.16889999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10594,18 +10571,18 @@
         <v>22</v>
       </c>
       <c r="H318">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I318">
         <v>300</v>
       </c>
       <c r="J318" s="1">
-        <v>0.15329999999999999</v>
+        <v>7.3300000000000004E-2</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10626,18 +10603,18 @@
         <v>184</v>
       </c>
       <c r="H319">
-        <v>365</v>
+        <v>184</v>
       </c>
       <c r="I319">
         <v>2196</v>
       </c>
       <c r="J319" s="1">
-        <v>0.16619999999999999</v>
+        <v>8.3799999999999999E-2</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10658,18 +10635,18 @@
         <v>3</v>
       </c>
       <c r="H320">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I320">
         <v>36</v>
       </c>
       <c r="J320" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10690,7 +10667,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10711,7 +10688,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10729,7 +10706,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10750,18 +10727,18 @@
         <v>96</v>
       </c>
       <c r="H324">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="I324">
         <v>2304</v>
       </c>
       <c r="J324" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10782,18 +10759,18 @@
         <v>17</v>
       </c>
       <c r="H325">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I325">
         <v>204</v>
       </c>
       <c r="J325" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10814,18 +10791,18 @@
         <v>109</v>
       </c>
       <c r="H326">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="I326">
         <v>1308</v>
       </c>
       <c r="J326" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10846,18 +10823,18 @@
         <v>8</v>
       </c>
       <c r="H327">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I327">
         <v>96</v>
       </c>
       <c r="J327" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10878,18 +10855,18 @@
         <v>34</v>
       </c>
       <c r="H328">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="I328">
         <v>408</v>
       </c>
       <c r="J328" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10910,18 +10887,18 @@
         <v>5</v>
       </c>
       <c r="H329">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I329">
         <v>120</v>
       </c>
       <c r="J329" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10942,18 +10919,18 @@
         <v>17</v>
       </c>
       <c r="H330">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I330">
         <v>204</v>
       </c>
       <c r="J330" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10974,18 +10951,18 @@
         <v>7</v>
       </c>
       <c r="H331">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I331">
         <v>84</v>
       </c>
       <c r="J331" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -11006,18 +10983,18 @@
         <v>200</v>
       </c>
       <c r="H332">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I332">
         <v>2400</v>
       </c>
       <c r="J332" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11038,18 +11015,18 @@
         <v>14</v>
       </c>
       <c r="H333">
-        <v>826</v>
+        <v>434</v>
       </c>
       <c r="I333">
         <v>5110</v>
       </c>
       <c r="J333" s="1">
-        <v>0.16159999999999999</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11081,7 +11058,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11113,7 +11090,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11145,7 +11122,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11177,7 +11154,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11198,18 +11175,18 @@
         <v>10</v>
       </c>
       <c r="H338">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I338">
         <v>120</v>
       </c>
       <c r="J338" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11241,7 +11218,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11262,7 +11239,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11283,7 +11260,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11304,7 +11281,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11325,18 +11302,18 @@
         <v>392</v>
       </c>
       <c r="H343">
-        <v>1568</v>
+        <v>784</v>
       </c>
       <c r="I343">
         <v>9250</v>
       </c>
       <c r="J343" s="1">
-        <v>0.16950000000000001</v>
+        <v>8.48E-2</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11357,18 +11334,18 @@
         <v>39</v>
       </c>
       <c r="H344">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I344">
         <v>468</v>
       </c>
       <c r="J344" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11389,18 +11366,18 @@
         <v>778</v>
       </c>
       <c r="H345">
-        <v>1556</v>
+        <v>767</v>
       </c>
       <c r="I345">
         <v>9201</v>
       </c>
       <c r="J345" s="1">
-        <v>0.1691</v>
+        <v>8.3400000000000002E-2</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11421,18 +11398,18 @@
         <v>16</v>
       </c>
       <c r="H346">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I346">
         <v>192</v>
       </c>
       <c r="J346" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11453,18 +11430,18 @@
         <v>26</v>
       </c>
       <c r="H347">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I347">
         <v>312</v>
       </c>
       <c r="J347" s="1">
-        <v>0.1699</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11485,18 +11462,18 @@
         <v>24</v>
       </c>
       <c r="H348">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="I348">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="J348" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.0500000000000002E-2</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11517,18 +11494,18 @@
         <v>7</v>
       </c>
       <c r="H349">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I349">
         <v>40</v>
       </c>
       <c r="J349" s="1">
-        <v>0.35</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11549,18 +11526,18 @@
         <v>9</v>
       </c>
       <c r="H350">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I350">
         <v>108</v>
       </c>
       <c r="J350" s="1">
-        <v>0.16669999999999999</v>
+        <v>6.4799999999999996E-2</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11581,18 +11558,18 @@
         <v>925</v>
       </c>
       <c r="H351">
-        <v>1850</v>
+        <v>910</v>
       </c>
       <c r="I351">
         <v>10766</v>
       </c>
       <c r="J351" s="1">
-        <v>0.17180000000000001</v>
+        <v>8.4500000000000006E-2</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11613,18 +11590,18 @@
         <v>45</v>
       </c>
       <c r="H352">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="I352">
         <v>540</v>
       </c>
       <c r="J352" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1500000000000003E-2</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11645,18 +11622,18 @@
         <v>35</v>
       </c>
       <c r="H353">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I353">
         <v>420</v>
       </c>
       <c r="J353" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11677,18 +11654,18 @@
         <v>145</v>
       </c>
       <c r="H354">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="I354">
         <v>1740</v>
       </c>
       <c r="J354" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11706,21 +11683,21 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H355">
-        <v>5518</v>
+        <v>2934</v>
       </c>
       <c r="I355">
-        <v>38161</v>
+        <v>36865</v>
       </c>
       <c r="J355" s="1">
-        <v>0.14460000000000001</v>
+        <v>7.9600000000000004E-2</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11741,18 +11718,18 @@
         <v>88</v>
       </c>
       <c r="H356">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I356">
         <v>352</v>
       </c>
       <c r="J356" s="1">
-        <v>0.11360000000000001</v>
+        <v>9.0899999999999995E-2</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11773,18 +11750,18 @@
         <v>88</v>
       </c>
       <c r="H357">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I357">
         <v>88</v>
       </c>
       <c r="J357" s="1">
-        <v>0.45450000000000002</v>
+        <v>0.36359999999999998</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11805,18 +11782,18 @@
         <v>33</v>
       </c>
       <c r="H358">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I358">
         <v>132</v>
       </c>
       <c r="J358" s="1">
-        <v>0.21970000000000001</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11837,18 +11814,18 @@
         <v>33</v>
       </c>
       <c r="H359">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I359">
         <v>33</v>
       </c>
       <c r="J359" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.18179999999999999</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11880,7 +11857,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11901,18 +11878,18 @@
         <v>10</v>
       </c>
       <c r="H361">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I361">
         <v>20</v>
       </c>
       <c r="J361" s="1">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11930,21 +11907,21 @@
         <v>26</v>
       </c>
       <c r="G362">
-        <v>3536</v>
+        <v>3296</v>
       </c>
       <c r="H362">
-        <v>7072</v>
+        <v>3296</v>
       </c>
       <c r="I362">
-        <v>42432</v>
+        <v>39552</v>
       </c>
       <c r="J362" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11965,18 +11942,18 @@
         <v>33</v>
       </c>
       <c r="H363">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="I363">
         <v>396</v>
       </c>
       <c r="J363" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11997,18 +11974,18 @@
         <v>11</v>
       </c>
       <c r="H364">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I364">
         <v>132</v>
       </c>
       <c r="J364" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12029,18 +12006,18 @@
         <v>24</v>
       </c>
       <c r="H365">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I365">
         <v>288</v>
       </c>
       <c r="J365" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12061,18 +12038,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12090,21 +12067,21 @@
         <v>26</v>
       </c>
       <c r="G367">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H367">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I367">
         <v>64</v>
       </c>
       <c r="J367" s="1">
-        <v>0.125</v>
+        <v>4.6899999999999997E-2</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12119,7 +12096,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12137,21 +12114,21 @@
         <v>25</v>
       </c>
       <c r="G369">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H369">
-        <v>688</v>
+        <v>556</v>
       </c>
       <c r="I369">
-        <v>6696</v>
+        <v>6672</v>
       </c>
       <c r="J369" s="1">
-        <v>0.1027</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12172,18 +12149,18 @@
         <v>129</v>
       </c>
       <c r="H370">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I370">
         <v>1548</v>
       </c>
       <c r="J370" s="1">
-        <v>0.10340000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12201,21 +12178,21 @@
         <v>26</v>
       </c>
       <c r="G371">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="H371">
-        <v>600</v>
+        <v>544</v>
       </c>
       <c r="I371">
-        <v>6396</v>
+        <v>6636</v>
       </c>
       <c r="J371" s="1">
-        <v>9.3799999999999994E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12236,18 +12213,18 @@
         <v>315</v>
       </c>
       <c r="H372">
-        <v>389</v>
+        <v>315</v>
       </c>
       <c r="I372">
-        <v>3786</v>
+        <v>3780</v>
       </c>
       <c r="J372" s="1">
-        <v>0.1027</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12268,18 +12245,18 @@
         <v>20</v>
       </c>
       <c r="H373">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I373">
         <v>240</v>
       </c>
       <c r="J373" s="1">
-        <v>9.1700000000000004E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12300,18 +12277,18 @@
         <v>19</v>
       </c>
       <c r="H374">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I374">
         <v>228</v>
       </c>
       <c r="J374" s="1">
-        <v>0.1009</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12329,21 +12306,21 @@
         <v>25</v>
       </c>
       <c r="G375">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H375">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I375">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="J375" s="1">
-        <v>9.5200000000000007E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12364,18 +12341,18 @@
         <v>86</v>
       </c>
       <c r="H376">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I376">
         <v>1032</v>
       </c>
       <c r="J376" s="1">
-        <v>9.11E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12396,7 +12373,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12428,7 +12405,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12449,18 +12426,18 @@
         <v>32</v>
       </c>
       <c r="H379">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I379">
         <v>384</v>
       </c>
       <c r="J379" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>8.0699999999999994E-2</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12478,21 +12455,21 @@
         <v>26</v>
       </c>
       <c r="G380">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="H380">
-        <v>699</v>
+        <v>604</v>
       </c>
       <c r="I380">
-        <v>7212</v>
+        <v>7380</v>
       </c>
       <c r="J380" s="1">
-        <v>9.69E-2</v>
+        <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12510,21 +12487,21 @@
         <v>43</v>
       </c>
       <c r="G381">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H381">
-        <v>1653</v>
+        <v>1597</v>
       </c>
       <c r="I381">
         <v>17695</v>
       </c>
       <c r="J381" s="1">
-        <v>9.3399999999999997E-2</v>
+        <v>9.0300000000000005E-2</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12545,18 +12522,18 @@
         <v>175</v>
       </c>
       <c r="H382">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I382">
         <v>700</v>
       </c>
       <c r="J382" s="1">
-        <v>0.19289999999999999</v>
+        <v>0.18709999999999999</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12577,18 +12554,18 @@
         <v>175</v>
       </c>
       <c r="H383">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I383">
         <v>175</v>
       </c>
       <c r="J383" s="1">
-        <v>0.77139999999999997</v>
+        <v>0.74860000000000004</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12609,18 +12586,18 @@
         <v>48</v>
       </c>
       <c r="H384">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I384">
         <v>192</v>
       </c>
       <c r="J384" s="1">
-        <v>0.25519999999999998</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12641,18 +12618,18 @@
         <v>48</v>
       </c>
       <c r="H385">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I385">
         <v>48</v>
       </c>
       <c r="J385" s="1">
-        <v>0.9375</v>
+        <v>0.85419999999999996</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12673,7 +12650,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12694,18 +12671,18 @@
         <v>13</v>
       </c>
       <c r="H387">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I387">
         <v>26</v>
       </c>
       <c r="J387" s="1">
-        <v>0.30769999999999997</v>
+        <v>0.26919999999999999</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12726,18 +12703,18 @@
         <v>50</v>
       </c>
       <c r="H388">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I388">
         <v>600</v>
       </c>
       <c r="J388" s="1">
-        <v>0.1</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12758,18 +12735,18 @@
         <v>48</v>
       </c>
       <c r="H389">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I389">
         <v>576</v>
       </c>
       <c r="J389" s="1">
-        <v>9.5500000000000002E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12790,18 +12767,18 @@
         <v>17</v>
       </c>
       <c r="H390">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I390">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="J390" s="1">
-        <v>9.2600000000000002E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12833,7 +12810,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>
@@ -12854,18 +12831,18 @@
         <v>62</v>
       </c>
       <c r="H392">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I392">
         <v>744</v>
       </c>
       <c r="J392" s="1">
-        <v>9.4100000000000003E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A393" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B393" s="2">
         <v>2026</v>
@@ -12883,16 +12860,16 @@
         <v>28</v>
       </c>
       <c r="G393">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H393">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I393">
-        <v>744</v>
+        <v>348</v>
       </c>
       <c r="J393" s="1">
-        <v>2.1499999999999998E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\1. Jan\KP\Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\2. Feb\KP\✓ Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085112EB-D43B-4AB1-809D-1C5DE0FD7057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3583CD-12D7-439D-A29E-9060A85D0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -787,7 +787,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -808,18 +808,18 @@
         <v>866</v>
       </c>
       <c r="H2">
-        <v>1715</v>
+        <v>3430</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -840,18 +840,18 @@
         <v>278</v>
       </c>
       <c r="H3">
-        <v>258</v>
+        <v>506</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>8.5300000000000001E-2</v>
+        <v>0.1673</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -872,18 +872,18 @@
         <v>1610</v>
       </c>
       <c r="H4">
-        <v>1609</v>
+        <v>3234</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>8.2900000000000001E-2</v>
+        <v>0.1666</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -904,18 +904,18 @@
         <v>2269</v>
       </c>
       <c r="H5">
-        <v>2278</v>
+        <v>4566</v>
       </c>
       <c r="I5">
-        <v>27444</v>
+        <v>27456</v>
       </c>
       <c r="J5" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -936,18 +936,18 @@
         <v>116</v>
       </c>
       <c r="H6">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>8.1900000000000001E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -968,18 +968,18 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>8.2699999999999996E-2</v>
+        <v>0.16550000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -1000,18 +1000,18 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>48</v>
       </c>
       <c r="J8" s="1">
-        <v>0.1042</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1032,18 +1032,18 @@
         <v>78</v>
       </c>
       <c r="H9">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>8.3199999999999996E-2</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1064,18 +1064,18 @@
         <v>290</v>
       </c>
       <c r="H10">
-        <v>296</v>
+        <v>592</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1096,18 +1096,18 @@
         <v>212</v>
       </c>
       <c r="H11">
-        <v>211</v>
+        <v>418</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>8.4099999999999994E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1128,18 +1128,18 @@
         <v>52</v>
       </c>
       <c r="H12">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1160,18 +1160,18 @@
         <v>58</v>
       </c>
       <c r="H13">
-        <v>2458</v>
+        <v>4641</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>9.6199999999999994E-2</v>
+        <v>0.18149999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1192,18 +1192,18 @@
         <v>55</v>
       </c>
       <c r="H14">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>7.46E-2</v>
+        <v>0.1711</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1224,18 +1224,18 @@
         <v>55</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>57</v>
       </c>
       <c r="J15" s="1">
-        <v>8.77E-2</v>
+        <v>0.1754</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1256,18 +1256,18 @@
         <v>133</v>
       </c>
       <c r="H16">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.13500000000000001</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1320,18 +1320,18 @@
         <v>43</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I18">
         <v>90</v>
       </c>
       <c r="J18" s="1">
-        <v>8.8900000000000007E-2</v>
+        <v>0.1444</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1352,18 +1352,18 @@
         <v>621</v>
       </c>
       <c r="H19">
-        <v>9707</v>
+        <v>20841</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>8.2699999999999996E-2</v>
+        <v>0.17760000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1384,18 +1384,18 @@
         <v>98</v>
       </c>
       <c r="H20">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>8.7800000000000003E-2</v>
+        <v>0.1673</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1416,18 +1416,18 @@
         <v>43</v>
       </c>
       <c r="H21">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>8.5300000000000001E-2</v>
+        <v>0.1686</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1448,18 +1448,18 @@
         <v>116</v>
       </c>
       <c r="H22">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>8.1900000000000001E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1543,7 +1543,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1564,18 +1564,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>8.1900000000000001E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1596,18 +1596,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16489999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1628,18 +1628,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1660,18 +1660,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>394</v>
+        <v>774</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>8.2500000000000004E-2</v>
+        <v>0.16209999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1692,18 +1692,18 @@
         <v>398</v>
       </c>
       <c r="H31">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="I31">
         <v>398</v>
       </c>
       <c r="J31" s="1">
-        <v>0.1457</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1724,18 +1724,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.1094</v>
+        <v>0.25779999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1756,18 +1756,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>6.5600000000000006E-2</v>
+        <v>0.18029999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1788,18 +1788,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.1017</v>
+        <v>0.40679999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1820,18 +1820,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>7.3599999999999999E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1852,18 +1852,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>4.1500000000000002E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1884,18 +1884,18 @@
         <v>72</v>
       </c>
       <c r="H37">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I37">
         <v>72</v>
       </c>
       <c r="J37" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.15279999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1916,18 +1916,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>4.1399999999999999E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1977,18 +1977,18 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I40">
         <v>60</v>
       </c>
       <c r="J40" s="1">
-        <v>6.6699999999999995E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2009,18 +2009,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.13420000000000001</v>
+        <v>0.33160000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2041,18 +2041,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>4.2500000000000003E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2073,18 +2073,18 @@
         <v>244</v>
       </c>
       <c r="H43">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I43">
         <v>244</v>
       </c>
       <c r="J43" s="1">
-        <v>0.20899999999999999</v>
+        <v>0.23769999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2105,18 +2105,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.14860000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2137,18 +2137,18 @@
         <v>61</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I45">
         <v>61</v>
       </c>
       <c r="J45" s="1">
-        <v>6.5600000000000006E-2</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2198,18 +2198,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>671122</v>
+        <v>1348606</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>8.09E-2</v>
+        <v>0.16259999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2230,18 +2230,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>109448</v>
+        <v>211349</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>7.9399999999999998E-2</v>
+        <v>0.15340000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2262,18 +2262,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>1195</v>
+        <v>2520</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.1623</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2291,21 +2291,21 @@
         <v>27</v>
       </c>
       <c r="G50">
-        <v>691280</v>
+        <v>691098</v>
       </c>
       <c r="H50">
-        <v>352697</v>
+        <v>548459</v>
       </c>
       <c r="I50">
-        <v>2765120</v>
+        <v>2764392</v>
       </c>
       <c r="J50" s="1">
-        <v>0.12759999999999999</v>
+        <v>0.19839999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2326,18 +2326,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>91147</v>
+        <v>178733</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.13189999999999999</v>
+        <v>0.2586</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2358,18 +2358,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>6.3799999999999996E-2</v>
+        <v>0.15290000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2390,18 +2390,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.1118</v>
+        <v>0.2555</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2422,18 +2422,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>6.4899999999999999E-2</v>
+        <v>0.1555</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2451,21 +2451,21 @@
         <v>44</v>
       </c>
       <c r="G55">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="H55">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="I55">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="J55" s="1">
-        <v>3.27E-2</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2485,16 +2485,19 @@
       <c r="G56">
         <v>331</v>
       </c>
+      <c r="H56">
+        <v>16</v>
+      </c>
       <c r="I56">
         <v>331</v>
       </c>
       <c r="J56" s="1">
-        <v>0</v>
+        <v>4.8300000000000003E-2</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2523,7 +2526,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2544,18 +2547,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>7.9799999999999996E-2</v>
+        <v>0.1653</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2576,18 +2579,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>7.6200000000000004E-2</v>
+        <v>0.16839999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2608,7 +2611,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2629,18 +2632,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>732</v>
+        <v>1464</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2661,18 +2664,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>244</v>
+        <v>488</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2693,18 +2696,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>640</v>
+        <v>1288</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16769999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2725,18 +2728,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>746</v>
+        <v>1486</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16600000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2757,18 +2760,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="I65">
         <v>1104</v>
       </c>
       <c r="J65" s="1">
-        <v>8.2400000000000001E-2</v>
+        <v>0.16489999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2789,18 +2792,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I66">
         <v>192</v>
       </c>
       <c r="J66" s="1">
-        <v>0.11459999999999999</v>
+        <v>0.21879999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2821,18 +2824,18 @@
         <v>25</v>
       </c>
       <c r="H67">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I67">
         <v>300</v>
       </c>
       <c r="J67" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.15670000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2853,18 +2856,18 @@
         <v>3</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2885,18 +2888,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="I69">
         <v>840</v>
       </c>
       <c r="J69" s="1">
-        <v>8.6900000000000005E-2</v>
+        <v>0.17380000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2917,18 +2920,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>139</v>
+        <v>278</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2949,18 +2952,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>273</v>
+        <v>546</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2981,18 +2984,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>434</v>
+        <v>826</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>8.4900000000000003E-2</v>
+        <v>0.16159999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3013,18 +3016,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.1</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3056,7 +3059,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3088,7 +3091,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3109,18 +3112,18 @@
         <v>47</v>
       </c>
       <c r="H76">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="I76">
         <v>52</v>
       </c>
       <c r="J76" s="1">
-        <v>0.15379999999999999</v>
+        <v>0.65380000000000005</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3152,7 +3155,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3173,18 +3176,18 @@
         <v>17</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I78">
         <v>34</v>
       </c>
       <c r="J78" s="1">
-        <v>5.8799999999999998E-2</v>
+        <v>0.44119999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3205,18 +3208,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>189</v>
+        <v>377</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16619999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3237,18 +3240,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>286</v>
+        <v>580</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.16839999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3269,18 +3272,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="I81">
-        <v>924</v>
+        <v>948</v>
       </c>
       <c r="J81" s="1">
-        <v>8.5500000000000007E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3301,18 +3304,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c r="I82">
         <v>1644</v>
       </c>
       <c r="J82" s="1">
-        <v>8.2100000000000006E-2</v>
+        <v>0.1636</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3333,7 +3336,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3354,18 +3357,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.15229999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3397,7 +3400,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3418,18 +3421,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>586</v>
+        <v>1172</v>
       </c>
       <c r="I86">
-        <v>7044</v>
+        <v>7032</v>
       </c>
       <c r="J86" s="1">
-        <v>8.3199999999999996E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3450,18 +3453,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>8.1100000000000005E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3493,7 +3496,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3514,18 +3517,18 @@
         <v>2</v>
       </c>
       <c r="H89">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I89">
         <v>24</v>
       </c>
       <c r="J89" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3546,18 +3549,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>749</v>
+        <v>1499</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1668</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3578,18 +3581,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="I91">
-        <v>2124</v>
+        <v>1932</v>
       </c>
       <c r="J91" s="1">
-        <v>7.1099999999999997E-2</v>
+        <v>0.1605</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3610,18 +3613,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="I92">
-        <v>1152</v>
+        <v>1128</v>
       </c>
       <c r="J92" s="1">
-        <v>7.7299999999999994E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3642,18 +3645,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.15609999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3674,7 +3677,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3695,18 +3698,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16300000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3727,7 +3730,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3748,18 +3751,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.12970000000000001</v>
+        <v>0.23469999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3780,18 +3783,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I98">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J98" s="1">
-        <v>0.1429</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3815,15 +3818,15 @@
         <v>6</v>
       </c>
       <c r="I99">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" s="1">
-        <v>0.42859999999999998</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3844,18 +3847,18 @@
         <v>33</v>
       </c>
       <c r="H100">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I100">
         <v>132</v>
       </c>
       <c r="J100" s="1">
-        <v>6.8199999999999997E-2</v>
+        <v>0.20449999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3872,11 +3875,22 @@
       <c r="F101" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J101" s="1"/>
+      <c r="G101">
+        <v>33</v>
+      </c>
+      <c r="H101">
+        <v>4</v>
+      </c>
+      <c r="I101">
+        <v>33</v>
+      </c>
+      <c r="J101" s="1">
+        <v>0.1212</v>
+      </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3900,15 +3914,15 @@
         <v>4</v>
       </c>
       <c r="I102">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J102" s="1">
-        <v>0.25</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3940,7 +3954,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3961,18 +3975,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16389999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -3993,18 +4007,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.15279999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4025,18 +4039,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="I106">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="J106" s="1">
-        <v>8.5199999999999998E-2</v>
+        <v>0.16300000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4057,7 +4071,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4078,18 +4092,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="I108">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="J108" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.1555</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4110,7 +4124,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4131,18 +4145,18 @@
         <v>16</v>
       </c>
       <c r="H110">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I110">
         <v>192</v>
       </c>
       <c r="J110" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4160,21 +4174,21 @@
         <v>25</v>
       </c>
       <c r="G111">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H111">
-        <v>429</v>
+        <v>1280</v>
       </c>
       <c r="I111">
-        <v>11016</v>
+        <v>10992</v>
       </c>
       <c r="J111" s="1">
-        <v>3.8899999999999997E-2</v>
+        <v>0.1164</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4195,18 +4209,18 @@
         <v>5</v>
       </c>
       <c r="H112">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I112">
         <v>60</v>
       </c>
       <c r="J112" s="1">
-        <v>0.15</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4227,18 +4241,18 @@
         <v>43</v>
       </c>
       <c r="H113">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I113">
         <v>516</v>
       </c>
       <c r="J113" s="1">
-        <v>0.1143</v>
+        <v>0.1221</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4256,21 +4270,21 @@
         <v>26</v>
       </c>
       <c r="G114">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="H114">
-        <v>780</v>
+        <v>1649</v>
       </c>
       <c r="I114">
-        <v>7908</v>
+        <v>7992</v>
       </c>
       <c r="J114" s="1">
-        <v>9.8599999999999993E-2</v>
+        <v>0.20630000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4288,21 +4302,21 @@
         <v>26</v>
       </c>
       <c r="G115">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="H115">
-        <v>449</v>
+        <v>1114</v>
       </c>
       <c r="I115">
-        <v>12432</v>
+        <v>12264</v>
       </c>
       <c r="J115" s="1">
-        <v>3.61E-2</v>
+        <v>9.0800000000000006E-2</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4323,18 +4337,18 @@
         <v>71</v>
       </c>
       <c r="H116">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="I116">
         <v>852</v>
       </c>
       <c r="J116" s="1">
-        <v>6.8099999999999994E-2</v>
+        <v>0.11849999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4355,18 +4369,18 @@
         <v>22</v>
       </c>
       <c r="H117">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="I117">
         <v>528</v>
       </c>
       <c r="J117" s="1">
-        <v>7.7700000000000005E-2</v>
+        <v>0.1023</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4387,18 +4401,18 @@
         <v>5</v>
       </c>
       <c r="H118">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I118">
         <v>60</v>
       </c>
       <c r="J118" s="1">
-        <v>0.05</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4419,18 +4433,18 @@
         <v>1</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119">
         <v>12</v>
       </c>
       <c r="J119" s="1">
-        <v>0</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4451,18 +4465,18 @@
         <v>81</v>
       </c>
       <c r="H120">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="I120">
         <v>972</v>
       </c>
       <c r="J120" s="1">
-        <v>5.7599999999999998E-2</v>
+        <v>0.12139999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4483,18 +4497,18 @@
         <v>52</v>
       </c>
       <c r="H121">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I121">
         <v>624</v>
       </c>
       <c r="J121" s="1">
-        <v>8.8099999999999998E-2</v>
+        <v>0.10580000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4515,18 +4529,18 @@
         <v>44</v>
       </c>
       <c r="H122">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I122">
         <v>528</v>
       </c>
       <c r="J122" s="1">
-        <v>0.108</v>
+        <v>8.7099999999999997E-2</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4547,18 +4561,18 @@
         <v>11</v>
       </c>
       <c r="H123">
-        <v>298</v>
+        <v>641</v>
       </c>
       <c r="I123">
         <v>4046</v>
       </c>
       <c r="J123" s="1">
-        <v>7.3700000000000002E-2</v>
+        <v>0.15840000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4576,21 +4590,21 @@
         <v>27</v>
       </c>
       <c r="G124">
+        <v>17</v>
+      </c>
+      <c r="H124">
         <v>16</v>
       </c>
-      <c r="H124">
-        <v>4</v>
-      </c>
       <c r="I124">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J124" s="1">
-        <v>6.25E-2</v>
+        <v>0.23530000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4608,21 +4622,21 @@
         <v>44</v>
       </c>
       <c r="G125">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J125" s="1">
-        <v>6.25E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4640,21 +4654,21 @@
         <v>27</v>
       </c>
       <c r="G126">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H126">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I126">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J126" s="1">
-        <v>5.6800000000000003E-2</v>
+        <v>9.4399999999999998E-2</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4672,21 +4686,21 @@
         <v>44</v>
       </c>
       <c r="G127">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H127">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I127">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J127" s="1">
-        <v>2.2700000000000001E-2</v>
+        <v>0.31109999999999999</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4718,7 +4732,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4739,18 +4753,18 @@
         <v>12</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I129">
         <v>24</v>
       </c>
       <c r="J129" s="1">
-        <v>4.1700000000000001E-2</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4768,21 +4782,21 @@
         <v>26</v>
       </c>
       <c r="G130">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="H130">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="I130">
-        <v>2040</v>
+        <v>2256</v>
       </c>
       <c r="J130" s="1">
-        <v>0.14660000000000001</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4803,18 +4817,18 @@
         <v>43</v>
       </c>
       <c r="H131">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I131">
         <v>516</v>
       </c>
       <c r="J131" s="1">
-        <v>7.5600000000000001E-2</v>
+        <v>0.1143</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4832,21 +4846,21 @@
         <v>26</v>
       </c>
       <c r="G132">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H132">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I132">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="J132" s="1">
-        <v>0.1623</v>
+        <v>0.16070000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4867,18 +4881,18 @@
         <v>52</v>
       </c>
       <c r="H133">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="I133">
         <v>624</v>
       </c>
       <c r="J133" s="1">
-        <v>0.1138</v>
+        <v>0.13780000000000001</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4899,7 +4913,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4920,7 +4934,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4941,7 +4955,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4962,18 +4976,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>8.1299999999999997E-2</v>
+        <v>0.1585</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -4994,18 +5008,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>586</v>
+        <v>1171</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>8.3500000000000005E-2</v>
+        <v>0.1668</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5026,18 +5040,18 @@
         <v>383</v>
       </c>
       <c r="H139">
-        <v>762</v>
+        <v>1508</v>
       </c>
       <c r="I139">
         <v>9144</v>
       </c>
       <c r="J139" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16489999999999999</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5058,18 +5072,18 @@
         <v>1</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I140">
         <v>12</v>
       </c>
       <c r="J140" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5090,18 +5104,18 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I141">
         <v>12</v>
       </c>
       <c r="J141" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5122,18 +5136,18 @@
         <v>22</v>
       </c>
       <c r="H142">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="I142">
         <v>264</v>
       </c>
       <c r="J142" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5154,18 +5168,18 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I143">
         <v>12</v>
       </c>
       <c r="J143" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5186,18 +5200,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>909</v>
+        <v>1819</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>8.4400000000000003E-2</v>
+        <v>0.16880000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5218,18 +5232,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>8.4699999999999998E-2</v>
+        <v>0.1673</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5250,18 +5264,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16370000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5282,18 +5296,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5314,18 +5328,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>8.1699999999999995E-2</v>
+        <v>0.1651</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5346,18 +5360,18 @@
         <v>7</v>
       </c>
       <c r="H149">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I149">
         <v>84</v>
       </c>
       <c r="J149" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5378,18 +5392,18 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I150">
         <v>48</v>
       </c>
       <c r="J150" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5421,7 +5435,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5442,18 +5456,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>483</v>
+        <v>924</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.1018</v>
+        <v>0.19470000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5474,18 +5488,18 @@
         <v>29</v>
       </c>
       <c r="H153">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I153">
         <v>112</v>
       </c>
       <c r="J153" s="1">
-        <v>0.16070000000000001</v>
+        <v>0.24110000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5517,7 +5531,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5538,18 +5552,18 @@
         <v>45</v>
       </c>
       <c r="H155">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I155">
         <v>180</v>
       </c>
       <c r="J155" s="1">
-        <v>0.21110000000000001</v>
+        <v>0.23330000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5581,7 +5595,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5602,18 +5616,18 @@
         <v>9</v>
       </c>
       <c r="H157">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I157">
         <v>18</v>
       </c>
       <c r="J157" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.27779999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5645,7 +5659,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5666,18 +5680,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>7.9299999999999995E-2</v>
+        <v>0.16259999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5698,18 +5712,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>7.6399999999999996E-2</v>
+        <v>0.15970000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5730,18 +5744,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1653</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5762,18 +5776,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>8.7900000000000006E-2</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5794,18 +5808,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>774</v>
+        <v>1539</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16569999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5826,18 +5840,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5858,18 +5872,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>594</v>
+        <v>1185</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>8.3900000000000002E-2</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5890,18 +5904,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>969</v>
+        <v>1920</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>8.3799999999999999E-2</v>
+        <v>0.16600000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5922,18 +5936,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1658</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5954,18 +5968,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -5986,18 +6000,18 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I169">
         <v>84</v>
       </c>
       <c r="J169" s="1">
-        <v>3.5700000000000003E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6018,18 +6032,18 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I170">
         <v>12</v>
       </c>
       <c r="J170" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6050,18 +6064,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>8.1799999999999998E-2</v>
+        <v>0.14510000000000001</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6082,18 +6096,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>8.1600000000000006E-2</v>
+        <v>0.16489999999999999</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6114,18 +6128,18 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I173">
         <v>84</v>
       </c>
       <c r="J173" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6146,18 +6160,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>1058</v>
+        <v>1958</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>9.6600000000000005E-2</v>
+        <v>0.17879999999999999</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6178,18 +6192,18 @@
         <v>57</v>
       </c>
       <c r="H175">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I175">
         <v>228</v>
       </c>
       <c r="J175" s="1">
-        <v>6.1400000000000003E-2</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6218,7 +6232,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6239,18 +6253,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>8.1100000000000005E-2</v>
+        <v>0.19589999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6282,7 +6296,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6314,7 +6328,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6346,7 +6360,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6367,18 +6381,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>162</v>
+        <v>322</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>7.9399999999999998E-2</v>
+        <v>0.1578</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6399,18 +6413,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16439999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6431,18 +6445,18 @@
         <v>13</v>
       </c>
       <c r="H183">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I183">
         <v>156</v>
       </c>
       <c r="J183" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6463,18 +6477,18 @@
         <v>9</v>
       </c>
       <c r="H184">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I184">
         <v>108</v>
       </c>
       <c r="J184" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6495,18 +6509,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>8.43E-2</v>
+        <v>0.16950000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6527,7 +6541,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6559,7 +6573,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6580,18 +6594,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6612,18 +6626,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6644,18 +6658,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6676,18 +6690,18 @@
         <v>59</v>
       </c>
       <c r="H191">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I191">
         <v>59</v>
       </c>
       <c r="J191" s="1">
-        <v>0.2034</v>
+        <v>0.30509999999999998</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6719,7 +6733,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6740,18 +6754,18 @@
         <v>9</v>
       </c>
       <c r="H193">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I193">
         <v>36</v>
       </c>
       <c r="J193" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6772,18 +6786,18 @@
         <v>9</v>
       </c>
       <c r="H194">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I194">
         <v>9</v>
       </c>
       <c r="J194" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6803,16 +6817,19 @@
       <c r="G195">
         <v>85</v>
       </c>
+      <c r="H195">
+        <v>19</v>
+      </c>
       <c r="I195">
         <v>85</v>
       </c>
       <c r="J195" s="1">
-        <v>0</v>
+        <v>0.2235</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6833,18 +6850,18 @@
         <v>27</v>
       </c>
       <c r="H196">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I196">
         <v>27</v>
       </c>
       <c r="J196" s="1">
-        <v>0.55559999999999998</v>
+        <v>0.77780000000000005</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6876,7 +6893,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6897,18 +6914,18 @@
         <v>41</v>
       </c>
       <c r="H198">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I198">
         <v>41</v>
       </c>
       <c r="J198" s="1">
-        <v>0.34150000000000003</v>
+        <v>0.78049999999999997</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6940,7 +6957,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6960,16 +6977,19 @@
       <c r="G200">
         <v>9</v>
       </c>
+      <c r="H200">
+        <v>9</v>
+      </c>
       <c r="I200">
         <v>36</v>
       </c>
       <c r="J200" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -6990,18 +7010,18 @@
         <v>45</v>
       </c>
       <c r="H201">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I201">
         <v>45</v>
       </c>
       <c r="J201" s="1">
-        <v>0.1111</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7022,18 +7042,18 @@
         <v>9</v>
       </c>
       <c r="H202">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I202">
         <v>36</v>
       </c>
       <c r="J202" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7065,7 +7085,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7086,18 +7106,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>188993</v>
+        <v>377986</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7118,18 +7138,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>12453</v>
+        <v>42045</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>3.39E-2</v>
+        <v>0.11459999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7150,18 +7170,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>348</v>
+        <v>696</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7182,18 +7202,18 @@
         <v>188993</v>
       </c>
       <c r="H207">
-        <v>69950</v>
+        <v>179681</v>
       </c>
       <c r="I207">
         <v>755972</v>
       </c>
       <c r="J207" s="1">
-        <v>9.2499999999999999E-2</v>
+        <v>0.23769999999999999</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7214,18 +7234,18 @@
         <v>188993</v>
       </c>
       <c r="H208">
-        <v>40025</v>
+        <v>49159</v>
       </c>
       <c r="I208">
         <v>188993</v>
       </c>
       <c r="J208" s="1">
-        <v>0.21179999999999999</v>
+        <v>0.2601</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7246,18 +7266,18 @@
         <v>98</v>
       </c>
       <c r="H209">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="I209">
         <v>392</v>
       </c>
       <c r="J209" s="1">
-        <v>7.6499999999999999E-2</v>
+        <v>0.19639999999999999</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7278,18 +7298,18 @@
         <v>127</v>
       </c>
       <c r="H210">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I210">
         <v>127</v>
       </c>
       <c r="J210" s="1">
-        <v>0.20469999999999999</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7310,18 +7330,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>3.5099999999999999E-2</v>
+        <v>0.12920000000000001</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7342,18 +7362,18 @@
         <v>133</v>
       </c>
       <c r="H212">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="I212">
         <v>133</v>
       </c>
       <c r="J212" s="1">
-        <v>0.15790000000000001</v>
+        <v>0.3609</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7374,18 +7394,18 @@
         <v>67</v>
       </c>
       <c r="H213">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I213">
         <v>67</v>
       </c>
       <c r="J213" s="1">
-        <v>0.17910000000000001</v>
+        <v>0.28360000000000002</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7406,18 +7426,18 @@
         <v>5482</v>
       </c>
       <c r="H214">
-        <v>370</v>
+        <v>3114</v>
       </c>
       <c r="I214">
         <v>10964</v>
       </c>
       <c r="J214" s="1">
-        <v>3.3700000000000001E-2</v>
+        <v>0.28399999999999997</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7438,7 +7458,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7459,18 +7479,18 @@
         <v>263</v>
       </c>
       <c r="H216">
-        <v>528</v>
+        <v>1052</v>
       </c>
       <c r="I216">
         <v>6312</v>
       </c>
       <c r="J216" s="1">
-        <v>8.3699999999999997E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7491,18 +7511,18 @@
         <v>40</v>
       </c>
       <c r="H217">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I217">
         <v>480</v>
       </c>
       <c r="J217" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7523,18 +7543,18 @@
         <v>408</v>
       </c>
       <c r="H218">
-        <v>390</v>
+        <v>818</v>
       </c>
       <c r="I218">
         <v>4896</v>
       </c>
       <c r="J218" s="1">
-        <v>7.9699999999999993E-2</v>
+        <v>0.1671</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7555,18 +7575,18 @@
         <v>550</v>
       </c>
       <c r="H219">
-        <v>552</v>
+        <v>1055</v>
       </c>
       <c r="I219">
         <v>6600</v>
       </c>
       <c r="J219" s="1">
-        <v>8.3599999999999994E-2</v>
+        <v>0.1598</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7587,18 +7607,18 @@
         <v>76</v>
       </c>
       <c r="H220">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="I220">
         <v>912</v>
       </c>
       <c r="J220" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16339999999999999</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7619,18 +7639,18 @@
         <v>6</v>
       </c>
       <c r="H221">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I221">
         <v>144</v>
       </c>
       <c r="J221" s="1">
-        <v>6.25E-2</v>
+        <v>0.15970000000000001</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7651,18 +7671,18 @@
         <v>19</v>
       </c>
       <c r="H222">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I222">
         <v>228</v>
       </c>
       <c r="J222" s="1">
-        <v>7.0199999999999999E-2</v>
+        <v>0.1623</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7694,7 +7714,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7715,18 +7735,18 @@
         <v>4</v>
       </c>
       <c r="H224">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I224">
         <v>48</v>
       </c>
       <c r="J224" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7747,18 +7767,18 @@
         <v>31</v>
       </c>
       <c r="H225">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="I225">
         <v>372</v>
       </c>
       <c r="J225" s="1">
-        <v>7.5300000000000006E-2</v>
+        <v>0.16400000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7779,18 +7799,18 @@
         <v>175</v>
       </c>
       <c r="H226">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="I226">
         <v>2100</v>
       </c>
       <c r="J226" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7811,18 +7831,18 @@
         <v>9</v>
       </c>
       <c r="H227">
-        <v>487</v>
+        <v>893</v>
       </c>
       <c r="I227">
         <v>3285</v>
       </c>
       <c r="J227" s="1">
-        <v>0.1482</v>
+        <v>0.27179999999999999</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7843,18 +7863,18 @@
         <v>9</v>
       </c>
       <c r="H228">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I228">
         <v>36</v>
       </c>
       <c r="J228" s="1">
-        <v>2.7799999999999998E-2</v>
+        <v>0.27779999999999999</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7874,16 +7894,19 @@
       <c r="G229">
         <v>9</v>
       </c>
+      <c r="H229">
+        <v>4</v>
+      </c>
       <c r="I229">
         <v>9</v>
       </c>
       <c r="J229" s="1">
-        <v>0</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7904,18 +7927,18 @@
         <v>34</v>
       </c>
       <c r="H230">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I230">
         <v>132</v>
       </c>
       <c r="J230" s="1">
-        <v>6.8199999999999997E-2</v>
+        <v>0.31059999999999999</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7944,7 +7967,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7976,7 +7999,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -7997,18 +8020,18 @@
         <v>3654</v>
       </c>
       <c r="H233">
-        <v>2898</v>
+        <v>6870</v>
       </c>
       <c r="I233">
         <v>43848</v>
       </c>
       <c r="J233" s="1">
-        <v>6.6100000000000006E-2</v>
+        <v>0.15670000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8029,7 +8052,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8050,7 +8073,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8071,7 +8094,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8092,7 +8115,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8113,7 +8136,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8134,7 +8157,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8163,7 +8186,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8184,18 +8207,18 @@
         <v>486</v>
       </c>
       <c r="H241">
-        <v>972</v>
+        <v>1949</v>
       </c>
       <c r="I241">
         <v>11664</v>
       </c>
       <c r="J241" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1671</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8216,18 +8239,18 @@
         <v>25</v>
       </c>
       <c r="H242">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="I242">
         <v>300</v>
       </c>
       <c r="J242" s="1">
-        <v>0.1133</v>
+        <v>0.19670000000000001</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8248,18 +8271,18 @@
         <v>68</v>
       </c>
       <c r="H243">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="I243">
         <v>816</v>
       </c>
       <c r="J243" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8280,18 +8303,18 @@
         <v>729</v>
       </c>
       <c r="H244">
-        <v>731</v>
+        <v>1463</v>
       </c>
       <c r="I244">
         <v>8772</v>
       </c>
       <c r="J244" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1668</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8312,18 +8335,18 @@
         <v>854</v>
       </c>
       <c r="H245">
-        <v>922</v>
+        <v>1842</v>
       </c>
       <c r="I245">
         <v>11040</v>
       </c>
       <c r="J245" s="1">
-        <v>8.3500000000000005E-2</v>
+        <v>0.1668</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8344,18 +8367,18 @@
         <v>121</v>
       </c>
       <c r="H246">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="I246">
         <v>1452</v>
       </c>
       <c r="J246" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8376,18 +8399,18 @@
         <v>27</v>
       </c>
       <c r="H247">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="I247">
         <v>648</v>
       </c>
       <c r="J247" s="1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.1744</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8408,7 +8431,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8429,18 +8452,18 @@
         <v>2</v>
       </c>
       <c r="H249">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I249">
         <v>24</v>
       </c>
       <c r="J249" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8461,18 +8484,18 @@
         <v>30</v>
       </c>
       <c r="H250">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I250">
         <v>360</v>
       </c>
       <c r="J250" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8493,18 +8516,18 @@
         <v>51</v>
       </c>
       <c r="H251">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="I251">
         <v>624</v>
       </c>
       <c r="J251" s="1">
-        <v>8.4900000000000003E-2</v>
+        <v>0.17150000000000001</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8525,18 +8548,18 @@
         <v>337</v>
       </c>
       <c r="H252">
-        <v>338</v>
+        <v>677</v>
       </c>
       <c r="I252">
         <v>4044</v>
       </c>
       <c r="J252" s="1">
-        <v>8.3599999999999994E-2</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8557,18 +8580,18 @@
         <v>50</v>
       </c>
       <c r="H253">
-        <v>1859</v>
+        <v>3516</v>
       </c>
       <c r="I253">
         <v>18972</v>
       </c>
       <c r="J253" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.18529999999999999</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8589,18 +8612,18 @@
         <v>58</v>
       </c>
       <c r="H254">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I254">
         <v>232</v>
       </c>
       <c r="J254" s="1">
-        <v>0.1293</v>
+        <v>0.1767</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8632,7 +8655,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8653,18 +8676,18 @@
         <v>56</v>
       </c>
       <c r="H256">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I256">
         <v>228</v>
       </c>
       <c r="J256" s="1">
-        <v>4.3900000000000002E-2</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8696,7 +8719,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8717,18 +8740,18 @@
         <v>4610</v>
       </c>
       <c r="H258">
-        <v>4796</v>
+        <v>9590</v>
       </c>
       <c r="I258">
         <v>55320</v>
       </c>
       <c r="J258" s="1">
-        <v>8.6699999999999999E-2</v>
+        <v>0.1734</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8749,18 +8772,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I259">
         <v>468</v>
       </c>
       <c r="J259" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8781,18 +8804,18 @@
         <v>44</v>
       </c>
       <c r="H260">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I260">
         <v>78</v>
       </c>
       <c r="J260" s="1">
-        <v>1.2800000000000001E-2</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8813,18 +8836,18 @@
         <v>90</v>
       </c>
       <c r="H261">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I261">
         <v>1080</v>
       </c>
       <c r="J261" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8845,18 +8868,18 @@
         <v>27</v>
       </c>
       <c r="H262">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I262">
         <v>192</v>
       </c>
       <c r="J262" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8877,18 +8900,18 @@
         <v>121</v>
       </c>
       <c r="H263">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="I263">
         <v>1428</v>
       </c>
       <c r="J263" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8909,18 +8932,18 @@
         <v>12</v>
       </c>
       <c r="H264">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I264">
         <v>24</v>
       </c>
       <c r="J264" s="1">
-        <v>4.1700000000000001E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8941,18 +8964,18 @@
         <v>351</v>
       </c>
       <c r="H265">
-        <v>366</v>
+        <v>712</v>
       </c>
       <c r="I265">
         <v>4291</v>
       </c>
       <c r="J265" s="1">
-        <v>8.5300000000000001E-2</v>
+        <v>0.16589999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8970,7 +8993,7 @@
         <v>26</v>
       </c>
       <c r="G266">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H266">
         <v>35</v>
@@ -8984,7 +9007,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9005,18 +9028,18 @@
         <v>232</v>
       </c>
       <c r="H267">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="I267">
         <v>2784</v>
       </c>
       <c r="J267" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9037,18 +9060,18 @@
         <v>66</v>
       </c>
       <c r="H268">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="I268">
         <v>792</v>
       </c>
       <c r="J268" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9069,18 +9092,18 @@
         <v>84</v>
       </c>
       <c r="H269">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="I269">
         <v>1008</v>
       </c>
       <c r="J269" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9101,7 +9124,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9122,18 +9145,18 @@
         <v>33</v>
       </c>
       <c r="H271">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I271">
         <v>384</v>
       </c>
       <c r="J271" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9154,18 +9177,18 @@
         <v>3</v>
       </c>
       <c r="H272">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I272">
         <v>36</v>
       </c>
       <c r="J272" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9186,7 +9209,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9207,7 +9230,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9228,18 +9251,18 @@
         <v>51</v>
       </c>
       <c r="H275">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="I275">
         <v>276</v>
       </c>
       <c r="J275" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9260,18 +9283,18 @@
         <v>445</v>
       </c>
       <c r="H276">
-        <v>445</v>
+        <v>890</v>
       </c>
       <c r="I276">
         <v>5340</v>
       </c>
       <c r="J276" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9292,18 +9315,18 @@
         <v>17</v>
       </c>
       <c r="H277">
-        <v>465</v>
+        <v>860</v>
       </c>
       <c r="I277">
         <v>5110</v>
       </c>
       <c r="J277" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.16830000000000001</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9335,7 +9358,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9356,18 +9379,18 @@
         <v>11</v>
       </c>
       <c r="H279">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I279">
         <v>11</v>
       </c>
       <c r="J279" s="1">
-        <v>9.0899999999999995E-2</v>
+        <v>0.45450000000000002</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9388,18 +9411,18 @@
         <v>34</v>
       </c>
       <c r="H280">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I280">
         <v>136</v>
       </c>
       <c r="J280" s="1">
-        <v>0.18379999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9431,7 +9454,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9452,18 +9475,18 @@
         <v>6</v>
       </c>
       <c r="H282">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I282">
         <v>12</v>
       </c>
       <c r="J282" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9495,7 +9518,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9527,7 +9550,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9548,18 +9571,18 @@
         <v>33</v>
       </c>
       <c r="H285">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I285">
         <v>396</v>
       </c>
       <c r="J285" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9580,18 +9603,18 @@
         <v>23</v>
       </c>
       <c r="H286">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I286">
         <v>276</v>
       </c>
       <c r="J286" s="1">
-        <v>7.9699999999999993E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9612,18 +9635,18 @@
         <v>79</v>
       </c>
       <c r="H287">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="I287">
         <v>948</v>
       </c>
       <c r="J287" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9644,7 +9667,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9665,18 +9688,18 @@
         <v>21</v>
       </c>
       <c r="H289">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="I289">
         <v>264</v>
       </c>
       <c r="J289" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9694,21 +9717,21 @@
         <v>28</v>
       </c>
       <c r="G290">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H290">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I290">
         <v>44</v>
       </c>
       <c r="J290" s="1">
-        <v>0.15909999999999999</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9729,18 +9752,18 @@
         <v>82</v>
       </c>
       <c r="H291">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="I291">
         <v>1968</v>
       </c>
       <c r="J291" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9761,18 +9784,18 @@
         <v>173</v>
       </c>
       <c r="H292">
-        <v>344</v>
+        <v>688</v>
       </c>
       <c r="I292">
         <v>4128</v>
       </c>
       <c r="J292" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9793,18 +9816,18 @@
         <v>74</v>
       </c>
       <c r="H293">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="I293">
         <v>888</v>
       </c>
       <c r="J293" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9825,18 +9848,18 @@
         <v>110</v>
       </c>
       <c r="H294">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="I294">
         <v>1320</v>
       </c>
       <c r="J294" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16289999999999999</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9857,18 +9880,18 @@
         <v>160</v>
       </c>
       <c r="H295">
-        <v>160</v>
+        <v>319</v>
       </c>
       <c r="I295">
         <v>1920</v>
       </c>
       <c r="J295" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1661</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9889,18 +9912,18 @@
         <v>311</v>
       </c>
       <c r="H296">
-        <v>311</v>
+        <v>615</v>
       </c>
       <c r="I296">
         <v>3732</v>
       </c>
       <c r="J296" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9921,18 +9944,18 @@
         <v>286</v>
       </c>
       <c r="H297">
-        <v>286</v>
+        <v>572</v>
       </c>
       <c r="I297">
         <v>3432</v>
       </c>
       <c r="J297" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9953,18 +9976,18 @@
         <v>12</v>
       </c>
       <c r="H298">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I298">
         <v>144</v>
       </c>
       <c r="J298" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -9985,18 +10008,18 @@
         <v>85</v>
       </c>
       <c r="H299">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="I299">
         <v>1020</v>
       </c>
       <c r="J299" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1676</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10017,18 +10040,18 @@
         <v>44</v>
       </c>
       <c r="H300">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I300">
         <v>528</v>
       </c>
       <c r="J300" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10049,18 +10072,18 @@
         <v>47</v>
       </c>
       <c r="H301">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="I301">
         <v>564</v>
       </c>
       <c r="J301" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10081,18 +10104,18 @@
         <v>91</v>
       </c>
       <c r="H302">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="I302">
         <v>1092</v>
       </c>
       <c r="J302" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10113,18 +10136,18 @@
         <v>13</v>
       </c>
       <c r="H303">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I303">
         <v>384</v>
       </c>
       <c r="J303" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10145,7 +10168,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10166,7 +10189,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10187,18 +10210,18 @@
         <v>17</v>
       </c>
       <c r="H306">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I306">
         <v>204</v>
       </c>
       <c r="J306" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10219,18 +10242,18 @@
         <v>48</v>
       </c>
       <c r="H307">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="I307">
         <v>564</v>
       </c>
       <c r="J307" s="1">
-        <v>8.5099999999999995E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10251,18 +10274,18 @@
         <v>227</v>
       </c>
       <c r="H308">
-        <v>227</v>
+        <v>449</v>
       </c>
       <c r="I308">
         <v>2724</v>
       </c>
       <c r="J308" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10283,18 +10306,18 @@
         <v>16</v>
       </c>
       <c r="H309">
-        <v>344</v>
+        <v>945</v>
       </c>
       <c r="I309">
         <v>5842</v>
       </c>
       <c r="J309" s="1">
-        <v>5.8900000000000001E-2</v>
+        <v>0.1618</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10315,18 +10338,18 @@
         <v>39</v>
       </c>
       <c r="H310">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I310">
         <v>156</v>
       </c>
       <c r="J310" s="1">
-        <v>0.1026</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10347,18 +10370,18 @@
         <v>39</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I311">
         <v>39</v>
       </c>
       <c r="J311" s="1">
-        <v>0</v>
+        <v>0.25640000000000002</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10379,18 +10402,18 @@
         <v>44</v>
       </c>
       <c r="H312">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I312">
         <v>180</v>
       </c>
       <c r="J312" s="1">
-        <v>0.1278</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10411,18 +10434,18 @@
         <v>44</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I313">
         <v>45</v>
       </c>
       <c r="J313" s="1">
-        <v>0</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10443,18 +10466,18 @@
         <v>2</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I314">
         <v>4</v>
       </c>
       <c r="J314" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10486,7 +10509,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10518,7 +10541,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10539,18 +10562,18 @@
         <v>228</v>
       </c>
       <c r="H317">
-        <v>228</v>
+        <v>462</v>
       </c>
       <c r="I317">
         <v>2736</v>
       </c>
       <c r="J317" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16889999999999999</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10571,18 +10594,18 @@
         <v>22</v>
       </c>
       <c r="H318">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I318">
         <v>300</v>
       </c>
       <c r="J318" s="1">
-        <v>7.3300000000000004E-2</v>
+        <v>0.15329999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10603,18 +10626,18 @@
         <v>184</v>
       </c>
       <c r="H319">
-        <v>184</v>
+        <v>365</v>
       </c>
       <c r="I319">
         <v>2196</v>
       </c>
       <c r="J319" s="1">
-        <v>8.3799999999999999E-2</v>
+        <v>0.16619999999999999</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10635,18 +10658,18 @@
         <v>3</v>
       </c>
       <c r="H320">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I320">
         <v>36</v>
       </c>
       <c r="J320" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10667,7 +10690,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10688,7 +10711,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10706,7 +10729,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10727,18 +10750,18 @@
         <v>96</v>
       </c>
       <c r="H324">
-        <v>192</v>
+        <v>384</v>
       </c>
       <c r="I324">
         <v>2304</v>
       </c>
       <c r="J324" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10759,18 +10782,18 @@
         <v>17</v>
       </c>
       <c r="H325">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I325">
         <v>204</v>
       </c>
       <c r="J325" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10791,18 +10814,18 @@
         <v>109</v>
       </c>
       <c r="H326">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="I326">
         <v>1308</v>
       </c>
       <c r="J326" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10823,18 +10846,18 @@
         <v>8</v>
       </c>
       <c r="H327">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I327">
         <v>96</v>
       </c>
       <c r="J327" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10855,18 +10878,18 @@
         <v>34</v>
       </c>
       <c r="H328">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I328">
         <v>408</v>
       </c>
       <c r="J328" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10887,18 +10910,18 @@
         <v>5</v>
       </c>
       <c r="H329">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I329">
         <v>120</v>
       </c>
       <c r="J329" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10919,18 +10942,18 @@
         <v>17</v>
       </c>
       <c r="H330">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I330">
         <v>204</v>
       </c>
       <c r="J330" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10951,18 +10974,18 @@
         <v>7</v>
       </c>
       <c r="H331">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I331">
         <v>84</v>
       </c>
       <c r="J331" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -10983,18 +11006,18 @@
         <v>200</v>
       </c>
       <c r="H332">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I332">
         <v>2400</v>
       </c>
       <c r="J332" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11015,18 +11038,18 @@
         <v>14</v>
       </c>
       <c r="H333">
-        <v>434</v>
+        <v>826</v>
       </c>
       <c r="I333">
         <v>5110</v>
       </c>
       <c r="J333" s="1">
-        <v>8.4900000000000003E-2</v>
+        <v>0.16159999999999999</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11058,7 +11081,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11090,7 +11113,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11122,7 +11145,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11154,7 +11177,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11175,18 +11198,18 @@
         <v>10</v>
       </c>
       <c r="H338">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I338">
         <v>120</v>
       </c>
       <c r="J338" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11218,7 +11241,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11239,7 +11262,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11260,7 +11283,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11281,7 +11304,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11302,18 +11325,18 @@
         <v>392</v>
       </c>
       <c r="H343">
-        <v>784</v>
+        <v>1568</v>
       </c>
       <c r="I343">
         <v>9250</v>
       </c>
       <c r="J343" s="1">
-        <v>8.48E-2</v>
+        <v>0.16950000000000001</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11334,18 +11357,18 @@
         <v>39</v>
       </c>
       <c r="H344">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I344">
         <v>468</v>
       </c>
       <c r="J344" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11366,18 +11389,18 @@
         <v>778</v>
       </c>
       <c r="H345">
-        <v>767</v>
+        <v>1556</v>
       </c>
       <c r="I345">
         <v>9201</v>
       </c>
       <c r="J345" s="1">
-        <v>8.3400000000000002E-2</v>
+        <v>0.1691</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11398,18 +11421,18 @@
         <v>16</v>
       </c>
       <c r="H346">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I346">
         <v>192</v>
       </c>
       <c r="J346" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11430,18 +11453,18 @@
         <v>26</v>
       </c>
       <c r="H347">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I347">
         <v>312</v>
       </c>
       <c r="J347" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1699</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11462,18 +11485,18 @@
         <v>24</v>
       </c>
       <c r="H348">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="I348">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="J348" s="1">
-        <v>8.0500000000000002E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11494,18 +11517,18 @@
         <v>7</v>
       </c>
       <c r="H349">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I349">
         <v>40</v>
       </c>
       <c r="J349" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11526,18 +11549,18 @@
         <v>9</v>
       </c>
       <c r="H350">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I350">
         <v>108</v>
       </c>
       <c r="J350" s="1">
-        <v>6.4799999999999996E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11558,18 +11581,18 @@
         <v>925</v>
       </c>
       <c r="H351">
-        <v>910</v>
+        <v>1850</v>
       </c>
       <c r="I351">
         <v>10766</v>
       </c>
       <c r="J351" s="1">
-        <v>8.4500000000000006E-2</v>
+        <v>0.17180000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11590,18 +11613,18 @@
         <v>45</v>
       </c>
       <c r="H352">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="I352">
         <v>540</v>
       </c>
       <c r="J352" s="1">
-        <v>8.1500000000000003E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11622,18 +11645,18 @@
         <v>35</v>
       </c>
       <c r="H353">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I353">
         <v>420</v>
       </c>
       <c r="J353" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11654,18 +11677,18 @@
         <v>145</v>
       </c>
       <c r="H354">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="I354">
         <v>1740</v>
       </c>
       <c r="J354" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11683,21 +11706,21 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H355">
-        <v>2934</v>
+        <v>5518</v>
       </c>
       <c r="I355">
-        <v>36865</v>
+        <v>38161</v>
       </c>
       <c r="J355" s="1">
-        <v>7.9600000000000004E-2</v>
+        <v>0.14460000000000001</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11718,18 +11741,18 @@
         <v>88</v>
       </c>
       <c r="H356">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I356">
         <v>352</v>
       </c>
       <c r="J356" s="1">
-        <v>9.0899999999999995E-2</v>
+        <v>0.11360000000000001</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11750,18 +11773,18 @@
         <v>88</v>
       </c>
       <c r="H357">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I357">
         <v>88</v>
       </c>
       <c r="J357" s="1">
-        <v>0.36359999999999998</v>
+        <v>0.45450000000000002</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11782,18 +11805,18 @@
         <v>33</v>
       </c>
       <c r="H358">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I358">
         <v>132</v>
       </c>
       <c r="J358" s="1">
-        <v>0.1061</v>
+        <v>0.21970000000000001</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11814,18 +11837,18 @@
         <v>33</v>
       </c>
       <c r="H359">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I359">
         <v>33</v>
       </c>
       <c r="J359" s="1">
-        <v>0.18179999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11857,7 +11880,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11878,18 +11901,18 @@
         <v>10</v>
       </c>
       <c r="H361">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I361">
         <v>20</v>
       </c>
       <c r="J361" s="1">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11907,21 +11930,21 @@
         <v>26</v>
       </c>
       <c r="G362">
-        <v>3296</v>
+        <v>3536</v>
       </c>
       <c r="H362">
-        <v>3296</v>
+        <v>7072</v>
       </c>
       <c r="I362">
-        <v>39552</v>
+        <v>42432</v>
       </c>
       <c r="J362" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11942,18 +11965,18 @@
         <v>33</v>
       </c>
       <c r="H363">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I363">
         <v>396</v>
       </c>
       <c r="J363" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11974,18 +11997,18 @@
         <v>11</v>
       </c>
       <c r="H364">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I364">
         <v>132</v>
       </c>
       <c r="J364" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12006,18 +12029,18 @@
         <v>24</v>
       </c>
       <c r="H365">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I365">
         <v>288</v>
       </c>
       <c r="J365" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12038,18 +12061,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12067,21 +12090,21 @@
         <v>26</v>
       </c>
       <c r="G367">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H367">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I367">
         <v>64</v>
       </c>
       <c r="J367" s="1">
-        <v>4.6899999999999997E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12096,7 +12119,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12114,21 +12137,21 @@
         <v>25</v>
       </c>
       <c r="G369">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H369">
-        <v>556</v>
+        <v>688</v>
       </c>
       <c r="I369">
-        <v>6672</v>
+        <v>6696</v>
       </c>
       <c r="J369" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12149,18 +12172,18 @@
         <v>129</v>
       </c>
       <c r="H370">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="I370">
         <v>1548</v>
       </c>
       <c r="J370" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.10340000000000001</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12178,21 +12201,21 @@
         <v>26</v>
       </c>
       <c r="G371">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="H371">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="I371">
-        <v>6636</v>
+        <v>6396</v>
       </c>
       <c r="J371" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12213,18 +12236,18 @@
         <v>315</v>
       </c>
       <c r="H372">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="I372">
-        <v>3780</v>
+        <v>3786</v>
       </c>
       <c r="J372" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12245,18 +12268,18 @@
         <v>20</v>
       </c>
       <c r="H373">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I373">
         <v>240</v>
       </c>
       <c r="J373" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>9.1700000000000004E-2</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12277,18 +12300,18 @@
         <v>19</v>
       </c>
       <c r="H374">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I374">
         <v>228</v>
       </c>
       <c r="J374" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1009</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12306,21 +12329,21 @@
         <v>25</v>
       </c>
       <c r="G375">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H375">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I375">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J375" s="1">
-        <v>7.9200000000000007E-2</v>
+        <v>9.5200000000000007E-2</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12341,18 +12364,18 @@
         <v>86</v>
       </c>
       <c r="H376">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I376">
         <v>1032</v>
       </c>
       <c r="J376" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>9.11E-2</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12373,7 +12396,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12405,7 +12428,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12426,18 +12449,18 @@
         <v>32</v>
       </c>
       <c r="H379">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I379">
         <v>384</v>
       </c>
       <c r="J379" s="1">
-        <v>8.0699999999999994E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12455,21 +12478,21 @@
         <v>26</v>
       </c>
       <c r="G380">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="H380">
-        <v>604</v>
+        <v>699</v>
       </c>
       <c r="I380">
-        <v>7380</v>
+        <v>7212</v>
       </c>
       <c r="J380" s="1">
-        <v>8.1799999999999998E-2</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12487,21 +12510,21 @@
         <v>43</v>
       </c>
       <c r="G381">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H381">
-        <v>1597</v>
+        <v>1653</v>
       </c>
       <c r="I381">
         <v>17695</v>
       </c>
       <c r="J381" s="1">
-        <v>9.0300000000000005E-2</v>
+        <v>9.3399999999999997E-2</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12522,18 +12545,18 @@
         <v>175</v>
       </c>
       <c r="H382">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I382">
         <v>700</v>
       </c>
       <c r="J382" s="1">
-        <v>0.18709999999999999</v>
+        <v>0.19289999999999999</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12554,18 +12577,18 @@
         <v>175</v>
       </c>
       <c r="H383">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I383">
         <v>175</v>
       </c>
       <c r="J383" s="1">
-        <v>0.74860000000000004</v>
+        <v>0.77139999999999997</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12586,18 +12609,18 @@
         <v>48</v>
       </c>
       <c r="H384">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I384">
         <v>192</v>
       </c>
       <c r="J384" s="1">
-        <v>0.25</v>
+        <v>0.25519999999999998</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12618,18 +12641,18 @@
         <v>48</v>
       </c>
       <c r="H385">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I385">
         <v>48</v>
       </c>
       <c r="J385" s="1">
-        <v>0.85419999999999996</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12650,7 +12673,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12671,18 +12694,18 @@
         <v>13</v>
       </c>
       <c r="H387">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I387">
         <v>26</v>
       </c>
       <c r="J387" s="1">
-        <v>0.26919999999999999</v>
+        <v>0.30769999999999997</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12703,18 +12726,18 @@
         <v>50</v>
       </c>
       <c r="H388">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I388">
         <v>600</v>
       </c>
       <c r="J388" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12735,18 +12758,18 @@
         <v>48</v>
       </c>
       <c r="H389">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I389">
         <v>576</v>
       </c>
       <c r="J389" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>9.5500000000000002E-2</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12767,18 +12790,18 @@
         <v>17</v>
       </c>
       <c r="H390">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I390">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J390" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>9.2600000000000002E-2</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12810,7 +12833,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>
@@ -12831,18 +12854,18 @@
         <v>62</v>
       </c>
       <c r="H392">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I392">
         <v>744</v>
       </c>
       <c r="J392" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A393" s="3">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B393" s="2">
         <v>2026</v>
@@ -12860,16 +12883,16 @@
         <v>28</v>
       </c>
       <c r="G393">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H393">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I393">
-        <v>348</v>
+        <v>744</v>
       </c>
       <c r="J393" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>2.1499999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\2. Feb\KP\✓ Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3583CD-12D7-439D-A29E-9060A85D0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC55627-9B3D-4BB7-9E67-9381B9E7D16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\✓ Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113C4718-5338-41FB-9940-0470BBE29917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C310E031-6058-46D4-8F62-4C6E8A2E7466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\2. Feb\KP\✓ Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\1. Jan\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EC911E-EB1E-4281-89D0-E9FE22AEABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085112EB-D43B-4AB1-809D-1C5DE0FD7057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -787,7 +787,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -808,18 +808,18 @@
         <v>866</v>
       </c>
       <c r="H2">
-        <v>3430</v>
+        <v>1715</v>
       </c>
       <c r="I2">
         <v>20580</v>
       </c>
       <c r="J2" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -840,18 +840,18 @@
         <v>278</v>
       </c>
       <c r="H3">
-        <v>506</v>
+        <v>258</v>
       </c>
       <c r="I3">
         <v>3024</v>
       </c>
       <c r="J3" s="1">
-        <v>0.1673</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -872,18 +872,18 @@
         <v>1610</v>
       </c>
       <c r="H4">
-        <v>3234</v>
+        <v>1609</v>
       </c>
       <c r="I4">
         <v>19416</v>
       </c>
       <c r="J4" s="1">
-        <v>0.1666</v>
+        <v>8.2900000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -904,18 +904,18 @@
         <v>2269</v>
       </c>
       <c r="H5">
-        <v>4566</v>
+        <v>2278</v>
       </c>
       <c r="I5">
-        <v>27456</v>
+        <v>27444</v>
       </c>
       <c r="J5" s="1">
-        <v>0.1663</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -936,18 +936,18 @@
         <v>116</v>
       </c>
       <c r="H6">
-        <v>234</v>
+        <v>115</v>
       </c>
       <c r="I6">
         <v>1404</v>
       </c>
       <c r="J6" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -968,18 +968,18 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>556</v>
       </c>
       <c r="J7" s="1">
-        <v>0.16550000000000001</v>
+        <v>8.2699999999999996E-2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -1000,18 +1000,18 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>48</v>
       </c>
       <c r="J8" s="1">
-        <v>0.1875</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1032,18 +1032,18 @@
         <v>78</v>
       </c>
       <c r="H9">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I9">
         <v>950</v>
       </c>
       <c r="J9" s="1">
-        <v>0.1663</v>
+        <v>8.3199999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1064,18 +1064,18 @@
         <v>290</v>
       </c>
       <c r="H10">
-        <v>592</v>
+        <v>296</v>
       </c>
       <c r="I10">
         <v>3552</v>
       </c>
       <c r="J10" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1096,18 +1096,18 @@
         <v>212</v>
       </c>
       <c r="H11">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="I11">
         <v>2508</v>
       </c>
       <c r="J11" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.4099999999999994E-2</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1128,18 +1128,18 @@
         <v>52</v>
       </c>
       <c r="H12">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="I12">
         <v>624</v>
       </c>
       <c r="J12" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1160,18 +1160,18 @@
         <v>58</v>
       </c>
       <c r="H13">
-        <v>4641</v>
+        <v>2458</v>
       </c>
       <c r="I13">
         <v>25564</v>
       </c>
       <c r="J13" s="1">
-        <v>0.18149999999999999</v>
+        <v>9.6199999999999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1192,18 +1192,18 @@
         <v>55</v>
       </c>
       <c r="H14">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I14">
         <v>228</v>
       </c>
       <c r="J14" s="1">
-        <v>0.1711</v>
+        <v>7.46E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1224,18 +1224,18 @@
         <v>55</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>57</v>
       </c>
       <c r="J15" s="1">
-        <v>0.1754</v>
+        <v>8.77E-2</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1256,18 +1256,18 @@
         <v>133</v>
       </c>
       <c r="H16">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="I16">
         <v>548</v>
       </c>
       <c r="J16" s="1">
-        <v>0.20799999999999999</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1320,18 +1320,18 @@
         <v>43</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>90</v>
       </c>
       <c r="J18" s="1">
-        <v>0.1444</v>
+        <v>8.8900000000000007E-2</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1352,18 +1352,18 @@
         <v>621</v>
       </c>
       <c r="H19">
-        <v>20841</v>
+        <v>9707</v>
       </c>
       <c r="I19">
         <v>117348</v>
       </c>
       <c r="J19" s="1">
-        <v>0.17760000000000001</v>
+        <v>8.2699999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1384,18 +1384,18 @@
         <v>98</v>
       </c>
       <c r="H20">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="I20">
         <v>1584</v>
       </c>
       <c r="J20" s="1">
-        <v>0.1673</v>
+        <v>8.7800000000000003E-2</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1416,18 +1416,18 @@
         <v>43</v>
       </c>
       <c r="H21">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="I21">
         <v>516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.1686</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1448,18 +1448,18 @@
         <v>116</v>
       </c>
       <c r="H22">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="I22">
         <v>1416</v>
       </c>
       <c r="J22" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1543,7 +1543,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1564,18 +1564,18 @@
         <v>59</v>
       </c>
       <c r="H27">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="I27">
         <v>1416</v>
       </c>
       <c r="J27" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1596,18 +1596,18 @@
         <v>47</v>
       </c>
       <c r="H28">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="I28">
         <v>564</v>
       </c>
       <c r="J28" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1628,18 +1628,18 @@
         <v>59</v>
       </c>
       <c r="H29">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I29">
         <v>708</v>
       </c>
       <c r="J29" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1660,18 +1660,18 @@
         <v>398</v>
       </c>
       <c r="H30">
-        <v>774</v>
+        <v>394</v>
       </c>
       <c r="I30">
         <v>4776</v>
       </c>
       <c r="J30" s="1">
-        <v>0.16209999999999999</v>
+        <v>8.2500000000000004E-2</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1692,18 +1692,18 @@
         <v>398</v>
       </c>
       <c r="H31">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="I31">
         <v>398</v>
       </c>
       <c r="J31" s="1">
-        <v>0.2286</v>
+        <v>0.1457</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1724,18 +1724,18 @@
         <v>64</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I32">
         <v>128</v>
       </c>
       <c r="J32" s="1">
-        <v>0.25779999999999997</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1756,18 +1756,18 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I33">
         <v>244</v>
       </c>
       <c r="J33" s="1">
-        <v>0.18029999999999999</v>
+        <v>6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1788,18 +1788,18 @@
         <v>59</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>59</v>
       </c>
       <c r="J34" s="1">
-        <v>0.40679999999999999</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1820,18 +1820,18 @@
         <v>163</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I35">
         <v>163</v>
       </c>
       <c r="J35" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>7.3599999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1852,18 +1852,18 @@
         <v>265</v>
       </c>
       <c r="H36">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I36">
         <v>265</v>
       </c>
       <c r="J36" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>4.1500000000000002E-2</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1884,18 +1884,18 @@
         <v>72</v>
       </c>
       <c r="H37">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>72</v>
       </c>
       <c r="J37" s="1">
-        <v>0.15279999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1916,18 +1916,18 @@
         <v>290</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I38">
         <v>290</v>
       </c>
       <c r="J38" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1977,18 +1977,18 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I40">
         <v>60</v>
       </c>
       <c r="J40" s="1">
-        <v>0.2</v>
+        <v>6.6699999999999995E-2</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2009,18 +2009,18 @@
         <v>395</v>
       </c>
       <c r="H41">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I41">
         <v>395</v>
       </c>
       <c r="J41" s="1">
-        <v>0.33160000000000001</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2041,18 +2041,18 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="I42">
         <v>400</v>
       </c>
       <c r="J42" s="1">
-        <v>0.125</v>
+        <v>4.2500000000000003E-2</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2073,18 +2073,18 @@
         <v>244</v>
       </c>
       <c r="H43">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I43">
         <v>244</v>
       </c>
       <c r="J43" s="1">
-        <v>0.23769999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2105,18 +2105,18 @@
         <v>69</v>
       </c>
       <c r="H44">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I44">
         <v>276</v>
       </c>
       <c r="J44" s="1">
-        <v>0.14860000000000001</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2137,18 +2137,18 @@
         <v>61</v>
       </c>
       <c r="H45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I45">
         <v>61</v>
       </c>
       <c r="J45" s="1">
-        <v>0.1148</v>
+        <v>6.5600000000000006E-2</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2198,18 +2198,18 @@
         <v>691280</v>
       </c>
       <c r="H47">
-        <v>1348606</v>
+        <v>671122</v>
       </c>
       <c r="I47">
         <v>8295360</v>
       </c>
       <c r="J47" s="1">
-        <v>0.16259999999999999</v>
+        <v>8.09E-2</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2230,18 +2230,18 @@
         <v>689046</v>
       </c>
       <c r="H48">
-        <v>211349</v>
+        <v>109448</v>
       </c>
       <c r="I48">
         <v>1378092</v>
       </c>
       <c r="J48" s="1">
-        <v>0.15340000000000001</v>
+        <v>7.9399999999999998E-2</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2262,18 +2262,18 @@
         <v>647</v>
       </c>
       <c r="H49">
-        <v>2520</v>
+        <v>1195</v>
       </c>
       <c r="I49">
         <v>15528</v>
       </c>
       <c r="J49" s="1">
-        <v>0.1623</v>
+        <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2291,21 +2291,21 @@
         <v>27</v>
       </c>
       <c r="G50">
-        <v>691098</v>
+        <v>691280</v>
       </c>
       <c r="H50">
-        <v>548459</v>
+        <v>352697</v>
       </c>
       <c r="I50">
-        <v>2764392</v>
+        <v>2765120</v>
       </c>
       <c r="J50" s="1">
-        <v>0.19839999999999999</v>
+        <v>0.12759999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2326,18 +2326,18 @@
         <v>691280</v>
       </c>
       <c r="H51">
-        <v>178733</v>
+        <v>91147</v>
       </c>
       <c r="I51">
         <v>691280</v>
       </c>
       <c r="J51" s="1">
-        <v>0.2586</v>
+        <v>0.13189999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2358,18 +2358,18 @@
         <v>345</v>
       </c>
       <c r="H52">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="I52">
         <v>1380</v>
       </c>
       <c r="J52" s="1">
-        <v>0.15290000000000001</v>
+        <v>6.3799999999999996E-2</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2390,18 +2390,18 @@
         <v>501</v>
       </c>
       <c r="H53">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="I53">
         <v>501</v>
       </c>
       <c r="J53" s="1">
-        <v>0.2555</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2422,18 +2422,18 @@
         <v>1109</v>
       </c>
       <c r="H54">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="I54">
         <v>2218</v>
       </c>
       <c r="J54" s="1">
-        <v>0.1555</v>
+        <v>6.4899999999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2451,21 +2451,21 @@
         <v>44</v>
       </c>
       <c r="G55">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="H55">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="I55">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="J55" s="1">
-        <v>0.114</v>
+        <v>3.27E-2</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2485,19 +2485,16 @@
       <c r="G56">
         <v>331</v>
       </c>
-      <c r="H56">
-        <v>16</v>
-      </c>
       <c r="I56">
         <v>331</v>
       </c>
       <c r="J56" s="1">
-        <v>4.8300000000000003E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2526,7 +2523,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2547,18 +2544,18 @@
         <v>59</v>
       </c>
       <c r="H58">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="I58">
         <v>1416</v>
       </c>
       <c r="J58" s="1">
-        <v>0.1653</v>
+        <v>7.9799999999999996E-2</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2579,18 +2576,18 @@
         <v>47</v>
       </c>
       <c r="H59">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="I59">
         <v>564</v>
       </c>
       <c r="J59" s="1">
-        <v>0.16839999999999999</v>
+        <v>7.6200000000000004E-2</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2611,7 +2608,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2632,18 +2629,18 @@
         <v>366</v>
       </c>
       <c r="H61">
-        <v>1464</v>
+        <v>732</v>
       </c>
       <c r="I61">
         <v>8784</v>
       </c>
       <c r="J61" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2664,18 +2661,18 @@
         <v>244</v>
       </c>
       <c r="H62">
-        <v>488</v>
+        <v>244</v>
       </c>
       <c r="I62">
         <v>2928</v>
       </c>
       <c r="J62" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2696,18 +2693,18 @@
         <v>640</v>
       </c>
       <c r="H63">
-        <v>1288</v>
+        <v>640</v>
       </c>
       <c r="I63">
         <v>7680</v>
       </c>
       <c r="J63" s="1">
-        <v>0.16769999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2728,18 +2725,18 @@
         <v>696</v>
       </c>
       <c r="H64">
-        <v>1486</v>
+        <v>746</v>
       </c>
       <c r="I64">
         <v>8952</v>
       </c>
       <c r="J64" s="1">
-        <v>0.16600000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2760,18 +2757,18 @@
         <v>90</v>
       </c>
       <c r="H65">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="I65">
         <v>1104</v>
       </c>
       <c r="J65" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.2400000000000001E-2</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2792,18 +2789,18 @@
         <v>8</v>
       </c>
       <c r="H66">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I66">
         <v>192</v>
       </c>
       <c r="J66" s="1">
-        <v>0.21879999999999999</v>
+        <v>0.11459999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2824,18 +2821,18 @@
         <v>25</v>
       </c>
       <c r="H67">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="I67">
         <v>300</v>
       </c>
       <c r="J67" s="1">
-        <v>0.15670000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2856,18 +2853,18 @@
         <v>3</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2888,18 +2885,18 @@
         <v>73</v>
       </c>
       <c r="H69">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="I69">
         <v>840</v>
       </c>
       <c r="J69" s="1">
-        <v>0.17380000000000001</v>
+        <v>8.6900000000000005E-2</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2920,18 +2917,18 @@
         <v>139</v>
       </c>
       <c r="H70">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="I70">
         <v>1668</v>
       </c>
       <c r="J70" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2952,18 +2949,18 @@
         <v>273</v>
       </c>
       <c r="H71">
-        <v>546</v>
+        <v>273</v>
       </c>
       <c r="I71">
         <v>3276</v>
       </c>
       <c r="J71" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2984,18 +2981,18 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>826</v>
+        <v>434</v>
       </c>
       <c r="I72">
         <v>5110</v>
       </c>
       <c r="J72" s="1">
-        <v>0.16159999999999999</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3016,18 +3013,18 @@
         <v>30</v>
       </c>
       <c r="H73">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I73">
         <v>120</v>
       </c>
       <c r="J73" s="1">
-        <v>0.1167</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3059,7 +3056,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3091,7 +3088,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3112,18 +3109,18 @@
         <v>47</v>
       </c>
       <c r="H76">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I76">
         <v>52</v>
       </c>
       <c r="J76" s="1">
-        <v>0.65380000000000005</v>
+        <v>0.15379999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3155,7 +3152,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3176,18 +3173,18 @@
         <v>17</v>
       </c>
       <c r="H78">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>34</v>
       </c>
       <c r="J78" s="1">
-        <v>0.44119999999999998</v>
+        <v>5.8799999999999998E-2</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3208,18 +3205,18 @@
         <v>189</v>
       </c>
       <c r="H79">
-        <v>377</v>
+        <v>189</v>
       </c>
       <c r="I79">
         <v>2268</v>
       </c>
       <c r="J79" s="1">
-        <v>0.16619999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3240,18 +3237,18 @@
         <v>287</v>
       </c>
       <c r="H80">
-        <v>580</v>
+        <v>286</v>
       </c>
       <c r="I80">
         <v>3444</v>
       </c>
       <c r="J80" s="1">
-        <v>0.16839999999999999</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3272,18 +3269,18 @@
         <v>74</v>
       </c>
       <c r="H81">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I81">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="J81" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.5500000000000007E-2</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3304,18 +3301,18 @@
         <v>123</v>
       </c>
       <c r="H82">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="I82">
         <v>1644</v>
       </c>
       <c r="J82" s="1">
-        <v>0.1636</v>
+        <v>8.2100000000000006E-2</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3336,7 +3333,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3357,18 +3354,18 @@
         <v>29</v>
       </c>
       <c r="H84">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I84">
         <v>348</v>
       </c>
       <c r="J84" s="1">
-        <v>0.15229999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3400,7 +3397,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3421,18 +3418,18 @@
         <v>293</v>
       </c>
       <c r="H86">
-        <v>1172</v>
+        <v>586</v>
       </c>
       <c r="I86">
-        <v>7032</v>
+        <v>7044</v>
       </c>
       <c r="J86" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3199999999999996E-2</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3453,18 +3450,18 @@
         <v>37</v>
       </c>
       <c r="H87">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="I87">
         <v>444</v>
       </c>
       <c r="J87" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1100000000000005E-2</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3496,7 +3493,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3517,18 +3514,18 @@
         <v>2</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I89">
         <v>24</v>
       </c>
       <c r="J89" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3549,18 +3546,18 @@
         <v>749</v>
       </c>
       <c r="H90">
-        <v>1499</v>
+        <v>749</v>
       </c>
       <c r="I90">
         <v>8988</v>
       </c>
       <c r="J90" s="1">
-        <v>0.1668</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3581,18 +3578,18 @@
         <v>177</v>
       </c>
       <c r="H91">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="I91">
-        <v>1932</v>
+        <v>2124</v>
       </c>
       <c r="J91" s="1">
-        <v>0.1605</v>
+        <v>7.1099999999999997E-2</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3613,18 +3610,18 @@
         <v>45</v>
       </c>
       <c r="H92">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="I92">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="J92" s="1">
-        <v>0.16669999999999999</v>
+        <v>7.7299999999999994E-2</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3645,18 +3642,18 @@
         <v>55</v>
       </c>
       <c r="H93">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="I93">
         <v>660</v>
       </c>
       <c r="J93" s="1">
-        <v>0.15609999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3677,7 +3674,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3698,18 +3695,18 @@
         <v>45</v>
       </c>
       <c r="H95">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I95">
         <v>540</v>
       </c>
       <c r="J95" s="1">
-        <v>0.16300000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3730,7 +3727,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3751,18 +3748,18 @@
         <v>3</v>
       </c>
       <c r="H97">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="I97">
         <v>1095</v>
       </c>
       <c r="J97" s="1">
-        <v>0.23469999999999999</v>
+        <v>0.12970000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3783,18 +3780,18 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I98">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J98" s="1">
-        <v>0.16669999999999999</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3818,15 +3815,15 @@
         <v>6</v>
       </c>
       <c r="I99">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J99" s="1">
-        <v>0.4</v>
+        <v>0.42859999999999998</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3847,18 +3844,18 @@
         <v>33</v>
       </c>
       <c r="H100">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I100">
         <v>132</v>
       </c>
       <c r="J100" s="1">
-        <v>0.20449999999999999</v>
+        <v>6.8199999999999997E-2</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3875,22 +3872,11 @@
       <c r="F101" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G101">
-        <v>33</v>
-      </c>
-      <c r="H101">
-        <v>4</v>
-      </c>
-      <c r="I101">
-        <v>33</v>
-      </c>
-      <c r="J101" s="1">
-        <v>0.1212</v>
-      </c>
+      <c r="J101" s="1"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3914,15 +3900,15 @@
         <v>4</v>
       </c>
       <c r="I102">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J102" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3954,7 +3940,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -3975,18 +3961,18 @@
         <v>30</v>
       </c>
       <c r="H104">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="I104">
         <v>360</v>
       </c>
       <c r="J104" s="1">
-        <v>0.16389999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4007,18 +3993,18 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I105">
         <v>72</v>
       </c>
       <c r="J105" s="1">
-        <v>0.15279999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4039,18 +4025,18 @@
         <v>45</v>
       </c>
       <c r="H106">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I106">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="J106" s="1">
-        <v>0.16300000000000001</v>
+        <v>8.5199999999999998E-2</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4071,7 +4057,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4092,18 +4078,18 @@
         <v>50</v>
       </c>
       <c r="H108">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="I108">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="J108" s="1">
-        <v>0.1555</v>
+        <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4124,7 +4110,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4145,18 +4131,18 @@
         <v>16</v>
       </c>
       <c r="H110">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I110">
         <v>192</v>
       </c>
       <c r="J110" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4174,21 +4160,21 @@
         <v>25</v>
       </c>
       <c r="G111">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H111">
-        <v>1280</v>
+        <v>429</v>
       </c>
       <c r="I111">
-        <v>10992</v>
+        <v>11016</v>
       </c>
       <c r="J111" s="1">
-        <v>0.1164</v>
+        <v>3.8899999999999997E-2</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4209,18 +4195,18 @@
         <v>5</v>
       </c>
       <c r="H112">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I112">
         <v>60</v>
       </c>
       <c r="J112" s="1">
-        <v>0.2167</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4241,18 +4227,18 @@
         <v>43</v>
       </c>
       <c r="H113">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I113">
         <v>516</v>
       </c>
       <c r="J113" s="1">
-        <v>0.1221</v>
+        <v>0.1143</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4270,21 +4256,21 @@
         <v>26</v>
       </c>
       <c r="G114">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="H114">
-        <v>1649</v>
+        <v>780</v>
       </c>
       <c r="I114">
-        <v>7992</v>
+        <v>7908</v>
       </c>
       <c r="J114" s="1">
-        <v>0.20630000000000001</v>
+        <v>9.8599999999999993E-2</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4302,21 +4288,21 @@
         <v>26</v>
       </c>
       <c r="G115">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="H115">
-        <v>1114</v>
+        <v>449</v>
       </c>
       <c r="I115">
-        <v>12264</v>
+        <v>12432</v>
       </c>
       <c r="J115" s="1">
-        <v>9.0800000000000006E-2</v>
+        <v>3.61E-2</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4337,18 +4323,18 @@
         <v>71</v>
       </c>
       <c r="H116">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="I116">
         <v>852</v>
       </c>
       <c r="J116" s="1">
-        <v>0.11849999999999999</v>
+        <v>6.8099999999999994E-2</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4369,18 +4355,18 @@
         <v>22</v>
       </c>
       <c r="H117">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="I117">
         <v>528</v>
       </c>
       <c r="J117" s="1">
-        <v>0.1023</v>
+        <v>7.7700000000000005E-2</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4401,18 +4387,18 @@
         <v>5</v>
       </c>
       <c r="H118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I118">
         <v>60</v>
       </c>
       <c r="J118" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4433,18 +4419,18 @@
         <v>1</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>12</v>
       </c>
       <c r="J119" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4465,18 +4451,18 @@
         <v>81</v>
       </c>
       <c r="H120">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="I120">
         <v>972</v>
       </c>
       <c r="J120" s="1">
-        <v>0.12139999999999999</v>
+        <v>5.7599999999999998E-2</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4497,18 +4483,18 @@
         <v>52</v>
       </c>
       <c r="H121">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I121">
         <v>624</v>
       </c>
       <c r="J121" s="1">
-        <v>0.10580000000000001</v>
+        <v>8.8099999999999998E-2</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4529,18 +4515,18 @@
         <v>44</v>
       </c>
       <c r="H122">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I122">
         <v>528</v>
       </c>
       <c r="J122" s="1">
-        <v>8.7099999999999997E-2</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4561,18 +4547,18 @@
         <v>11</v>
       </c>
       <c r="H123">
-        <v>641</v>
+        <v>298</v>
       </c>
       <c r="I123">
         <v>4046</v>
       </c>
       <c r="J123" s="1">
-        <v>0.15840000000000001</v>
+        <v>7.3700000000000002E-2</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4590,21 +4576,21 @@
         <v>27</v>
       </c>
       <c r="G124">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H124">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I124">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J124" s="1">
-        <v>0.23530000000000001</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4622,21 +4608,21 @@
         <v>44</v>
       </c>
       <c r="G125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J125" s="1">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4654,21 +4640,21 @@
         <v>27</v>
       </c>
       <c r="G126">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H126">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I126">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J126" s="1">
-        <v>9.4399999999999998E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4686,21 +4672,21 @@
         <v>44</v>
       </c>
       <c r="G127">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H127">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I127">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J127" s="1">
-        <v>0.31109999999999999</v>
+        <v>2.2700000000000001E-2</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4732,7 +4718,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4753,18 +4739,18 @@
         <v>12</v>
       </c>
       <c r="H129">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I129">
         <v>24</v>
       </c>
       <c r="J129" s="1">
-        <v>0.375</v>
+        <v>4.1700000000000001E-2</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4782,21 +4768,21 @@
         <v>26</v>
       </c>
       <c r="G130">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="H130">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="I130">
-        <v>2256</v>
+        <v>2040</v>
       </c>
       <c r="J130" s="1">
-        <v>0.1547</v>
+        <v>0.14660000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4817,18 +4803,18 @@
         <v>43</v>
       </c>
       <c r="H131">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I131">
         <v>516</v>
       </c>
       <c r="J131" s="1">
-        <v>0.1143</v>
+        <v>7.5600000000000001E-2</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4846,21 +4832,21 @@
         <v>26</v>
       </c>
       <c r="G132">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H132">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I132">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="J132" s="1">
-        <v>0.16070000000000001</v>
+        <v>0.1623</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4881,18 +4867,18 @@
         <v>52</v>
       </c>
       <c r="H133">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I133">
         <v>624</v>
       </c>
       <c r="J133" s="1">
-        <v>0.13780000000000001</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4913,7 +4899,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -4934,7 +4920,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -4955,7 +4941,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -4976,18 +4962,18 @@
         <v>41</v>
       </c>
       <c r="H137">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I137">
         <v>492</v>
       </c>
       <c r="J137" s="1">
-        <v>0.1585</v>
+        <v>8.1299999999999997E-2</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5008,18 +4994,18 @@
         <v>585</v>
       </c>
       <c r="H138">
-        <v>1171</v>
+        <v>586</v>
       </c>
       <c r="I138">
         <v>7020</v>
       </c>
       <c r="J138" s="1">
-        <v>0.1668</v>
+        <v>8.3500000000000005E-2</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5040,18 +5026,18 @@
         <v>383</v>
       </c>
       <c r="H139">
-        <v>1508</v>
+        <v>762</v>
       </c>
       <c r="I139">
         <v>9144</v>
       </c>
       <c r="J139" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5072,18 +5058,18 @@
         <v>1</v>
       </c>
       <c r="H140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>12</v>
       </c>
       <c r="J140" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5104,18 +5090,18 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141">
         <v>12</v>
       </c>
       <c r="J141" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5136,18 +5122,18 @@
         <v>22</v>
       </c>
       <c r="H142">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I142">
         <v>264</v>
       </c>
       <c r="J142" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5168,18 +5154,18 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143">
         <v>12</v>
       </c>
       <c r="J143" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5200,18 +5186,18 @@
         <v>898</v>
       </c>
       <c r="H144">
-        <v>1819</v>
+        <v>909</v>
       </c>
       <c r="I144">
         <v>10776</v>
       </c>
       <c r="J144" s="1">
-        <v>0.16880000000000001</v>
+        <v>8.4400000000000003E-2</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5232,18 +5218,18 @@
         <v>126</v>
       </c>
       <c r="H145">
-        <v>253</v>
+        <v>128</v>
       </c>
       <c r="I145">
         <v>1512</v>
       </c>
       <c r="J145" s="1">
-        <v>0.1673</v>
+        <v>8.4699999999999998E-2</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5264,18 +5250,18 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="I146">
         <v>336</v>
       </c>
       <c r="J146" s="1">
-        <v>0.16370000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5296,18 +5282,18 @@
         <v>60</v>
       </c>
       <c r="H147">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I147">
         <v>720</v>
       </c>
       <c r="J147" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5328,18 +5314,18 @@
         <v>51</v>
       </c>
       <c r="H148">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="I148">
         <v>624</v>
       </c>
       <c r="J148" s="1">
-        <v>0.1651</v>
+        <v>8.1699999999999995E-2</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5360,18 +5346,18 @@
         <v>7</v>
       </c>
       <c r="H149">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I149">
         <v>84</v>
       </c>
       <c r="J149" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5392,18 +5378,18 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I150">
         <v>48</v>
       </c>
       <c r="J150" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5435,7 +5421,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5456,18 +5442,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>924</v>
+        <v>483</v>
       </c>
       <c r="I152">
         <v>4745</v>
       </c>
       <c r="J152" s="1">
-        <v>0.19470000000000001</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5488,18 +5474,18 @@
         <v>29</v>
       </c>
       <c r="H153">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I153">
         <v>112</v>
       </c>
       <c r="J153" s="1">
-        <v>0.24110000000000001</v>
+        <v>0.16070000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5531,7 +5517,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5552,18 +5538,18 @@
         <v>45</v>
       </c>
       <c r="H155">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I155">
         <v>180</v>
       </c>
       <c r="J155" s="1">
-        <v>0.23330000000000001</v>
+        <v>0.21110000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5595,7 +5581,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5616,18 +5602,18 @@
         <v>9</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I157">
         <v>18</v>
       </c>
       <c r="J157" s="1">
-        <v>0.27779999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5659,7 +5645,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5680,18 +5666,18 @@
         <v>42</v>
       </c>
       <c r="H159">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="I159">
         <v>492</v>
       </c>
       <c r="J159" s="1">
-        <v>0.16259999999999999</v>
+        <v>7.9299999999999995E-2</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5712,18 +5698,18 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I160">
         <v>144</v>
       </c>
       <c r="J160" s="1">
-        <v>0.15970000000000001</v>
+        <v>7.6399999999999996E-2</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5744,18 +5730,18 @@
         <v>58</v>
       </c>
       <c r="H161">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="I161">
         <v>708</v>
       </c>
       <c r="J161" s="1">
-        <v>0.1653</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5776,18 +5762,18 @@
         <v>64</v>
       </c>
       <c r="H162">
-        <v>344</v>
+        <v>172</v>
       </c>
       <c r="I162">
         <v>1956</v>
       </c>
       <c r="J162" s="1">
-        <v>0.1759</v>
+        <v>8.7900000000000006E-2</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5808,18 +5794,18 @@
         <v>387</v>
       </c>
       <c r="H163">
-        <v>1539</v>
+        <v>774</v>
       </c>
       <c r="I163">
         <v>9288</v>
       </c>
       <c r="J163" s="1">
-        <v>0.16569999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5840,18 +5826,18 @@
         <v>39</v>
       </c>
       <c r="H164">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I164">
         <v>468</v>
       </c>
       <c r="J164" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5872,18 +5858,18 @@
         <v>590</v>
       </c>
       <c r="H165">
-        <v>1185</v>
+        <v>594</v>
       </c>
       <c r="I165">
         <v>7080</v>
       </c>
       <c r="J165" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.3900000000000002E-2</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5904,18 +5890,18 @@
         <v>964</v>
       </c>
       <c r="H166">
-        <v>1920</v>
+        <v>969</v>
       </c>
       <c r="I166">
         <v>11568</v>
       </c>
       <c r="J166" s="1">
-        <v>0.16600000000000001</v>
+        <v>8.3799999999999999E-2</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -5936,18 +5922,18 @@
         <v>96</v>
       </c>
       <c r="H167">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="I167">
         <v>1152</v>
       </c>
       <c r="J167" s="1">
-        <v>0.1658</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -5968,18 +5954,18 @@
         <v>13</v>
       </c>
       <c r="H168">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I168">
         <v>312</v>
       </c>
       <c r="J168" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6000,18 +5986,18 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I169">
         <v>84</v>
       </c>
       <c r="J169" s="1">
-        <v>0.16669999999999999</v>
+        <v>3.5700000000000003E-2</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6032,18 +6018,18 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I170">
         <v>12</v>
       </c>
       <c r="J170" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6064,18 +6050,18 @@
         <v>108</v>
       </c>
       <c r="H171">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I171">
         <v>1296</v>
       </c>
       <c r="J171" s="1">
-        <v>0.14510000000000001</v>
+        <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6096,18 +6082,18 @@
         <v>47</v>
       </c>
       <c r="H172">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="I172">
         <v>564</v>
       </c>
       <c r="J172" s="1">
-        <v>0.16489999999999999</v>
+        <v>8.1600000000000006E-2</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6128,18 +6114,18 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I173">
         <v>84</v>
       </c>
       <c r="J173" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6160,18 +6146,18 @@
         <v>30</v>
       </c>
       <c r="H174">
-        <v>1958</v>
+        <v>1058</v>
       </c>
       <c r="I174">
         <v>10950</v>
       </c>
       <c r="J174" s="1">
-        <v>0.17879999999999999</v>
+        <v>9.6600000000000005E-2</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6192,18 +6178,18 @@
         <v>57</v>
       </c>
       <c r="H175">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I175">
         <v>228</v>
       </c>
       <c r="J175" s="1">
-        <v>0.1404</v>
+        <v>6.1400000000000003E-2</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6232,7 +6218,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6253,18 +6239,18 @@
         <v>37</v>
       </c>
       <c r="H177">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I177">
         <v>148</v>
       </c>
       <c r="J177" s="1">
-        <v>0.19589999999999999</v>
+        <v>8.1100000000000005E-2</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6296,7 +6282,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6328,7 +6314,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6360,7 +6346,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6381,18 +6367,18 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>322</v>
+        <v>162</v>
       </c>
       <c r="I181">
         <v>2040</v>
       </c>
       <c r="J181" s="1">
-        <v>0.1578</v>
+        <v>7.9399999999999998E-2</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6413,18 +6399,18 @@
         <v>36</v>
       </c>
       <c r="H182">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="I182">
         <v>432</v>
       </c>
       <c r="J182" s="1">
-        <v>0.16439999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6445,18 +6431,18 @@
         <v>13</v>
       </c>
       <c r="H183">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I183">
         <v>156</v>
       </c>
       <c r="J183" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6477,18 +6463,18 @@
         <v>9</v>
       </c>
       <c r="H184">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I184">
         <v>108</v>
       </c>
       <c r="J184" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6509,18 +6495,18 @@
         <v>88</v>
       </c>
       <c r="H185">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I185">
         <v>1056</v>
       </c>
       <c r="J185" s="1">
-        <v>0.16950000000000001</v>
+        <v>8.43E-2</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6541,7 +6527,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6573,7 +6559,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6594,18 +6580,18 @@
         <v>9</v>
       </c>
       <c r="H188">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I188">
         <v>216</v>
       </c>
       <c r="J188" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6626,18 +6612,18 @@
         <v>9</v>
       </c>
       <c r="H189">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I189">
         <v>108</v>
       </c>
       <c r="J189" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6658,18 +6644,18 @@
         <v>59</v>
       </c>
       <c r="H190">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I190">
         <v>708</v>
       </c>
       <c r="J190" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6690,18 +6676,18 @@
         <v>59</v>
       </c>
       <c r="H191">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I191">
         <v>59</v>
       </c>
       <c r="J191" s="1">
-        <v>0.30509999999999998</v>
+        <v>0.2034</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6733,7 +6719,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6754,18 +6740,18 @@
         <v>9</v>
       </c>
       <c r="H193">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I193">
         <v>36</v>
       </c>
       <c r="J193" s="1">
-        <v>0.25</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6786,18 +6772,18 @@
         <v>9</v>
       </c>
       <c r="H194">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I194">
         <v>9</v>
       </c>
       <c r="J194" s="1">
-        <v>0.66669999999999996</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6817,19 +6803,16 @@
       <c r="G195">
         <v>85</v>
       </c>
-      <c r="H195">
-        <v>19</v>
-      </c>
       <c r="I195">
         <v>85</v>
       </c>
       <c r="J195" s="1">
-        <v>0.2235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6850,18 +6833,18 @@
         <v>27</v>
       </c>
       <c r="H196">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I196">
         <v>27</v>
       </c>
       <c r="J196" s="1">
-        <v>0.77780000000000005</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6893,7 +6876,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -6914,18 +6897,18 @@
         <v>41</v>
       </c>
       <c r="H198">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I198">
         <v>41</v>
       </c>
       <c r="J198" s="1">
-        <v>0.78049999999999997</v>
+        <v>0.34150000000000003</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -6957,7 +6940,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -6977,19 +6960,16 @@
       <c r="G200">
         <v>9</v>
       </c>
-      <c r="H200">
-        <v>9</v>
-      </c>
       <c r="I200">
         <v>36</v>
       </c>
       <c r="J200" s="1">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7010,18 +6990,18 @@
         <v>45</v>
       </c>
       <c r="H201">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I201">
         <v>45</v>
       </c>
       <c r="J201" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7042,18 +7022,18 @@
         <v>9</v>
       </c>
       <c r="H202">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I202">
         <v>36</v>
       </c>
       <c r="J202" s="1">
-        <v>0.1389</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7085,7 +7065,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7106,18 +7086,18 @@
         <v>188993</v>
       </c>
       <c r="H204">
-        <v>377986</v>
+        <v>188993</v>
       </c>
       <c r="I204">
         <v>2267916</v>
       </c>
       <c r="J204" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7138,18 +7118,18 @@
         <v>183511</v>
       </c>
       <c r="H205">
-        <v>42045</v>
+        <v>12453</v>
       </c>
       <c r="I205">
         <v>367022</v>
       </c>
       <c r="J205" s="1">
-        <v>0.11459999999999999</v>
+        <v>3.39E-2</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7170,18 +7150,18 @@
         <v>174</v>
       </c>
       <c r="H206">
-        <v>696</v>
+        <v>348</v>
       </c>
       <c r="I206">
         <v>4176</v>
       </c>
       <c r="J206" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7202,18 +7182,18 @@
         <v>188993</v>
       </c>
       <c r="H207">
-        <v>179681</v>
+        <v>69950</v>
       </c>
       <c r="I207">
         <v>755972</v>
       </c>
       <c r="J207" s="1">
-        <v>0.23769999999999999</v>
+        <v>9.2499999999999999E-2</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7234,18 +7214,18 @@
         <v>188993</v>
       </c>
       <c r="H208">
-        <v>49159</v>
+        <v>40025</v>
       </c>
       <c r="I208">
         <v>188993</v>
       </c>
       <c r="J208" s="1">
-        <v>0.2601</v>
+        <v>0.21179999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7266,18 +7246,18 @@
         <v>98</v>
       </c>
       <c r="H209">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="I209">
         <v>392</v>
       </c>
       <c r="J209" s="1">
-        <v>0.19639999999999999</v>
+        <v>7.6499999999999999E-2</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7298,18 +7278,18 @@
         <v>127</v>
       </c>
       <c r="H210">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I210">
         <v>127</v>
       </c>
       <c r="J210" s="1">
-        <v>0.252</v>
+        <v>0.20469999999999999</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7330,18 +7310,18 @@
         <v>271</v>
       </c>
       <c r="H211">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="I211">
         <v>542</v>
       </c>
       <c r="J211" s="1">
-        <v>0.12920000000000001</v>
+        <v>3.5099999999999999E-2</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7362,18 +7342,18 @@
         <v>133</v>
       </c>
       <c r="H212">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I212">
         <v>133</v>
       </c>
       <c r="J212" s="1">
-        <v>0.3609</v>
+        <v>0.15790000000000001</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7394,18 +7374,18 @@
         <v>67</v>
       </c>
       <c r="H213">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I213">
         <v>67</v>
       </c>
       <c r="J213" s="1">
-        <v>0.28360000000000002</v>
+        <v>0.17910000000000001</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7426,18 +7406,18 @@
         <v>5482</v>
       </c>
       <c r="H214">
-        <v>3114</v>
+        <v>370</v>
       </c>
       <c r="I214">
         <v>10964</v>
       </c>
       <c r="J214" s="1">
-        <v>0.28399999999999997</v>
+        <v>3.3700000000000001E-2</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7458,7 +7438,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7479,18 +7459,18 @@
         <v>263</v>
       </c>
       <c r="H216">
-        <v>1052</v>
+        <v>528</v>
       </c>
       <c r="I216">
         <v>6312</v>
       </c>
       <c r="J216" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3699999999999997E-2</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7511,18 +7491,18 @@
         <v>40</v>
       </c>
       <c r="H217">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I217">
         <v>480</v>
       </c>
       <c r="J217" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7543,18 +7523,18 @@
         <v>408</v>
       </c>
       <c r="H218">
-        <v>818</v>
+        <v>390</v>
       </c>
       <c r="I218">
         <v>4896</v>
       </c>
       <c r="J218" s="1">
-        <v>0.1671</v>
+        <v>7.9699999999999993E-2</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7575,18 +7555,18 @@
         <v>550</v>
       </c>
       <c r="H219">
-        <v>1055</v>
+        <v>552</v>
       </c>
       <c r="I219">
         <v>6600</v>
       </c>
       <c r="J219" s="1">
-        <v>0.1598</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7607,18 +7587,18 @@
         <v>76</v>
       </c>
       <c r="H220">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="I220">
         <v>912</v>
       </c>
       <c r="J220" s="1">
-        <v>0.16339999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7639,18 +7619,18 @@
         <v>6</v>
       </c>
       <c r="H221">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I221">
         <v>144</v>
       </c>
       <c r="J221" s="1">
-        <v>0.15970000000000001</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7671,18 +7651,18 @@
         <v>19</v>
       </c>
       <c r="H222">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I222">
         <v>228</v>
       </c>
       <c r="J222" s="1">
-        <v>0.1623</v>
+        <v>7.0199999999999999E-2</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7714,7 +7694,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7735,18 +7715,18 @@
         <v>4</v>
       </c>
       <c r="H224">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I224">
         <v>48</v>
       </c>
       <c r="J224" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7767,18 +7747,18 @@
         <v>31</v>
       </c>
       <c r="H225">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="I225">
         <v>372</v>
       </c>
       <c r="J225" s="1">
-        <v>0.16400000000000001</v>
+        <v>7.5300000000000006E-2</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7799,18 +7779,18 @@
         <v>175</v>
       </c>
       <c r="H226">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="I226">
         <v>2100</v>
       </c>
       <c r="J226" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7831,18 +7811,18 @@
         <v>9</v>
       </c>
       <c r="H227">
-        <v>893</v>
+        <v>487</v>
       </c>
       <c r="I227">
         <v>3285</v>
       </c>
       <c r="J227" s="1">
-        <v>0.27179999999999999</v>
+        <v>0.1482</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7863,18 +7843,18 @@
         <v>9</v>
       </c>
       <c r="H228">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I228">
         <v>36</v>
       </c>
       <c r="J228" s="1">
-        <v>0.27779999999999999</v>
+        <v>2.7799999999999998E-2</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -7894,19 +7874,16 @@
       <c r="G229">
         <v>9</v>
       </c>
-      <c r="H229">
-        <v>4</v>
-      </c>
       <c r="I229">
         <v>9</v>
       </c>
       <c r="J229" s="1">
-        <v>0.44440000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -7927,18 +7904,18 @@
         <v>34</v>
       </c>
       <c r="H230">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I230">
         <v>132</v>
       </c>
       <c r="J230" s="1">
-        <v>0.31059999999999999</v>
+        <v>6.8199999999999997E-2</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -7967,7 +7944,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -7999,7 +7976,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8020,18 +7997,18 @@
         <v>3654</v>
       </c>
       <c r="H233">
-        <v>6870</v>
+        <v>2898</v>
       </c>
       <c r="I233">
         <v>43848</v>
       </c>
       <c r="J233" s="1">
-        <v>0.15670000000000001</v>
+        <v>6.6100000000000006E-2</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8052,7 +8029,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8073,7 +8050,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8094,7 +8071,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8115,7 +8092,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8136,7 +8113,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8157,7 +8134,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8186,7 +8163,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8207,18 +8184,18 @@
         <v>486</v>
       </c>
       <c r="H241">
-        <v>1949</v>
+        <v>972</v>
       </c>
       <c r="I241">
         <v>11664</v>
       </c>
       <c r="J241" s="1">
-        <v>0.1671</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8239,18 +8216,18 @@
         <v>25</v>
       </c>
       <c r="H242">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="I242">
         <v>300</v>
       </c>
       <c r="J242" s="1">
-        <v>0.19670000000000001</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8271,18 +8248,18 @@
         <v>68</v>
       </c>
       <c r="H243">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="I243">
         <v>816</v>
       </c>
       <c r="J243" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8303,18 +8280,18 @@
         <v>729</v>
       </c>
       <c r="H244">
-        <v>1463</v>
+        <v>731</v>
       </c>
       <c r="I244">
         <v>8772</v>
       </c>
       <c r="J244" s="1">
-        <v>0.1668</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8335,18 +8312,18 @@
         <v>854</v>
       </c>
       <c r="H245">
-        <v>1842</v>
+        <v>922</v>
       </c>
       <c r="I245">
         <v>11040</v>
       </c>
       <c r="J245" s="1">
-        <v>0.1668</v>
+        <v>8.3500000000000005E-2</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8367,18 +8344,18 @@
         <v>121</v>
       </c>
       <c r="H246">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="I246">
         <v>1452</v>
       </c>
       <c r="J246" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8399,18 +8376,18 @@
         <v>27</v>
       </c>
       <c r="H247">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="I247">
         <v>648</v>
       </c>
       <c r="J247" s="1">
-        <v>0.1744</v>
+        <v>8.7999999999999995E-2</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8431,7 +8408,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8452,18 +8429,18 @@
         <v>2</v>
       </c>
       <c r="H249">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I249">
         <v>24</v>
       </c>
       <c r="J249" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8484,18 +8461,18 @@
         <v>30</v>
       </c>
       <c r="H250">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I250">
         <v>360</v>
       </c>
       <c r="J250" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8516,18 +8493,18 @@
         <v>51</v>
       </c>
       <c r="H251">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="I251">
         <v>624</v>
       </c>
       <c r="J251" s="1">
-        <v>0.17150000000000001</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8548,18 +8525,18 @@
         <v>337</v>
       </c>
       <c r="H252">
-        <v>677</v>
+        <v>338</v>
       </c>
       <c r="I252">
         <v>4044</v>
       </c>
       <c r="J252" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8580,18 +8557,18 @@
         <v>50</v>
       </c>
       <c r="H253">
-        <v>3516</v>
+        <v>1859</v>
       </c>
       <c r="I253">
         <v>18972</v>
       </c>
       <c r="J253" s="1">
-        <v>0.18529999999999999</v>
+        <v>9.8000000000000004E-2</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8612,18 +8589,18 @@
         <v>58</v>
       </c>
       <c r="H254">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I254">
         <v>232</v>
       </c>
       <c r="J254" s="1">
-        <v>0.1767</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8655,7 +8632,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8676,18 +8653,18 @@
         <v>56</v>
       </c>
       <c r="H256">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I256">
         <v>228</v>
       </c>
       <c r="J256" s="1">
-        <v>0.114</v>
+        <v>4.3900000000000002E-2</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8719,7 +8696,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8740,18 +8717,18 @@
         <v>4610</v>
       </c>
       <c r="H258">
-        <v>9590</v>
+        <v>4796</v>
       </c>
       <c r="I258">
         <v>55320</v>
       </c>
       <c r="J258" s="1">
-        <v>0.1734</v>
+        <v>8.6699999999999999E-2</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8772,18 +8749,18 @@
         <v>44</v>
       </c>
       <c r="H259">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I259">
         <v>468</v>
       </c>
       <c r="J259" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -8804,18 +8781,18 @@
         <v>44</v>
       </c>
       <c r="H260">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I260">
         <v>78</v>
       </c>
       <c r="J260" s="1">
-        <v>0.1026</v>
+        <v>1.2800000000000001E-2</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -8836,18 +8813,18 @@
         <v>90</v>
       </c>
       <c r="H261">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I261">
         <v>1080</v>
       </c>
       <c r="J261" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -8868,18 +8845,18 @@
         <v>27</v>
       </c>
       <c r="H262">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I262">
         <v>192</v>
       </c>
       <c r="J262" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -8900,18 +8877,18 @@
         <v>121</v>
       </c>
       <c r="H263">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="I263">
         <v>1428</v>
       </c>
       <c r="J263" s="1">
-        <v>0.16739999999999999</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -8932,18 +8909,18 @@
         <v>12</v>
       </c>
       <c r="H264">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I264">
         <v>24</v>
       </c>
       <c r="J264" s="1">
-        <v>0.125</v>
+        <v>4.1700000000000001E-2</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -8964,18 +8941,18 @@
         <v>351</v>
       </c>
       <c r="H265">
-        <v>712</v>
+        <v>366</v>
       </c>
       <c r="I265">
         <v>4291</v>
       </c>
       <c r="J265" s="1">
-        <v>0.16589999999999999</v>
+        <v>8.5300000000000001E-2</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -8993,7 +8970,7 @@
         <v>26</v>
       </c>
       <c r="G266">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H266">
         <v>35</v>
@@ -9007,7 +8984,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9028,18 +9005,18 @@
         <v>232</v>
       </c>
       <c r="H267">
-        <v>464</v>
+        <v>232</v>
       </c>
       <c r="I267">
         <v>2784</v>
       </c>
       <c r="J267" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9060,18 +9037,18 @@
         <v>66</v>
       </c>
       <c r="H268">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="I268">
         <v>792</v>
       </c>
       <c r="J268" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9092,18 +9069,18 @@
         <v>84</v>
       </c>
       <c r="H269">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="I269">
         <v>1008</v>
       </c>
       <c r="J269" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9124,7 +9101,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9145,18 +9122,18 @@
         <v>33</v>
       </c>
       <c r="H271">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I271">
         <v>384</v>
       </c>
       <c r="J271" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9177,18 +9154,18 @@
         <v>3</v>
       </c>
       <c r="H272">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I272">
         <v>36</v>
       </c>
       <c r="J272" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9209,7 +9186,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9230,7 +9207,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9251,18 +9228,18 @@
         <v>51</v>
       </c>
       <c r="H275">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I275">
         <v>276</v>
       </c>
       <c r="J275" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9283,18 +9260,18 @@
         <v>445</v>
       </c>
       <c r="H276">
-        <v>890</v>
+        <v>445</v>
       </c>
       <c r="I276">
         <v>5340</v>
       </c>
       <c r="J276" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9315,18 +9292,18 @@
         <v>17</v>
       </c>
       <c r="H277">
-        <v>860</v>
+        <v>465</v>
       </c>
       <c r="I277">
         <v>5110</v>
       </c>
       <c r="J277" s="1">
-        <v>0.16830000000000001</v>
+        <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9358,7 +9335,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9379,18 +9356,18 @@
         <v>11</v>
       </c>
       <c r="H279">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I279">
         <v>11</v>
       </c>
       <c r="J279" s="1">
-        <v>0.45450000000000002</v>
+        <v>9.0899999999999995E-2</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9411,18 +9388,18 @@
         <v>34</v>
       </c>
       <c r="H280">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I280">
         <v>136</v>
       </c>
       <c r="J280" s="1">
-        <v>0.25</v>
+        <v>0.18379999999999999</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9454,7 +9431,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9475,18 +9452,18 @@
         <v>6</v>
       </c>
       <c r="H282">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I282">
         <v>12</v>
       </c>
       <c r="J282" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9518,7 +9495,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9550,7 +9527,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9571,18 +9548,18 @@
         <v>33</v>
       </c>
       <c r="H285">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="I285">
         <v>396</v>
       </c>
       <c r="J285" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9603,18 +9580,18 @@
         <v>23</v>
       </c>
       <c r="H286">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I286">
         <v>276</v>
       </c>
       <c r="J286" s="1">
-        <v>0.16669999999999999</v>
+        <v>7.9699999999999993E-2</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9635,18 +9612,18 @@
         <v>79</v>
       </c>
       <c r="H287">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="I287">
         <v>948</v>
       </c>
       <c r="J287" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9667,7 +9644,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9688,18 +9665,18 @@
         <v>21</v>
       </c>
       <c r="H289">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I289">
         <v>264</v>
       </c>
       <c r="J289" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9717,21 +9694,21 @@
         <v>28</v>
       </c>
       <c r="G290">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H290">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I290">
         <v>44</v>
       </c>
       <c r="J290" s="1">
-        <v>0.2727</v>
+        <v>0.15909999999999999</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9752,18 +9729,18 @@
         <v>82</v>
       </c>
       <c r="H291">
-        <v>328</v>
+        <v>164</v>
       </c>
       <c r="I291">
         <v>1968</v>
       </c>
       <c r="J291" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -9784,18 +9761,18 @@
         <v>173</v>
       </c>
       <c r="H292">
-        <v>688</v>
+        <v>344</v>
       </c>
       <c r="I292">
         <v>4128</v>
       </c>
       <c r="J292" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -9816,18 +9793,18 @@
         <v>74</v>
       </c>
       <c r="H293">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="I293">
         <v>888</v>
       </c>
       <c r="J293" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -9848,18 +9825,18 @@
         <v>110</v>
       </c>
       <c r="H294">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="I294">
         <v>1320</v>
       </c>
       <c r="J294" s="1">
-        <v>0.16289999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -9880,18 +9857,18 @@
         <v>160</v>
       </c>
       <c r="H295">
-        <v>319</v>
+        <v>160</v>
       </c>
       <c r="I295">
         <v>1920</v>
       </c>
       <c r="J295" s="1">
-        <v>0.1661</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -9912,18 +9889,18 @@
         <v>311</v>
       </c>
       <c r="H296">
-        <v>615</v>
+        <v>311</v>
       </c>
       <c r="I296">
         <v>3732</v>
       </c>
       <c r="J296" s="1">
-        <v>0.1648</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -9944,18 +9921,18 @@
         <v>286</v>
       </c>
       <c r="H297">
-        <v>572</v>
+        <v>286</v>
       </c>
       <c r="I297">
         <v>3432</v>
       </c>
       <c r="J297" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -9976,18 +9953,18 @@
         <v>12</v>
       </c>
       <c r="H298">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I298">
         <v>144</v>
       </c>
       <c r="J298" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10008,18 +9985,18 @@
         <v>85</v>
       </c>
       <c r="H299">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="I299">
         <v>1020</v>
       </c>
       <c r="J299" s="1">
-        <v>0.1676</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10040,18 +10017,18 @@
         <v>44</v>
       </c>
       <c r="H300">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I300">
         <v>528</v>
       </c>
       <c r="J300" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10072,18 +10049,18 @@
         <v>47</v>
       </c>
       <c r="H301">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="I301">
         <v>564</v>
       </c>
       <c r="J301" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10104,18 +10081,18 @@
         <v>91</v>
       </c>
       <c r="H302">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="I302">
         <v>1092</v>
       </c>
       <c r="J302" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10136,18 +10113,18 @@
         <v>13</v>
       </c>
       <c r="H303">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I303">
         <v>384</v>
       </c>
       <c r="J303" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10168,7 +10145,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10189,7 +10166,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10210,18 +10187,18 @@
         <v>17</v>
       </c>
       <c r="H306">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I306">
         <v>204</v>
       </c>
       <c r="J306" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10242,18 +10219,18 @@
         <v>48</v>
       </c>
       <c r="H307">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="I307">
         <v>564</v>
       </c>
       <c r="J307" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.5099999999999995E-2</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10274,18 +10251,18 @@
         <v>227</v>
       </c>
       <c r="H308">
-        <v>449</v>
+        <v>227</v>
       </c>
       <c r="I308">
         <v>2724</v>
       </c>
       <c r="J308" s="1">
-        <v>0.1648</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10306,18 +10283,18 @@
         <v>16</v>
       </c>
       <c r="H309">
-        <v>945</v>
+        <v>344</v>
       </c>
       <c r="I309">
         <v>5842</v>
       </c>
       <c r="J309" s="1">
-        <v>0.1618</v>
+        <v>5.8900000000000001E-2</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10338,18 +10315,18 @@
         <v>39</v>
       </c>
       <c r="H310">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I310">
         <v>156</v>
       </c>
       <c r="J310" s="1">
-        <v>0.25</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10370,18 +10347,18 @@
         <v>39</v>
       </c>
       <c r="H311">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I311">
         <v>39</v>
       </c>
       <c r="J311" s="1">
-        <v>0.25640000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10402,18 +10379,18 @@
         <v>44</v>
       </c>
       <c r="H312">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I312">
         <v>180</v>
       </c>
       <c r="J312" s="1">
-        <v>0.2167</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10434,18 +10411,18 @@
         <v>44</v>
       </c>
       <c r="H313">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I313">
         <v>45</v>
       </c>
       <c r="J313" s="1">
-        <v>0.22220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10466,18 +10443,18 @@
         <v>2</v>
       </c>
       <c r="H314">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I314">
         <v>4</v>
       </c>
       <c r="J314" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10509,7 +10486,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10541,7 +10518,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10562,18 +10539,18 @@
         <v>228</v>
       </c>
       <c r="H317">
-        <v>462</v>
+        <v>228</v>
       </c>
       <c r="I317">
         <v>2736</v>
       </c>
       <c r="J317" s="1">
-        <v>0.16889999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10594,18 +10571,18 @@
         <v>22</v>
       </c>
       <c r="H318">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I318">
         <v>300</v>
       </c>
       <c r="J318" s="1">
-        <v>0.15329999999999999</v>
+        <v>7.3300000000000004E-2</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10626,18 +10603,18 @@
         <v>184</v>
       </c>
       <c r="H319">
-        <v>365</v>
+        <v>184</v>
       </c>
       <c r="I319">
         <v>2196</v>
       </c>
       <c r="J319" s="1">
-        <v>0.16619999999999999</v>
+        <v>8.3799999999999999E-2</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10658,18 +10635,18 @@
         <v>3</v>
       </c>
       <c r="H320">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I320">
         <v>36</v>
       </c>
       <c r="J320" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10690,7 +10667,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10711,7 +10688,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -10729,7 +10706,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -10750,18 +10727,18 @@
         <v>96</v>
       </c>
       <c r="H324">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="I324">
         <v>2304</v>
       </c>
       <c r="J324" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -10782,18 +10759,18 @@
         <v>17</v>
       </c>
       <c r="H325">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I325">
         <v>204</v>
       </c>
       <c r="J325" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -10814,18 +10791,18 @@
         <v>109</v>
       </c>
       <c r="H326">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="I326">
         <v>1308</v>
       </c>
       <c r="J326" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -10846,18 +10823,18 @@
         <v>8</v>
       </c>
       <c r="H327">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I327">
         <v>96</v>
       </c>
       <c r="J327" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -10878,18 +10855,18 @@
         <v>34</v>
       </c>
       <c r="H328">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="I328">
         <v>408</v>
       </c>
       <c r="J328" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -10910,18 +10887,18 @@
         <v>5</v>
       </c>
       <c r="H329">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I329">
         <v>120</v>
       </c>
       <c r="J329" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -10942,18 +10919,18 @@
         <v>17</v>
       </c>
       <c r="H330">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I330">
         <v>204</v>
       </c>
       <c r="J330" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -10974,18 +10951,18 @@
         <v>7</v>
       </c>
       <c r="H331">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I331">
         <v>84</v>
       </c>
       <c r="J331" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -11006,18 +10983,18 @@
         <v>200</v>
       </c>
       <c r="H332">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I332">
         <v>2400</v>
       </c>
       <c r="J332" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11038,18 +11015,18 @@
         <v>14</v>
       </c>
       <c r="H333">
-        <v>826</v>
+        <v>434</v>
       </c>
       <c r="I333">
         <v>5110</v>
       </c>
       <c r="J333" s="1">
-        <v>0.16159999999999999</v>
+        <v>8.4900000000000003E-2</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11081,7 +11058,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11113,7 +11090,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11145,7 +11122,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11177,7 +11154,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11198,18 +11175,18 @@
         <v>10</v>
       </c>
       <c r="H338">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I338">
         <v>120</v>
       </c>
       <c r="J338" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11241,7 +11218,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11262,7 +11239,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11283,7 +11260,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11304,7 +11281,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11325,18 +11302,18 @@
         <v>392</v>
       </c>
       <c r="H343">
-        <v>1568</v>
+        <v>784</v>
       </c>
       <c r="I343">
         <v>9250</v>
       </c>
       <c r="J343" s="1">
-        <v>0.16950000000000001</v>
+        <v>8.48E-2</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11357,18 +11334,18 @@
         <v>39</v>
       </c>
       <c r="H344">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I344">
         <v>468</v>
       </c>
       <c r="J344" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11389,18 +11366,18 @@
         <v>778</v>
       </c>
       <c r="H345">
-        <v>1556</v>
+        <v>767</v>
       </c>
       <c r="I345">
         <v>9201</v>
       </c>
       <c r="J345" s="1">
-        <v>0.1691</v>
+        <v>8.3400000000000002E-2</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11421,18 +11398,18 @@
         <v>16</v>
       </c>
       <c r="H346">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I346">
         <v>192</v>
       </c>
       <c r="J346" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11453,18 +11430,18 @@
         <v>26</v>
       </c>
       <c r="H347">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I347">
         <v>312</v>
       </c>
       <c r="J347" s="1">
-        <v>0.1699</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11485,18 +11462,18 @@
         <v>24</v>
       </c>
       <c r="H348">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="I348">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="J348" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.0500000000000002E-2</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11517,18 +11494,18 @@
         <v>7</v>
       </c>
       <c r="H349">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I349">
         <v>40</v>
       </c>
       <c r="J349" s="1">
-        <v>0.35</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11549,18 +11526,18 @@
         <v>9</v>
       </c>
       <c r="H350">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I350">
         <v>108</v>
       </c>
       <c r="J350" s="1">
-        <v>0.16669999999999999</v>
+        <v>6.4799999999999996E-2</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11581,18 +11558,18 @@
         <v>925</v>
       </c>
       <c r="H351">
-        <v>1850</v>
+        <v>910</v>
       </c>
       <c r="I351">
         <v>10766</v>
       </c>
       <c r="J351" s="1">
-        <v>0.17180000000000001</v>
+        <v>8.4500000000000006E-2</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11613,18 +11590,18 @@
         <v>45</v>
       </c>
       <c r="H352">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="I352">
         <v>540</v>
       </c>
       <c r="J352" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.1500000000000003E-2</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11645,18 +11622,18 @@
         <v>35</v>
       </c>
       <c r="H353">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I353">
         <v>420</v>
       </c>
       <c r="J353" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -11677,18 +11654,18 @@
         <v>145</v>
       </c>
       <c r="H354">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="I354">
         <v>1740</v>
       </c>
       <c r="J354" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -11706,21 +11683,21 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H355">
-        <v>5518</v>
+        <v>2934</v>
       </c>
       <c r="I355">
-        <v>38161</v>
+        <v>36865</v>
       </c>
       <c r="J355" s="1">
-        <v>0.14460000000000001</v>
+        <v>7.9600000000000004E-2</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -11741,18 +11718,18 @@
         <v>88</v>
       </c>
       <c r="H356">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I356">
         <v>352</v>
       </c>
       <c r="J356" s="1">
-        <v>0.11360000000000001</v>
+        <v>9.0899999999999995E-2</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -11773,18 +11750,18 @@
         <v>88</v>
       </c>
       <c r="H357">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I357">
         <v>88</v>
       </c>
       <c r="J357" s="1">
-        <v>0.45450000000000002</v>
+        <v>0.36359999999999998</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -11805,18 +11782,18 @@
         <v>33</v>
       </c>
       <c r="H358">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I358">
         <v>132</v>
       </c>
       <c r="J358" s="1">
-        <v>0.21970000000000001</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -11837,18 +11814,18 @@
         <v>33</v>
       </c>
       <c r="H359">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I359">
         <v>33</v>
       </c>
       <c r="J359" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.18179999999999999</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B360" s="2">
         <v>2026</v>
@@ -11880,7 +11857,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B361" s="2">
         <v>2026</v>
@@ -11901,18 +11878,18 @@
         <v>10</v>
       </c>
       <c r="H361">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I361">
         <v>20</v>
       </c>
       <c r="J361" s="1">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B362" s="2">
         <v>2026</v>
@@ -11930,21 +11907,21 @@
         <v>26</v>
       </c>
       <c r="G362">
-        <v>3536</v>
+        <v>3296</v>
       </c>
       <c r="H362">
-        <v>7072</v>
+        <v>3296</v>
       </c>
       <c r="I362">
-        <v>42432</v>
+        <v>39552</v>
       </c>
       <c r="J362" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B363" s="2">
         <v>2026</v>
@@ -11965,18 +11942,18 @@
         <v>33</v>
       </c>
       <c r="H363">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="I363">
         <v>396</v>
       </c>
       <c r="J363" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B364" s="2">
         <v>2026</v>
@@ -11997,18 +11974,18 @@
         <v>11</v>
       </c>
       <c r="H364">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I364">
         <v>132</v>
       </c>
       <c r="J364" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B365" s="2">
         <v>2026</v>
@@ -12029,18 +12006,18 @@
         <v>24</v>
       </c>
       <c r="H365">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I365">
         <v>288</v>
       </c>
       <c r="J365" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B366" s="2">
         <v>2026</v>
@@ -12061,18 +12038,18 @@
         <v>4</v>
       </c>
       <c r="H366">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I366">
         <v>48</v>
       </c>
       <c r="J366" s="1">
-        <v>0.16669999999999999</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B367" s="2">
         <v>2026</v>
@@ -12090,21 +12067,21 @@
         <v>26</v>
       </c>
       <c r="G367">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H367">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I367">
         <v>64</v>
       </c>
       <c r="J367" s="1">
-        <v>0.125</v>
+        <v>4.6899999999999997E-2</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B368" s="2">
         <v>2026</v>
@@ -12119,7 +12096,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B369" s="2">
         <v>2026</v>
@@ -12137,21 +12114,21 @@
         <v>25</v>
       </c>
       <c r="G369">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H369">
-        <v>688</v>
+        <v>556</v>
       </c>
       <c r="I369">
-        <v>6696</v>
+        <v>6672</v>
       </c>
       <c r="J369" s="1">
-        <v>0.1027</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B370" s="2">
         <v>2026</v>
@@ -12172,18 +12149,18 @@
         <v>129</v>
       </c>
       <c r="H370">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I370">
         <v>1548</v>
       </c>
       <c r="J370" s="1">
-        <v>0.10340000000000001</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B371" s="2">
         <v>2026</v>
@@ -12201,21 +12178,21 @@
         <v>26</v>
       </c>
       <c r="G371">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="H371">
-        <v>600</v>
+        <v>544</v>
       </c>
       <c r="I371">
-        <v>6396</v>
+        <v>6636</v>
       </c>
       <c r="J371" s="1">
-        <v>9.3799999999999994E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B372" s="2">
         <v>2026</v>
@@ -12236,18 +12213,18 @@
         <v>315</v>
       </c>
       <c r="H372">
-        <v>389</v>
+        <v>315</v>
       </c>
       <c r="I372">
-        <v>3786</v>
+        <v>3780</v>
       </c>
       <c r="J372" s="1">
-        <v>0.1027</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B373" s="2">
         <v>2026</v>
@@ -12268,18 +12245,18 @@
         <v>20</v>
       </c>
       <c r="H373">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I373">
         <v>240</v>
       </c>
       <c r="J373" s="1">
-        <v>9.1700000000000004E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B374" s="2">
         <v>2026</v>
@@ -12300,18 +12277,18 @@
         <v>19</v>
       </c>
       <c r="H374">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I374">
         <v>228</v>
       </c>
       <c r="J374" s="1">
-        <v>0.1009</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B375" s="2">
         <v>2026</v>
@@ -12329,21 +12306,21 @@
         <v>25</v>
       </c>
       <c r="G375">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H375">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I375">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="J375" s="1">
-        <v>9.5200000000000007E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B376" s="2">
         <v>2026</v>
@@ -12364,18 +12341,18 @@
         <v>86</v>
       </c>
       <c r="H376">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I376">
         <v>1032</v>
       </c>
       <c r="J376" s="1">
-        <v>9.11E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B377" s="2">
         <v>2026</v>
@@ -12396,7 +12373,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A378" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B378" s="2">
         <v>2026</v>
@@ -12428,7 +12405,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A379" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B379" s="2">
         <v>2026</v>
@@ -12449,18 +12426,18 @@
         <v>32</v>
       </c>
       <c r="H379">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I379">
         <v>384</v>
       </c>
       <c r="J379" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>8.0699999999999994E-2</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A380" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B380" s="2">
         <v>2026</v>
@@ -12478,21 +12455,21 @@
         <v>26</v>
       </c>
       <c r="G380">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="H380">
-        <v>699</v>
+        <v>604</v>
       </c>
       <c r="I380">
-        <v>7212</v>
+        <v>7380</v>
       </c>
       <c r="J380" s="1">
-        <v>9.69E-2</v>
+        <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A381" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B381" s="2">
         <v>2026</v>
@@ -12510,21 +12487,21 @@
         <v>43</v>
       </c>
       <c r="G381">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H381">
-        <v>1653</v>
+        <v>1597</v>
       </c>
       <c r="I381">
         <v>17695</v>
       </c>
       <c r="J381" s="1">
-        <v>9.3399999999999997E-2</v>
+        <v>9.0300000000000005E-2</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A382" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B382" s="2">
         <v>2026</v>
@@ -12545,18 +12522,18 @@
         <v>175</v>
       </c>
       <c r="H382">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I382">
         <v>700</v>
       </c>
       <c r="J382" s="1">
-        <v>0.19289999999999999</v>
+        <v>0.18709999999999999</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A383" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B383" s="2">
         <v>2026</v>
@@ -12577,18 +12554,18 @@
         <v>175</v>
       </c>
       <c r="H383">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I383">
         <v>175</v>
       </c>
       <c r="J383" s="1">
-        <v>0.77139999999999997</v>
+        <v>0.74860000000000004</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A384" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B384" s="2">
         <v>2026</v>
@@ -12609,18 +12586,18 @@
         <v>48</v>
       </c>
       <c r="H384">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I384">
         <v>192</v>
       </c>
       <c r="J384" s="1">
-        <v>0.25519999999999998</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A385" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B385" s="2">
         <v>2026</v>
@@ -12641,18 +12618,18 @@
         <v>48</v>
       </c>
       <c r="H385">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I385">
         <v>48</v>
       </c>
       <c r="J385" s="1">
-        <v>0.9375</v>
+        <v>0.85419999999999996</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A386" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B386" s="2">
         <v>2026</v>
@@ -12673,7 +12650,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A387" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B387" s="2">
         <v>2026</v>
@@ -12694,18 +12671,18 @@
         <v>13</v>
       </c>
       <c r="H387">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I387">
         <v>26</v>
       </c>
       <c r="J387" s="1">
-        <v>0.30769999999999997</v>
+        <v>0.26919999999999999</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A388" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B388" s="2">
         <v>2026</v>
@@ -12726,18 +12703,18 @@
         <v>50</v>
       </c>
       <c r="H388">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I388">
         <v>600</v>
       </c>
       <c r="J388" s="1">
-        <v>0.1</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A389" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B389" s="2">
         <v>2026</v>
@@ -12758,18 +12735,18 @@
         <v>48</v>
       </c>
       <c r="H389">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I389">
         <v>576</v>
       </c>
       <c r="J389" s="1">
-        <v>9.5500000000000002E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A390" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B390" s="2">
         <v>2026</v>
@@ -12790,18 +12767,18 @@
         <v>17</v>
       </c>
       <c r="H390">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I390">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="J390" s="1">
-        <v>9.2600000000000002E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A391" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B391" s="2">
         <v>2026</v>
@@ -12833,7 +12810,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A392" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B392" s="2">
         <v>2026</v>
@@ -12854,18 +12831,18 @@
         <v>62</v>
       </c>
       <c r="H392">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I392">
         <v>744</v>
       </c>
       <c r="J392" s="1">
-        <v>9.4100000000000003E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A393" s="3">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B393" s="2">
         <v>2026</v>
@@ -12883,16 +12860,16 @@
         <v>28</v>
       </c>
       <c r="G393">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H393">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I393">
-        <v>744</v>
+        <v>348</v>
       </c>
       <c r="J393" s="1">
-        <v>2.1499999999999998E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\✓ Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD735507-0F8A-4CCF-B87C-D3351755BFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B87F87-CF07-4C62-8781-D448CF718B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -318,7 +318,7 @@
     <t>Divre II Pd</t>
   </si>
   <si>
-    <t>Divre I SU</t>
+    <t>Divre I Su</t>
   </si>
 </sst>
 </file>
@@ -727,7 +727,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -855,7 +855,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1719,7 +1719,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2647,7 +2647,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2775,7 +2775,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3191,7 +3191,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3767,7 +3767,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3895,7 +3895,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3927,7 +3927,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4631,7 +4631,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4727,7 +4727,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -5015,7 +5015,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -5079,7 +5079,7 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5175,7 +5175,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5335,7 +5335,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5431,7 +5431,7 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5687,7 +5687,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5719,7 +5719,7 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5847,7 +5847,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -6071,7 +6071,7 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6199,7 +6199,7 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6551,7 +6551,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6583,7 +6583,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6999,7 +6999,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7255,7 +7255,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7351,7 +7351,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7383,7 +7383,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7543,7 +7543,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7575,7 +7575,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7639,7 +7639,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7895,7 +7895,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -8023,7 +8023,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -8087,7 +8087,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -8119,7 +8119,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8151,7 +8151,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8343,7 +8343,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8375,7 +8375,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8439,7 +8439,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8471,7 +8471,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8503,7 +8503,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8535,7 +8535,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8567,7 +8567,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8599,7 +8599,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8663,7 +8663,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8759,7 +8759,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8887,7 +8887,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8919,7 +8919,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8951,7 +8951,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8983,7 +8983,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -9015,7 +9015,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -9079,7 +9079,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -9111,7 +9111,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -9175,7 +9175,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -9207,7 +9207,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9239,7 +9239,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9271,7 +9271,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9303,7 +9303,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9367,7 +9367,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9399,7 +9399,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9431,7 +9431,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9527,7 +9527,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9591,7 +9591,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9623,7 +9623,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9655,7 +9655,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9687,7 +9687,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9751,7 +9751,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9847,7 +9847,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9879,7 +9879,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9911,7 +9911,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9943,7 +9943,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9975,7 +9975,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -10103,7 +10103,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -10135,7 +10135,7 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -10167,7 +10167,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -10199,7 +10199,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -10231,7 +10231,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10263,7 +10263,7 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10295,7 +10295,7 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10391,7 +10391,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10423,7 +10423,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10455,7 +10455,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10487,7 +10487,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10583,7 +10583,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10615,7 +10615,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10647,7 +10647,7 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10711,7 +10711,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10775,7 +10775,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10839,7 +10839,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10871,7 +10871,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10903,7 +10903,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10935,7 +10935,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -11031,7 +11031,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -11063,7 +11063,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -11095,7 +11095,7 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -11127,7 +11127,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -11191,7 +11191,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -11223,7 +11223,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -11255,7 +11255,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11351,7 +11351,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11383,7 +11383,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11415,7 +11415,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11447,7 +11447,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11543,7 +11543,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11575,7 +11575,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11607,7 +11607,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11671,7 +11671,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11703,7 +11703,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11735,7 +11735,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11767,7 +11767,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11799,7 +11799,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11831,7 +11831,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11855,7 +11855,7 @@
         <v>6183</v>
       </c>
       <c r="I349">
-        <v>17695.2</v>
+        <v>17695</v>
       </c>
       <c r="J349" s="1">
         <v>0.34939999999999999</v>
@@ -11863,7 +11863,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11895,7 +11895,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11927,7 +11927,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11959,7 +11959,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -12023,7 +12023,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -12055,7 +12055,7 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -12087,7 +12087,7 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -12119,7 +12119,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -12151,7 +12151,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\4. Apr\KP\✓ Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B87F87-CF07-4C62-8781-D448CF718B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B9A980-00B3-476A-934C-C4CE31DB2514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Perawatan" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Perawatan!$A$1:$J$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Perawatan!$A$1:$J$386</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="93">
   <si>
     <t>Tahun</t>
   </si>
@@ -680,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045E82A1-AFA5-46B1-A9F4-12F5B515B637}">
-  <dimension ref="A1:J391"/>
+  <dimension ref="A1:J386"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
@@ -748,13 +748,13 @@
         <v>59</v>
       </c>
       <c r="H2">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="I2">
         <v>1416</v>
       </c>
       <c r="J2" s="1">
-        <v>0.33050000000000002</v>
+        <v>0.36370000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
@@ -780,13 +780,13 @@
         <v>47</v>
       </c>
       <c r="H3">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I3">
         <v>564</v>
       </c>
       <c r="J3" s="1">
-        <v>0.33510000000000001</v>
+        <v>0.3528</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
@@ -812,13 +812,13 @@
         <v>59</v>
       </c>
       <c r="H4">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I4">
         <v>708</v>
       </c>
       <c r="J4" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36020000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
@@ -844,13 +844,13 @@
         <v>398</v>
       </c>
       <c r="H5">
-        <v>1585</v>
+        <v>1689</v>
       </c>
       <c r="I5">
         <v>4776</v>
       </c>
       <c r="J5" s="1">
-        <v>0.33189999999999997</v>
+        <v>0.35360000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
@@ -876,13 +876,13 @@
         <v>398</v>
       </c>
       <c r="H6">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="I6">
         <v>398</v>
       </c>
       <c r="J6" s="1">
-        <v>0.50249999999999995</v>
+        <v>0.53269999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
@@ -940,13 +940,13 @@
         <v>61</v>
       </c>
       <c r="H8">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I8">
         <v>244</v>
       </c>
       <c r="J8" s="1">
-        <v>0.33200000000000002</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
@@ -972,13 +972,13 @@
         <v>59</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9">
         <v>59</v>
       </c>
       <c r="J9" s="1">
-        <v>0.67800000000000005</v>
+        <v>0.69489999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
@@ -1036,13 +1036,13 @@
         <v>265</v>
       </c>
       <c r="H11">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I11">
         <v>265</v>
       </c>
       <c r="J11" s="1">
-        <v>0.19620000000000001</v>
+        <v>0.21890000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -1068,13 +1068,13 @@
         <v>72</v>
       </c>
       <c r="H12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12">
         <v>72</v>
       </c>
       <c r="J12" s="1">
-        <v>0.31940000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
@@ -1100,13 +1100,13 @@
         <v>289</v>
       </c>
       <c r="H13">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>289</v>
       </c>
       <c r="J13" s="1">
-        <v>0.2145</v>
+        <v>0.2422</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
@@ -1196,13 +1196,13 @@
         <v>395</v>
       </c>
       <c r="H16">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I16">
         <v>395</v>
       </c>
       <c r="J16" s="1">
-        <v>0.53669999999999995</v>
+        <v>0.55189999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
@@ -1228,13 +1228,13 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I17">
         <v>400</v>
       </c>
       <c r="J17" s="1">
-        <v>0.31</v>
+        <v>0.34250000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
@@ -1260,13 +1260,13 @@
         <v>245</v>
       </c>
       <c r="H18">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I18">
         <v>245</v>
       </c>
       <c r="J18" s="1">
-        <v>0.39589999999999997</v>
+        <v>0.40410000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
@@ -1292,13 +1292,13 @@
         <v>69</v>
       </c>
       <c r="H19">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I19">
         <v>276</v>
       </c>
       <c r="J19" s="1">
-        <v>0.32969999999999999</v>
+        <v>0.35870000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
@@ -1388,13 +1388,13 @@
         <v>691280</v>
       </c>
       <c r="H22">
-        <v>2725277</v>
+        <v>3004367</v>
       </c>
       <c r="I22">
         <v>8295360</v>
       </c>
       <c r="J22" s="1">
-        <v>0.32850000000000001</v>
+        <v>0.36220000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
@@ -1420,13 +1420,13 @@
         <v>689046</v>
       </c>
       <c r="H23">
-        <v>422223.3</v>
+        <v>455300.3</v>
       </c>
       <c r="I23">
         <v>1378092</v>
       </c>
       <c r="J23" s="1">
-        <v>0.30640000000000001</v>
+        <v>0.33040000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
@@ -1452,13 +1452,13 @@
         <v>647</v>
       </c>
       <c r="H24">
-        <v>5158</v>
+        <v>5565</v>
       </c>
       <c r="I24">
         <v>15528</v>
       </c>
       <c r="J24" s="1">
-        <v>0.3322</v>
+        <v>0.3584</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
@@ -1484,13 +1484,13 @@
         <v>691280</v>
       </c>
       <c r="H25">
-        <v>984867</v>
+        <v>1042197</v>
       </c>
       <c r="I25">
         <v>2765120</v>
       </c>
       <c r="J25" s="1">
-        <v>0.35620000000000002</v>
+        <v>0.37690000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
@@ -1516,13 +1516,13 @@
         <v>691280</v>
       </c>
       <c r="H26">
-        <v>326911</v>
+        <v>345340</v>
       </c>
       <c r="I26">
         <v>691280</v>
       </c>
       <c r="J26" s="1">
-        <v>0.47289999999999999</v>
+        <v>0.49959999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
@@ -1548,13 +1548,13 @@
         <v>346</v>
       </c>
       <c r="H27">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I27">
         <v>1384</v>
       </c>
       <c r="J27" s="1">
-        <v>0.31</v>
+        <v>0.31719999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
@@ -1580,13 +1580,13 @@
         <v>501</v>
       </c>
       <c r="H28">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I28">
         <v>501</v>
       </c>
       <c r="J28" s="1">
-        <v>0.43909999999999999</v>
+        <v>0.46710000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
@@ -1612,13 +1612,13 @@
         <v>1109</v>
       </c>
       <c r="H29">
-        <v>691</v>
+        <v>736</v>
       </c>
       <c r="I29">
         <v>2218</v>
       </c>
       <c r="J29" s="1">
-        <v>0.3115</v>
+        <v>0.33179999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
@@ -1644,13 +1644,13 @@
         <v>649</v>
       </c>
       <c r="H30">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I30">
         <v>649</v>
       </c>
       <c r="J30" s="1">
-        <v>0.34820000000000001</v>
+        <v>0.35749999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
@@ -1676,13 +1676,13 @@
         <v>331</v>
       </c>
       <c r="H31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I31">
         <v>331</v>
       </c>
       <c r="J31" s="1">
-        <v>0.2024</v>
+        <v>0.2175</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
@@ -1740,13 +1740,13 @@
         <v>59</v>
       </c>
       <c r="H33">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="I33">
         <v>1416</v>
       </c>
       <c r="J33" s="1">
-        <v>0.32490000000000002</v>
+        <v>0.35809999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
@@ -1772,13 +1772,13 @@
         <v>47</v>
       </c>
       <c r="H34">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="I34">
         <v>564</v>
       </c>
       <c r="J34" s="1">
-        <v>0.32619999999999999</v>
+        <v>0.3599</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
@@ -1804,13 +1804,13 @@
         <v>691280</v>
       </c>
       <c r="H35">
-        <v>2710957</v>
+        <v>3011115</v>
       </c>
       <c r="I35">
         <v>8295360</v>
       </c>
       <c r="J35" s="1">
-        <v>0.32679999999999998</v>
+        <v>0.36299999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
@@ -1836,13 +1836,13 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>6844</v>
+        <v>7708</v>
       </c>
       <c r="I36">
         <v>20580</v>
       </c>
       <c r="J36" s="1">
-        <v>0.33260000000000001</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
@@ -1868,13 +1868,13 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>984</v>
+        <v>1091</v>
       </c>
       <c r="I37">
         <v>3024</v>
       </c>
       <c r="J37" s="1">
-        <v>0.32540000000000002</v>
+        <v>0.36080000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>6360</v>
+        <v>6895</v>
       </c>
       <c r="I38">
         <v>19416</v>
       </c>
       <c r="J38" s="1">
-        <v>0.3276</v>
+        <v>0.35510000000000003</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
@@ -1932,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>8963</v>
+        <v>9815</v>
       </c>
       <c r="I39">
         <v>27456</v>
       </c>
       <c r="J39" s="1">
-        <v>0.32640000000000002</v>
+        <v>0.35749999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
@@ -1964,13 +1964,13 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="I40">
         <v>1404</v>
       </c>
       <c r="J40" s="1">
-        <v>0.31480000000000002</v>
+        <v>0.35039999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
@@ -1996,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="I41">
         <v>556</v>
       </c>
       <c r="J41" s="1">
-        <v>0.33090000000000003</v>
+        <v>0.37230000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42">
         <v>48</v>
       </c>
       <c r="J42" s="1">
-        <v>0.35420000000000001</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="I43">
         <v>950</v>
       </c>
       <c r="J43" s="1">
-        <v>0.32629999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1158</v>
+        <v>1249</v>
       </c>
       <c r="I44">
         <v>3552</v>
       </c>
       <c r="J44" s="1">
-        <v>0.32600000000000001</v>
+        <v>0.35160000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
@@ -2124,13 +2124,13 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>804</v>
+        <v>882</v>
       </c>
       <c r="I45">
         <v>2508</v>
       </c>
       <c r="J45" s="1">
-        <v>0.3206</v>
+        <v>0.35170000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
@@ -2156,13 +2156,13 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="I46">
         <v>624</v>
       </c>
       <c r="J46" s="1">
-        <v>0.33810000000000001</v>
+        <v>0.3574</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>9481</v>
+        <v>10520</v>
       </c>
       <c r="I47">
         <v>25564</v>
       </c>
       <c r="J47" s="1">
-        <v>0.37090000000000001</v>
+        <v>0.41149999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
@@ -2220,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I48">
         <v>228</v>
       </c>
       <c r="J48" s="1">
-        <v>0.34210000000000002</v>
+        <v>0.39910000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
@@ -2252,13 +2252,13 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I49">
         <v>57</v>
       </c>
       <c r="J49" s="1">
-        <v>0.38600000000000001</v>
+        <v>0.54390000000000005</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
@@ -2284,13 +2284,13 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="I50">
         <v>548</v>
       </c>
       <c r="J50" s="1">
-        <v>0.34489999999999998</v>
+        <v>0.37230000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
@@ -2348,13 +2348,13 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I52">
         <v>90</v>
       </c>
       <c r="J52" s="1">
-        <v>0.23330000000000001</v>
+        <v>0.35560000000000003</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
@@ -2380,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>42897</v>
+        <v>46345</v>
       </c>
       <c r="I53">
         <v>117348</v>
       </c>
       <c r="J53" s="1">
-        <v>0.36559999999999998</v>
+        <v>0.39489999999999997</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
@@ -2412,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="I54">
         <v>1584</v>
       </c>
       <c r="J54" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35610000000000003</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
@@ -2444,13 +2444,13 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I55">
         <v>516</v>
       </c>
       <c r="J55" s="1">
-        <v>0.31590000000000001</v>
+        <v>0.34499999999999997</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="I56">
         <v>1416</v>
       </c>
       <c r="J56" s="1">
-        <v>0.32269999999999999</v>
+        <v>0.35170000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
@@ -2508,13 +2508,13 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="I57">
         <v>137</v>
       </c>
       <c r="J57" s="1">
-        <v>0.47449999999999998</v>
+        <v>0.63500000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
@@ -2540,13 +2540,13 @@
         <v>366</v>
       </c>
       <c r="H58">
-        <v>2928</v>
+        <v>3236</v>
       </c>
       <c r="I58">
         <v>8784</v>
       </c>
       <c r="J58" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36840000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
@@ -2572,13 +2572,13 @@
         <v>244</v>
       </c>
       <c r="H59">
-        <v>975</v>
+        <v>1171</v>
       </c>
       <c r="I59">
         <v>2928</v>
       </c>
       <c r="J59" s="1">
-        <v>0.33300000000000002</v>
+        <v>0.39989999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
@@ -2604,13 +2604,13 @@
         <v>640</v>
       </c>
       <c r="H60">
-        <v>2576</v>
+        <v>2628</v>
       </c>
       <c r="I60">
         <v>7680</v>
       </c>
       <c r="J60" s="1">
-        <v>0.33539999999999998</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
@@ -2636,13 +2636,13 @@
         <v>696</v>
       </c>
       <c r="H61">
-        <v>2982</v>
+        <v>3112</v>
       </c>
       <c r="I61">
         <v>8952</v>
       </c>
       <c r="J61" s="1">
-        <v>0.33310000000000001</v>
+        <v>0.34760000000000002</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
@@ -2668,13 +2668,13 @@
         <v>90</v>
       </c>
       <c r="H62">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="I62">
         <v>1092</v>
       </c>
       <c r="J62" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34429999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
@@ -2700,13 +2700,13 @@
         <v>8</v>
       </c>
       <c r="H63">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I63">
         <v>240</v>
       </c>
       <c r="J63" s="1">
-        <v>0.3417</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
@@ -2732,13 +2732,13 @@
         <v>25</v>
       </c>
       <c r="H64">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="I64">
         <v>300</v>
       </c>
       <c r="J64" s="1">
-        <v>0.32329999999999998</v>
+        <v>0.3967</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
@@ -2764,13 +2764,13 @@
         <v>3</v>
       </c>
       <c r="H65">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I65">
         <v>36</v>
       </c>
       <c r="J65" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38890000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
@@ -2796,13 +2796,13 @@
         <v>73</v>
       </c>
       <c r="H66">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="I66">
         <v>876</v>
       </c>
       <c r="J66" s="1">
-        <v>0.32879999999999998</v>
+        <v>0.34250000000000003</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
@@ -2828,13 +2828,13 @@
         <v>139</v>
       </c>
       <c r="H67">
-        <v>564</v>
+        <v>651</v>
       </c>
       <c r="I67">
         <v>1668</v>
       </c>
       <c r="J67" s="1">
-        <v>0.33810000000000001</v>
+        <v>0.39029999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
@@ -2860,13 +2860,13 @@
         <v>273</v>
       </c>
       <c r="H68">
-        <v>1084</v>
+        <v>1150</v>
       </c>
       <c r="I68">
         <v>3276</v>
       </c>
       <c r="J68" s="1">
-        <v>0.33090000000000003</v>
+        <v>0.35099999999999998</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
@@ -2892,13 +2892,13 @@
         <v>14</v>
       </c>
       <c r="H69">
-        <v>1680</v>
+        <v>1820</v>
       </c>
       <c r="I69">
         <v>5110</v>
       </c>
       <c r="J69" s="1">
-        <v>0.32879999999999998</v>
+        <v>0.35620000000000002</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
@@ -3116,13 +3116,13 @@
         <v>189</v>
       </c>
       <c r="H76">
-        <v>755</v>
+        <v>858</v>
       </c>
       <c r="I76">
         <v>2268</v>
       </c>
       <c r="J76" s="1">
-        <v>0.33289999999999997</v>
+        <v>0.37830000000000003</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
@@ -3148,13 +3148,13 @@
         <v>287</v>
       </c>
       <c r="H77">
-        <v>1159</v>
+        <v>1357</v>
       </c>
       <c r="I77">
         <v>3444</v>
       </c>
       <c r="J77" s="1">
-        <v>0.33650000000000002</v>
+        <v>0.39400000000000002</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
@@ -3180,13 +3180,13 @@
         <v>74</v>
       </c>
       <c r="H78">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="I78">
         <v>948</v>
       </c>
       <c r="J78" s="1">
-        <v>0.33860000000000001</v>
+        <v>0.38819999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>123</v>
       </c>
       <c r="H79">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="I79">
         <v>1632</v>
       </c>
       <c r="J79" s="1">
-        <v>0.32169999999999999</v>
+        <v>0.33090000000000003</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="H80">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I80">
         <v>348</v>
       </c>
       <c r="J80" s="1">
-        <v>0.33050000000000002</v>
+        <v>0.34200000000000003</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
@@ -3308,13 +3308,13 @@
         <v>293</v>
       </c>
       <c r="H82">
-        <v>2345</v>
+        <v>2599</v>
       </c>
       <c r="I82">
         <v>7032</v>
       </c>
       <c r="J82" s="1">
-        <v>0.33350000000000002</v>
+        <v>0.36959999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
@@ -3331,22 +3331,22 @@
         <v>22</v>
       </c>
       <c r="E83" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G83">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H83">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="I83">
-        <v>444</v>
+        <v>192</v>
       </c>
       <c r="J83" s="1">
-        <v>0.33560000000000001</v>
+        <v>0.35420000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
@@ -3363,22 +3363,22 @@
         <v>22</v>
       </c>
       <c r="E84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G84">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="H84">
-        <v>2018</v>
+        <v>162</v>
       </c>
       <c r="I84">
-        <v>5916</v>
+        <v>444</v>
       </c>
       <c r="J84" s="1">
-        <v>0.34110000000000001</v>
+        <v>0.3649</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
@@ -3395,22 +3395,22 @@
         <v>22</v>
       </c>
       <c r="E85" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G85">
-        <v>749</v>
+        <v>493</v>
       </c>
       <c r="H85">
-        <v>2998</v>
+        <v>2141</v>
       </c>
       <c r="I85">
-        <v>8988</v>
+        <v>5916</v>
       </c>
       <c r="J85" s="1">
-        <v>0.33360000000000001</v>
+        <v>0.3619</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
@@ -3427,22 +3427,22 @@
         <v>22</v>
       </c>
       <c r="E86" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G86">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="H86">
-        <v>241</v>
+        <v>7</v>
       </c>
       <c r="I86">
-        <v>660</v>
+        <v>24</v>
       </c>
       <c r="J86" s="1">
-        <v>0.36520000000000002</v>
+        <v>0.29170000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
@@ -3459,22 +3459,22 @@
         <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G87">
-        <v>47</v>
+        <v>749</v>
       </c>
       <c r="H87">
-        <v>376</v>
+        <v>3251</v>
       </c>
       <c r="I87">
-        <v>1128</v>
+        <v>8988</v>
       </c>
       <c r="J87" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36170000000000002</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
@@ -3497,16 +3497,16 @@
         <v>26</v>
       </c>
       <c r="G88">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="H88">
-        <v>641</v>
+        <v>692</v>
       </c>
       <c r="I88">
         <v>1932</v>
       </c>
       <c r="J88" s="1">
-        <v>0.33179999999999998</v>
+        <v>0.35820000000000002</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
@@ -3523,22 +3523,22 @@
         <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="H89">
-        <v>7</v>
+        <v>416</v>
       </c>
       <c r="I89">
-        <v>24</v>
+        <v>1128</v>
       </c>
       <c r="J89" s="1">
-        <v>0.29170000000000001</v>
+        <v>0.36880000000000002</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
@@ -3555,22 +3555,22 @@
         <v>22</v>
       </c>
       <c r="E90" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G90">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H90">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="I90">
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="J90" s="1">
-        <v>0.33150000000000002</v>
+        <v>0.38179999999999997</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
@@ -3584,25 +3584,25 @@
         <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H91">
-        <v>526</v>
+        <v>190</v>
       </c>
       <c r="I91">
-        <v>1095</v>
+        <v>540</v>
       </c>
       <c r="J91" s="1">
-        <v>0.48039999999999999</v>
+        <v>0.35189999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
@@ -3619,22 +3619,22 @@
         <v>23</v>
       </c>
       <c r="E92" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G92">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H92">
-        <v>18</v>
+        <v>572</v>
       </c>
       <c r="I92">
-        <v>60</v>
+        <v>1095</v>
       </c>
       <c r="J92" s="1">
-        <v>0.3</v>
+        <v>0.52239999999999998</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
@@ -3651,22 +3651,22 @@
         <v>23</v>
       </c>
       <c r="E93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G93">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H93">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I93">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="J93" s="1">
-        <v>0.5333</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
@@ -3683,22 +3683,22 @@
         <v>23</v>
       </c>
       <c r="E94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G94">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H94">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="I94">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="J94" s="1">
-        <v>0.26519999999999999</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
@@ -3715,22 +3715,22 @@
         <v>23</v>
       </c>
       <c r="E95" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G95">
         <v>33</v>
       </c>
       <c r="H95">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I95">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="J95" s="1">
-        <v>0.2424</v>
+        <v>0.29549999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
@@ -3747,22 +3747,22 @@
         <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G96">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I96">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J96" s="1">
-        <v>0.25</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
@@ -3785,16 +3785,16 @@
         <v>28</v>
       </c>
       <c r="G97">
+        <v>9</v>
+      </c>
+      <c r="H97">
         <v>8</v>
-      </c>
-      <c r="H97">
-        <v>6</v>
       </c>
       <c r="I97">
         <v>18</v>
       </c>
       <c r="J97" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
@@ -3811,22 +3811,22 @@
         <v>23</v>
       </c>
       <c r="E98" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G98">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H98">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="I98">
-        <v>552</v>
+        <v>4</v>
       </c>
       <c r="J98" s="1">
-        <v>0.33879999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
@@ -3852,13 +3852,13 @@
         <v>30</v>
       </c>
       <c r="H99">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I99">
         <v>360</v>
       </c>
       <c r="J99" s="1">
-        <v>0.33610000000000001</v>
+        <v>0.3639</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
@@ -3884,13 +3884,13 @@
         <v>6</v>
       </c>
       <c r="H100">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I100">
         <v>72</v>
       </c>
       <c r="J100" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34720000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
@@ -3913,16 +3913,16 @@
         <v>26</v>
       </c>
       <c r="G101">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H101">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="I101">
         <v>623</v>
       </c>
       <c r="J101" s="1">
-        <v>0.34189999999999998</v>
+        <v>0.35959999999999998</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
@@ -3936,25 +3936,25 @@
         <v>13</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E102" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G102">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H102">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="I102">
-        <v>192</v>
+        <v>552</v>
       </c>
       <c r="J102" s="1">
-        <v>0.35420000000000001</v>
+        <v>0.35870000000000002</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
@@ -3980,13 +3980,13 @@
         <v>458</v>
       </c>
       <c r="H103">
-        <v>3464</v>
+        <v>4104</v>
       </c>
       <c r="I103">
         <v>10992</v>
       </c>
       <c r="J103" s="1">
-        <v>0.31509999999999999</v>
+        <v>0.37340000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
@@ -4012,13 +4012,13 @@
         <v>5</v>
       </c>
       <c r="H104">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I104">
         <v>60</v>
       </c>
       <c r="J104" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
@@ -4044,13 +4044,13 @@
         <v>43</v>
       </c>
       <c r="H105">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I105">
         <v>516</v>
       </c>
       <c r="J105" s="1">
-        <v>0.29260000000000003</v>
+        <v>0.34689999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
@@ -4076,13 +4076,13 @@
         <v>665</v>
       </c>
       <c r="H106">
-        <v>2666</v>
+        <v>2832</v>
       </c>
       <c r="I106">
         <v>7992</v>
       </c>
       <c r="J106" s="1">
-        <v>0.33360000000000001</v>
+        <v>0.35439999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
@@ -4108,13 +4108,13 @@
         <v>1043</v>
       </c>
       <c r="H107">
-        <v>3620</v>
+        <v>4283</v>
       </c>
       <c r="I107">
         <v>12264</v>
       </c>
       <c r="J107" s="1">
-        <v>0.29520000000000002</v>
+        <v>0.34920000000000001</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
@@ -4140,13 +4140,13 @@
         <v>71</v>
       </c>
       <c r="H108">
-        <v>263</v>
+        <v>306</v>
       </c>
       <c r="I108">
         <v>852</v>
       </c>
       <c r="J108" s="1">
-        <v>0.30869999999999997</v>
+        <v>0.35920000000000002</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
@@ -4172,13 +4172,13 @@
         <v>22</v>
       </c>
       <c r="H109">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="I109">
         <v>528</v>
       </c>
       <c r="J109" s="1">
-        <v>0.29360000000000003</v>
+        <v>0.36170000000000002</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
@@ -4204,13 +4204,13 @@
         <v>5</v>
       </c>
       <c r="H110">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I110">
         <v>60</v>
       </c>
       <c r="J110" s="1">
-        <v>0.26669999999999999</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
@@ -4268,13 +4268,13 @@
         <v>81</v>
       </c>
       <c r="H112">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="I112">
         <v>972</v>
       </c>
       <c r="J112" s="1">
-        <v>0.31069999999999998</v>
+        <v>0.35389999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
@@ -4300,13 +4300,13 @@
         <v>52</v>
       </c>
       <c r="H113">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="I113">
         <v>624</v>
       </c>
       <c r="J113" s="1">
-        <v>0.28210000000000002</v>
+        <v>0.33650000000000002</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
@@ -4332,13 +4332,13 @@
         <v>44</v>
       </c>
       <c r="H114">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I114">
         <v>528</v>
       </c>
       <c r="J114" s="1">
-        <v>0.3125</v>
+        <v>0.34470000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
@@ -4355,22 +4355,22 @@
         <v>23</v>
       </c>
       <c r="E115" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G115">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H115">
-        <v>1573</v>
+        <v>2</v>
       </c>
       <c r="I115">
-        <v>4046</v>
+        <v>4</v>
       </c>
       <c r="J115" s="1">
-        <v>0.38879999999999998</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
@@ -4387,22 +4387,22 @@
         <v>23</v>
       </c>
       <c r="E116" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G116">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H116">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I116">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="J116" s="1">
-        <v>0.38240000000000002</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
@@ -4419,22 +4419,22 @@
         <v>23</v>
       </c>
       <c r="E117" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G117">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="I117">
-        <v>17</v>
+        <v>2256</v>
       </c>
       <c r="J117" s="1">
-        <v>0</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
@@ -4451,22 +4451,22 @@
         <v>23</v>
       </c>
       <c r="E118" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G118">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H118">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="I118">
-        <v>180</v>
+        <v>516</v>
       </c>
       <c r="J118" s="1">
-        <v>0.35</v>
+        <v>0.3508</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
@@ -4483,22 +4483,22 @@
         <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G119">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H119">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="I119">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="J119" s="1">
-        <v>0.31109999999999999</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
@@ -4515,22 +4515,22 @@
         <v>23</v>
       </c>
       <c r="E120" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G120">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="I120">
-        <v>4</v>
+        <v>624</v>
       </c>
       <c r="J120" s="1">
-        <v>0.5</v>
+        <v>0.34129999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
@@ -4541,28 +4541,28 @@
         <v>2026</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E121" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G121">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H121">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="I121">
-        <v>24</v>
+        <v>492</v>
       </c>
       <c r="J121" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.35160000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
@@ -4573,28 +4573,28 @@
         <v>2026</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E122" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G122">
-        <v>188</v>
+        <v>585</v>
       </c>
       <c r="H122">
-        <v>619</v>
+        <v>2593</v>
       </c>
       <c r="I122">
-        <v>2256</v>
+        <v>7020</v>
       </c>
       <c r="J122" s="1">
-        <v>0.27439999999999998</v>
+        <v>0.36940000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
@@ -4605,28 +4605,28 @@
         <v>2026</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E123" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G123">
-        <v>43</v>
+        <v>383</v>
       </c>
       <c r="H123">
-        <v>146</v>
+        <v>3431</v>
       </c>
       <c r="I123">
-        <v>516</v>
+        <v>9144</v>
       </c>
       <c r="J123" s="1">
-        <v>0.28289999999999998</v>
+        <v>0.37519999999999998</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
@@ -4637,28 +4637,28 @@
         <v>2026</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E124" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G124">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H124">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="I124">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="J124" s="1">
-        <v>0.34520000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
@@ -4669,28 +4669,28 @@
         <v>2026</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G125">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="I125">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="J125" s="1">
-        <v>0.31569999999999998</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
@@ -4707,22 +4707,22 @@
         <v>22</v>
       </c>
       <c r="E126" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G126">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H126">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="I126">
-        <v>492</v>
+        <v>264</v>
       </c>
       <c r="J126" s="1">
-        <v>0.33129999999999998</v>
+        <v>0.39019999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
@@ -4739,22 +4739,22 @@
         <v>22</v>
       </c>
       <c r="E127" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G127">
-        <v>585</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>2343</v>
+        <v>4</v>
       </c>
       <c r="I127">
-        <v>7020</v>
+        <v>12</v>
       </c>
       <c r="J127" s="1">
-        <v>0.33379999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
@@ -4771,22 +4771,22 @@
         <v>22</v>
       </c>
       <c r="E128" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G128">
-        <v>383</v>
+        <v>898</v>
       </c>
       <c r="H128">
-        <v>3050</v>
+        <v>4017</v>
       </c>
       <c r="I128">
-        <v>9144</v>
+        <v>10776</v>
       </c>
       <c r="J128" s="1">
-        <v>0.33360000000000001</v>
+        <v>0.37280000000000002</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
@@ -4803,22 +4803,22 @@
         <v>22</v>
       </c>
       <c r="E129" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="H129">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="I129">
-        <v>12</v>
+        <v>1512</v>
       </c>
       <c r="J129" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.37369999999999998</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
@@ -4835,22 +4835,22 @@
         <v>22</v>
       </c>
       <c r="E130" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H130">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="I130">
-        <v>12</v>
+        <v>336</v>
       </c>
       <c r="J130" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
@@ -4867,22 +4867,22 @@
         <v>22</v>
       </c>
       <c r="E131" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G131">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H131">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="I131">
-        <v>264</v>
+        <v>720</v>
       </c>
       <c r="J131" s="1">
-        <v>0.34089999999999998</v>
+        <v>0.34720000000000001</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
@@ -4899,22 +4899,22 @@
         <v>22</v>
       </c>
       <c r="E132" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H132">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="I132">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="J132" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.33810000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
@@ -4931,22 +4931,22 @@
         <v>22</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G133">
-        <v>898</v>
+        <v>7</v>
       </c>
       <c r="H133">
-        <v>3640</v>
+        <v>35</v>
       </c>
       <c r="I133">
-        <v>10776</v>
+        <v>84</v>
       </c>
       <c r="J133" s="1">
-        <v>0.33779999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
@@ -4963,22 +4963,22 @@
         <v>22</v>
       </c>
       <c r="E134" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G134">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="H134">
-        <v>509</v>
+        <v>16</v>
       </c>
       <c r="I134">
-        <v>1512</v>
+        <v>48</v>
       </c>
       <c r="J134" s="1">
-        <v>0.33660000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
@@ -4995,22 +4995,22 @@
         <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G135">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H135">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="I135">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="J135" s="1">
-        <v>0.33040000000000003</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
@@ -5024,25 +5024,25 @@
         <v>15</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E136" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G136">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="H136">
-        <v>240</v>
+        <v>2136</v>
       </c>
       <c r="I136">
-        <v>720</v>
+        <v>4745</v>
       </c>
       <c r="J136" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.45019999999999999</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
@@ -5056,25 +5056,25 @@
         <v>15</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E137" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G137">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="H137">
-        <v>208</v>
+        <v>50</v>
       </c>
       <c r="I137">
-        <v>624</v>
+        <v>112</v>
       </c>
       <c r="J137" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44640000000000002</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
@@ -5088,25 +5088,25 @@
         <v>15</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E138" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G138">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H138">
+        <v>8</v>
+      </c>
+      <c r="I138">
         <v>28</v>
       </c>
-      <c r="I138">
-        <v>84</v>
-      </c>
       <c r="J138" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.28570000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
@@ -5120,25 +5120,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E139" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G139">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H139">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I139">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J139" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
@@ -5152,25 +5152,25 @@
         <v>15</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E140" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G140">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H140">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="I140">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J140" s="1">
-        <v>0.5</v>
+        <v>0.64439999999999997</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
@@ -5187,22 +5187,22 @@
         <v>23</v>
       </c>
       <c r="E141" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G141">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H141">
-        <v>1981</v>
+        <v>9</v>
       </c>
       <c r="I141">
-        <v>4745</v>
+        <v>18</v>
       </c>
       <c r="J141" s="1">
-        <v>0.41749999999999998</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
@@ -5219,22 +5219,22 @@
         <v>23</v>
       </c>
       <c r="E142" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G142">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="I142">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="J142" s="1">
-        <v>0.40179999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
@@ -5251,22 +5251,22 @@
         <v>23</v>
       </c>
       <c r="E143" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G143">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="I143">
-        <v>28</v>
+        <v>492</v>
       </c>
       <c r="J143" s="1">
-        <v>0</v>
+        <v>0.34960000000000002</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
@@ -5283,22 +5283,22 @@
         <v>23</v>
       </c>
       <c r="E144" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G144">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H144">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="I144">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="J144" s="1">
-        <v>0.43890000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
@@ -5315,22 +5315,22 @@
         <v>23</v>
       </c>
       <c r="E145" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G145">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H145">
-        <v>29</v>
+        <v>248</v>
       </c>
       <c r="I145">
-        <v>45</v>
+        <v>708</v>
       </c>
       <c r="J145" s="1">
-        <v>0.64439999999999997</v>
+        <v>0.3503</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
@@ -5347,22 +5347,22 @@
         <v>23</v>
       </c>
       <c r="E146" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G146">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="H146">
-        <v>9</v>
+        <v>696</v>
       </c>
       <c r="I146">
-        <v>18</v>
+        <v>1956</v>
       </c>
       <c r="J146" s="1">
-        <v>0.5</v>
+        <v>0.35580000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
@@ -5373,28 +5373,28 @@
         <v>2026</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E147" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>3448</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>9288</v>
       </c>
       <c r="J147" s="1">
-        <v>0.5</v>
+        <v>0.37119999999999997</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
@@ -5405,28 +5405,28 @@
         <v>2026</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E148" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G148">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H148">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I148">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="J148" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36109999999999998</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
@@ -5437,28 +5437,28 @@
         <v>2026</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E149" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G149">
-        <v>12</v>
+        <v>590</v>
       </c>
       <c r="H149">
-        <v>47</v>
+        <v>2431</v>
       </c>
       <c r="I149">
-        <v>144</v>
+        <v>7080</v>
       </c>
       <c r="J149" s="1">
-        <v>0.32640000000000002</v>
+        <v>0.34339999999999998</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
@@ -5469,28 +5469,28 @@
         <v>2026</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E150" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G150">
-        <v>58</v>
+        <v>964</v>
       </c>
       <c r="H150">
-        <v>238</v>
+        <v>4250</v>
       </c>
       <c r="I150">
-        <v>708</v>
+        <v>11568</v>
       </c>
       <c r="J150" s="1">
-        <v>0.3362</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
@@ -5501,28 +5501,28 @@
         <v>2026</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E151" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G151">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="H151">
-        <v>683</v>
+        <v>393</v>
       </c>
       <c r="I151">
-        <v>2016</v>
+        <v>1152</v>
       </c>
       <c r="J151" s="1">
-        <v>0.33879999999999999</v>
+        <v>0.34110000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
@@ -5539,22 +5539,22 @@
         <v>22</v>
       </c>
       <c r="E152" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G152">
-        <v>387</v>
+        <v>13</v>
       </c>
       <c r="H152">
-        <v>3096</v>
+        <v>119</v>
       </c>
       <c r="I152">
-        <v>9288</v>
+        <v>312</v>
       </c>
       <c r="J152" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38140000000000002</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
@@ -5571,22 +5571,22 @@
         <v>22</v>
       </c>
       <c r="E153" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G153">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H153">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="I153">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="J153" s="1">
-        <v>0.33550000000000002</v>
+        <v>0.32140000000000002</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
@@ -5603,22 +5603,22 @@
         <v>22</v>
       </c>
       <c r="E154" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G154">
-        <v>590</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>2354</v>
+        <v>4</v>
       </c>
       <c r="I154">
-        <v>7080</v>
+        <v>12</v>
       </c>
       <c r="J154" s="1">
-        <v>0.33250000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
@@ -5635,22 +5635,22 @@
         <v>22</v>
       </c>
       <c r="E155" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G155">
-        <v>964</v>
+        <v>108</v>
       </c>
       <c r="H155">
-        <v>3903</v>
+        <v>376</v>
       </c>
       <c r="I155">
-        <v>11568</v>
+        <v>1296</v>
       </c>
       <c r="J155" s="1">
-        <v>0.33739999999999998</v>
+        <v>0.29010000000000002</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
@@ -5667,22 +5667,22 @@
         <v>22</v>
       </c>
       <c r="E156" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G156">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H156">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="I156">
-        <v>1152</v>
+        <v>564</v>
       </c>
       <c r="J156" s="1">
-        <v>0.32550000000000001</v>
+        <v>0.35460000000000003</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
@@ -5699,22 +5699,22 @@
         <v>22</v>
       </c>
       <c r="E157" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G157">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H157">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="I157">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="J157" s="1">
-        <v>0.3301</v>
+        <v>0.36899999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
@@ -5728,25 +5728,25 @@
         <v>16</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E158" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G158">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H158">
-        <v>26</v>
+        <v>4307</v>
       </c>
       <c r="I158">
-        <v>84</v>
+        <v>10950</v>
       </c>
       <c r="J158" s="1">
-        <v>0.3095</v>
+        <v>0.39329999999999998</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
@@ -5760,25 +5760,25 @@
         <v>16</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E159" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H159">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="I159">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="J159" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.29820000000000002</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
@@ -5792,25 +5792,25 @@
         <v>16</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E160" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G160">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="H160">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="I160">
-        <v>1296</v>
+        <v>57</v>
       </c>
       <c r="J160" s="1">
-        <v>0.28470000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
@@ -5824,25 +5824,25 @@
         <v>16</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E161" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G161">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H161">
-        <v>183</v>
+        <v>51</v>
       </c>
       <c r="I161">
-        <v>564</v>
+        <v>148</v>
       </c>
       <c r="J161" s="1">
-        <v>0.32450000000000001</v>
+        <v>0.34460000000000002</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
@@ -5856,25 +5856,25 @@
         <v>16</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E162" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G162">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H162">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="I162">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="J162" s="1">
-        <v>0.35709999999999997</v>
+        <v>0.29730000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
@@ -5891,22 +5891,22 @@
         <v>23</v>
       </c>
       <c r="E163" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G163">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H163">
-        <v>4012</v>
+        <v>1</v>
       </c>
       <c r="I163">
-        <v>10950</v>
+        <v>4</v>
       </c>
       <c r="J163" s="1">
-        <v>0.3664</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
@@ -5923,22 +5923,22 @@
         <v>23</v>
       </c>
       <c r="E164" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G164">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="H164">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="I164">
-        <v>228</v>
+        <v>18</v>
       </c>
       <c r="J164" s="1">
-        <v>0.29820000000000002</v>
+        <v>0.22220000000000001</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
@@ -5955,22 +5955,22 @@
         <v>23</v>
       </c>
       <c r="E165" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G165">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="I165">
-        <v>57</v>
+        <v>2040</v>
       </c>
       <c r="J165" s="1">
-        <v>0</v>
+        <v>0.35930000000000001</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
@@ -5987,22 +5987,22 @@
         <v>23</v>
       </c>
       <c r="E166" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G166">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H166">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="I166">
-        <v>148</v>
+        <v>432</v>
       </c>
       <c r="J166" s="1">
-        <v>0.32429999999999998</v>
+        <v>0.35880000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
@@ -6016,25 +6016,25 @@
         <v>16</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E167" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G167">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H167">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="I167">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="J167" s="1">
-        <v>0.2432</v>
+        <v>0.4551</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
@@ -6051,22 +6051,22 @@
         <v>23</v>
       </c>
       <c r="E168" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G168">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H168">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="I168">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="J168" s="1">
-        <v>0.25</v>
+        <v>0.35189999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
@@ -6083,22 +6083,22 @@
         <v>23</v>
       </c>
       <c r="E169" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G169">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="H169">
-        <v>4</v>
+        <v>370</v>
       </c>
       <c r="I169">
-        <v>18</v>
+        <v>1056</v>
       </c>
       <c r="J169" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.35039999999999999</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
@@ -6112,25 +6112,25 @@
         <v>16</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E170" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G170">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="H170">
-        <v>681</v>
+        <v>3</v>
       </c>
       <c r="I170">
-        <v>2040</v>
+        <v>8</v>
       </c>
       <c r="J170" s="1">
-        <v>0.33379999999999999</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
@@ -6144,25 +6144,25 @@
         <v>16</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E171" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G171">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H171">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="I171">
-        <v>432</v>
+        <v>216</v>
       </c>
       <c r="J171" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36570000000000003</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
@@ -6176,25 +6176,25 @@
         <v>16</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E172" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G172">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H172">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I172">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="J172" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36109999999999998</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
@@ -6208,25 +6208,25 @@
         <v>16</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E173" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G173">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="H173">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="I173">
-        <v>108</v>
+        <v>708</v>
       </c>
       <c r="J173" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.33900000000000002</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
@@ -6240,25 +6240,25 @@
         <v>16</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E174" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G174">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="H174">
-        <v>354</v>
+        <v>40</v>
       </c>
       <c r="I174">
-        <v>1056</v>
+        <v>59</v>
       </c>
       <c r="J174" s="1">
-        <v>0.3352</v>
+        <v>0.67800000000000005</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
@@ -6272,25 +6272,25 @@
         <v>16</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E175" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G175">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H175">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I175">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J175" s="1">
-        <v>0.375</v>
+        <v>0.61109999999999998</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
@@ -6307,22 +6307,22 @@
         <v>24</v>
       </c>
       <c r="E176" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G176">
         <v>9</v>
       </c>
       <c r="H176">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="I176">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="J176" s="1">
-        <v>0.33800000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
@@ -6339,22 +6339,22 @@
         <v>24</v>
       </c>
       <c r="E177" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G177">
         <v>9</v>
       </c>
       <c r="H177">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I177">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="J177" s="1">
-        <v>0.34260000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
@@ -6371,22 +6371,22 @@
         <v>24</v>
       </c>
       <c r="E178" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G178">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="H178">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="I178">
-        <v>708</v>
+        <v>85</v>
       </c>
       <c r="J178" s="1">
-        <v>0.33050000000000002</v>
+        <v>0.4471</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
@@ -6403,22 +6403,22 @@
         <v>24</v>
       </c>
       <c r="E179" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G179">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H179">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I179">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="J179" s="1">
-        <v>0.67800000000000005</v>
+        <v>0.77780000000000005</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
@@ -6435,22 +6435,22 @@
         <v>24</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G180">
         <v>9</v>
       </c>
       <c r="H180">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I180">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J180" s="1">
-        <v>0.61109999999999998</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
@@ -6467,22 +6467,22 @@
         <v>24</v>
       </c>
       <c r="E181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G181">
+        <v>41</v>
+      </c>
+      <c r="H181">
         <v>36</v>
       </c>
-      <c r="F181" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G181">
-        <v>9</v>
-      </c>
-      <c r="H181">
-        <v>12</v>
-      </c>
       <c r="I181">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J181" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
@@ -6499,22 +6499,22 @@
         <v>24</v>
       </c>
       <c r="E182" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G182">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="H182">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I182">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="J182" s="1">
-        <v>1</v>
+        <v>0.69489999999999996</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
@@ -6531,22 +6531,22 @@
         <v>24</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G183">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="H183">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="I183">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="J183" s="1">
-        <v>0.4471</v>
+        <v>0.30559999999999998</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
@@ -6563,22 +6563,22 @@
         <v>24</v>
       </c>
       <c r="E184" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G184">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H184">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I184">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J184" s="1">
-        <v>0.77780000000000005</v>
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
@@ -6595,22 +6595,22 @@
         <v>24</v>
       </c>
       <c r="E185" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G185">
         <v>9</v>
       </c>
       <c r="H185">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I185">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J185" s="1">
-        <v>0.55559999999999998</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
@@ -6627,22 +6627,22 @@
         <v>24</v>
       </c>
       <c r="E186" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G186">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H186">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I186">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J186" s="1">
-        <v>0.78049999999999997</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
@@ -6659,22 +6659,22 @@
         <v>24</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G187">
-        <v>59</v>
+        <v>188993</v>
       </c>
       <c r="H187">
-        <v>41</v>
+        <v>810883</v>
       </c>
       <c r="I187">
-        <v>59</v>
+        <v>2267916</v>
       </c>
       <c r="J187" s="1">
-        <v>0.69489999999999996</v>
+        <v>0.35749999999999998</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
@@ -6691,22 +6691,22 @@
         <v>24</v>
       </c>
       <c r="E188" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G188">
-        <v>9</v>
+        <v>183511</v>
       </c>
       <c r="H188">
-        <v>9</v>
+        <v>121201</v>
       </c>
       <c r="I188">
-        <v>36</v>
+        <v>367022</v>
       </c>
       <c r="J188" s="1">
-        <v>0.25</v>
+        <v>0.33019999999999999</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
@@ -6723,22 +6723,22 @@
         <v>24</v>
       </c>
       <c r="E189" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G189">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="H189">
-        <v>30</v>
+        <v>1497</v>
       </c>
       <c r="I189">
-        <v>45</v>
+        <v>4176</v>
       </c>
       <c r="J189" s="1">
-        <v>0.66669999999999996</v>
+        <v>0.35849999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
@@ -6755,22 +6755,22 @@
         <v>24</v>
       </c>
       <c r="E190" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G190">
-        <v>9</v>
+        <v>188993</v>
       </c>
       <c r="H190">
-        <v>12</v>
+        <v>277905</v>
       </c>
       <c r="I190">
-        <v>36</v>
+        <v>755972</v>
       </c>
       <c r="J190" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36759999999999998</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
@@ -6787,22 +6787,22 @@
         <v>24</v>
       </c>
       <c r="E191" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G191">
-        <v>9</v>
+        <v>188993</v>
       </c>
       <c r="H191">
-        <v>3</v>
+        <v>66841</v>
       </c>
       <c r="I191">
-        <v>9</v>
+        <v>188993</v>
       </c>
       <c r="J191" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35370000000000001</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
@@ -6819,22 +6819,22 @@
         <v>24</v>
       </c>
       <c r="E192" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G192">
-        <v>188993</v>
+        <v>98</v>
       </c>
       <c r="H192">
-        <v>748905</v>
+        <v>136</v>
       </c>
       <c r="I192">
-        <v>2267916</v>
+        <v>392</v>
       </c>
       <c r="J192" s="1">
-        <v>0.33019999999999999</v>
+        <v>0.34689999999999999</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
@@ -6851,22 +6851,22 @@
         <v>24</v>
       </c>
       <c r="E193" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G193">
-        <v>183511</v>
+        <v>127</v>
       </c>
       <c r="H193">
-        <v>112306</v>
+        <v>44</v>
       </c>
       <c r="I193">
-        <v>367022</v>
+        <v>127</v>
       </c>
       <c r="J193" s="1">
-        <v>0.30599999999999999</v>
+        <v>0.34649999999999997</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
@@ -6883,22 +6883,22 @@
         <v>24</v>
       </c>
       <c r="E194" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G194">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="H194">
-        <v>1379</v>
+        <v>182</v>
       </c>
       <c r="I194">
-        <v>4176</v>
+        <v>542</v>
       </c>
       <c r="J194" s="1">
-        <v>0.33019999999999999</v>
+        <v>0.33579999999999999</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
@@ -6915,22 +6915,22 @@
         <v>24</v>
       </c>
       <c r="E195" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G195">
-        <v>188993</v>
+        <v>133</v>
       </c>
       <c r="H195">
-        <v>260084</v>
+        <v>78</v>
       </c>
       <c r="I195">
-        <v>755972</v>
+        <v>133</v>
       </c>
       <c r="J195" s="1">
-        <v>0.34399999999999997</v>
+        <v>0.58650000000000002</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
@@ -6947,22 +6947,22 @@
         <v>24</v>
       </c>
       <c r="E196" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G196">
-        <v>188993</v>
+        <v>67</v>
       </c>
       <c r="H196">
-        <v>60411</v>
+        <v>38</v>
       </c>
       <c r="I196">
-        <v>188993</v>
+        <v>67</v>
       </c>
       <c r="J196" s="1">
-        <v>0.3196</v>
+        <v>0.56720000000000004</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
@@ -6979,22 +6979,22 @@
         <v>24</v>
       </c>
       <c r="E197" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G197">
-        <v>98</v>
+        <v>5482</v>
       </c>
       <c r="H197">
-        <v>121</v>
+        <v>4942</v>
       </c>
       <c r="I197">
-        <v>392</v>
+        <v>10964</v>
       </c>
       <c r="J197" s="1">
-        <v>0.30869999999999997</v>
+        <v>0.45069999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
@@ -7011,22 +7011,22 @@
         <v>24</v>
       </c>
       <c r="E198" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G198">
-        <v>127</v>
+        <v>188377</v>
       </c>
       <c r="H198">
-        <v>40</v>
+        <v>763037</v>
       </c>
       <c r="I198">
-        <v>127</v>
+        <v>2260524</v>
       </c>
       <c r="J198" s="1">
-        <v>0.315</v>
+        <v>0.33750000000000002</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
@@ -7043,22 +7043,22 @@
         <v>24</v>
       </c>
       <c r="E199" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G199">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="H199">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I199">
-        <v>542</v>
+        <v>216</v>
       </c>
       <c r="J199" s="1">
-        <v>0.31</v>
+        <v>0.37959999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
@@ -7069,28 +7069,28 @@
         <v>2026</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E200" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G200">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="H200">
-        <v>66</v>
+        <v>2370</v>
       </c>
       <c r="I200">
-        <v>133</v>
+        <v>6312</v>
       </c>
       <c r="J200" s="1">
-        <v>0.49619999999999997</v>
+        <v>0.3755</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
@@ -7101,28 +7101,28 @@
         <v>2026</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E201" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G201">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="H201">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="I201">
-        <v>67</v>
+        <v>480</v>
       </c>
       <c r="J201" s="1">
-        <v>0.49249999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
@@ -7133,28 +7133,28 @@
         <v>2026</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E202" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G202">
-        <v>5482</v>
+        <v>408</v>
       </c>
       <c r="H202">
-        <v>4942</v>
+        <v>1661</v>
       </c>
       <c r="I202">
-        <v>10964</v>
+        <v>4896</v>
       </c>
       <c r="J202" s="1">
-        <v>0.45069999999999999</v>
+        <v>0.33929999999999999</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
@@ -7165,28 +7165,28 @@
         <v>2026</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E203" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G203">
-        <v>188377</v>
+        <v>550</v>
       </c>
       <c r="H203">
-        <v>717745</v>
+        <v>2326</v>
       </c>
       <c r="I203">
-        <v>2260524</v>
+        <v>6600</v>
       </c>
       <c r="J203" s="1">
-        <v>0.3175</v>
+        <v>0.35239999999999999</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
@@ -7197,28 +7197,28 @@
         <v>2026</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E204" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G204">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="H204">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="I204">
-        <v>216</v>
+        <v>912</v>
       </c>
       <c r="J204" s="1">
-        <v>0.35189999999999999</v>
+        <v>0.35310000000000002</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
@@ -7235,22 +7235,22 @@
         <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G205">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="H205">
-        <v>2104</v>
+        <v>53</v>
       </c>
       <c r="I205">
-        <v>6312</v>
+        <v>144</v>
       </c>
       <c r="J205" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36809999999999998</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
@@ -7267,19 +7267,19 @@
         <v>22</v>
       </c>
       <c r="E206" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G206">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H206">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="I206">
-        <v>480</v>
+        <v>228</v>
       </c>
       <c r="J206" s="1">
         <v>0.33329999999999999</v>
@@ -7299,22 +7299,22 @@
         <v>22</v>
       </c>
       <c r="E207" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G207">
-        <v>408</v>
+        <v>1</v>
       </c>
       <c r="H207">
-        <v>1636</v>
+        <v>4</v>
       </c>
       <c r="I207">
-        <v>4896</v>
+        <v>12</v>
       </c>
       <c r="J207" s="1">
-        <v>0.3342</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
@@ -7331,22 +7331,22 @@
         <v>22</v>
       </c>
       <c r="E208" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G208">
-        <v>550</v>
+        <v>4</v>
       </c>
       <c r="H208">
-        <v>2204</v>
+        <v>16</v>
       </c>
       <c r="I208">
-        <v>6600</v>
+        <v>48</v>
       </c>
       <c r="J208" s="1">
-        <v>0.33389999999999997</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
@@ -7363,22 +7363,22 @@
         <v>22</v>
       </c>
       <c r="E209" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G209">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="H209">
-        <v>304</v>
+        <v>129</v>
       </c>
       <c r="I209">
-        <v>912</v>
+        <v>372</v>
       </c>
       <c r="J209" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3468</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
@@ -7395,22 +7395,22 @@
         <v>22</v>
       </c>
       <c r="E210" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G210">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="H210">
-        <v>48</v>
+        <v>756</v>
       </c>
       <c r="I210">
-        <v>144</v>
+        <v>2100</v>
       </c>
       <c r="J210" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
@@ -7424,25 +7424,25 @@
         <v>17</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E211" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G211">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H211">
-        <v>76</v>
+        <v>2152</v>
       </c>
       <c r="I211">
-        <v>228</v>
+        <v>32856</v>
       </c>
       <c r="J211" s="1">
-        <v>0.33329999999999999</v>
+        <v>6.5500000000000003E-2</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
@@ -7456,25 +7456,25 @@
         <v>17</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E212" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G212">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H212">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I212">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J212" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.83330000000000004</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
@@ -7488,25 +7488,25 @@
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E213" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G213">
+        <v>9</v>
+      </c>
+      <c r="H213">
         <v>4</v>
       </c>
-      <c r="H213">
-        <v>16</v>
-      </c>
       <c r="I213">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J213" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
@@ -7520,25 +7520,25 @@
         <v>17</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E214" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G214">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H214">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="I214">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="J214" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.68179999999999996</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
@@ -7552,25 +7552,25 @@
         <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E215" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G215">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="H215">
-        <v>700</v>
+        <v>2</v>
       </c>
       <c r="I215">
-        <v>2100</v>
+        <v>4</v>
       </c>
       <c r="J215" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
@@ -7587,22 +7587,22 @@
         <v>23</v>
       </c>
       <c r="E216" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G216">
         <v>9</v>
       </c>
       <c r="H216">
-        <v>2040</v>
+        <v>10</v>
       </c>
       <c r="I216">
-        <v>3285</v>
+        <v>18</v>
       </c>
       <c r="J216" s="1">
-        <v>0.621</v>
+        <v>0.55559999999999998</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
@@ -7619,22 +7619,22 @@
         <v>23</v>
       </c>
       <c r="E217" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G217">
-        <v>9</v>
+        <v>3654</v>
       </c>
       <c r="H217">
-        <v>30</v>
+        <v>15340</v>
       </c>
       <c r="I217">
-        <v>36</v>
+        <v>43848</v>
       </c>
       <c r="J217" s="1">
-        <v>0.83330000000000004</v>
+        <v>0.3498</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
@@ -7651,22 +7651,22 @@
         <v>23</v>
       </c>
       <c r="E218" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G218">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I218">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J218" s="1">
-        <v>0.44440000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
@@ -7677,28 +7677,28 @@
         <v>2026</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E219" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G219">
-        <v>34</v>
+        <v>486</v>
       </c>
       <c r="H219">
-        <v>89</v>
+        <v>4315</v>
       </c>
       <c r="I219">
-        <v>132</v>
+        <v>11664</v>
       </c>
       <c r="J219" s="1">
-        <v>0.67420000000000002</v>
+        <v>0.36990000000000001</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
@@ -7709,28 +7709,28 @@
         <v>2026</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E220" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G220">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H220">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="I220">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="J220" s="1">
-        <v>0.5</v>
+        <v>0.37330000000000002</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
@@ -7741,28 +7741,28 @@
         <v>2026</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E221" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G221">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="H221">
-        <v>10</v>
+        <v>297</v>
       </c>
       <c r="I221">
-        <v>18</v>
+        <v>816</v>
       </c>
       <c r="J221" s="1">
-        <v>0.55559999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
@@ -7773,28 +7773,28 @@
         <v>2026</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E222" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G222">
-        <v>3654</v>
+        <v>729</v>
       </c>
       <c r="H222">
-        <v>14616</v>
+        <v>3192</v>
       </c>
       <c r="I222">
-        <v>43848</v>
+        <v>8772</v>
       </c>
       <c r="J222" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3639</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
@@ -7805,28 +7805,28 @@
         <v>2026</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E223" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G223">
-        <v>33</v>
+        <v>854</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>3971</v>
       </c>
       <c r="I223">
-        <v>33</v>
+        <v>11040</v>
       </c>
       <c r="J223" s="1">
-        <v>0</v>
+        <v>0.35970000000000002</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
@@ -7843,22 +7843,22 @@
         <v>22</v>
       </c>
       <c r="E224" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G224">
-        <v>486</v>
+        <v>121</v>
       </c>
       <c r="H224">
-        <v>3890</v>
+        <v>513</v>
       </c>
       <c r="I224">
-        <v>11664</v>
+        <v>1452</v>
       </c>
       <c r="J224" s="1">
-        <v>0.33350000000000002</v>
+        <v>0.3533</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
@@ -7875,22 +7875,22 @@
         <v>22</v>
       </c>
       <c r="E225" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G225">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H225">
-        <v>110</v>
+        <v>249</v>
       </c>
       <c r="I225">
-        <v>300</v>
+        <v>648</v>
       </c>
       <c r="J225" s="1">
-        <v>0.36670000000000003</v>
+        <v>0.38429999999999997</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
@@ -7907,22 +7907,22 @@
         <v>22</v>
       </c>
       <c r="E226" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G226">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="H226">
-        <v>275</v>
+        <v>8</v>
       </c>
       <c r="I226">
-        <v>816</v>
+        <v>24</v>
       </c>
       <c r="J226" s="1">
-        <v>0.33700000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
@@ -7939,22 +7939,22 @@
         <v>22</v>
       </c>
       <c r="E227" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G227">
-        <v>729</v>
+        <v>30</v>
       </c>
       <c r="H227">
-        <v>2930</v>
+        <v>142</v>
       </c>
       <c r="I227">
-        <v>8772</v>
+        <v>360</v>
       </c>
       <c r="J227" s="1">
-        <v>0.33400000000000002</v>
+        <v>0.39439999999999997</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
@@ -7971,22 +7971,22 @@
         <v>22</v>
       </c>
       <c r="E228" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G228">
-        <v>854</v>
+        <v>51</v>
       </c>
       <c r="H228">
-        <v>3607</v>
+        <v>238</v>
       </c>
       <c r="I228">
-        <v>11040</v>
+        <v>624</v>
       </c>
       <c r="J228" s="1">
-        <v>0.32669999999999999</v>
+        <v>0.38140000000000002</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
@@ -8003,22 +8003,22 @@
         <v>22</v>
       </c>
       <c r="E229" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G229">
-        <v>121</v>
+        <v>337</v>
       </c>
       <c r="H229">
-        <v>485</v>
+        <v>1518</v>
       </c>
       <c r="I229">
-        <v>1452</v>
+        <v>4044</v>
       </c>
       <c r="J229" s="1">
-        <v>0.33400000000000002</v>
+        <v>0.37540000000000001</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
@@ -8032,25 +8032,25 @@
         <v>18</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E230" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="G230">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="H230">
-        <v>225</v>
+        <v>7692</v>
       </c>
       <c r="I230">
-        <v>648</v>
+        <v>18972</v>
       </c>
       <c r="J230" s="1">
-        <v>0.34720000000000001</v>
+        <v>0.40539999999999998</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
@@ -8064,25 +8064,25 @@
         <v>18</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E231" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G231">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="H231">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="I231">
-        <v>24</v>
+        <v>232</v>
       </c>
       <c r="J231" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3836</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
@@ -8096,25 +8096,25 @@
         <v>18</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E232" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G232">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H232">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I232">
-        <v>360</v>
+        <v>58</v>
       </c>
       <c r="J232" s="1">
-        <v>0.33329999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
@@ -8128,25 +8128,25 @@
         <v>18</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E233" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G233">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H233">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="I233">
-        <v>624</v>
+        <v>228</v>
       </c>
       <c r="J233" s="1">
-        <v>0.36380000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
@@ -8160,25 +8160,25 @@
         <v>18</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E234" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G234">
-        <v>337</v>
+        <v>3</v>
       </c>
       <c r="H234">
-        <v>1354</v>
+        <v>3</v>
       </c>
       <c r="I234">
-        <v>4044</v>
+        <v>6</v>
       </c>
       <c r="J234" s="1">
-        <v>0.33479999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
@@ -8195,22 +8195,22 @@
         <v>23</v>
       </c>
       <c r="E235" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="G235">
-        <v>50</v>
+        <v>4610</v>
       </c>
       <c r="H235">
-        <v>7111</v>
+        <v>19984</v>
       </c>
       <c r="I235">
-        <v>18972</v>
+        <v>55320</v>
       </c>
       <c r="J235" s="1">
-        <v>0.37480000000000002</v>
+        <v>0.36120000000000002</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
@@ -8224,25 +8224,25 @@
         <v>18</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E236" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G236">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H236">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="I236">
-        <v>232</v>
+        <v>468</v>
       </c>
       <c r="J236" s="1">
-        <v>0.35339999999999999</v>
+        <v>0.3654</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
@@ -8256,25 +8256,25 @@
         <v>18</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E237" t="s">
+        <v>88</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G237">
+        <v>44</v>
+      </c>
+      <c r="H237">
+        <v>37</v>
+      </c>
+      <c r="I237">
         <v>78</v>
       </c>
-      <c r="F237" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G237">
-        <v>58</v>
-      </c>
-      <c r="H237">
-        <v>0</v>
-      </c>
-      <c r="I237">
-        <v>58</v>
-      </c>
       <c r="J237" s="1">
-        <v>0</v>
+        <v>0.47439999999999999</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
@@ -8291,22 +8291,22 @@
         <v>23</v>
       </c>
       <c r="E238" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G238">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="H238">
-        <v>61</v>
+        <v>387</v>
       </c>
       <c r="I238">
-        <v>228</v>
+        <v>1080</v>
       </c>
       <c r="J238" s="1">
-        <v>0.26750000000000002</v>
+        <v>0.35830000000000001</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
@@ -8323,22 +8323,22 @@
         <v>23</v>
       </c>
       <c r="E239" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G239">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I239">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="J239" s="1">
-        <v>0</v>
+        <v>0.3594</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
@@ -8355,22 +8355,22 @@
         <v>23</v>
       </c>
       <c r="E240" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G240">
-        <v>4610</v>
+        <v>121</v>
       </c>
       <c r="H240">
-        <v>19095</v>
+        <v>506</v>
       </c>
       <c r="I240">
-        <v>55320</v>
+        <v>1428</v>
       </c>
       <c r="J240" s="1">
-        <v>0.34520000000000001</v>
+        <v>0.3543</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
@@ -8384,25 +8384,25 @@
         <v>18</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E241" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G241">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H241">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="I241">
-        <v>468</v>
+        <v>24</v>
       </c>
       <c r="J241" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
@@ -8413,28 +8413,28 @@
         <v>2026</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E242" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G242">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H242">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="I242">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="J242" s="1">
-        <v>0.47439999999999999</v>
+        <v>0.37380000000000002</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
@@ -8445,28 +8445,28 @@
         <v>2026</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E243" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G243">
-        <v>90</v>
+        <v>228</v>
       </c>
       <c r="H243">
-        <v>366</v>
+        <v>1013</v>
       </c>
       <c r="I243">
-        <v>1080</v>
+        <v>2784</v>
       </c>
       <c r="J243" s="1">
-        <v>0.33889999999999998</v>
+        <v>0.3639</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
@@ -8477,28 +8477,28 @@
         <v>2026</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E244" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G244">
-        <v>27</v>
+        <v>264</v>
       </c>
       <c r="H244">
-        <v>65</v>
+        <v>1566</v>
       </c>
       <c r="I244">
-        <v>192</v>
+        <v>4291</v>
       </c>
       <c r="J244" s="1">
-        <v>0.33850000000000002</v>
+        <v>0.3649</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
@@ -8509,28 +8509,28 @@
         <v>2026</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E245" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G245">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="H245">
-        <v>478</v>
+        <v>145</v>
       </c>
       <c r="I245">
-        <v>1428</v>
+        <v>384</v>
       </c>
       <c r="J245" s="1">
-        <v>0.3347</v>
+        <v>0.37759999999999999</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
@@ -8541,28 +8541,28 @@
         <v>2026</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E246" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G246">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H246">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I246">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J246" s="1">
-        <v>0.20830000000000001</v>
+        <v>0.36109999999999998</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
@@ -8579,22 +8579,22 @@
         <v>22</v>
       </c>
       <c r="E247" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G247">
-        <v>35</v>
+        <v>451</v>
       </c>
       <c r="H247">
-        <v>140</v>
+        <v>1941</v>
       </c>
       <c r="I247">
-        <v>420</v>
+        <v>5340</v>
       </c>
       <c r="J247" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36349999999999999</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
@@ -8611,22 +8611,22 @@
         <v>22</v>
       </c>
       <c r="E248" t="s">
+        <v>67</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G248">
         <v>66</v>
       </c>
-      <c r="F248" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G248">
-        <v>228</v>
-      </c>
       <c r="H248">
-        <v>928</v>
+        <v>296</v>
       </c>
       <c r="I248">
-        <v>2784</v>
+        <v>792</v>
       </c>
       <c r="J248" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.37369999999999998</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
@@ -8643,22 +8643,22 @@
         <v>22</v>
       </c>
       <c r="E249" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G249">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="H249">
-        <v>1434</v>
+        <v>355</v>
       </c>
       <c r="I249">
-        <v>4291</v>
+        <v>1008</v>
       </c>
       <c r="J249" s="1">
-        <v>0.3342</v>
+        <v>0.35220000000000001</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
@@ -8675,22 +8675,22 @@
         <v>22</v>
       </c>
       <c r="E250" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G250">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H250">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="I250">
-        <v>384</v>
+        <v>276</v>
       </c>
       <c r="J250" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35139999999999999</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
@@ -8704,25 +8704,25 @@
         <v>19</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E251" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G251">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H251">
-        <v>12</v>
+        <v>1934</v>
       </c>
       <c r="I251">
-        <v>36</v>
+        <v>5110</v>
       </c>
       <c r="J251" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3785</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
@@ -8736,25 +8736,25 @@
         <v>19</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E252" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G252">
-        <v>451</v>
+        <v>11</v>
       </c>
       <c r="H252">
-        <v>1780</v>
+        <v>18</v>
       </c>
       <c r="I252">
-        <v>5340</v>
+        <v>44</v>
       </c>
       <c r="J252" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.40910000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
@@ -8768,25 +8768,25 @@
         <v>19</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E253" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G253">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H253">
-        <v>264</v>
+        <v>8</v>
       </c>
       <c r="I253">
-        <v>792</v>
+        <v>11</v>
       </c>
       <c r="J253" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.72729999999999995</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
@@ -8800,25 +8800,25 @@
         <v>19</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E254" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G254">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="H254">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="I254">
-        <v>1008</v>
+        <v>136</v>
       </c>
       <c r="J254" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.47789999999999999</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
@@ -8832,25 +8832,25 @@
         <v>19</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E255" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G255">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H255">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="I255">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="J255" s="1">
-        <v>0.33700000000000002</v>
+        <v>0.55879999999999996</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
@@ -8867,22 +8867,22 @@
         <v>23</v>
       </c>
       <c r="E256" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G256">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H256">
-        <v>1775</v>
+        <v>6</v>
       </c>
       <c r="I256">
-        <v>5110</v>
+        <v>12</v>
       </c>
       <c r="J256" s="1">
-        <v>0.34739999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
@@ -8899,22 +8899,22 @@
         <v>23</v>
       </c>
       <c r="E257" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G257">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H257">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I257">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="J257" s="1">
-        <v>0.40910000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
@@ -8931,22 +8931,22 @@
         <v>23</v>
       </c>
       <c r="E258" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G258">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H258">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="I258">
-        <v>11</v>
+        <v>396</v>
       </c>
       <c r="J258" s="1">
-        <v>0.72729999999999995</v>
+        <v>0.35610000000000003</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
@@ -8963,22 +8963,22 @@
         <v>23</v>
       </c>
       <c r="E259" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G259">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H259">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="I259">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="J259" s="1">
-        <v>0.4632</v>
+        <v>0.35139999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
@@ -8995,22 +8995,22 @@
         <v>23</v>
       </c>
       <c r="E260" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G260">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="H260">
-        <v>19</v>
+        <v>334</v>
       </c>
       <c r="I260">
-        <v>34</v>
+        <v>948</v>
       </c>
       <c r="J260" s="1">
-        <v>0.55879999999999996</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
@@ -9027,22 +9027,22 @@
         <v>23</v>
       </c>
       <c r="E261" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G261">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="H261">
-        <v>6</v>
+        <v>2040</v>
       </c>
       <c r="I261">
-        <v>12</v>
+        <v>5904</v>
       </c>
       <c r="J261" s="1">
-        <v>0.5</v>
+        <v>0.34549999999999997</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
@@ -9056,25 +9056,25 @@
         <v>19</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E262" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G262">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H262">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="I262">
-        <v>4</v>
+        <v>264</v>
       </c>
       <c r="J262" s="1">
-        <v>0.5</v>
+        <v>0.35980000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
@@ -9088,25 +9088,25 @@
         <v>19</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E263" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G263">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H263">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="I263">
-        <v>396</v>
+        <v>44</v>
       </c>
       <c r="J263" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.4773</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
@@ -9117,28 +9117,28 @@
         <v>2026</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E264" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G264">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H264">
-        <v>92</v>
+        <v>316</v>
       </c>
       <c r="I264">
-        <v>276</v>
+        <v>888</v>
       </c>
       <c r="J264" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35589999999999999</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
@@ -9149,28 +9149,28 @@
         <v>2026</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E265" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G265">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="H265">
-        <v>317</v>
+        <v>691</v>
       </c>
       <c r="I265">
-        <v>948</v>
+        <v>1920</v>
       </c>
       <c r="J265" s="1">
-        <v>0.33439999999999998</v>
+        <v>0.3599</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
@@ -9181,28 +9181,28 @@
         <v>2026</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E266" t="s">
+        <v>64</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G266">
         <v>82</v>
       </c>
-      <c r="F266" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G266">
-        <v>276</v>
-      </c>
       <c r="H266">
-        <v>1980</v>
+        <v>708</v>
       </c>
       <c r="I266">
-        <v>5904</v>
+        <v>1968</v>
       </c>
       <c r="J266" s="1">
-        <v>0.33539999999999998</v>
+        <v>0.35980000000000001</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
@@ -9213,28 +9213,28 @@
         <v>2026</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E267" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G267">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="H267">
-        <v>88</v>
+        <v>939</v>
       </c>
       <c r="I267">
-        <v>264</v>
+        <v>2724</v>
       </c>
       <c r="J267" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34470000000000001</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
@@ -9245,28 +9245,28 @@
         <v>2026</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E268" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G268">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="H268">
-        <v>21</v>
+        <v>1445</v>
       </c>
       <c r="I268">
-        <v>44</v>
+        <v>4128</v>
       </c>
       <c r="J268" s="1">
-        <v>0.4773</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
@@ -9283,19 +9283,19 @@
         <v>22</v>
       </c>
       <c r="E269" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G269">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="H269">
-        <v>296</v>
+        <v>12</v>
       </c>
       <c r="I269">
-        <v>888</v>
+        <v>36</v>
       </c>
       <c r="J269" s="1">
         <v>0.33329999999999999</v>
@@ -9315,22 +9315,22 @@
         <v>22</v>
       </c>
       <c r="E270" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G270">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H270">
-        <v>640</v>
+        <v>453</v>
       </c>
       <c r="I270">
-        <v>1920</v>
+        <v>1320</v>
       </c>
       <c r="J270" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
@@ -9347,22 +9347,22 @@
         <v>22</v>
       </c>
       <c r="E271" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G271">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="H271">
-        <v>656</v>
+        <v>1279</v>
       </c>
       <c r="I271">
-        <v>1968</v>
+        <v>3732</v>
       </c>
       <c r="J271" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3427</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
@@ -9379,22 +9379,22 @@
         <v>22</v>
       </c>
       <c r="E272" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G272">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="H272">
-        <v>908</v>
+        <v>1174</v>
       </c>
       <c r="I272">
-        <v>2724</v>
+        <v>3432</v>
       </c>
       <c r="J272" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34210000000000002</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
@@ -9411,19 +9411,19 @@
         <v>22</v>
       </c>
       <c r="E273" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G273">
-        <v>172</v>
+        <v>12</v>
       </c>
       <c r="H273">
-        <v>1376</v>
+        <v>48</v>
       </c>
       <c r="I273">
-        <v>4128</v>
+        <v>144</v>
       </c>
       <c r="J273" s="1">
         <v>0.33329999999999999</v>
@@ -9443,22 +9443,22 @@
         <v>22</v>
       </c>
       <c r="E274" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G274">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="H274">
-        <v>12</v>
+        <v>356</v>
       </c>
       <c r="I274">
-        <v>36</v>
+        <v>1020</v>
       </c>
       <c r="J274" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
@@ -9475,22 +9475,22 @@
         <v>22</v>
       </c>
       <c r="E275" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G275">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H275">
-        <v>440</v>
+        <v>194</v>
       </c>
       <c r="I275">
-        <v>1320</v>
+        <v>528</v>
       </c>
       <c r="J275" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
@@ -9507,22 +9507,22 @@
         <v>22</v>
       </c>
       <c r="E276" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G276">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="H276">
-        <v>1244</v>
+        <v>215</v>
       </c>
       <c r="I276">
-        <v>3732</v>
+        <v>564</v>
       </c>
       <c r="J276" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38119999999999998</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
@@ -9539,22 +9539,22 @@
         <v>22</v>
       </c>
       <c r="E277" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G277">
-        <v>286</v>
+        <v>17</v>
       </c>
       <c r="H277">
-        <v>1144</v>
+        <v>74</v>
       </c>
       <c r="I277">
-        <v>3432</v>
+        <v>204</v>
       </c>
       <c r="J277" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36270000000000002</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
@@ -9571,22 +9571,22 @@
         <v>22</v>
       </c>
       <c r="E278" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G278">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H278">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="I278">
-        <v>144</v>
+        <v>384</v>
       </c>
       <c r="J278" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35160000000000002</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
@@ -9603,22 +9603,22 @@
         <v>22</v>
       </c>
       <c r="E279" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G279">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H279">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="I279">
-        <v>1020</v>
+        <v>1092</v>
       </c>
       <c r="J279" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3498</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
@@ -9635,22 +9635,22 @@
         <v>22</v>
       </c>
       <c r="E280" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G280">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H280">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="I280">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="J280" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35460000000000003</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
@@ -9664,25 +9664,25 @@
         <v>92</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E281" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G281">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="H281">
-        <v>188</v>
+        <v>1952</v>
       </c>
       <c r="I281">
-        <v>564</v>
+        <v>5842</v>
       </c>
       <c r="J281" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.33410000000000001</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
@@ -9696,25 +9696,25 @@
         <v>92</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E282" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G282">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H282">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="I282">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="J282" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35260000000000002</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
@@ -9728,25 +9728,25 @@
         <v>92</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E283" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G283">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H283">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="I283">
-        <v>384</v>
+        <v>39</v>
       </c>
       <c r="J283" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.76919999999999999</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
@@ -9760,25 +9760,25 @@
         <v>92</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E284" t="s">
+        <v>79</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G284">
+        <v>44</v>
+      </c>
+      <c r="H284">
         <v>68</v>
       </c>
-      <c r="F284" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G284">
-        <v>91</v>
-      </c>
-      <c r="H284">
-        <v>364</v>
-      </c>
       <c r="I284">
-        <v>1092</v>
+        <v>180</v>
       </c>
       <c r="J284" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.37780000000000002</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
@@ -9792,25 +9792,25 @@
         <v>92</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E285" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G285">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H285">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="I285">
-        <v>564</v>
+        <v>45</v>
       </c>
       <c r="J285" s="1">
-        <v>0.34039999999999998</v>
+        <v>0.68889999999999996</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
@@ -9827,22 +9827,22 @@
         <v>23</v>
       </c>
       <c r="E286" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G286">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H286">
-        <v>1923</v>
+        <v>8</v>
       </c>
       <c r="I286">
-        <v>5842</v>
+        <v>18</v>
       </c>
       <c r="J286" s="1">
-        <v>0.32919999999999999</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
@@ -9859,22 +9859,22 @@
         <v>23</v>
       </c>
       <c r="E287" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G287">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H287">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="I287">
-        <v>156</v>
+        <v>4</v>
       </c>
       <c r="J287" s="1">
-        <v>0.35260000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
@@ -9891,22 +9891,22 @@
         <v>23</v>
       </c>
       <c r="E288" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G288">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="H288">
-        <v>30</v>
+        <v>971</v>
       </c>
       <c r="I288">
-        <v>39</v>
+        <v>2736</v>
       </c>
       <c r="J288" s="1">
-        <v>0.76919999999999999</v>
+        <v>0.35489999999999999</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
@@ -9923,22 +9923,22 @@
         <v>23</v>
       </c>
       <c r="E289" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G289">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H289">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="I289">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="J289" s="1">
-        <v>0.36670000000000003</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
@@ -9955,22 +9955,22 @@
         <v>23</v>
       </c>
       <c r="E290" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G290">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="H290">
-        <v>31</v>
+        <v>780</v>
       </c>
       <c r="I290">
-        <v>45</v>
+        <v>2196</v>
       </c>
       <c r="J290" s="1">
-        <v>0.68889999999999996</v>
+        <v>0.35520000000000002</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
@@ -9987,22 +9987,22 @@
         <v>23</v>
       </c>
       <c r="E291" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G291">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="H291">
-        <v>8</v>
+        <v>366</v>
       </c>
       <c r="I291">
-        <v>18</v>
+        <v>1044</v>
       </c>
       <c r="J291" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.35060000000000002</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
@@ -10013,28 +10013,28 @@
         <v>2026</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E292" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G292">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="H292">
-        <v>2</v>
+        <v>859</v>
       </c>
       <c r="I292">
-        <v>4</v>
+        <v>2304</v>
       </c>
       <c r="J292" s="1">
-        <v>0.5</v>
+        <v>0.37280000000000002</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
@@ -10045,28 +10045,28 @@
         <v>2026</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E293" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G293">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c r="H293">
-        <v>912</v>
+        <v>75</v>
       </c>
       <c r="I293">
-        <v>2736</v>
+        <v>204</v>
       </c>
       <c r="J293" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36759999999999998</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
@@ -10077,28 +10077,28 @@
         <v>2026</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E294" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G294">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="H294">
-        <v>96</v>
+        <v>472</v>
       </c>
       <c r="I294">
-        <v>300</v>
+        <v>1308</v>
       </c>
       <c r="J294" s="1">
-        <v>0.32</v>
+        <v>0.3609</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
@@ -10109,28 +10109,28 @@
         <v>2026</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E295" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G295">
-        <v>185</v>
+        <v>8</v>
       </c>
       <c r="H295">
-        <v>740</v>
+        <v>34</v>
       </c>
       <c r="I295">
-        <v>2196</v>
+        <v>96</v>
       </c>
       <c r="J295" s="1">
-        <v>0.33700000000000002</v>
+        <v>0.35420000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
@@ -10141,28 +10141,28 @@
         <v>2026</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E296" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G296">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="H296">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="I296">
-        <v>1044</v>
+        <v>408</v>
       </c>
       <c r="J296" s="1">
-        <v>0.3372</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
@@ -10179,22 +10179,22 @@
         <v>22</v>
       </c>
       <c r="E297" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G297">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="H297">
-        <v>768</v>
+        <v>45</v>
       </c>
       <c r="I297">
-        <v>2304</v>
+        <v>120</v>
       </c>
       <c r="J297" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
@@ -10211,7 +10211,7 @@
         <v>22</v>
       </c>
       <c r="E298" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>26</v>
@@ -10220,13 +10220,13 @@
         <v>17</v>
       </c>
       <c r="H298">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I298">
         <v>204</v>
       </c>
       <c r="J298" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36759999999999998</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
@@ -10243,22 +10243,22 @@
         <v>22</v>
       </c>
       <c r="E299" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G299">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="H299">
-        <v>436</v>
+        <v>29</v>
       </c>
       <c r="I299">
-        <v>1308</v>
+        <v>84</v>
       </c>
       <c r="J299" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34520000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
@@ -10275,22 +10275,22 @@
         <v>22</v>
       </c>
       <c r="E300" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G300">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="H300">
-        <v>32</v>
+        <v>892</v>
       </c>
       <c r="I300">
-        <v>96</v>
+        <v>2400</v>
       </c>
       <c r="J300" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.37169999999999997</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
@@ -10304,25 +10304,25 @@
         <v>91</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E301" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G301">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H301">
-        <v>136</v>
+        <v>1818</v>
       </c>
       <c r="I301">
-        <v>408</v>
+        <v>5110</v>
       </c>
       <c r="J301" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35580000000000001</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
@@ -10336,25 +10336,25 @@
         <v>91</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E302" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G302">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H302">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I302">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="J302" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
@@ -10368,25 +10368,25 @@
         <v>91</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E303" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G303">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H303">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I303">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="J303" s="1">
-        <v>0.33329999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
@@ -10400,25 +10400,25 @@
         <v>91</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E304" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G304">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H304">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I304">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="J304" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
@@ -10432,25 +10432,25 @@
         <v>91</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E305" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G305">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H305">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="I305">
-        <v>2400</v>
+        <v>4</v>
       </c>
       <c r="J305" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
@@ -10467,22 +10467,22 @@
         <v>23</v>
       </c>
       <c r="E306" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="G306">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H306">
-        <v>1680</v>
+        <v>42</v>
       </c>
       <c r="I306">
-        <v>5110</v>
+        <v>120</v>
       </c>
       <c r="J306" s="1">
-        <v>0.32879999999999998</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
@@ -10499,22 +10499,22 @@
         <v>23</v>
       </c>
       <c r="E307" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G307">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H307">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I307">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="J307" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
@@ -10525,28 +10525,28 @@
         <v>2026</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E308" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G308">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I308">
-        <v>19</v>
+        <v>468</v>
       </c>
       <c r="J308" s="1">
-        <v>0</v>
+        <v>0.36320000000000002</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
@@ -10557,28 +10557,28 @@
         <v>2026</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E309" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G309">
-        <v>5</v>
+        <v>778</v>
       </c>
       <c r="H309">
-        <v>5</v>
+        <v>3274</v>
       </c>
       <c r="I309">
-        <v>20</v>
+        <v>9336</v>
       </c>
       <c r="J309" s="1">
-        <v>0.25</v>
+        <v>0.35070000000000001</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
@@ -10589,28 +10589,28 @@
         <v>2026</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E310" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G310">
-        <v>2</v>
+        <v>392</v>
       </c>
       <c r="H310">
-        <v>1</v>
+        <v>3504</v>
       </c>
       <c r="I310">
-        <v>4</v>
+        <v>9408</v>
       </c>
       <c r="J310" s="1">
-        <v>0.25</v>
+        <v>0.37240000000000001</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
@@ -10621,28 +10621,28 @@
         <v>2026</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E311" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G311">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H311">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I311">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="J311" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
@@ -10653,28 +10653,28 @@
         <v>2026</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E312" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G312">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H312">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I312">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="J312" s="1">
-        <v>1</v>
+        <v>0.34260000000000002</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
@@ -10691,22 +10691,22 @@
         <v>22</v>
       </c>
       <c r="E313" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G313">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="H313">
-        <v>156</v>
+        <v>614</v>
       </c>
       <c r="I313">
-        <v>468</v>
+        <v>1740</v>
       </c>
       <c r="J313" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
@@ -10723,22 +10723,22 @@
         <v>22</v>
       </c>
       <c r="E314" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G314">
-        <v>778</v>
+        <v>925</v>
       </c>
       <c r="H314">
-        <v>3112</v>
+        <v>3842</v>
       </c>
       <c r="I314">
-        <v>9336</v>
+        <v>11100</v>
       </c>
       <c r="J314" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34610000000000002</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
@@ -10755,22 +10755,22 @@
         <v>22</v>
       </c>
       <c r="E315" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G315">
-        <v>392</v>
+        <v>45</v>
       </c>
       <c r="H315">
-        <v>3136</v>
+        <v>187</v>
       </c>
       <c r="I315">
-        <v>9408</v>
+        <v>540</v>
       </c>
       <c r="J315" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3463</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
@@ -10787,22 +10787,22 @@
         <v>22</v>
       </c>
       <c r="E316" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G316">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H316">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="I316">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="J316" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36980000000000002</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
@@ -10819,22 +10819,22 @@
         <v>22</v>
       </c>
       <c r="E317" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G317">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H317">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="I317">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="J317" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36330000000000001</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
@@ -10851,22 +10851,22 @@
         <v>22</v>
       </c>
       <c r="E318" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G318">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="H318">
-        <v>580</v>
+        <v>153</v>
       </c>
       <c r="I318">
-        <v>1740</v>
+        <v>420</v>
       </c>
       <c r="J318" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.36430000000000001</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
@@ -10883,22 +10883,22 @@
         <v>22</v>
       </c>
       <c r="E319" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G319">
-        <v>925</v>
+        <v>4</v>
       </c>
       <c r="H319">
-        <v>3700</v>
+        <v>20</v>
       </c>
       <c r="I319">
-        <v>11100</v>
+        <v>48</v>
       </c>
       <c r="J319" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
@@ -10915,22 +10915,22 @@
         <v>22</v>
       </c>
       <c r="E320" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G320">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H320">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="I320">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="J320" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38019999999999998</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
@@ -10947,22 +10947,22 @@
         <v>22</v>
       </c>
       <c r="E321" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G321">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H321">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="I321">
-        <v>576</v>
+        <v>48</v>
       </c>
       <c r="J321" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
@@ -10976,25 +10976,25 @@
         <v>20</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E322" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G322">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="H322">
-        <v>103</v>
+        <v>12346</v>
       </c>
       <c r="I322">
-        <v>300</v>
+        <v>38325</v>
       </c>
       <c r="J322" s="1">
-        <v>0.34329999999999999</v>
+        <v>0.3221</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
@@ -11008,25 +11008,25 @@
         <v>20</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E323" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G323">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H323">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="I323">
-        <v>420</v>
+        <v>260</v>
       </c>
       <c r="J323" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.37690000000000001</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
@@ -11040,25 +11040,25 @@
         <v>20</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E324" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G324">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="H324">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="I324">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="J324" s="1">
-        <v>0.33329999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
@@ -11072,25 +11072,25 @@
         <v>20</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E325" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G325">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H325">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I325">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="J325" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.43180000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
@@ -11104,25 +11104,25 @@
         <v>20</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E326" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G326">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H326">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I326">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J326" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.72729999999999995</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
@@ -11139,22 +11139,22 @@
         <v>23</v>
       </c>
       <c r="E327" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G327">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="H327">
-        <v>11501</v>
+        <v>8</v>
       </c>
       <c r="I327">
-        <v>38325</v>
+        <v>20</v>
       </c>
       <c r="J327" s="1">
-        <v>0.30009999999999998</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
@@ -11171,22 +11171,22 @@
         <v>23</v>
       </c>
       <c r="E328" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G328">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="H328">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="I328">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="J328" s="1">
-        <v>0.31919999999999998</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
@@ -11203,22 +11203,22 @@
         <v>23</v>
       </c>
       <c r="E329" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G329">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="H329">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="I329">
-        <v>65</v>
+        <v>396</v>
       </c>
       <c r="J329" s="1">
-        <v>1</v>
+        <v>0.37369999999999998</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
@@ -11235,22 +11235,22 @@
         <v>23</v>
       </c>
       <c r="E330" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G330">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H330">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I330">
         <v>132</v>
       </c>
       <c r="J330" s="1">
-        <v>0.40910000000000002</v>
+        <v>0.36359999999999998</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
@@ -11267,22 +11267,22 @@
         <v>23</v>
       </c>
       <c r="E331" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G331">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H331">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="I331">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="J331" s="1">
-        <v>0.72729999999999995</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
@@ -11299,22 +11299,22 @@
         <v>23</v>
       </c>
       <c r="E332" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G332">
-        <v>10</v>
+        <v>3536</v>
       </c>
       <c r="H332">
-        <v>10</v>
+        <v>15428</v>
       </c>
       <c r="I332">
-        <v>20</v>
+        <v>42432</v>
       </c>
       <c r="J332" s="1">
-        <v>0.5</v>
+        <v>0.36359999999999998</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
@@ -11325,28 +11325,28 @@
         <v>2026</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E333" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G333">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="H333">
-        <v>12</v>
+        <v>2383</v>
       </c>
       <c r="I333">
-        <v>24</v>
+        <v>6648</v>
       </c>
       <c r="J333" s="1">
-        <v>0.5</v>
+        <v>0.35849999999999999</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
@@ -11357,28 +11357,28 @@
         <v>2026</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E334" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G334">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="H334">
-        <v>132</v>
+        <v>540</v>
       </c>
       <c r="I334">
-        <v>396</v>
+        <v>1548</v>
       </c>
       <c r="J334" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3488</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
@@ -11389,28 +11389,28 @@
         <v>2026</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E335" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G335">
-        <v>11</v>
+        <v>553</v>
       </c>
       <c r="H335">
-        <v>44</v>
+        <v>2331</v>
       </c>
       <c r="I335">
-        <v>132</v>
+        <v>6636</v>
       </c>
       <c r="J335" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3513</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
@@ -11421,28 +11421,28 @@
         <v>2026</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E336" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G336">
-        <v>23</v>
+        <v>315</v>
       </c>
       <c r="H336">
-        <v>95</v>
+        <v>1364</v>
       </c>
       <c r="I336">
-        <v>276</v>
+        <v>3780</v>
       </c>
       <c r="J336" s="1">
-        <v>0.34420000000000001</v>
+        <v>0.36080000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
@@ -11453,28 +11453,28 @@
         <v>2026</v>
       </c>
       <c r="C337" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E337" t="s">
+        <v>68</v>
+      </c>
+      <c r="F337" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G337">
         <v>20</v>
       </c>
-      <c r="D337" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E337" t="s">
-        <v>82</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G337">
-        <v>3536</v>
-      </c>
       <c r="H337">
-        <v>14144</v>
+        <v>83</v>
       </c>
       <c r="I337">
-        <v>42432</v>
+        <v>240</v>
       </c>
       <c r="J337" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.3458</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
@@ -11491,22 +11491,22 @@
         <v>22</v>
       </c>
       <c r="E338" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G338">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="H338">
-        <v>2099</v>
+        <v>79</v>
       </c>
       <c r="I338">
-        <v>6672</v>
+        <v>228</v>
       </c>
       <c r="J338" s="1">
-        <v>0.31459999999999999</v>
+        <v>0.34649999999999997</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
@@ -11523,22 +11523,22 @@
         <v>22</v>
       </c>
       <c r="E339" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G339">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="H339">
-        <v>478</v>
+        <v>161</v>
       </c>
       <c r="I339">
-        <v>1548</v>
+        <v>456</v>
       </c>
       <c r="J339" s="1">
-        <v>0.30880000000000002</v>
+        <v>0.35310000000000002</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
@@ -11555,22 +11555,22 @@
         <v>22</v>
       </c>
       <c r="E340" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G340">
-        <v>553</v>
+        <v>86</v>
       </c>
       <c r="H340">
-        <v>2013</v>
+        <v>357</v>
       </c>
       <c r="I340">
-        <v>6636</v>
+        <v>1032</v>
       </c>
       <c r="J340" s="1">
-        <v>0.30330000000000001</v>
+        <v>0.34589999999999999</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
@@ -11587,22 +11587,22 @@
         <v>22</v>
       </c>
       <c r="E341" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G341">
-        <v>315</v>
+        <v>2</v>
       </c>
       <c r="H341">
-        <v>1152</v>
+        <v>8</v>
       </c>
       <c r="I341">
-        <v>3780</v>
+        <v>24</v>
       </c>
       <c r="J341" s="1">
-        <v>0.30480000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
@@ -11619,22 +11619,22 @@
         <v>22</v>
       </c>
       <c r="E342" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G342">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H342">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="I342">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="J342" s="1">
-        <v>0.31669999999999998</v>
+        <v>0.33069999999999999</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
@@ -11651,22 +11651,22 @@
         <v>22</v>
       </c>
       <c r="E343" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F343" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G343">
-        <v>19</v>
+        <v>615</v>
       </c>
       <c r="H343">
-        <v>74</v>
+        <v>2617</v>
       </c>
       <c r="I343">
-        <v>228</v>
+        <v>7380</v>
       </c>
       <c r="J343" s="1">
-        <v>0.3246</v>
+        <v>0.35460000000000003</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
@@ -11680,25 +11680,25 @@
         <v>21</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E344" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="G344">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="H344">
-        <v>139</v>
+        <v>6345</v>
       </c>
       <c r="I344">
-        <v>456</v>
+        <v>17695</v>
       </c>
       <c r="J344" s="1">
-        <v>0.30480000000000002</v>
+        <v>0.35859999999999997</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
@@ -11712,25 +11712,25 @@
         <v>21</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E345" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G345">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="H345">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I345">
-        <v>1032</v>
+        <v>700</v>
       </c>
       <c r="J345" s="1">
-        <v>0.30620000000000003</v>
+        <v>0.43709999999999999</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
@@ -11744,25 +11744,25 @@
         <v>21</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E346" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G346">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="H346">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="I346">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="J346" s="1">
-        <v>0.25</v>
+        <v>1.0170999999999999</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
@@ -11776,25 +11776,25 @@
         <v>21</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E347" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G347">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H347">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="I347">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="J347" s="1">
-        <v>0.30470000000000003</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
@@ -11808,25 +11808,25 @@
         <v>21</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E348" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G348">
-        <v>615</v>
+        <v>48</v>
       </c>
       <c r="H348">
-        <v>2297</v>
+        <v>41</v>
       </c>
       <c r="I348">
-        <v>7380</v>
+        <v>48</v>
       </c>
       <c r="J348" s="1">
-        <v>0.31119999999999998</v>
+        <v>0.85419999999999996</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
@@ -11843,22 +11843,22 @@
         <v>23</v>
       </c>
       <c r="E349" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G349">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="H349">
-        <v>6183</v>
+        <v>12</v>
       </c>
       <c r="I349">
-        <v>17695</v>
+        <v>26</v>
       </c>
       <c r="J349" s="1">
-        <v>0.34939999999999999</v>
+        <v>0.46150000000000002</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
@@ -11875,22 +11875,22 @@
         <v>23</v>
       </c>
       <c r="E350" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G350">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="H350">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="I350">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J350" s="1">
-        <v>0.43859999999999999</v>
+        <v>0.3483</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
@@ -11907,22 +11907,22 @@
         <v>23</v>
       </c>
       <c r="E351" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G351">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="H351">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="I351">
-        <v>175</v>
+        <v>576</v>
       </c>
       <c r="J351" s="1">
-        <v>1.0170999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
@@ -11939,22 +11939,22 @@
         <v>23</v>
       </c>
       <c r="E352" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G352">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H352">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I352">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="J352" s="1">
-        <v>0.40629999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
@@ -11968,25 +11968,25 @@
         <v>21</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E353" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G353">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H353">
-        <v>41</v>
+        <v>251</v>
       </c>
       <c r="I353">
-        <v>48</v>
+        <v>744</v>
       </c>
       <c r="J353" s="1">
-        <v>0.85419999999999996</v>
+        <v>0.33739999999999998</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
@@ -12000,186 +12000,46 @@
         <v>21</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E354" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G354">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H354">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="I354">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="J354" s="1">
-        <v>0.46150000000000002</v>
+        <v>0.37330000000000002</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A355" s="3">
-        <v>46152</v>
-      </c>
-      <c r="B355" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D355" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E355" t="s">
-        <v>82</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G355">
-        <v>50</v>
-      </c>
-      <c r="H355">
-        <v>186</v>
-      </c>
-      <c r="I355">
-        <v>600</v>
-      </c>
-      <c r="J355" s="1">
-        <v>0.31</v>
-      </c>
+      <c r="A355" s="3"/>
+      <c r="J355" s="1"/>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A356" s="3">
-        <v>46152</v>
-      </c>
-      <c r="B356" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D356" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E356" t="s">
-        <v>83</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G356">
-        <v>48</v>
-      </c>
-      <c r="H356">
-        <v>180</v>
-      </c>
-      <c r="I356">
-        <v>576</v>
-      </c>
-      <c r="J356" s="1">
-        <v>0.3125</v>
-      </c>
+      <c r="A356" s="3"/>
+      <c r="J356" s="1"/>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A357" s="3">
-        <v>46152</v>
-      </c>
-      <c r="B357" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D357" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E357" t="s">
-        <v>84</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G357">
-        <v>17</v>
-      </c>
-      <c r="H357">
-        <v>65</v>
-      </c>
-      <c r="I357">
-        <v>204</v>
-      </c>
-      <c r="J357" s="1">
-        <v>0.31859999999999999</v>
-      </c>
+      <c r="A357" s="3"/>
+      <c r="J357" s="1"/>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A358" s="3">
-        <v>46152</v>
-      </c>
-      <c r="B358" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D358" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E358" t="s">
-        <v>87</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G358">
-        <v>62</v>
-      </c>
-      <c r="H358">
-        <v>220</v>
-      </c>
-      <c r="I358">
-        <v>744</v>
-      </c>
-      <c r="J358" s="1">
-        <v>0.29570000000000002</v>
-      </c>
+      <c r="A358" s="3"/>
+      <c r="J358" s="1"/>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A359" s="3">
-        <v>46152</v>
-      </c>
-      <c r="B359" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D359" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E359" t="s">
-        <v>89</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G359">
-        <v>25</v>
-      </c>
-      <c r="H359">
-        <v>108</v>
-      </c>
-      <c r="I359">
-        <v>300</v>
-      </c>
-      <c r="J359" s="1">
-        <v>0.36</v>
-      </c>
+      <c r="A359" s="3"/>
+      <c r="J359" s="1"/>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="3"/>
@@ -12289,28 +12149,8 @@
       <c r="A386" s="3"/>
       <c r="J386" s="1"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A387" s="3"/>
-      <c r="J387" s="1"/>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A388" s="3"/>
-      <c r="J388" s="1"/>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A389" s="3"/>
-      <c r="J389" s="1"/>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A390" s="3"/>
-      <c r="J390" s="1"/>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A391" s="3"/>
-      <c r="J391" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J391" xr:uid="{045E82A1-AFA5-46B1-A9F4-12F5B515B637}"/>
+  <autoFilter ref="A1:J386" xr:uid="{045E82A1-AFA5-46B1-A9F4-12F5B515B637}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B9A980-00B3-476A-934C-C4CE31DB2514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B856A-AE8D-4E5E-B451-8A9DD48FA325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -727,7 +727,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -748,18 +748,18 @@
         <v>59</v>
       </c>
       <c r="H2">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="I2">
         <v>1416</v>
       </c>
       <c r="J2" s="1">
-        <v>0.36370000000000002</v>
+        <v>0.38279999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -780,18 +780,18 @@
         <v>47</v>
       </c>
       <c r="H3">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="I3">
         <v>564</v>
       </c>
       <c r="J3" s="1">
-        <v>0.3528</v>
+        <v>0.39179999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -812,18 +812,18 @@
         <v>59</v>
       </c>
       <c r="H4">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="I4">
         <v>708</v>
       </c>
       <c r="J4" s="1">
-        <v>0.36020000000000002</v>
+        <v>0.38700000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -844,18 +844,18 @@
         <v>398</v>
       </c>
       <c r="H5">
-        <v>1689</v>
+        <v>1760</v>
       </c>
       <c r="I5">
         <v>4776</v>
       </c>
       <c r="J5" s="1">
-        <v>0.35360000000000003</v>
+        <v>0.36849999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -876,18 +876,18 @@
         <v>398</v>
       </c>
       <c r="H6">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I6">
         <v>398</v>
       </c>
       <c r="J6" s="1">
-        <v>0.53269999999999995</v>
+        <v>0.54769999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -908,18 +908,18 @@
         <v>64</v>
       </c>
       <c r="H7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I7">
         <v>128</v>
       </c>
       <c r="J7" s="1">
-        <v>0.40629999999999999</v>
+        <v>0.41410000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -940,18 +940,18 @@
         <v>61</v>
       </c>
       <c r="H8">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I8">
         <v>244</v>
       </c>
       <c r="J8" s="1">
-        <v>0.373</v>
+        <v>0.39750000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -972,18 +972,18 @@
         <v>59</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9">
         <v>59</v>
       </c>
       <c r="J9" s="1">
-        <v>0.69489999999999996</v>
+        <v>0.71189999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1004,18 +1004,18 @@
         <v>161</v>
       </c>
       <c r="H10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I10">
         <v>161</v>
       </c>
       <c r="J10" s="1">
-        <v>0.16769999999999999</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1036,18 +1036,18 @@
         <v>265</v>
       </c>
       <c r="H11">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11">
         <v>265</v>
       </c>
       <c r="J11" s="1">
-        <v>0.21890000000000001</v>
+        <v>0.23769999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1068,18 +1068,18 @@
         <v>72</v>
       </c>
       <c r="H12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12">
         <v>72</v>
       </c>
       <c r="J12" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.34720000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1100,18 +1100,18 @@
         <v>289</v>
       </c>
       <c r="H13">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>289</v>
       </c>
       <c r="J13" s="1">
-        <v>0.2422</v>
+        <v>0.26300000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1196,18 +1196,18 @@
         <v>395</v>
       </c>
       <c r="H16">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="I16">
         <v>395</v>
       </c>
       <c r="J16" s="1">
-        <v>0.55189999999999995</v>
+        <v>0.58230000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1228,18 +1228,18 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="I17">
         <v>400</v>
       </c>
       <c r="J17" s="1">
-        <v>0.34250000000000003</v>
+        <v>0.38250000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1260,18 +1260,18 @@
         <v>245</v>
       </c>
       <c r="H18">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I18">
         <v>245</v>
       </c>
       <c r="J18" s="1">
-        <v>0.40410000000000001</v>
+        <v>0.42449999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1292,18 +1292,18 @@
         <v>69</v>
       </c>
       <c r="H19">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19">
         <v>276</v>
       </c>
       <c r="J19" s="1">
-        <v>0.35870000000000002</v>
+        <v>0.37319999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1388,18 +1388,18 @@
         <v>691280</v>
       </c>
       <c r="H22">
-        <v>3004367</v>
+        <v>3174377</v>
       </c>
       <c r="I22">
         <v>8295360</v>
       </c>
       <c r="J22" s="1">
-        <v>0.36220000000000002</v>
+        <v>0.38269999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1420,18 +1420,18 @@
         <v>689046</v>
       </c>
       <c r="H23">
-        <v>455300.3</v>
+        <v>479246.3</v>
       </c>
       <c r="I23">
         <v>1378092</v>
       </c>
       <c r="J23" s="1">
-        <v>0.33040000000000003</v>
+        <v>0.3478</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1452,18 +1452,18 @@
         <v>647</v>
       </c>
       <c r="H24">
-        <v>5565</v>
+        <v>5842</v>
       </c>
       <c r="I24">
         <v>15528</v>
       </c>
       <c r="J24" s="1">
-        <v>0.3584</v>
+        <v>0.37619999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1484,18 +1484,18 @@
         <v>691280</v>
       </c>
       <c r="H25">
-        <v>1042197</v>
+        <v>1104477</v>
       </c>
       <c r="I25">
         <v>2765120</v>
       </c>
       <c r="J25" s="1">
-        <v>0.37690000000000001</v>
+        <v>0.39939999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1516,18 +1516,18 @@
         <v>691280</v>
       </c>
       <c r="H26">
-        <v>345340</v>
+        <v>361410</v>
       </c>
       <c r="I26">
         <v>691280</v>
       </c>
       <c r="J26" s="1">
-        <v>0.49959999999999999</v>
+        <v>0.52280000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1548,18 +1548,18 @@
         <v>346</v>
       </c>
       <c r="H27">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="I27">
         <v>1384</v>
       </c>
       <c r="J27" s="1">
-        <v>0.31719999999999998</v>
+        <v>0.33090000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1580,18 +1580,18 @@
         <v>501</v>
       </c>
       <c r="H28">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="I28">
         <v>501</v>
       </c>
       <c r="J28" s="1">
-        <v>0.46710000000000002</v>
+        <v>0.48099999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1612,18 +1612,18 @@
         <v>1109</v>
       </c>
       <c r="H29">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="I29">
         <v>2218</v>
       </c>
       <c r="J29" s="1">
-        <v>0.33179999999999998</v>
+        <v>0.34989999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1644,18 +1644,18 @@
         <v>649</v>
       </c>
       <c r="H30">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="I30">
         <v>649</v>
       </c>
       <c r="J30" s="1">
-        <v>0.35749999999999998</v>
+        <v>0.40060000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1676,18 +1676,18 @@
         <v>331</v>
       </c>
       <c r="H31">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I31">
         <v>331</v>
       </c>
       <c r="J31" s="1">
-        <v>0.2175</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1719,7 +1719,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1740,18 +1740,18 @@
         <v>59</v>
       </c>
       <c r="H33">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="I33">
         <v>1416</v>
       </c>
       <c r="J33" s="1">
-        <v>0.35809999999999997</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1772,18 +1772,18 @@
         <v>47</v>
       </c>
       <c r="H34">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="I34">
         <v>564</v>
       </c>
       <c r="J34" s="1">
-        <v>0.3599</v>
+        <v>0.38479999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1804,18 +1804,18 @@
         <v>691280</v>
       </c>
       <c r="H35">
-        <v>3011115</v>
+        <v>3160555</v>
       </c>
       <c r="I35">
         <v>8295360</v>
       </c>
       <c r="J35" s="1">
-        <v>0.36299999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1836,18 +1836,18 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>7708</v>
+        <v>8059</v>
       </c>
       <c r="I36">
         <v>20580</v>
       </c>
       <c r="J36" s="1">
-        <v>0.3745</v>
+        <v>0.3916</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1868,18 +1868,18 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1091</v>
+        <v>1124</v>
       </c>
       <c r="I37">
         <v>3024</v>
       </c>
       <c r="J37" s="1">
-        <v>0.36080000000000001</v>
+        <v>0.37169999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1900,18 +1900,18 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>6895</v>
+        <v>7329</v>
       </c>
       <c r="I38">
         <v>19416</v>
       </c>
       <c r="J38" s="1">
-        <v>0.35510000000000003</v>
+        <v>0.3775</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1932,18 +1932,18 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>9815</v>
+        <v>10383</v>
       </c>
       <c r="I39">
         <v>27456</v>
       </c>
       <c r="J39" s="1">
-        <v>0.35749999999999998</v>
+        <v>0.37819999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1964,18 +1964,18 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="I40">
         <v>1404</v>
       </c>
       <c r="J40" s="1">
-        <v>0.35039999999999999</v>
+        <v>0.36969999999999997</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -1996,18 +1996,18 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I41">
         <v>556</v>
       </c>
       <c r="J41" s="1">
-        <v>0.37230000000000002</v>
+        <v>0.38490000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2028,18 +2028,18 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42">
         <v>48</v>
       </c>
       <c r="J42" s="1">
-        <v>0.375</v>
+        <v>0.39579999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2060,18 +2060,18 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I43">
         <v>950</v>
       </c>
       <c r="J43" s="1">
-        <v>0.34320000000000001</v>
+        <v>0.34839999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2092,18 +2092,18 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1249</v>
+        <v>1343</v>
       </c>
       <c r="I44">
         <v>3552</v>
       </c>
       <c r="J44" s="1">
-        <v>0.35160000000000002</v>
+        <v>0.37809999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2124,18 +2124,18 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="I45">
         <v>2508</v>
       </c>
       <c r="J45" s="1">
-        <v>0.35170000000000001</v>
+        <v>0.36199999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2156,18 +2156,18 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="I46">
         <v>624</v>
       </c>
       <c r="J46" s="1">
-        <v>0.3574</v>
+        <v>0.37819999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2188,18 +2188,18 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>10520</v>
+        <v>11065</v>
       </c>
       <c r="I47">
         <v>25564</v>
       </c>
       <c r="J47" s="1">
-        <v>0.41149999999999998</v>
+        <v>0.43280000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2220,18 +2220,18 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I48">
         <v>228</v>
       </c>
       <c r="J48" s="1">
-        <v>0.39910000000000001</v>
+        <v>0.4123</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>46345</v>
+        <v>48317</v>
       </c>
       <c r="I53">
         <v>117348</v>
       </c>
       <c r="J53" s="1">
-        <v>0.39489999999999997</v>
+        <v>0.41170000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2412,18 +2412,18 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="I54">
         <v>1584</v>
       </c>
       <c r="J54" s="1">
-        <v>0.35610000000000003</v>
+        <v>0.36430000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2444,18 +2444,18 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I55">
         <v>516</v>
       </c>
       <c r="J55" s="1">
-        <v>0.34499999999999997</v>
+        <v>0.35849999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2476,18 +2476,18 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="I56">
         <v>1416</v>
       </c>
       <c r="J56" s="1">
-        <v>0.35170000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2540,18 +2540,18 @@
         <v>366</v>
       </c>
       <c r="H58">
-        <v>3236</v>
+        <v>3345</v>
       </c>
       <c r="I58">
         <v>8784</v>
       </c>
       <c r="J58" s="1">
-        <v>0.36840000000000001</v>
+        <v>0.38080000000000003</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2572,18 +2572,18 @@
         <v>244</v>
       </c>
       <c r="H59">
-        <v>1171</v>
+        <v>1185</v>
       </c>
       <c r="I59">
         <v>2928</v>
       </c>
       <c r="J59" s="1">
-        <v>0.39989999999999998</v>
+        <v>0.4047</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2604,18 +2604,18 @@
         <v>640</v>
       </c>
       <c r="H60">
-        <v>2628</v>
+        <v>2959</v>
       </c>
       <c r="I60">
         <v>7680</v>
       </c>
       <c r="J60" s="1">
-        <v>0.3422</v>
+        <v>0.38529999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2636,18 +2636,18 @@
         <v>696</v>
       </c>
       <c r="H61">
-        <v>3112</v>
+        <v>3428</v>
       </c>
       <c r="I61">
         <v>8952</v>
       </c>
       <c r="J61" s="1">
-        <v>0.34760000000000002</v>
+        <v>0.38290000000000002</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2668,18 +2668,18 @@
         <v>90</v>
       </c>
       <c r="H62">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="I62">
         <v>1092</v>
       </c>
       <c r="J62" s="1">
-        <v>0.34429999999999999</v>
+        <v>0.36449999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2700,18 +2700,18 @@
         <v>8</v>
       </c>
       <c r="H63">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I63">
         <v>240</v>
       </c>
       <c r="J63" s="1">
-        <v>0.375</v>
+        <v>0.39579999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2764,18 +2764,18 @@
         <v>3</v>
       </c>
       <c r="H65">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I65">
         <v>36</v>
       </c>
       <c r="J65" s="1">
-        <v>0.38890000000000002</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2796,18 +2796,18 @@
         <v>73</v>
       </c>
       <c r="H66">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="I66">
         <v>876</v>
       </c>
       <c r="J66" s="1">
-        <v>0.34250000000000003</v>
+        <v>0.35049999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2828,18 +2828,18 @@
         <v>139</v>
       </c>
       <c r="H67">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="I67">
         <v>1668</v>
       </c>
       <c r="J67" s="1">
-        <v>0.39029999999999998</v>
+        <v>0.39929999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2860,18 +2860,18 @@
         <v>273</v>
       </c>
       <c r="H68">
-        <v>1150</v>
+        <v>1286</v>
       </c>
       <c r="I68">
         <v>3276</v>
       </c>
       <c r="J68" s="1">
-        <v>0.35099999999999998</v>
+        <v>0.3926</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2892,18 +2892,18 @@
         <v>14</v>
       </c>
       <c r="H69">
-        <v>1820</v>
+        <v>1918</v>
       </c>
       <c r="I69">
         <v>5110</v>
       </c>
       <c r="J69" s="1">
-        <v>0.35620000000000002</v>
+        <v>0.37530000000000002</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2924,18 +2924,18 @@
         <v>30</v>
       </c>
       <c r="H70">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I70">
         <v>120</v>
       </c>
       <c r="J70" s="1">
-        <v>0.30830000000000002</v>
+        <v>0.35830000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2956,18 +2956,18 @@
         <v>30</v>
       </c>
       <c r="H71">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I71">
         <v>30</v>
       </c>
       <c r="J71" s="1">
-        <v>0.23330000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2988,18 +2988,18 @@
         <v>52</v>
       </c>
       <c r="H72">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I72">
         <v>208</v>
       </c>
       <c r="J72" s="1">
-        <v>0.41349999999999998</v>
+        <v>0.41830000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3020,18 +3020,18 @@
         <v>47</v>
       </c>
       <c r="H73">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I73">
         <v>52</v>
       </c>
       <c r="J73" s="1">
-        <v>0.82689999999999997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3116,18 +3116,18 @@
         <v>189</v>
       </c>
       <c r="H76">
-        <v>858</v>
+        <v>881</v>
       </c>
       <c r="I76">
         <v>2268</v>
       </c>
       <c r="J76" s="1">
-        <v>0.37830000000000003</v>
+        <v>0.38840000000000002</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3148,18 +3148,18 @@
         <v>287</v>
       </c>
       <c r="H77">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="I77">
         <v>3444</v>
       </c>
       <c r="J77" s="1">
-        <v>0.39400000000000002</v>
+        <v>0.39579999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3180,18 +3180,18 @@
         <v>74</v>
       </c>
       <c r="H78">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I78">
         <v>948</v>
       </c>
       <c r="J78" s="1">
-        <v>0.38819999999999999</v>
+        <v>0.39029999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3212,18 +3212,18 @@
         <v>123</v>
       </c>
       <c r="H79">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="I79">
         <v>1632</v>
       </c>
       <c r="J79" s="1">
-        <v>0.33090000000000003</v>
+        <v>0.34989999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3244,18 +3244,18 @@
         <v>29</v>
       </c>
       <c r="H80">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I80">
         <v>348</v>
       </c>
       <c r="J80" s="1">
-        <v>0.34200000000000003</v>
+        <v>0.35060000000000002</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3308,18 +3308,18 @@
         <v>293</v>
       </c>
       <c r="H82">
-        <v>2599</v>
+        <v>2759</v>
       </c>
       <c r="I82">
         <v>7032</v>
       </c>
       <c r="J82" s="1">
-        <v>0.36959999999999998</v>
+        <v>0.39229999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3340,18 +3340,18 @@
         <v>16</v>
       </c>
       <c r="H83">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I83">
         <v>192</v>
       </c>
       <c r="J83" s="1">
-        <v>0.35420000000000001</v>
+        <v>0.36459999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3372,18 +3372,18 @@
         <v>37</v>
       </c>
       <c r="H84">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I84">
         <v>444</v>
       </c>
       <c r="J84" s="1">
-        <v>0.3649</v>
+        <v>0.38290000000000002</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3404,18 +3404,18 @@
         <v>493</v>
       </c>
       <c r="H85">
-        <v>2141</v>
+        <v>2207</v>
       </c>
       <c r="I85">
         <v>5916</v>
       </c>
       <c r="J85" s="1">
-        <v>0.3619</v>
+        <v>0.37309999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3436,18 +3436,18 @@
         <v>2</v>
       </c>
       <c r="H86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I86">
         <v>24</v>
       </c>
       <c r="J86" s="1">
-        <v>0.29170000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3468,18 +3468,18 @@
         <v>749</v>
       </c>
       <c r="H87">
-        <v>3251</v>
+        <v>3432</v>
       </c>
       <c r="I87">
         <v>8988</v>
       </c>
       <c r="J87" s="1">
-        <v>0.36170000000000002</v>
+        <v>0.38179999999999997</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3500,18 +3500,18 @@
         <v>161</v>
       </c>
       <c r="H88">
-        <v>692</v>
+        <v>749</v>
       </c>
       <c r="I88">
         <v>1932</v>
       </c>
       <c r="J88" s="1">
-        <v>0.35820000000000002</v>
+        <v>0.38769999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3532,18 +3532,18 @@
         <v>47</v>
       </c>
       <c r="H89">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="I89">
         <v>1128</v>
       </c>
       <c r="J89" s="1">
-        <v>0.36880000000000002</v>
+        <v>0.39269999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3564,18 +3564,18 @@
         <v>55</v>
       </c>
       <c r="H90">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="I90">
         <v>660</v>
       </c>
       <c r="J90" s="1">
-        <v>0.38179999999999997</v>
+        <v>0.39389999999999997</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3596,18 +3596,18 @@
         <v>45</v>
       </c>
       <c r="H91">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="I91">
         <v>540</v>
       </c>
       <c r="J91" s="1">
-        <v>0.35189999999999999</v>
+        <v>0.37590000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3628,18 +3628,18 @@
         <v>3</v>
       </c>
       <c r="H92">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="I92">
         <v>1095</v>
       </c>
       <c r="J92" s="1">
-        <v>0.52239999999999998</v>
+        <v>0.54790000000000005</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3724,18 +3724,18 @@
         <v>33</v>
       </c>
       <c r="H95">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I95">
         <v>132</v>
       </c>
       <c r="J95" s="1">
-        <v>0.29549999999999998</v>
+        <v>0.34849999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3767,7 +3767,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3788,18 +3788,18 @@
         <v>9</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I97">
         <v>18</v>
       </c>
       <c r="J97" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3852,18 +3852,18 @@
         <v>30</v>
       </c>
       <c r="H99">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I99">
         <v>360</v>
       </c>
       <c r="J99" s="1">
-        <v>0.3639</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3884,18 +3884,18 @@
         <v>6</v>
       </c>
       <c r="H100">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I100">
         <v>72</v>
       </c>
       <c r="J100" s="1">
-        <v>0.34720000000000001</v>
+        <v>0.36109999999999998</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3916,18 +3916,18 @@
         <v>52</v>
       </c>
       <c r="H101">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="I101">
         <v>623</v>
       </c>
       <c r="J101" s="1">
-        <v>0.35959999999999998</v>
+        <v>0.37080000000000002</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3948,18 +3948,18 @@
         <v>46</v>
       </c>
       <c r="H102">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="I102">
         <v>552</v>
       </c>
       <c r="J102" s="1">
-        <v>0.35870000000000002</v>
+        <v>0.37319999999999998</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3980,18 +3980,18 @@
         <v>458</v>
       </c>
       <c r="H103">
-        <v>4104</v>
+        <v>4262</v>
       </c>
       <c r="I103">
         <v>10992</v>
       </c>
       <c r="J103" s="1">
-        <v>0.37340000000000001</v>
+        <v>0.38769999999999999</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4044,18 +4044,18 @@
         <v>43</v>
       </c>
       <c r="H105">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I105">
         <v>516</v>
       </c>
       <c r="J105" s="1">
-        <v>0.34689999999999999</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4076,18 +4076,18 @@
         <v>665</v>
       </c>
       <c r="H106">
-        <v>2832</v>
+        <v>2974</v>
       </c>
       <c r="I106">
         <v>7992</v>
       </c>
       <c r="J106" s="1">
-        <v>0.35439999999999999</v>
+        <v>0.37209999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4108,18 +4108,18 @@
         <v>1043</v>
       </c>
       <c r="H107">
-        <v>4283</v>
+        <v>4586</v>
       </c>
       <c r="I107">
         <v>12264</v>
       </c>
       <c r="J107" s="1">
-        <v>0.34920000000000001</v>
+        <v>0.37390000000000001</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4140,18 +4140,18 @@
         <v>71</v>
       </c>
       <c r="H108">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="I108">
         <v>852</v>
       </c>
       <c r="J108" s="1">
-        <v>0.35920000000000002</v>
+        <v>0.36620000000000003</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4172,18 +4172,18 @@
         <v>22</v>
       </c>
       <c r="H109">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I109">
         <v>528</v>
       </c>
       <c r="J109" s="1">
-        <v>0.36170000000000002</v>
+        <v>0.37119999999999997</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4268,18 +4268,18 @@
         <v>81</v>
       </c>
       <c r="H112">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="I112">
         <v>972</v>
       </c>
       <c r="J112" s="1">
-        <v>0.35389999999999999</v>
+        <v>0.37959999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4300,18 +4300,18 @@
         <v>52</v>
       </c>
       <c r="H113">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="I113">
         <v>624</v>
       </c>
       <c r="J113" s="1">
-        <v>0.33650000000000002</v>
+        <v>0.35420000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4332,18 +4332,18 @@
         <v>44</v>
       </c>
       <c r="H114">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="I114">
         <v>528</v>
       </c>
       <c r="J114" s="1">
-        <v>0.34470000000000001</v>
+        <v>0.38829999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4428,18 +4428,18 @@
         <v>188</v>
       </c>
       <c r="H117">
-        <v>752</v>
+        <v>806</v>
       </c>
       <c r="I117">
         <v>2256</v>
       </c>
       <c r="J117" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35730000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4460,18 +4460,18 @@
         <v>43</v>
       </c>
       <c r="H118">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I118">
         <v>516</v>
       </c>
       <c r="J118" s="1">
-        <v>0.3508</v>
+        <v>0.36049999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4492,18 +4492,18 @@
         <v>14</v>
       </c>
       <c r="H119">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I119">
         <v>168</v>
       </c>
       <c r="J119" s="1">
-        <v>0.375</v>
+        <v>0.38690000000000002</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4524,18 +4524,18 @@
         <v>52</v>
       </c>
       <c r="H120">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I120">
         <v>624</v>
       </c>
       <c r="J120" s="1">
-        <v>0.34129999999999999</v>
+        <v>0.34939999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4556,18 +4556,18 @@
         <v>41</v>
       </c>
       <c r="H121">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I121">
         <v>492</v>
       </c>
       <c r="J121" s="1">
-        <v>0.35160000000000002</v>
+        <v>0.36180000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4588,18 +4588,18 @@
         <v>585</v>
       </c>
       <c r="H122">
-        <v>2593</v>
+        <v>2757</v>
       </c>
       <c r="I122">
         <v>7020</v>
       </c>
       <c r="J122" s="1">
-        <v>0.36940000000000001</v>
+        <v>0.39269999999999999</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4620,18 +4620,18 @@
         <v>383</v>
       </c>
       <c r="H123">
-        <v>3431</v>
+        <v>3591</v>
       </c>
       <c r="I123">
         <v>9144</v>
       </c>
       <c r="J123" s="1">
-        <v>0.37519999999999998</v>
+        <v>0.39269999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4684,18 +4684,18 @@
         <v>1</v>
       </c>
       <c r="H125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I125">
         <v>12</v>
       </c>
       <c r="J125" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4716,18 +4716,18 @@
         <v>22</v>
       </c>
       <c r="H126">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I126">
         <v>264</v>
       </c>
       <c r="J126" s="1">
-        <v>0.39019999999999999</v>
+        <v>0.40910000000000002</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4780,18 +4780,18 @@
         <v>898</v>
       </c>
       <c r="H128">
-        <v>4017</v>
+        <v>4273</v>
       </c>
       <c r="I128">
         <v>10776</v>
       </c>
       <c r="J128" s="1">
-        <v>0.37280000000000002</v>
+        <v>0.39650000000000002</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4812,18 +4812,18 @@
         <v>126</v>
       </c>
       <c r="H129">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="I129">
         <v>1512</v>
       </c>
       <c r="J129" s="1">
-        <v>0.37369999999999998</v>
+        <v>0.3962</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4844,18 +4844,18 @@
         <v>14</v>
       </c>
       <c r="H130">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I130">
         <v>336</v>
       </c>
       <c r="J130" s="1">
-        <v>0.372</v>
+        <v>0.38690000000000002</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4876,18 +4876,18 @@
         <v>60</v>
       </c>
       <c r="H131">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I131">
         <v>720</v>
       </c>
       <c r="J131" s="1">
-        <v>0.34720000000000001</v>
+        <v>0.35139999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4908,18 +4908,18 @@
         <v>51</v>
       </c>
       <c r="H132">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I132">
         <v>624</v>
       </c>
       <c r="J132" s="1">
-        <v>0.33810000000000001</v>
+        <v>0.34939999999999999</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -5015,7 +5015,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -5036,18 +5036,18 @@
         <v>13</v>
       </c>
       <c r="H136">
-        <v>2136</v>
+        <v>2245</v>
       </c>
       <c r="I136">
         <v>4745</v>
       </c>
       <c r="J136" s="1">
-        <v>0.45019999999999999</v>
+        <v>0.47310000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -5068,18 +5068,18 @@
         <v>29</v>
       </c>
       <c r="H137">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I137">
         <v>112</v>
       </c>
       <c r="J137" s="1">
-        <v>0.44640000000000002</v>
+        <v>0.46429999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5100,18 +5100,18 @@
         <v>29</v>
       </c>
       <c r="H138">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I138">
         <v>28</v>
       </c>
       <c r="J138" s="1">
-        <v>0.28570000000000001</v>
+        <v>0.35709999999999997</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5132,18 +5132,18 @@
         <v>45</v>
       </c>
       <c r="H139">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I139">
         <v>180</v>
       </c>
       <c r="J139" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.4556</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5175,7 +5175,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5260,18 +5260,18 @@
         <v>42</v>
       </c>
       <c r="H143">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I143">
         <v>492</v>
       </c>
       <c r="J143" s="1">
-        <v>0.34960000000000002</v>
+        <v>0.36380000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5335,7 +5335,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5388,18 +5388,18 @@
         <v>387</v>
       </c>
       <c r="H147">
-        <v>3448</v>
+        <v>3591</v>
       </c>
       <c r="I147">
         <v>9288</v>
       </c>
       <c r="J147" s="1">
-        <v>0.37119999999999997</v>
+        <v>0.3866</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5420,18 +5420,18 @@
         <v>39</v>
       </c>
       <c r="H148">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="I148">
         <v>468</v>
       </c>
       <c r="J148" s="1">
-        <v>0.36109999999999998</v>
+        <v>0.37819999999999998</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5452,18 +5452,18 @@
         <v>590</v>
       </c>
       <c r="H149">
-        <v>2431</v>
+        <v>2641</v>
       </c>
       <c r="I149">
         <v>7080</v>
       </c>
       <c r="J149" s="1">
-        <v>0.34339999999999998</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5484,18 +5484,18 @@
         <v>964</v>
       </c>
       <c r="H150">
-        <v>4250</v>
+        <v>4532</v>
       </c>
       <c r="I150">
         <v>11568</v>
       </c>
       <c r="J150" s="1">
-        <v>0.3674</v>
+        <v>0.39179999999999998</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5516,18 +5516,18 @@
         <v>96</v>
       </c>
       <c r="H151">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="I151">
         <v>1152</v>
       </c>
       <c r="J151" s="1">
-        <v>0.34110000000000001</v>
+        <v>0.35759999999999997</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5548,18 +5548,18 @@
         <v>13</v>
       </c>
       <c r="H152">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I152">
         <v>312</v>
       </c>
       <c r="J152" s="1">
-        <v>0.38140000000000002</v>
+        <v>0.40060000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5580,18 +5580,18 @@
         <v>7</v>
       </c>
       <c r="H153">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I153">
         <v>84</v>
       </c>
       <c r="J153" s="1">
-        <v>0.32140000000000002</v>
+        <v>0.35709999999999997</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5612,18 +5612,18 @@
         <v>1</v>
       </c>
       <c r="H154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I154">
         <v>12</v>
       </c>
       <c r="J154" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5644,18 +5644,18 @@
         <v>108</v>
       </c>
       <c r="H155">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="I155">
         <v>1296</v>
       </c>
       <c r="J155" s="1">
-        <v>0.29010000000000002</v>
+        <v>0.30020000000000002</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5676,18 +5676,18 @@
         <v>47</v>
       </c>
       <c r="H156">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I156">
         <v>564</v>
       </c>
       <c r="J156" s="1">
-        <v>0.35460000000000003</v>
+        <v>0.37230000000000002</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5719,7 +5719,7 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5740,18 +5740,18 @@
         <v>30</v>
       </c>
       <c r="H158">
-        <v>4307</v>
+        <v>4549</v>
       </c>
       <c r="I158">
         <v>10950</v>
       </c>
       <c r="J158" s="1">
-        <v>0.39329999999999998</v>
+        <v>0.41539999999999999</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5836,18 +5836,18 @@
         <v>37</v>
       </c>
       <c r="H161">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I161">
         <v>148</v>
       </c>
       <c r="J161" s="1">
-        <v>0.34460000000000002</v>
+        <v>0.39860000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5964,18 +5964,18 @@
         <v>170</v>
       </c>
       <c r="H165">
-        <v>733</v>
+        <v>751</v>
       </c>
       <c r="I165">
         <v>2040</v>
       </c>
       <c r="J165" s="1">
-        <v>0.35930000000000001</v>
+        <v>0.36809999999999998</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -5996,18 +5996,18 @@
         <v>36</v>
       </c>
       <c r="H166">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I166">
         <v>432</v>
       </c>
       <c r="J166" s="1">
-        <v>0.35880000000000001</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -6060,18 +6060,18 @@
         <v>9</v>
       </c>
       <c r="H168">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I168">
         <v>108</v>
       </c>
       <c r="J168" s="1">
-        <v>0.35189999999999999</v>
+        <v>0.37040000000000001</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6092,18 +6092,18 @@
         <v>88</v>
       </c>
       <c r="H169">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="I169">
         <v>1056</v>
       </c>
       <c r="J169" s="1">
-        <v>0.35039999999999999</v>
+        <v>0.36840000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6156,18 +6156,18 @@
         <v>9</v>
       </c>
       <c r="H171">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I171">
         <v>216</v>
       </c>
       <c r="J171" s="1">
-        <v>0.36570000000000003</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6188,18 +6188,18 @@
         <v>9</v>
       </c>
       <c r="H172">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I172">
         <v>108</v>
       </c>
       <c r="J172" s="1">
-        <v>0.36109999999999998</v>
+        <v>0.39810000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6220,18 +6220,18 @@
         <v>59</v>
       </c>
       <c r="H173">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="I173">
         <v>708</v>
       </c>
       <c r="J173" s="1">
-        <v>0.33900000000000002</v>
+        <v>0.34749999999999998</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6540,18 +6540,18 @@
         <v>9</v>
       </c>
       <c r="H183">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I183">
         <v>36</v>
       </c>
       <c r="J183" s="1">
-        <v>0.30559999999999998</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6583,7 +6583,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6668,18 +6668,18 @@
         <v>188993</v>
       </c>
       <c r="H187">
-        <v>810883</v>
+        <v>884015</v>
       </c>
       <c r="I187">
         <v>2267916</v>
       </c>
       <c r="J187" s="1">
-        <v>0.35749999999999998</v>
+        <v>0.38979999999999998</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6700,18 +6700,18 @@
         <v>183511</v>
       </c>
       <c r="H188">
-        <v>121201</v>
+        <v>137544</v>
       </c>
       <c r="I188">
         <v>367022</v>
       </c>
       <c r="J188" s="1">
-        <v>0.33019999999999999</v>
+        <v>0.37480000000000002</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6732,18 +6732,18 @@
         <v>174</v>
       </c>
       <c r="H189">
-        <v>1497</v>
+        <v>1598</v>
       </c>
       <c r="I189">
         <v>4176</v>
       </c>
       <c r="J189" s="1">
-        <v>0.35849999999999999</v>
+        <v>0.38269999999999998</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6764,18 +6764,18 @@
         <v>188993</v>
       </c>
       <c r="H190">
-        <v>277905</v>
+        <v>297147</v>
       </c>
       <c r="I190">
         <v>755972</v>
       </c>
       <c r="J190" s="1">
-        <v>0.36759999999999998</v>
+        <v>0.3931</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6796,18 +6796,18 @@
         <v>188993</v>
       </c>
       <c r="H191">
-        <v>66841</v>
+        <v>75281</v>
       </c>
       <c r="I191">
         <v>188993</v>
       </c>
       <c r="J191" s="1">
-        <v>0.35370000000000001</v>
+        <v>0.39829999999999999</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6828,18 +6828,18 @@
         <v>98</v>
       </c>
       <c r="H192">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="I192">
         <v>392</v>
       </c>
       <c r="J192" s="1">
-        <v>0.34689999999999999</v>
+        <v>0.40050000000000002</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6892,18 +6892,18 @@
         <v>271</v>
       </c>
       <c r="H194">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="I194">
         <v>542</v>
       </c>
       <c r="J194" s="1">
-        <v>0.33579999999999999</v>
+        <v>0.38190000000000002</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6924,18 +6924,18 @@
         <v>133</v>
       </c>
       <c r="H195">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I195">
         <v>133</v>
       </c>
       <c r="J195" s="1">
-        <v>0.58650000000000002</v>
+        <v>0.60150000000000003</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6988,18 +6988,18 @@
         <v>5482</v>
       </c>
       <c r="H197">
-        <v>4942</v>
+        <v>5238</v>
       </c>
       <c r="I197">
         <v>10964</v>
       </c>
       <c r="J197" s="1">
-        <v>0.45069999999999999</v>
+        <v>0.47770000000000001</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -7020,18 +7020,18 @@
         <v>188377</v>
       </c>
       <c r="H198">
-        <v>763037</v>
+        <v>814738</v>
       </c>
       <c r="I198">
         <v>2260524</v>
       </c>
       <c r="J198" s="1">
-        <v>0.33750000000000002</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -7052,18 +7052,18 @@
         <v>9</v>
       </c>
       <c r="H199">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I199">
         <v>216</v>
       </c>
       <c r="J199" s="1">
-        <v>0.37959999999999999</v>
+        <v>0.40279999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -7084,18 +7084,18 @@
         <v>263</v>
       </c>
       <c r="H200">
-        <v>2370</v>
+        <v>2462</v>
       </c>
       <c r="I200">
         <v>6312</v>
       </c>
       <c r="J200" s="1">
-        <v>0.3755</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7116,18 +7116,18 @@
         <v>40</v>
       </c>
       <c r="H201">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I201">
         <v>480</v>
       </c>
       <c r="J201" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35420000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7148,18 +7148,18 @@
         <v>408</v>
       </c>
       <c r="H202">
-        <v>1661</v>
+        <v>1776</v>
       </c>
       <c r="I202">
         <v>4896</v>
       </c>
       <c r="J202" s="1">
-        <v>0.33929999999999999</v>
+        <v>0.36270000000000002</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7180,18 +7180,18 @@
         <v>550</v>
       </c>
       <c r="H203">
-        <v>2326</v>
+        <v>2560</v>
       </c>
       <c r="I203">
         <v>6600</v>
       </c>
       <c r="J203" s="1">
-        <v>0.35239999999999999</v>
+        <v>0.38790000000000002</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7212,18 +7212,18 @@
         <v>76</v>
       </c>
       <c r="H204">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="I204">
         <v>912</v>
       </c>
       <c r="J204" s="1">
-        <v>0.35310000000000002</v>
+        <v>0.37719999999999998</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7244,18 +7244,18 @@
         <v>6</v>
       </c>
       <c r="H205">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I205">
         <v>144</v>
       </c>
       <c r="J205" s="1">
-        <v>0.36809999999999998</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7276,18 +7276,18 @@
         <v>19</v>
       </c>
       <c r="H206">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I206">
         <v>228</v>
       </c>
       <c r="J206" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35089999999999999</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7351,7 +7351,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7372,18 +7372,18 @@
         <v>31</v>
       </c>
       <c r="H209">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I209">
         <v>372</v>
       </c>
       <c r="J209" s="1">
-        <v>0.3468</v>
+        <v>0.36559999999999998</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7404,18 +7404,18 @@
         <v>175</v>
       </c>
       <c r="H210">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="I210">
         <v>2100</v>
       </c>
       <c r="J210" s="1">
-        <v>0.36</v>
+        <v>0.37480000000000002</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7436,18 +7436,18 @@
         <v>9</v>
       </c>
       <c r="H211">
-        <v>2152</v>
+        <v>2273</v>
       </c>
       <c r="I211">
         <v>32856</v>
       </c>
       <c r="J211" s="1">
-        <v>6.5500000000000003E-2</v>
+        <v>6.9199999999999998E-2</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7468,18 +7468,18 @@
         <v>9</v>
       </c>
       <c r="H212">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I212">
         <v>36</v>
       </c>
       <c r="J212" s="1">
-        <v>0.83330000000000004</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7532,18 +7532,18 @@
         <v>34</v>
       </c>
       <c r="H214">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I214">
         <v>132</v>
       </c>
       <c r="J214" s="1">
-        <v>0.68179999999999996</v>
+        <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7575,7 +7575,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7596,18 +7596,18 @@
         <v>9</v>
       </c>
       <c r="H216">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I216">
         <v>18</v>
       </c>
       <c r="J216" s="1">
-        <v>0.55559999999999998</v>
+        <v>0.61109999999999998</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7628,18 +7628,18 @@
         <v>3654</v>
       </c>
       <c r="H217">
-        <v>15340</v>
+        <v>16851</v>
       </c>
       <c r="I217">
         <v>43848</v>
       </c>
       <c r="J217" s="1">
-        <v>0.3498</v>
+        <v>0.38429999999999997</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7692,18 +7692,18 @@
         <v>486</v>
       </c>
       <c r="H219">
-        <v>4315</v>
+        <v>4513</v>
       </c>
       <c r="I219">
         <v>11664</v>
       </c>
       <c r="J219" s="1">
-        <v>0.36990000000000001</v>
+        <v>0.38690000000000002</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7724,18 +7724,18 @@
         <v>25</v>
       </c>
       <c r="H220">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="I220">
         <v>300</v>
       </c>
       <c r="J220" s="1">
-        <v>0.37330000000000002</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7756,18 +7756,18 @@
         <v>68</v>
       </c>
       <c r="H221">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="I221">
         <v>816</v>
       </c>
       <c r="J221" s="1">
-        <v>0.36399999999999999</v>
+        <v>0.38240000000000002</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7788,18 +7788,18 @@
         <v>729</v>
       </c>
       <c r="H222">
-        <v>3192</v>
+        <v>3349</v>
       </c>
       <c r="I222">
         <v>8772</v>
       </c>
       <c r="J222" s="1">
-        <v>0.3639</v>
+        <v>0.38179999999999997</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7820,18 +7820,18 @@
         <v>854</v>
       </c>
       <c r="H223">
-        <v>3971</v>
+        <v>4209</v>
       </c>
       <c r="I223">
         <v>11040</v>
       </c>
       <c r="J223" s="1">
-        <v>0.35970000000000002</v>
+        <v>0.38129999999999997</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7852,18 +7852,18 @@
         <v>121</v>
       </c>
       <c r="H224">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="I224">
         <v>1452</v>
       </c>
       <c r="J224" s="1">
-        <v>0.3533</v>
+        <v>0.37119999999999997</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7884,18 +7884,18 @@
         <v>27</v>
       </c>
       <c r="H225">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I225">
         <v>648</v>
       </c>
       <c r="J225" s="1">
-        <v>0.38429999999999997</v>
+        <v>0.3997</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7916,18 +7916,18 @@
         <v>2</v>
       </c>
       <c r="H226">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I226">
         <v>24</v>
       </c>
       <c r="J226" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7948,18 +7948,18 @@
         <v>30</v>
       </c>
       <c r="H227">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I227">
         <v>360</v>
       </c>
       <c r="J227" s="1">
-        <v>0.39439999999999997</v>
+        <v>0.42780000000000001</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7980,18 +7980,18 @@
         <v>51</v>
       </c>
       <c r="H228">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="I228">
         <v>624</v>
       </c>
       <c r="J228" s="1">
-        <v>0.38140000000000002</v>
+        <v>0.4199</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -8012,18 +8012,18 @@
         <v>337</v>
       </c>
       <c r="H229">
-        <v>1518</v>
+        <v>1608</v>
       </c>
       <c r="I229">
         <v>4044</v>
       </c>
       <c r="J229" s="1">
-        <v>0.37540000000000001</v>
+        <v>0.39760000000000001</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -8044,18 +8044,18 @@
         <v>50</v>
       </c>
       <c r="H230">
-        <v>7692</v>
+        <v>8098</v>
       </c>
       <c r="I230">
         <v>18972</v>
       </c>
       <c r="J230" s="1">
-        <v>0.40539999999999998</v>
+        <v>0.42680000000000001</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -8076,18 +8076,18 @@
         <v>58</v>
       </c>
       <c r="H231">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I231">
         <v>232</v>
       </c>
       <c r="J231" s="1">
-        <v>0.3836</v>
+        <v>0.39660000000000001</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -8119,7 +8119,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8140,18 +8140,18 @@
         <v>56</v>
       </c>
       <c r="H233">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I233">
         <v>228</v>
       </c>
       <c r="J233" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35089999999999999</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8204,18 +8204,18 @@
         <v>4610</v>
       </c>
       <c r="H235">
-        <v>19984</v>
+        <v>21433</v>
       </c>
       <c r="I235">
         <v>55320</v>
       </c>
       <c r="J235" s="1">
-        <v>0.36120000000000002</v>
+        <v>0.38740000000000002</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8236,18 +8236,18 @@
         <v>44</v>
       </c>
       <c r="H236">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I236">
         <v>468</v>
       </c>
       <c r="J236" s="1">
-        <v>0.3654</v>
+        <v>0.37819999999999998</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8300,18 +8300,18 @@
         <v>90</v>
       </c>
       <c r="H238">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="I238">
         <v>1080</v>
       </c>
       <c r="J238" s="1">
-        <v>0.35830000000000001</v>
+        <v>0.38150000000000001</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8332,18 +8332,18 @@
         <v>27</v>
       </c>
       <c r="H239">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I239">
         <v>192</v>
       </c>
       <c r="J239" s="1">
-        <v>0.3594</v>
+        <v>0.40100000000000002</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8364,18 +8364,18 @@
         <v>121</v>
       </c>
       <c r="H240">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="I240">
         <v>1428</v>
       </c>
       <c r="J240" s="1">
-        <v>0.3543</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8428,18 +8428,18 @@
         <v>35</v>
       </c>
       <c r="H242">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I242">
         <v>420</v>
       </c>
       <c r="J242" s="1">
-        <v>0.37380000000000002</v>
+        <v>0.39050000000000001</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8460,18 +8460,18 @@
         <v>228</v>
       </c>
       <c r="H243">
-        <v>1013</v>
+        <v>1061</v>
       </c>
       <c r="I243">
         <v>2784</v>
       </c>
       <c r="J243" s="1">
-        <v>0.3639</v>
+        <v>0.38109999999999999</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8492,18 +8492,18 @@
         <v>264</v>
       </c>
       <c r="H244">
-        <v>1566</v>
+        <v>1648</v>
       </c>
       <c r="I244">
         <v>4291</v>
       </c>
       <c r="J244" s="1">
-        <v>0.3649</v>
+        <v>0.3841</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8524,18 +8524,18 @@
         <v>33</v>
       </c>
       <c r="H245">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I245">
         <v>384</v>
       </c>
       <c r="J245" s="1">
-        <v>0.37759999999999999</v>
+        <v>0.39579999999999999</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8567,7 +8567,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8588,18 +8588,18 @@
         <v>451</v>
       </c>
       <c r="H247">
-        <v>1941</v>
+        <v>2031</v>
       </c>
       <c r="I247">
         <v>5340</v>
       </c>
       <c r="J247" s="1">
-        <v>0.36349999999999999</v>
+        <v>0.38030000000000003</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8620,18 +8620,18 @@
         <v>66</v>
       </c>
       <c r="H248">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="I248">
         <v>792</v>
       </c>
       <c r="J248" s="1">
-        <v>0.37369999999999998</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8652,18 +8652,18 @@
         <v>84</v>
       </c>
       <c r="H249">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="I249">
         <v>1008</v>
       </c>
       <c r="J249" s="1">
-        <v>0.35220000000000001</v>
+        <v>0.38490000000000002</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8684,18 +8684,18 @@
         <v>23</v>
       </c>
       <c r="H250">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I250">
         <v>276</v>
       </c>
       <c r="J250" s="1">
-        <v>0.35139999999999999</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8716,18 +8716,18 @@
         <v>14</v>
       </c>
       <c r="H251">
-        <v>1934</v>
+        <v>2046</v>
       </c>
       <c r="I251">
         <v>5110</v>
       </c>
       <c r="J251" s="1">
-        <v>0.3785</v>
+        <v>0.40039999999999998</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8748,18 +8748,18 @@
         <v>11</v>
       </c>
       <c r="H252">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I252">
         <v>44</v>
       </c>
       <c r="J252" s="1">
-        <v>0.40910000000000002</v>
+        <v>0.43180000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8844,18 +8844,18 @@
         <v>34</v>
       </c>
       <c r="H255">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I255">
         <v>34</v>
       </c>
       <c r="J255" s="1">
-        <v>0.55879999999999996</v>
+        <v>0.58819999999999995</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8887,7 +8887,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8919,7 +8919,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8940,18 +8940,18 @@
         <v>33</v>
       </c>
       <c r="H258">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I258">
         <v>396</v>
       </c>
       <c r="J258" s="1">
-        <v>0.35610000000000003</v>
+        <v>0.37369999999999998</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8972,18 +8972,18 @@
         <v>23</v>
       </c>
       <c r="H259">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I259">
         <v>276</v>
       </c>
       <c r="J259" s="1">
-        <v>0.35139999999999999</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -9004,18 +9004,18 @@
         <v>79</v>
       </c>
       <c r="H260">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="I260">
         <v>948</v>
       </c>
       <c r="J260" s="1">
-        <v>0.3523</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -9036,18 +9036,18 @@
         <v>276</v>
       </c>
       <c r="H261">
-        <v>2040</v>
+        <v>2136</v>
       </c>
       <c r="I261">
         <v>5904</v>
       </c>
       <c r="J261" s="1">
-        <v>0.34549999999999997</v>
+        <v>0.36180000000000001</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -9068,18 +9068,18 @@
         <v>21</v>
       </c>
       <c r="H262">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I262">
         <v>264</v>
       </c>
       <c r="J262" s="1">
-        <v>0.35980000000000001</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -9111,7 +9111,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -9132,18 +9132,18 @@
         <v>74</v>
       </c>
       <c r="H264">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I264">
         <v>888</v>
       </c>
       <c r="J264" s="1">
-        <v>0.35589999999999999</v>
+        <v>0.36259999999999998</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -9164,18 +9164,18 @@
         <v>160</v>
       </c>
       <c r="H265">
-        <v>691</v>
+        <v>756</v>
       </c>
       <c r="I265">
         <v>1920</v>
       </c>
       <c r="J265" s="1">
-        <v>0.3599</v>
+        <v>0.39379999999999998</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -9196,18 +9196,18 @@
         <v>82</v>
       </c>
       <c r="H266">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="I266">
         <v>1968</v>
       </c>
       <c r="J266" s="1">
-        <v>0.35980000000000001</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9228,18 +9228,18 @@
         <v>227</v>
       </c>
       <c r="H267">
-        <v>939</v>
+        <v>1048</v>
       </c>
       <c r="I267">
         <v>2724</v>
       </c>
       <c r="J267" s="1">
-        <v>0.34470000000000001</v>
+        <v>0.38469999999999999</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9260,18 +9260,18 @@
         <v>172</v>
       </c>
       <c r="H268">
-        <v>1445</v>
+        <v>1488</v>
       </c>
       <c r="I268">
         <v>4128</v>
       </c>
       <c r="J268" s="1">
-        <v>0.35</v>
+        <v>0.36049999999999999</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9292,18 +9292,18 @@
         <v>3</v>
       </c>
       <c r="H269">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I269">
         <v>36</v>
       </c>
       <c r="J269" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38890000000000002</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9324,18 +9324,18 @@
         <v>110</v>
       </c>
       <c r="H270">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="I270">
         <v>1320</v>
       </c>
       <c r="J270" s="1">
-        <v>0.34320000000000001</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9356,18 +9356,18 @@
         <v>311</v>
       </c>
       <c r="H271">
-        <v>1279</v>
+        <v>1366</v>
       </c>
       <c r="I271">
         <v>3732</v>
       </c>
       <c r="J271" s="1">
-        <v>0.3427</v>
+        <v>0.36599999999999999</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9388,18 +9388,18 @@
         <v>286</v>
       </c>
       <c r="H272">
-        <v>1174</v>
+        <v>1237</v>
       </c>
       <c r="I272">
         <v>3432</v>
       </c>
       <c r="J272" s="1">
-        <v>0.34210000000000002</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9420,18 +9420,18 @@
         <v>12</v>
       </c>
       <c r="H273">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I273">
         <v>144</v>
       </c>
       <c r="J273" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9452,18 +9452,18 @@
         <v>85</v>
       </c>
       <c r="H274">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I274">
         <v>1020</v>
       </c>
       <c r="J274" s="1">
-        <v>0.34899999999999998</v>
+        <v>0.35880000000000001</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9484,18 +9484,18 @@
         <v>44</v>
       </c>
       <c r="H275">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="I275">
         <v>528</v>
       </c>
       <c r="J275" s="1">
-        <v>0.3674</v>
+        <v>0.40150000000000002</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9516,18 +9516,18 @@
         <v>47</v>
       </c>
       <c r="H276">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="I276">
         <v>564</v>
       </c>
       <c r="J276" s="1">
-        <v>0.38119999999999998</v>
+        <v>0.4113</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9548,18 +9548,18 @@
         <v>17</v>
       </c>
       <c r="H277">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I277">
         <v>204</v>
       </c>
       <c r="J277" s="1">
-        <v>0.36270000000000002</v>
+        <v>0.39219999999999999</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9580,18 +9580,18 @@
         <v>16</v>
       </c>
       <c r="H278">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I278">
         <v>384</v>
       </c>
       <c r="J278" s="1">
-        <v>0.35160000000000002</v>
+        <v>0.36980000000000002</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9612,18 +9612,18 @@
         <v>91</v>
       </c>
       <c r="H279">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I279">
         <v>1092</v>
       </c>
       <c r="J279" s="1">
-        <v>0.3498</v>
+        <v>0.35260000000000002</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9644,18 +9644,18 @@
         <v>48</v>
       </c>
       <c r="H280">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="I280">
         <v>564</v>
       </c>
       <c r="J280" s="1">
-        <v>0.35460000000000003</v>
+        <v>0.36880000000000002</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9676,18 +9676,18 @@
         <v>16</v>
       </c>
       <c r="H281">
-        <v>1952</v>
+        <v>2013</v>
       </c>
       <c r="I281">
         <v>5842</v>
       </c>
       <c r="J281" s="1">
-        <v>0.33410000000000001</v>
+        <v>0.34460000000000002</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9751,7 +9751,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9847,7 +9847,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9879,7 +9879,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9900,18 +9900,18 @@
         <v>228</v>
       </c>
       <c r="H288">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="I288">
         <v>2736</v>
       </c>
       <c r="J288" s="1">
-        <v>0.35489999999999999</v>
+        <v>0.36259999999999998</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9932,18 +9932,18 @@
         <v>24</v>
       </c>
       <c r="H289">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I289">
         <v>300</v>
       </c>
       <c r="J289" s="1">
-        <v>0.32</v>
+        <v>0.34670000000000001</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9964,18 +9964,18 @@
         <v>185</v>
       </c>
       <c r="H290">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="I290">
         <v>2196</v>
       </c>
       <c r="J290" s="1">
-        <v>0.35520000000000002</v>
+        <v>0.3584</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -9996,18 +9996,18 @@
         <v>87</v>
       </c>
       <c r="H291">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="I291">
         <v>1044</v>
       </c>
       <c r="J291" s="1">
-        <v>0.35060000000000002</v>
+        <v>0.35630000000000001</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -10028,18 +10028,18 @@
         <v>96</v>
       </c>
       <c r="H292">
-        <v>859</v>
+        <v>882</v>
       </c>
       <c r="I292">
         <v>2304</v>
       </c>
       <c r="J292" s="1">
-        <v>0.37280000000000002</v>
+        <v>0.38279999999999997</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -10060,18 +10060,18 @@
         <v>17</v>
       </c>
       <c r="H293">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I293">
         <v>204</v>
       </c>
       <c r="J293" s="1">
-        <v>0.36759999999999998</v>
+        <v>0.40689999999999998</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -10092,18 +10092,18 @@
         <v>109</v>
       </c>
       <c r="H294">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="I294">
         <v>1308</v>
       </c>
       <c r="J294" s="1">
-        <v>0.3609</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -10124,18 +10124,18 @@
         <v>8</v>
       </c>
       <c r="H295">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I295">
         <v>96</v>
       </c>
       <c r="J295" s="1">
-        <v>0.35420000000000001</v>
+        <v>0.40629999999999999</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -10167,7 +10167,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -10188,18 +10188,18 @@
         <v>5</v>
       </c>
       <c r="H297">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I297">
         <v>120</v>
       </c>
       <c r="J297" s="1">
-        <v>0.375</v>
+        <v>0.38329999999999997</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -10220,18 +10220,18 @@
         <v>17</v>
       </c>
       <c r="H298">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I298">
         <v>204</v>
       </c>
       <c r="J298" s="1">
-        <v>0.36759999999999998</v>
+        <v>0.40689999999999998</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10252,18 +10252,18 @@
         <v>7</v>
       </c>
       <c r="H299">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I299">
         <v>84</v>
       </c>
       <c r="J299" s="1">
-        <v>0.34520000000000001</v>
+        <v>0.40479999999999999</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10284,18 +10284,18 @@
         <v>200</v>
       </c>
       <c r="H300">
-        <v>892</v>
+        <v>967</v>
       </c>
       <c r="I300">
         <v>2400</v>
       </c>
       <c r="J300" s="1">
-        <v>0.37169999999999997</v>
+        <v>0.40289999999999998</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10316,18 +10316,18 @@
         <v>14</v>
       </c>
       <c r="H301">
-        <v>1818</v>
+        <v>1918</v>
       </c>
       <c r="I301">
         <v>5110</v>
       </c>
       <c r="J301" s="1">
-        <v>0.35580000000000001</v>
+        <v>0.37530000000000002</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10391,7 +10391,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10423,7 +10423,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10455,7 +10455,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10476,18 +10476,18 @@
         <v>10</v>
       </c>
       <c r="H306">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I306">
         <v>120</v>
       </c>
       <c r="J306" s="1">
-        <v>0.35</v>
+        <v>0.4083</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10540,18 +10540,18 @@
         <v>39</v>
       </c>
       <c r="H308">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I308">
         <v>468</v>
       </c>
       <c r="J308" s="1">
-        <v>0.36320000000000002</v>
+        <v>0.38679999999999998</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10572,18 +10572,18 @@
         <v>778</v>
       </c>
       <c r="H309">
-        <v>3274</v>
+        <v>3574</v>
       </c>
       <c r="I309">
         <v>9336</v>
       </c>
       <c r="J309" s="1">
-        <v>0.35070000000000001</v>
+        <v>0.38279999999999997</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10604,18 +10604,18 @@
         <v>392</v>
       </c>
       <c r="H310">
-        <v>3504</v>
+        <v>3601</v>
       </c>
       <c r="I310">
         <v>9408</v>
       </c>
       <c r="J310" s="1">
-        <v>0.37240000000000001</v>
+        <v>0.38279999999999997</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10636,18 +10636,18 @@
         <v>7</v>
       </c>
       <c r="H311">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I311">
         <v>84</v>
       </c>
       <c r="J311" s="1">
-        <v>0.38100000000000001</v>
+        <v>0.40479999999999999</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10668,18 +10668,18 @@
         <v>9</v>
       </c>
       <c r="H312">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I312">
         <v>108</v>
       </c>
       <c r="J312" s="1">
-        <v>0.34260000000000002</v>
+        <v>0.36109999999999998</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10700,18 +10700,18 @@
         <v>145</v>
       </c>
       <c r="H313">
-        <v>614</v>
+        <v>663</v>
       </c>
       <c r="I313">
         <v>1740</v>
       </c>
       <c r="J313" s="1">
-        <v>0.35289999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10732,18 +10732,18 @@
         <v>925</v>
       </c>
       <c r="H314">
-        <v>3842</v>
+        <v>4149</v>
       </c>
       <c r="I314">
         <v>11100</v>
       </c>
       <c r="J314" s="1">
-        <v>0.34610000000000002</v>
+        <v>0.37380000000000002</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10764,18 +10764,18 @@
         <v>45</v>
       </c>
       <c r="H315">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I315">
         <v>540</v>
       </c>
       <c r="J315" s="1">
-        <v>0.3463</v>
+        <v>0.36670000000000003</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10796,18 +10796,18 @@
         <v>24</v>
       </c>
       <c r="H316">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I316">
         <v>576</v>
       </c>
       <c r="J316" s="1">
-        <v>0.36980000000000002</v>
+        <v>0.37669999999999998</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10828,18 +10828,18 @@
         <v>25</v>
       </c>
       <c r="H317">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I317">
         <v>300</v>
       </c>
       <c r="J317" s="1">
-        <v>0.36330000000000001</v>
+        <v>0.3967</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10860,18 +10860,18 @@
         <v>25</v>
       </c>
       <c r="H318">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I318">
         <v>420</v>
       </c>
       <c r="J318" s="1">
-        <v>0.36430000000000001</v>
+        <v>0.38329999999999997</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10903,7 +10903,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10924,18 +10924,18 @@
         <v>16</v>
       </c>
       <c r="H320">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I320">
         <v>192</v>
       </c>
       <c r="J320" s="1">
-        <v>0.38019999999999998</v>
+        <v>0.38540000000000002</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10988,18 +10988,18 @@
         <v>105</v>
       </c>
       <c r="H322">
-        <v>12346</v>
+        <v>12986</v>
       </c>
       <c r="I322">
         <v>38325</v>
       </c>
       <c r="J322" s="1">
-        <v>0.3221</v>
+        <v>0.33879999999999999</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -11020,18 +11020,18 @@
         <v>65</v>
       </c>
       <c r="H323">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I323">
         <v>260</v>
       </c>
       <c r="J323" s="1">
-        <v>0.37690000000000001</v>
+        <v>0.38850000000000001</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -11063,7 +11063,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -11084,18 +11084,18 @@
         <v>33</v>
       </c>
       <c r="H325">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I325">
         <v>132</v>
       </c>
       <c r="J325" s="1">
-        <v>0.43180000000000002</v>
+        <v>0.44700000000000001</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -11127,7 +11127,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -11191,7 +11191,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -11212,18 +11212,18 @@
         <v>33</v>
       </c>
       <c r="H329">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I329">
         <v>396</v>
       </c>
       <c r="J329" s="1">
-        <v>0.37369999999999998</v>
+        <v>0.39140000000000003</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -11255,7 +11255,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -11276,18 +11276,18 @@
         <v>23</v>
       </c>
       <c r="H331">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I331">
         <v>276</v>
       </c>
       <c r="J331" s="1">
-        <v>0.3659</v>
+        <v>0.39860000000000001</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -11308,18 +11308,18 @@
         <v>3536</v>
       </c>
       <c r="H332">
-        <v>15428</v>
+        <v>16418</v>
       </c>
       <c r="I332">
         <v>42432</v>
       </c>
       <c r="J332" s="1">
-        <v>0.36359999999999998</v>
+        <v>0.38690000000000002</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11340,18 +11340,18 @@
         <v>277</v>
       </c>
       <c r="H333">
-        <v>2383</v>
+        <v>2514</v>
       </c>
       <c r="I333">
         <v>6648</v>
       </c>
       <c r="J333" s="1">
-        <v>0.35849999999999999</v>
+        <v>0.37819999999999998</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11372,18 +11372,18 @@
         <v>129</v>
       </c>
       <c r="H334">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="I334">
         <v>1548</v>
       </c>
       <c r="J334" s="1">
-        <v>0.3488</v>
+        <v>0.38950000000000001</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11404,18 +11404,18 @@
         <v>553</v>
       </c>
       <c r="H335">
-        <v>2331</v>
+        <v>2587</v>
       </c>
       <c r="I335">
         <v>6636</v>
       </c>
       <c r="J335" s="1">
-        <v>0.3513</v>
+        <v>0.38979999999999998</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11436,18 +11436,18 @@
         <v>315</v>
       </c>
       <c r="H336">
-        <v>1364</v>
+        <v>1506</v>
       </c>
       <c r="I336">
         <v>3780</v>
       </c>
       <c r="J336" s="1">
-        <v>0.36080000000000001</v>
+        <v>0.39839999999999998</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11468,18 +11468,18 @@
         <v>20</v>
       </c>
       <c r="H337">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I337">
         <v>240</v>
       </c>
       <c r="J337" s="1">
-        <v>0.3458</v>
+        <v>0.36670000000000003</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11500,18 +11500,18 @@
         <v>19</v>
       </c>
       <c r="H338">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I338">
         <v>228</v>
       </c>
       <c r="J338" s="1">
-        <v>0.34649999999999997</v>
+        <v>0.36840000000000001</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11532,18 +11532,18 @@
         <v>19</v>
       </c>
       <c r="H339">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I339">
         <v>456</v>
       </c>
       <c r="J339" s="1">
-        <v>0.35310000000000002</v>
+        <v>0.36620000000000003</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11564,18 +11564,18 @@
         <v>86</v>
       </c>
       <c r="H340">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="I340">
         <v>1032</v>
       </c>
       <c r="J340" s="1">
-        <v>0.34589999999999999</v>
+        <v>0.38469999999999999</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11607,7 +11607,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11628,18 +11628,18 @@
         <v>32</v>
       </c>
       <c r="H342">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I342">
         <v>384</v>
       </c>
       <c r="J342" s="1">
-        <v>0.33069999999999999</v>
+        <v>0.35160000000000002</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11660,18 +11660,18 @@
         <v>615</v>
       </c>
       <c r="H343">
-        <v>2617</v>
+        <v>2837</v>
       </c>
       <c r="I343">
         <v>7380</v>
       </c>
       <c r="J343" s="1">
-        <v>0.35460000000000003</v>
+        <v>0.38440000000000002</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11692,18 +11692,18 @@
         <v>172</v>
       </c>
       <c r="H344">
-        <v>6345</v>
+        <v>7104</v>
       </c>
       <c r="I344">
         <v>17695</v>
       </c>
       <c r="J344" s="1">
-        <v>0.35859999999999997</v>
+        <v>0.40150000000000002</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11724,18 +11724,18 @@
         <v>175</v>
       </c>
       <c r="H345">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="I345">
         <v>700</v>
       </c>
       <c r="J345" s="1">
-        <v>0.43709999999999999</v>
+        <v>0.44429999999999997</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11767,7 +11767,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11799,7 +11799,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11831,7 +11831,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11863,7 +11863,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11884,18 +11884,18 @@
         <v>50</v>
       </c>
       <c r="H350">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="I350">
         <v>600</v>
       </c>
       <c r="J350" s="1">
-        <v>0.3483</v>
+        <v>0.37169999999999997</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11916,18 +11916,18 @@
         <v>48</v>
       </c>
       <c r="H351">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="I351">
         <v>576</v>
       </c>
       <c r="J351" s="1">
-        <v>0.34899999999999998</v>
+        <v>0.38190000000000002</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11948,18 +11948,18 @@
         <v>17</v>
       </c>
       <c r="H352">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I352">
         <v>204</v>
       </c>
       <c r="J352" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.35780000000000001</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11980,18 +11980,18 @@
         <v>62</v>
       </c>
       <c r="H353">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="I353">
         <v>744</v>
       </c>
       <c r="J353" s="1">
-        <v>0.33739999999999998</v>
+        <v>0.36559999999999998</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -12012,13 +12012,13 @@
         <v>25</v>
       </c>
       <c r="H354">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I354">
         <v>300</v>
       </c>
       <c r="J354" s="1">
-        <v>0.37330000000000002</v>
+        <v>0.40329999999999999</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585552BE-D173-42CE-9EFD-7ED54904404C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99C105-78F4-427A-9230-1242394EC625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -7276,13 +7276,13 @@
         <v>40</v>
       </c>
       <c r="H206">
-        <v>2009</v>
+        <v>200</v>
       </c>
       <c r="I206">
         <v>480</v>
       </c>
       <c r="J206" s="1">
-        <v>4.1853999999999996</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99C105-78F4-427A-9230-1242394EC625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37A9FA-729E-4E81-96E0-C1BF81BA08B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -3980,13 +3980,13 @@
         <v>458</v>
       </c>
       <c r="H103">
-        <v>497</v>
+        <v>4593</v>
       </c>
       <c r="I103">
         <v>10992</v>
       </c>
       <c r="J103" s="1">
-        <v>4.5199999999999997E-2</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\Perawatan Peralatan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\6. Jun\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37A9FA-729E-4E81-96E0-C1BF81BA08B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFDAFA7-C6A6-4A16-993F-F585C1EABC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="93">
   <si>
     <t>Tahun</t>
   </si>
@@ -727,7 +727,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -748,18 +748,18 @@
         <v>59</v>
       </c>
       <c r="H2">
-        <v>590</v>
+        <v>684</v>
       </c>
       <c r="I2">
         <v>1416</v>
       </c>
       <c r="J2" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48309999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -780,18 +780,18 @@
         <v>47</v>
       </c>
       <c r="H3">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="I3">
         <v>564</v>
       </c>
       <c r="J3" s="1">
-        <v>0.43440000000000001</v>
+        <v>0.49819999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -812,18 +812,18 @@
         <v>59</v>
       </c>
       <c r="H4">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="I4">
         <v>708</v>
       </c>
       <c r="J4" s="1">
-        <v>0.4153</v>
+        <v>0.49009999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -844,18 +844,18 @@
         <v>398</v>
       </c>
       <c r="H5">
-        <v>1996</v>
+        <v>2261</v>
       </c>
       <c r="I5">
         <v>4776</v>
       </c>
       <c r="J5" s="1">
-        <v>0.41789999999999999</v>
+        <v>0.47339999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -876,18 +876,18 @@
         <v>398</v>
       </c>
       <c r="H6">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="I6">
         <v>398</v>
       </c>
       <c r="J6" s="1">
-        <v>0.57789999999999997</v>
+        <v>0.6482</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -908,18 +908,18 @@
         <v>64</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I7">
         <v>128</v>
       </c>
       <c r="J7" s="1">
-        <v>0.46879999999999999</v>
+        <v>0.49220000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -940,18 +940,18 @@
         <v>61</v>
       </c>
       <c r="H8">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I8">
         <v>244</v>
       </c>
       <c r="J8" s="1">
-        <v>0.45490000000000003</v>
+        <v>0.48359999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1004,18 +1004,18 @@
         <v>161</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="I10">
         <v>161</v>
       </c>
       <c r="J10" s="1">
-        <v>0.21740000000000001</v>
+        <v>0.35399999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1036,18 +1036,18 @@
         <v>265</v>
       </c>
       <c r="H11">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I11">
         <v>265</v>
       </c>
       <c r="J11" s="1">
-        <v>0.29430000000000001</v>
+        <v>0.34720000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1068,18 +1068,18 @@
         <v>72</v>
       </c>
       <c r="H12">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I12">
         <v>72</v>
       </c>
       <c r="J12" s="1">
-        <v>0.36109999999999998</v>
+        <v>0.47220000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1100,18 +1100,18 @@
         <v>289</v>
       </c>
       <c r="H13">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="I13">
         <v>289</v>
       </c>
       <c r="J13" s="1">
-        <v>0.29759999999999998</v>
+        <v>0.4083</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1132,18 +1132,18 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
       <c r="J14" s="1">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1164,18 +1164,18 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I15">
         <v>60</v>
       </c>
       <c r="J15" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48330000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1196,18 +1196,18 @@
         <v>395</v>
       </c>
       <c r="H16">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="I16">
         <v>395</v>
       </c>
       <c r="J16" s="1">
-        <v>0.62529999999999997</v>
+        <v>0.68610000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1228,18 +1228,18 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I17">
         <v>400</v>
       </c>
       <c r="J17" s="1">
-        <v>0.46500000000000002</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1260,18 +1260,18 @@
         <v>245</v>
       </c>
       <c r="H18">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I18">
         <v>245</v>
       </c>
       <c r="J18" s="1">
-        <v>0.44080000000000003</v>
+        <v>0.47760000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1292,18 +1292,18 @@
         <v>69</v>
       </c>
       <c r="H19">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="I19">
         <v>276</v>
       </c>
       <c r="J19" s="1">
-        <v>0.40579999999999999</v>
+        <v>0.45650000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1324,18 +1324,18 @@
         <v>61</v>
       </c>
       <c r="H20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I20">
         <v>61</v>
       </c>
       <c r="J20" s="1">
-        <v>0.34429999999999999</v>
+        <v>0.39340000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1388,18 +1388,18 @@
         <v>691280</v>
       </c>
       <c r="H22">
-        <v>3432613</v>
+        <v>3995932</v>
       </c>
       <c r="I22">
         <v>8295360</v>
       </c>
       <c r="J22" s="1">
-        <v>0.4138</v>
+        <v>0.48170000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1420,18 +1420,18 @@
         <v>689046</v>
       </c>
       <c r="H23">
-        <v>529157.30000000005</v>
+        <v>634235.30000000005</v>
       </c>
       <c r="I23">
         <v>1378092</v>
       </c>
       <c r="J23" s="1">
-        <v>0.38400000000000001</v>
+        <v>0.4602</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1452,18 +1452,18 @@
         <v>647</v>
       </c>
       <c r="H24">
-        <v>6484</v>
+        <v>7408</v>
       </c>
       <c r="I24">
         <v>15528</v>
       </c>
       <c r="J24" s="1">
-        <v>0.41760000000000003</v>
+        <v>0.47710000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1484,18 +1484,18 @@
         <v>691280</v>
       </c>
       <c r="H25">
-        <v>1195674</v>
+        <v>1353557</v>
       </c>
       <c r="I25">
         <v>2765120</v>
       </c>
       <c r="J25" s="1">
-        <v>0.43240000000000001</v>
+        <v>0.48949999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1516,18 +1516,18 @@
         <v>691280</v>
       </c>
       <c r="H26">
-        <v>382132</v>
+        <v>433791</v>
       </c>
       <c r="I26">
         <v>691280</v>
       </c>
       <c r="J26" s="1">
-        <v>0.55279999999999996</v>
+        <v>0.62749999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1548,18 +1548,18 @@
         <v>346</v>
       </c>
       <c r="H27">
-        <v>515</v>
+        <v>661</v>
       </c>
       <c r="I27">
         <v>1384</v>
       </c>
       <c r="J27" s="1">
-        <v>0.37209999999999999</v>
+        <v>0.47760000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1580,18 +1580,18 @@
         <v>501</v>
       </c>
       <c r="H28">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="I28">
         <v>501</v>
       </c>
       <c r="J28" s="1">
-        <v>0.505</v>
+        <v>0.61480000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1612,18 +1612,18 @@
         <v>1109</v>
       </c>
       <c r="H29">
-        <v>837</v>
+        <v>1037</v>
       </c>
       <c r="I29">
         <v>2218</v>
       </c>
       <c r="J29" s="1">
-        <v>0.37740000000000001</v>
+        <v>0.46750000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1644,18 +1644,18 @@
         <v>649</v>
       </c>
       <c r="H30">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="I30">
         <v>649</v>
       </c>
       <c r="J30" s="1">
-        <v>0.43140000000000001</v>
+        <v>0.50539999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
@@ -1673,21 +1673,21 @@
         <v>34</v>
       </c>
       <c r="G31">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H31">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I31">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="J31" s="1">
-        <v>0.27789999999999998</v>
+        <v>0.31290000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
@@ -1719,7 +1719,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
@@ -1740,18 +1740,18 @@
         <v>59</v>
       </c>
       <c r="H33">
-        <v>589</v>
+        <v>677</v>
       </c>
       <c r="I33">
         <v>1416</v>
       </c>
       <c r="J33" s="1">
-        <v>0.41599999999999998</v>
+        <v>0.47810000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
@@ -1772,18 +1772,18 @@
         <v>47</v>
       </c>
       <c r="H34">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="I34">
         <v>564</v>
       </c>
       <c r="J34" s="1">
-        <v>0.41489999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
@@ -1804,18 +1804,18 @@
         <v>691280</v>
       </c>
       <c r="H35">
-        <v>3415203</v>
+        <v>3968731</v>
       </c>
       <c r="I35">
         <v>8295360</v>
       </c>
       <c r="J35" s="1">
-        <v>0.41170000000000001</v>
+        <v>0.47839999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
@@ -1836,18 +1836,18 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>8602</v>
+        <v>10170</v>
       </c>
       <c r="I36">
         <v>20580</v>
       </c>
       <c r="J36" s="1">
-        <v>0.41799999999999998</v>
+        <v>0.49419999999999997</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
@@ -1868,18 +1868,18 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1266</v>
+        <v>1451</v>
       </c>
       <c r="I37">
         <v>3024</v>
       </c>
       <c r="J37" s="1">
-        <v>0.41870000000000002</v>
+        <v>0.4798</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
@@ -1900,18 +1900,18 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>8109</v>
+        <v>9111</v>
       </c>
       <c r="I38">
         <v>19416</v>
       </c>
       <c r="J38" s="1">
-        <v>0.41760000000000003</v>
+        <v>0.46929999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
@@ -1932,18 +1932,18 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>11411</v>
+        <v>12856</v>
       </c>
       <c r="I39">
         <v>27456</v>
       </c>
       <c r="J39" s="1">
-        <v>0.41560000000000002</v>
+        <v>0.46820000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
@@ -1964,18 +1964,18 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>586</v>
+        <v>648</v>
       </c>
       <c r="I40">
         <v>1404</v>
       </c>
       <c r="J40" s="1">
-        <v>0.41739999999999999</v>
+        <v>0.46150000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
@@ -1996,18 +1996,18 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="I41">
         <v>556</v>
       </c>
       <c r="J41" s="1">
-        <v>0.41549999999999998</v>
+        <v>0.48920000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B42" s="2">
         <v>2026</v>
@@ -2028,18 +2028,18 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I42">
         <v>48</v>
       </c>
       <c r="J42" s="1">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B43" s="2">
         <v>2026</v>
@@ -2060,18 +2060,18 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="I43">
         <v>950</v>
       </c>
       <c r="J43" s="1">
-        <v>0.40949999999999998</v>
+        <v>0.43580000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B44" s="2">
         <v>2026</v>
@@ -2092,18 +2092,18 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1478</v>
+        <v>1659</v>
       </c>
       <c r="I44">
         <v>3552</v>
       </c>
       <c r="J44" s="1">
-        <v>0.41610000000000003</v>
+        <v>0.46710000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B45" s="2">
         <v>2026</v>
@@ -2124,18 +2124,18 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1025</v>
+        <v>1150</v>
       </c>
       <c r="I45">
         <v>2508</v>
       </c>
       <c r="J45" s="1">
-        <v>0.40870000000000001</v>
+        <v>0.45850000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B46" s="2">
         <v>2026</v>
@@ -2156,18 +2156,18 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="I46">
         <v>624</v>
       </c>
       <c r="J46" s="1">
-        <v>0.42149999999999999</v>
+        <v>0.46789999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B47" s="2">
         <v>2026</v>
@@ -2188,18 +2188,18 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>12136</v>
+        <v>13670</v>
       </c>
       <c r="I47">
         <v>25564</v>
       </c>
       <c r="J47" s="1">
-        <v>0.47470000000000001</v>
+        <v>0.53469999999999995</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B48" s="2">
         <v>2026</v>
@@ -2220,18 +2220,18 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="I48">
         <v>228</v>
       </c>
       <c r="J48" s="1">
-        <v>0.43419999999999997</v>
+        <v>0.49120000000000003</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B49" s="2">
         <v>2026</v>
@@ -2252,18 +2252,18 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I49">
         <v>57</v>
       </c>
       <c r="J49" s="1">
-        <v>0.57889999999999997</v>
+        <v>0.63160000000000005</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B50" s="2">
         <v>2026</v>
@@ -2284,18 +2284,18 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="I50">
         <v>548</v>
       </c>
       <c r="J50" s="1">
-        <v>0.38869999999999999</v>
+        <v>0.41420000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B51" s="2">
         <v>2026</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B52" s="2">
         <v>2026</v>
@@ -2348,18 +2348,18 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I52">
         <v>90</v>
       </c>
       <c r="J52" s="1">
-        <v>0.35560000000000003</v>
+        <v>0.4778</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B53" s="2">
         <v>2026</v>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>55927</v>
+        <v>61874</v>
       </c>
       <c r="I53">
         <v>117348</v>
       </c>
       <c r="J53" s="1">
-        <v>0.47660000000000002</v>
+        <v>0.52729999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B54" s="2">
         <v>2026</v>
@@ -2412,18 +2412,18 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>670</v>
+        <v>751</v>
       </c>
       <c r="I54">
         <v>1584</v>
       </c>
       <c r="J54" s="1">
-        <v>0.42299999999999999</v>
+        <v>0.47410000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B55" s="2">
         <v>2026</v>
@@ -2444,18 +2444,18 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="I55">
         <v>516</v>
       </c>
       <c r="J55" s="1">
-        <v>0.39529999999999998</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B56" s="2">
         <v>2026</v>
@@ -2476,18 +2476,18 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>594</v>
+        <v>654</v>
       </c>
       <c r="I56">
         <v>1416</v>
       </c>
       <c r="J56" s="1">
-        <v>0.41949999999999998</v>
+        <v>0.46189999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B57" s="2">
         <v>2026</v>
@@ -2508,18 +2508,18 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I57">
         <v>137</v>
       </c>
       <c r="J57" s="1">
-        <v>0.63500000000000001</v>
+        <v>0.64229999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B58" s="2">
         <v>2026</v>
@@ -2540,18 +2540,18 @@
         <v>366</v>
       </c>
       <c r="H58">
-        <v>3689</v>
+        <v>4164</v>
       </c>
       <c r="I58">
         <v>8784</v>
       </c>
       <c r="J58" s="1">
-        <v>0.42</v>
+        <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B59" s="2">
         <v>2026</v>
@@ -2572,18 +2572,18 @@
         <v>244</v>
       </c>
       <c r="H59">
-        <v>1233</v>
+        <v>1488</v>
       </c>
       <c r="I59">
         <v>2928</v>
       </c>
       <c r="J59" s="1">
-        <v>0.42109999999999997</v>
+        <v>0.50819999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B60" s="2">
         <v>2026</v>
@@ -2604,18 +2604,18 @@
         <v>640</v>
       </c>
       <c r="H60">
-        <v>3210</v>
+        <v>3739</v>
       </c>
       <c r="I60">
         <v>7680</v>
       </c>
       <c r="J60" s="1">
-        <v>0.41799999999999998</v>
+        <v>0.48680000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B61" s="2">
         <v>2026</v>
@@ -2636,18 +2636,18 @@
         <v>696</v>
       </c>
       <c r="H61">
-        <v>3729</v>
+        <v>4363</v>
       </c>
       <c r="I61">
         <v>8952</v>
       </c>
       <c r="J61" s="1">
-        <v>0.41660000000000003</v>
+        <v>0.4874</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B62" s="2">
         <v>2026</v>
@@ -2668,18 +2668,18 @@
         <v>90</v>
       </c>
       <c r="H62">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="I62">
         <v>1092</v>
       </c>
       <c r="J62" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4496</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B63" s="2">
         <v>2026</v>
@@ -2700,18 +2700,18 @@
         <v>8</v>
       </c>
       <c r="H63">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="I63">
         <v>240</v>
       </c>
       <c r="J63" s="1">
-        <v>0.42920000000000003</v>
+        <v>0.47920000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B64" s="2">
         <v>2026</v>
@@ -2732,18 +2732,18 @@
         <v>25</v>
       </c>
       <c r="H64">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="I64">
         <v>300</v>
       </c>
       <c r="J64" s="1">
-        <v>0.40329999999999999</v>
+        <v>0.48670000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B65" s="2">
         <v>2026</v>
@@ -2764,18 +2764,18 @@
         <v>3</v>
       </c>
       <c r="H65">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I65">
         <v>36</v>
       </c>
       <c r="J65" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47220000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B66" s="2">
         <v>2026</v>
@@ -2796,18 +2796,18 @@
         <v>73</v>
       </c>
       <c r="H66">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="I66">
         <v>876</v>
       </c>
       <c r="J66" s="1">
-        <v>0.4098</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B67" s="2">
         <v>2026</v>
@@ -2828,18 +2828,18 @@
         <v>139</v>
       </c>
       <c r="H67">
-        <v>718</v>
+        <v>824</v>
       </c>
       <c r="I67">
         <v>1668</v>
       </c>
       <c r="J67" s="1">
-        <v>0.43049999999999999</v>
+        <v>0.49399999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
@@ -2860,18 +2860,18 @@
         <v>273</v>
       </c>
       <c r="H68">
-        <v>1373</v>
+        <v>1589</v>
       </c>
       <c r="I68">
         <v>3276</v>
       </c>
       <c r="J68" s="1">
-        <v>0.41909999999999997</v>
+        <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B69" s="2">
         <v>2026</v>
@@ -2892,18 +2892,18 @@
         <v>14</v>
       </c>
       <c r="H69">
-        <v>2128</v>
+        <v>2422</v>
       </c>
       <c r="I69">
         <v>5110</v>
       </c>
       <c r="J69" s="1">
-        <v>0.41639999999999999</v>
+        <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B70" s="2">
         <v>2026</v>
@@ -2924,18 +2924,18 @@
         <v>30</v>
       </c>
       <c r="H70">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I70">
         <v>120</v>
       </c>
       <c r="J70" s="1">
-        <v>0.375</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B71" s="2">
         <v>2026</v>
@@ -2956,18 +2956,18 @@
         <v>30</v>
       </c>
       <c r="H71">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I71">
         <v>30</v>
       </c>
       <c r="J71" s="1">
-        <v>0.36670000000000003</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B72" s="2">
         <v>2026</v>
@@ -2988,18 +2988,18 @@
         <v>52</v>
       </c>
       <c r="H72">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I72">
         <v>208</v>
       </c>
       <c r="J72" s="1">
-        <v>0.4471</v>
+        <v>0.49519999999999997</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B73" s="2">
         <v>2026</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B74" s="2">
         <v>2026</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B75" s="2">
         <v>2026</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B76" s="2">
         <v>2026</v>
@@ -3116,18 +3116,18 @@
         <v>189</v>
       </c>
       <c r="H76">
-        <v>960</v>
+        <v>1099</v>
       </c>
       <c r="I76">
         <v>2268</v>
       </c>
       <c r="J76" s="1">
-        <v>0.42330000000000001</v>
+        <v>0.48459999999999998</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B77" s="2">
         <v>2026</v>
@@ -3148,18 +3148,18 @@
         <v>287</v>
       </c>
       <c r="H77">
-        <v>1465</v>
+        <v>1711</v>
       </c>
       <c r="I77">
         <v>3444</v>
       </c>
       <c r="J77" s="1">
-        <v>0.4254</v>
+        <v>0.49680000000000002</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B78" s="2">
         <v>2026</v>
@@ -3180,18 +3180,18 @@
         <v>74</v>
       </c>
       <c r="H78">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="I78">
         <v>948</v>
       </c>
       <c r="J78" s="1">
-        <v>0.42830000000000001</v>
+        <v>0.48209999999999997</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B79" s="2">
         <v>2026</v>
@@ -3212,18 +3212,18 @@
         <v>123</v>
       </c>
       <c r="H79">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="I79">
         <v>1632</v>
       </c>
       <c r="J79" s="1">
-        <v>0.40439999999999998</v>
+        <v>0.43319999999999997</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B80" s="2">
         <v>2026</v>
@@ -3244,18 +3244,18 @@
         <v>29</v>
       </c>
       <c r="H80">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I80">
         <v>348</v>
       </c>
       <c r="J80" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.44540000000000002</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B81" s="2">
         <v>2026</v>
@@ -3276,18 +3276,18 @@
         <v>15</v>
       </c>
       <c r="H81">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I81">
         <v>30</v>
       </c>
       <c r="J81" s="1">
-        <v>0.43330000000000002</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B82" s="2">
         <v>2026</v>
@@ -3308,18 +3308,18 @@
         <v>293</v>
       </c>
       <c r="H82">
-        <v>2931</v>
+        <v>3450</v>
       </c>
       <c r="I82">
         <v>7032</v>
       </c>
       <c r="J82" s="1">
-        <v>0.4168</v>
+        <v>0.49059999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B83" s="2">
         <v>2026</v>
@@ -3340,18 +3340,18 @@
         <v>16</v>
       </c>
       <c r="H83">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I83">
         <v>192</v>
       </c>
       <c r="J83" s="1">
-        <v>0.4375</v>
+        <v>0.47920000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B84" s="2">
         <v>2026</v>
@@ -3372,18 +3372,18 @@
         <v>37</v>
       </c>
       <c r="H84">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="I84">
         <v>444</v>
       </c>
       <c r="J84" s="1">
-        <v>0.42120000000000002</v>
+        <v>0.4617</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B85" s="2">
         <v>2026</v>
@@ -3404,18 +3404,18 @@
         <v>493</v>
       </c>
       <c r="H85">
-        <v>2521</v>
+        <v>2872</v>
       </c>
       <c r="I85">
         <v>5916</v>
       </c>
       <c r="J85" s="1">
-        <v>0.42609999999999998</v>
+        <v>0.48549999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B86" s="2">
         <v>2026</v>
@@ -3436,18 +3436,18 @@
         <v>2</v>
       </c>
       <c r="H86">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I86">
         <v>24</v>
       </c>
       <c r="J86" s="1">
-        <v>0.375</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B87" s="2">
         <v>2026</v>
@@ -3468,18 +3468,18 @@
         <v>749</v>
       </c>
       <c r="H87">
-        <v>3747</v>
+        <v>4371</v>
       </c>
       <c r="I87">
         <v>8988</v>
       </c>
       <c r="J87" s="1">
-        <v>0.41689999999999999</v>
+        <v>0.48630000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B88" s="2">
         <v>2026</v>
@@ -3500,18 +3500,18 @@
         <v>161</v>
       </c>
       <c r="H88">
-        <v>791</v>
+        <v>926</v>
       </c>
       <c r="I88">
         <v>1932</v>
       </c>
       <c r="J88" s="1">
-        <v>0.40939999999999999</v>
+        <v>0.4793</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B89" s="2">
         <v>2026</v>
@@ -3532,18 +3532,18 @@
         <v>47</v>
       </c>
       <c r="H89">
-        <v>470</v>
+        <v>555</v>
       </c>
       <c r="I89">
         <v>1128</v>
       </c>
       <c r="J89" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49199999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -3564,18 +3564,18 @@
         <v>55</v>
       </c>
       <c r="H90">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="I90">
         <v>660</v>
       </c>
       <c r="J90" s="1">
-        <v>0.4652</v>
+        <v>0.50760000000000005</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -3596,18 +3596,18 @@
         <v>45</v>
       </c>
       <c r="H91">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="I91">
         <v>540</v>
       </c>
       <c r="J91" s="1">
-        <v>0.4148</v>
+        <v>0.45190000000000002</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B92" s="2">
         <v>2026</v>
@@ -3628,18 +3628,18 @@
         <v>3</v>
       </c>
       <c r="H92">
-        <v>661</v>
+        <v>743</v>
       </c>
       <c r="I92">
         <v>1095</v>
       </c>
       <c r="J92" s="1">
-        <v>0.60370000000000001</v>
+        <v>0.67849999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B93" s="2">
         <v>2026</v>
@@ -3660,18 +3660,18 @@
         <v>15</v>
       </c>
       <c r="H93">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I93">
         <v>60</v>
       </c>
       <c r="J93" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.43330000000000002</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B94" s="2">
         <v>2026</v>
@@ -3692,18 +3692,18 @@
         <v>15</v>
       </c>
       <c r="H94">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I94">
         <v>15</v>
       </c>
       <c r="J94" s="1">
-        <v>0.6</v>
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B95" s="2">
         <v>2026</v>
@@ -3724,18 +3724,18 @@
         <v>33</v>
       </c>
       <c r="H95">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I95">
         <v>132</v>
       </c>
       <c r="J95" s="1">
-        <v>0.46210000000000001</v>
+        <v>0.4924</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B96" s="2">
         <v>2026</v>
@@ -3756,18 +3756,18 @@
         <v>33</v>
       </c>
       <c r="H96">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I96">
         <v>33</v>
       </c>
       <c r="J96" s="1">
-        <v>0.2424</v>
+        <v>0.57579999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B97" s="2">
         <v>2026</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B98" s="2">
         <v>2026</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B99" s="2">
         <v>2026</v>
@@ -3852,18 +3852,18 @@
         <v>30</v>
       </c>
       <c r="H99">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="I99">
         <v>360</v>
       </c>
       <c r="J99" s="1">
-        <v>0.42780000000000001</v>
+        <v>0.47220000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B100" s="2">
         <v>2026</v>
@@ -3884,18 +3884,18 @@
         <v>6</v>
       </c>
       <c r="H100">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I100">
         <v>72</v>
       </c>
       <c r="J100" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.45829999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B101" s="2">
         <v>2026</v>
@@ -3916,18 +3916,18 @@
         <v>52</v>
       </c>
       <c r="H101">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="I101">
         <v>624</v>
       </c>
       <c r="J101" s="1">
-        <v>0.4279</v>
+        <v>0.46789999999999998</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B102" s="2">
         <v>2026</v>
@@ -3948,18 +3948,18 @@
         <v>46</v>
       </c>
       <c r="H102">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="I102">
         <v>552</v>
       </c>
       <c r="J102" s="1">
-        <v>0.42570000000000002</v>
+        <v>0.46379999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B103" s="2">
         <v>2026</v>
@@ -3980,18 +3980,18 @@
         <v>458</v>
       </c>
       <c r="H103">
-        <v>4593</v>
+        <v>5468</v>
       </c>
       <c r="I103">
         <v>10992</v>
       </c>
       <c r="J103" s="1">
-        <v>0.4178</v>
+        <v>0.4975</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B104" s="2">
         <v>2026</v>
@@ -4012,18 +4012,18 @@
         <v>5</v>
       </c>
       <c r="H104">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I104">
         <v>60</v>
       </c>
       <c r="J104" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B105" s="2">
         <v>2026</v>
@@ -4044,18 +4044,18 @@
         <v>43</v>
       </c>
       <c r="H105">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="I105">
         <v>516</v>
       </c>
       <c r="J105" s="1">
-        <v>0.41860000000000003</v>
+        <v>0.47089999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B106" s="2">
         <v>2026</v>
@@ -4076,18 +4076,18 @@
         <v>665</v>
       </c>
       <c r="H106">
-        <v>3316</v>
+        <v>3666</v>
       </c>
       <c r="I106">
         <v>7992</v>
       </c>
       <c r="J106" s="1">
-        <v>0.41489999999999999</v>
+        <v>0.4587</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B107" s="2">
         <v>2026</v>
@@ -4108,18 +4108,18 @@
         <v>1043</v>
       </c>
       <c r="H107">
-        <v>5176</v>
+        <v>5804</v>
       </c>
       <c r="I107">
-        <v>12264</v>
+        <v>12516</v>
       </c>
       <c r="J107" s="1">
-        <v>0.42199999999999999</v>
+        <v>0.4637</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B108" s="2">
         <v>2026</v>
@@ -4140,18 +4140,18 @@
         <v>71</v>
       </c>
       <c r="H108">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="I108">
         <v>852</v>
       </c>
       <c r="J108" s="1">
-        <v>0.43080000000000002</v>
+        <v>0.46360000000000001</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B109" s="2">
         <v>2026</v>
@@ -4172,18 +4172,18 @@
         <v>22</v>
       </c>
       <c r="H109">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="I109">
         <v>528</v>
       </c>
       <c r="J109" s="1">
-        <v>0.40910000000000002</v>
+        <v>0.49809999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B110" s="2">
         <v>2026</v>
@@ -4204,18 +4204,18 @@
         <v>5</v>
       </c>
       <c r="H110">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I110">
         <v>60</v>
       </c>
       <c r="J110" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B111" s="2">
         <v>2026</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B112" s="2">
         <v>2026</v>
@@ -4268,18 +4268,18 @@
         <v>81</v>
       </c>
       <c r="H112">
-        <v>402</v>
+        <v>456</v>
       </c>
       <c r="I112">
         <v>972</v>
       </c>
       <c r="J112" s="1">
-        <v>0.41360000000000002</v>
+        <v>0.46910000000000002</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B113" s="2">
         <v>2026</v>
@@ -4300,18 +4300,18 @@
         <v>52</v>
       </c>
       <c r="H113">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="I113">
         <v>624</v>
       </c>
       <c r="J113" s="1">
-        <v>0.41510000000000002</v>
+        <v>0.46310000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
@@ -4332,18 +4332,18 @@
         <v>44</v>
       </c>
       <c r="H114">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I114">
         <v>528</v>
       </c>
       <c r="J114" s="1">
-        <v>0.4375</v>
+        <v>0.44319999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B115" s="2">
         <v>2026</v>
@@ -4364,18 +4364,18 @@
         <v>11</v>
       </c>
       <c r="H115">
-        <v>2078</v>
+        <v>2907</v>
       </c>
       <c r="I115">
         <v>4046</v>
       </c>
       <c r="J115" s="1">
-        <v>0.51359999999999995</v>
+        <v>0.71850000000000003</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B117" s="2">
         <v>2026</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B118" s="2">
         <v>2026</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B119" s="2">
         <v>2026</v>
@@ -4492,18 +4492,18 @@
         <v>45</v>
       </c>
       <c r="H119">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I119">
         <v>45</v>
       </c>
       <c r="J119" s="1">
-        <v>0.31109999999999999</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B120" s="2">
         <v>2026</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B121" s="2">
         <v>2026</v>
@@ -4556,18 +4556,18 @@
         <v>12</v>
       </c>
       <c r="H121">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I121">
         <v>24</v>
       </c>
       <c r="J121" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.45829999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B122" s="2">
         <v>2026</v>
@@ -4588,18 +4588,18 @@
         <v>188</v>
       </c>
       <c r="H122">
-        <v>926</v>
+        <v>1032</v>
       </c>
       <c r="I122">
         <v>2256</v>
       </c>
       <c r="J122" s="1">
-        <v>0.41049999999999998</v>
+        <v>0.45739999999999997</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B123" s="2">
         <v>2026</v>
@@ -4620,18 +4620,18 @@
         <v>43</v>
       </c>
       <c r="H123">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="I123">
         <v>516</v>
       </c>
       <c r="J123" s="1">
-        <v>0.41089999999999999</v>
+        <v>0.46710000000000002</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B124" s="2">
         <v>2026</v>
@@ -4652,18 +4652,18 @@
         <v>14</v>
       </c>
       <c r="H124">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I124">
         <v>168</v>
       </c>
       <c r="J124" s="1">
-        <v>0.45240000000000002</v>
+        <v>0.49399999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B125" s="2">
         <v>2026</v>
@@ -4684,18 +4684,18 @@
         <v>52</v>
       </c>
       <c r="H125">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="I125">
         <v>624</v>
       </c>
       <c r="J125" s="1">
-        <v>0.41830000000000001</v>
+        <v>0.45350000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B126" s="2">
         <v>2026</v>
@@ -4716,18 +4716,18 @@
         <v>41</v>
       </c>
       <c r="H126">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="I126">
         <v>492</v>
       </c>
       <c r="J126" s="1">
-        <v>0.42480000000000001</v>
+        <v>0.46750000000000003</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B127" s="2">
         <v>2026</v>
@@ -4748,18 +4748,18 @@
         <v>585</v>
       </c>
       <c r="H127">
-        <v>2903</v>
+        <v>3370</v>
       </c>
       <c r="I127">
         <v>7020</v>
       </c>
       <c r="J127" s="1">
-        <v>0.41349999999999998</v>
+        <v>0.48010000000000003</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B128" s="2">
         <v>2026</v>
@@ -4780,18 +4780,18 @@
         <v>383</v>
       </c>
       <c r="H128">
-        <v>3812</v>
+        <v>4546</v>
       </c>
       <c r="I128">
         <v>9144</v>
       </c>
       <c r="J128" s="1">
-        <v>0.41689999999999999</v>
+        <v>0.49719999999999998</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B129" s="2">
         <v>2026</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B130" s="2">
         <v>2026</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B131" s="2">
         <v>2026</v>
@@ -4876,18 +4876,18 @@
         <v>22</v>
       </c>
       <c r="H131">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I131">
         <v>264</v>
       </c>
       <c r="J131" s="1">
-        <v>0.42420000000000002</v>
+        <v>0.47349999999999998</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
@@ -4940,18 +4940,18 @@
         <v>898</v>
       </c>
       <c r="H133">
-        <v>4542</v>
+        <v>5330</v>
       </c>
       <c r="I133">
         <v>10776</v>
       </c>
       <c r="J133" s="1">
-        <v>0.42149999999999999</v>
+        <v>0.49459999999999998</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
@@ -4972,18 +4972,18 @@
         <v>126</v>
       </c>
       <c r="H134">
-        <v>638</v>
+        <v>748</v>
       </c>
       <c r="I134">
         <v>1512</v>
       </c>
       <c r="J134" s="1">
-        <v>0.42199999999999999</v>
+        <v>0.49469999999999997</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B135" s="2">
         <v>2026</v>
@@ -5004,18 +5004,18 @@
         <v>14</v>
       </c>
       <c r="H135">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="I135">
         <v>336</v>
       </c>
       <c r="J135" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49109999999999998</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
@@ -5036,18 +5036,18 @@
         <v>60</v>
       </c>
       <c r="H136">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="I136">
         <v>720</v>
       </c>
       <c r="J136" s="1">
-        <v>0.41389999999999999</v>
+        <v>0.44169999999999998</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
@@ -5068,18 +5068,18 @@
         <v>51</v>
       </c>
       <c r="H137">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="I137">
         <v>624</v>
       </c>
       <c r="J137" s="1">
-        <v>0.41189999999999999</v>
+        <v>0.45190000000000002</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
@@ -5100,18 +5100,18 @@
         <v>7</v>
       </c>
       <c r="H138">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I138">
         <v>84</v>
       </c>
       <c r="J138" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
@@ -5175,7 +5175,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
@@ -5196,18 +5196,18 @@
         <v>13</v>
       </c>
       <c r="H141">
-        <v>2473</v>
+        <v>2806</v>
       </c>
       <c r="I141">
         <v>4745</v>
       </c>
       <c r="J141" s="1">
-        <v>0.5212</v>
+        <v>0.59140000000000004</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
@@ -5228,18 +5228,18 @@
         <v>29</v>
       </c>
       <c r="H142">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I142">
         <v>112</v>
       </c>
       <c r="J142" s="1">
-        <v>0.49109999999999998</v>
+        <v>0.55359999999999998</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
@@ -5260,18 +5260,18 @@
         <v>29</v>
       </c>
       <c r="H143">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I143">
         <v>28</v>
       </c>
       <c r="J143" s="1">
-        <v>0.46429999999999999</v>
+        <v>0.60709999999999997</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
@@ -5292,18 +5292,18 @@
         <v>45</v>
       </c>
       <c r="H144">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I144">
         <v>180</v>
       </c>
       <c r="J144" s="1">
-        <v>0.48330000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
@@ -5335,7 +5335,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -5420,18 +5420,18 @@
         <v>42</v>
       </c>
       <c r="H148">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="I148">
         <v>492</v>
       </c>
       <c r="J148" s="1">
-        <v>0.378</v>
+        <v>0.45529999999999998</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -5452,18 +5452,18 @@
         <v>12</v>
       </c>
       <c r="H149">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I149">
         <v>144</v>
       </c>
       <c r="J149" s="1">
-        <v>0.40970000000000001</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -5484,18 +5484,18 @@
         <v>58</v>
       </c>
       <c r="H150">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="I150">
         <v>708</v>
       </c>
       <c r="J150" s="1">
-        <v>0.41810000000000003</v>
+        <v>0.44919999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
@@ -5516,18 +5516,18 @@
         <v>64</v>
       </c>
       <c r="H151">
-        <v>857</v>
+        <v>917</v>
       </c>
       <c r="I151">
         <v>1956</v>
       </c>
       <c r="J151" s="1">
-        <v>0.43809999999999999</v>
+        <v>0.46879999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
@@ -5548,18 +5548,18 @@
         <v>387</v>
       </c>
       <c r="H152">
-        <v>3852</v>
+        <v>4603</v>
       </c>
       <c r="I152">
         <v>9288</v>
       </c>
       <c r="J152" s="1">
-        <v>0.41470000000000001</v>
+        <v>0.49559999999999998</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
@@ -5580,18 +5580,18 @@
         <v>39</v>
       </c>
       <c r="H153">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="I153">
         <v>468</v>
       </c>
       <c r="J153" s="1">
-        <v>0.44019999999999998</v>
+        <v>0.47439999999999999</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
@@ -5612,18 +5612,18 @@
         <v>590</v>
       </c>
       <c r="H154">
-        <v>2945</v>
+        <v>3193</v>
       </c>
       <c r="I154">
         <v>7080</v>
       </c>
       <c r="J154" s="1">
-        <v>0.41599999999999998</v>
+        <v>0.45100000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
@@ -5644,18 +5644,18 @@
         <v>964</v>
       </c>
       <c r="H155">
-        <v>4813</v>
+        <v>5391</v>
       </c>
       <c r="I155">
         <v>11568</v>
       </c>
       <c r="J155" s="1">
-        <v>0.41610000000000003</v>
+        <v>0.46600000000000003</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
@@ -5676,18 +5676,18 @@
         <v>96</v>
       </c>
       <c r="H156">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="I156">
         <v>1152</v>
       </c>
       <c r="J156" s="1">
-        <v>0.4123</v>
+        <v>0.45569999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -5708,18 +5708,18 @@
         <v>13</v>
       </c>
       <c r="H157">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="I157">
         <v>312</v>
       </c>
       <c r="J157" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.50960000000000005</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -5804,18 +5804,18 @@
         <v>108</v>
       </c>
       <c r="H160">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="I160">
         <v>1296</v>
       </c>
       <c r="J160" s="1">
-        <v>0.3387</v>
+        <v>0.35880000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -5836,18 +5836,18 @@
         <v>47</v>
       </c>
       <c r="H161">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="I161">
         <v>564</v>
       </c>
       <c r="J161" s="1">
-        <v>0.4007</v>
+        <v>0.43969999999999998</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B162" s="2">
         <v>2026</v>
@@ -5868,18 +5868,18 @@
         <v>7</v>
       </c>
       <c r="H162">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I162">
         <v>84</v>
       </c>
       <c r="J162" s="1">
-        <v>0.45240000000000002</v>
+        <v>0.48809999999999998</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
@@ -5900,18 +5900,18 @@
         <v>30</v>
       </c>
       <c r="H163">
-        <v>5037</v>
+        <v>5718</v>
       </c>
       <c r="I163">
         <v>10950</v>
       </c>
       <c r="J163" s="1">
-        <v>0.46</v>
+        <v>0.5222</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
@@ -5932,18 +5932,18 @@
         <v>57</v>
       </c>
       <c r="H164">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I164">
         <v>228</v>
       </c>
       <c r="J164" s="1">
-        <v>0.35089999999999999</v>
+        <v>0.37280000000000002</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
@@ -6071,7 +6071,7 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B169" s="2">
         <v>2026</v>
@@ -6092,18 +6092,18 @@
         <v>9</v>
       </c>
       <c r="H169">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I169">
         <v>18</v>
       </c>
       <c r="J169" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.38890000000000002</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B170" s="2">
         <v>2026</v>
@@ -6124,18 +6124,18 @@
         <v>170</v>
       </c>
       <c r="H170">
-        <v>840</v>
+        <v>922</v>
       </c>
       <c r="I170">
         <v>2040</v>
       </c>
       <c r="J170" s="1">
-        <v>0.4118</v>
+        <v>0.45200000000000001</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B171" s="2">
         <v>2026</v>
@@ -6156,18 +6156,18 @@
         <v>36</v>
       </c>
       <c r="H171">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I171">
         <v>432</v>
       </c>
       <c r="J171" s="1">
-        <v>0.40739999999999998</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B172" s="2">
         <v>2026</v>
@@ -6188,18 +6188,18 @@
         <v>13</v>
       </c>
       <c r="H172">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I172">
         <v>156</v>
       </c>
       <c r="J172" s="1">
-        <v>0.4551</v>
+        <v>0.53849999999999998</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B173" s="2">
         <v>2026</v>
@@ -6220,18 +6220,18 @@
         <v>9</v>
       </c>
       <c r="H173">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I173">
         <v>108</v>
       </c>
       <c r="J173" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.43519999999999998</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B174" s="2">
         <v>2026</v>
@@ -6252,18 +6252,18 @@
         <v>88</v>
       </c>
       <c r="H174">
-        <v>451</v>
+        <v>499</v>
       </c>
       <c r="I174">
         <v>1056</v>
       </c>
       <c r="J174" s="1">
-        <v>0.42709999999999998</v>
+        <v>0.47249999999999998</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B175" s="2">
         <v>2026</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B176" s="2">
         <v>2026</v>
@@ -6316,18 +6316,18 @@
         <v>9</v>
       </c>
       <c r="H176">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="I176">
         <v>216</v>
       </c>
       <c r="J176" s="1">
-        <v>0.41199999999999998</v>
+        <v>0.45829999999999999</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B177" s="2">
         <v>2026</v>
@@ -6348,18 +6348,18 @@
         <v>9</v>
       </c>
       <c r="H177">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I177">
         <v>108</v>
       </c>
       <c r="J177" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47220000000000001</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B178" s="2">
         <v>2026</v>
@@ -6380,18 +6380,18 @@
         <v>59</v>
       </c>
       <c r="H178">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="I178">
         <v>708</v>
       </c>
       <c r="J178" s="1">
-        <v>0.39119999999999999</v>
+        <v>0.4647</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B179" s="2">
         <v>2026</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B180" s="2">
         <v>2026</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B181" s="2">
         <v>2026</v>
@@ -6476,18 +6476,18 @@
         <v>9</v>
       </c>
       <c r="H181">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I181">
         <v>36</v>
       </c>
       <c r="J181" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B182" s="2">
         <v>2026</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B183" s="2">
         <v>2026</v>
@@ -6540,18 +6540,18 @@
         <v>85</v>
       </c>
       <c r="H183">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I183">
         <v>85</v>
       </c>
       <c r="J183" s="1">
-        <v>0.54120000000000001</v>
+        <v>0.64710000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B184" s="2">
         <v>2026</v>
@@ -6583,7 +6583,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B185" s="2">
         <v>2026</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B186" s="2">
         <v>2026</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B187" s="2">
         <v>2026</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B188" s="2">
         <v>2026</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B189" s="2">
         <v>2026</v>
@@ -6732,18 +6732,18 @@
         <v>45</v>
       </c>
       <c r="H189">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I189">
         <v>45</v>
       </c>
       <c r="J189" s="1">
-        <v>0.66669999999999996</v>
+        <v>0.77780000000000005</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B190" s="2">
         <v>2026</v>
@@ -6764,18 +6764,18 @@
         <v>9</v>
       </c>
       <c r="H190">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I190">
         <v>36</v>
       </c>
       <c r="J190" s="1">
-        <v>0.38890000000000002</v>
+        <v>0.52780000000000005</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B191" s="2">
         <v>2026</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B192" s="2">
         <v>2026</v>
@@ -6828,18 +6828,18 @@
         <v>188993</v>
       </c>
       <c r="H192">
-        <v>942154</v>
+        <v>1093028</v>
       </c>
       <c r="I192">
         <v>2267916</v>
       </c>
       <c r="J192" s="1">
-        <v>0.41539999999999999</v>
+        <v>0.48199999999999998</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B193" s="2">
         <v>2026</v>
@@ -6860,18 +6860,18 @@
         <v>183511</v>
       </c>
       <c r="H193">
-        <v>152168</v>
+        <v>178573</v>
       </c>
       <c r="I193">
         <v>367022</v>
       </c>
       <c r="J193" s="1">
-        <v>0.41460000000000002</v>
+        <v>0.48649999999999999</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B194" s="2">
         <v>2026</v>
@@ -6892,18 +6892,18 @@
         <v>174</v>
       </c>
       <c r="H194">
-        <v>1738</v>
+        <v>1953</v>
       </c>
       <c r="I194">
         <v>4176</v>
       </c>
       <c r="J194" s="1">
-        <v>0.41620000000000001</v>
+        <v>0.4677</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B195" s="2">
         <v>2026</v>
@@ -6924,18 +6924,18 @@
         <v>188993</v>
       </c>
       <c r="H195">
-        <v>360377</v>
+        <v>366009</v>
       </c>
       <c r="I195">
         <v>755972</v>
       </c>
       <c r="J195" s="1">
-        <v>0.47670000000000001</v>
+        <v>0.48420000000000002</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B196" s="2">
         <v>2026</v>
@@ -6956,18 +6956,18 @@
         <v>188993</v>
       </c>
       <c r="H196">
-        <v>89422</v>
+        <v>101620</v>
       </c>
       <c r="I196">
         <v>188993</v>
       </c>
       <c r="J196" s="1">
-        <v>0.47310000000000002</v>
+        <v>0.53769999999999996</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B197" s="2">
         <v>2026</v>
@@ -6988,18 +6988,18 @@
         <v>98</v>
       </c>
       <c r="H197">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I197">
         <v>392</v>
       </c>
       <c r="J197" s="1">
-        <v>0.44900000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B198" s="2">
         <v>2026</v>
@@ -7020,18 +7020,18 @@
         <v>127</v>
       </c>
       <c r="H198">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I198">
         <v>127</v>
       </c>
       <c r="J198" s="1">
-        <v>0.42520000000000002</v>
+        <v>0.48820000000000002</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B199" s="2">
         <v>2026</v>
@@ -7052,18 +7052,18 @@
         <v>271</v>
       </c>
       <c r="H199">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="I199">
         <v>542</v>
       </c>
       <c r="J199" s="1">
-        <v>0.41699999999999998</v>
+        <v>0.48149999999999998</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B200" s="2">
         <v>2026</v>
@@ -7084,18 +7084,18 @@
         <v>133</v>
       </c>
       <c r="H200">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I200">
         <v>133</v>
       </c>
       <c r="J200" s="1">
-        <v>0.60150000000000003</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B201" s="2">
         <v>2026</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B202" s="2">
         <v>2026</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B203" s="2">
         <v>2026</v>
@@ -7180,18 +7180,18 @@
         <v>188377</v>
       </c>
       <c r="H203">
-        <v>877149</v>
+        <v>991757</v>
       </c>
       <c r="I203">
         <v>2260524</v>
       </c>
       <c r="J203" s="1">
-        <v>0.38800000000000001</v>
+        <v>0.43869999999999998</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B204" s="2">
         <v>2026</v>
@@ -7212,18 +7212,18 @@
         <v>9</v>
       </c>
       <c r="H204">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I204">
         <v>216</v>
       </c>
       <c r="J204" s="1">
-        <v>0.43980000000000002</v>
+        <v>0.47220000000000001</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B205" s="2">
         <v>2026</v>
@@ -7244,18 +7244,18 @@
         <v>263</v>
       </c>
       <c r="H205">
-        <v>2630</v>
+        <v>3140</v>
       </c>
       <c r="I205">
         <v>6312</v>
       </c>
       <c r="J205" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4975</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B206" s="2">
         <v>2026</v>
@@ -7276,18 +7276,18 @@
         <v>40</v>
       </c>
       <c r="H206">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="I206">
         <v>480</v>
       </c>
       <c r="J206" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46250000000000002</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B207" s="2">
         <v>2026</v>
@@ -7308,18 +7308,18 @@
         <v>408</v>
       </c>
       <c r="H207">
-        <v>2045</v>
+        <v>2216</v>
       </c>
       <c r="I207">
         <v>4896</v>
       </c>
       <c r="J207" s="1">
-        <v>0.41770000000000002</v>
+        <v>0.4526</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B208" s="2">
         <v>2026</v>
@@ -7340,18 +7340,18 @@
         <v>550</v>
       </c>
       <c r="H208">
-        <v>2750</v>
+        <v>3216</v>
       </c>
       <c r="I208">
         <v>6600</v>
       </c>
       <c r="J208" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48730000000000001</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B209" s="2">
         <v>2026</v>
@@ -7372,18 +7372,18 @@
         <v>76</v>
       </c>
       <c r="H209">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="I209">
         <v>912</v>
       </c>
       <c r="J209" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46820000000000001</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B210" s="2">
         <v>2026</v>
@@ -7404,18 +7404,18 @@
         <v>6</v>
       </c>
       <c r="H210">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I210">
         <v>144</v>
       </c>
       <c r="J210" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47920000000000001</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B211" s="2">
         <v>2026</v>
@@ -7436,18 +7436,18 @@
         <v>19</v>
       </c>
       <c r="H211">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I211">
         <v>228</v>
       </c>
       <c r="J211" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46489999999999998</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B212" s="2">
         <v>2026</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B213" s="2">
         <v>2026</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B214" s="2">
         <v>2026</v>
@@ -7532,18 +7532,18 @@
         <v>31</v>
       </c>
       <c r="H214">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I214">
         <v>372</v>
       </c>
       <c r="J214" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4597</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B215" s="2">
         <v>2026</v>
@@ -7564,18 +7564,18 @@
         <v>175</v>
       </c>
       <c r="H215">
-        <v>875</v>
+        <v>1001</v>
       </c>
       <c r="I215">
         <v>2100</v>
       </c>
       <c r="J215" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47670000000000001</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B216" s="2">
         <v>2026</v>
@@ -7596,18 +7596,18 @@
         <v>9</v>
       </c>
       <c r="H216">
-        <v>2400</v>
+        <v>2596</v>
       </c>
       <c r="I216">
         <v>3735</v>
       </c>
       <c r="J216" s="1">
-        <v>0.64259999999999995</v>
+        <v>0.69499999999999995</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B217" s="2">
         <v>2026</v>
@@ -7639,7 +7639,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B218" s="2">
         <v>2026</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B219" s="2">
         <v>2026</v>
@@ -7692,18 +7692,18 @@
         <v>34</v>
       </c>
       <c r="H219">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="I219">
         <v>132</v>
       </c>
       <c r="J219" s="1">
-        <v>0.75</v>
+        <v>0.85609999999999997</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B220" s="2">
         <v>2026</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B221" s="2">
         <v>2026</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B222" s="2">
         <v>2026</v>
@@ -7788,18 +7788,18 @@
         <v>3654</v>
       </c>
       <c r="H222">
-        <v>18270</v>
+        <v>21658</v>
       </c>
       <c r="I222">
         <v>43848</v>
       </c>
       <c r="J222" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49390000000000001</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B223" s="2">
         <v>2026</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B224" s="2">
         <v>2026</v>
@@ -7852,18 +7852,18 @@
         <v>486</v>
       </c>
       <c r="H224">
-        <v>4862</v>
+        <v>5758</v>
       </c>
       <c r="I224">
         <v>11664</v>
       </c>
       <c r="J224" s="1">
-        <v>0.4168</v>
+        <v>0.49370000000000003</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B225" s="2">
         <v>2026</v>
@@ -7884,18 +7884,18 @@
         <v>25</v>
       </c>
       <c r="H225">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="I225">
         <v>300</v>
       </c>
       <c r="J225" s="1">
-        <v>0.45</v>
+        <v>0.50329999999999997</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B226" s="2">
         <v>2026</v>
@@ -7916,18 +7916,18 @@
         <v>68</v>
       </c>
       <c r="H226">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="I226">
         <v>816</v>
       </c>
       <c r="J226" s="1">
-        <v>0.42159999999999997</v>
+        <v>0.45960000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B227" s="2">
         <v>2026</v>
@@ -7948,18 +7948,18 @@
         <v>729</v>
       </c>
       <c r="H227">
-        <v>3669</v>
+        <v>4177</v>
       </c>
       <c r="I227">
         <v>8772</v>
       </c>
       <c r="J227" s="1">
-        <v>0.41830000000000001</v>
+        <v>0.47620000000000001</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B228" s="2">
         <v>2026</v>
@@ -7980,18 +7980,18 @@
         <v>854</v>
       </c>
       <c r="H228">
-        <v>4594</v>
+        <v>5283</v>
       </c>
       <c r="I228">
         <v>11040</v>
       </c>
       <c r="J228" s="1">
-        <v>0.41610000000000003</v>
+        <v>0.47849999999999998</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B229" s="2">
         <v>2026</v>
@@ -8012,18 +8012,18 @@
         <v>121</v>
       </c>
       <c r="H229">
-        <v>606</v>
+        <v>663</v>
       </c>
       <c r="I229">
         <v>1452</v>
       </c>
       <c r="J229" s="1">
-        <v>0.41739999999999999</v>
+        <v>0.45660000000000001</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B230" s="2">
         <v>2026</v>
@@ -8044,18 +8044,18 @@
         <v>27</v>
       </c>
       <c r="H230">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="I230">
         <v>648</v>
       </c>
       <c r="J230" s="1">
-        <v>0.43359999999999999</v>
+        <v>0.50619999999999998</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B231" s="2">
         <v>2026</v>
@@ -8087,7 +8087,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B232" s="2">
         <v>2026</v>
@@ -8108,18 +8108,18 @@
         <v>30</v>
       </c>
       <c r="H232">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="I232">
         <v>360</v>
       </c>
       <c r="J232" s="1">
-        <v>0.44169999999999998</v>
+        <v>0.5111</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B233" s="2">
         <v>2026</v>
@@ -8140,18 +8140,18 @@
         <v>51</v>
       </c>
       <c r="H233">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="I233">
         <v>624</v>
       </c>
       <c r="J233" s="1">
-        <v>0.4375</v>
+        <v>0.4824</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B234" s="2">
         <v>2026</v>
@@ -8172,18 +8172,18 @@
         <v>337</v>
       </c>
       <c r="H234">
-        <v>1700</v>
+        <v>1973</v>
       </c>
       <c r="I234">
         <v>4044</v>
       </c>
       <c r="J234" s="1">
-        <v>0.4204</v>
+        <v>0.4879</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B235" s="2">
         <v>2026</v>
@@ -8204,18 +8204,18 @@
         <v>50</v>
       </c>
       <c r="H235">
-        <v>8911</v>
+        <v>10131</v>
       </c>
       <c r="I235">
         <v>18972</v>
       </c>
       <c r="J235" s="1">
-        <v>0.46970000000000001</v>
+        <v>0.53400000000000003</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B236" s="2">
         <v>2026</v>
@@ -8236,18 +8236,18 @@
         <v>58</v>
       </c>
       <c r="H236">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I236">
         <v>232</v>
       </c>
       <c r="J236" s="1">
-        <v>0.42670000000000002</v>
+        <v>0.44829999999999998</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B237" s="2">
         <v>2026</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B238" s="2">
         <v>2026</v>
@@ -8300,18 +8300,18 @@
         <v>56</v>
       </c>
       <c r="H238">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I238">
         <v>228</v>
       </c>
       <c r="J238" s="1">
-        <v>0.37719999999999998</v>
+        <v>0.40789999999999998</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B239" s="2">
         <v>2026</v>
@@ -8343,7 +8343,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B240" s="2">
         <v>2026</v>
@@ -8364,18 +8364,18 @@
         <v>4610</v>
       </c>
       <c r="H240">
-        <v>24021</v>
+        <v>25721</v>
       </c>
       <c r="I240">
         <v>55320</v>
       </c>
       <c r="J240" s="1">
-        <v>0.43419999999999997</v>
+        <v>0.46489999999999998</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B241" s="2">
         <v>2026</v>
@@ -8396,18 +8396,18 @@
         <v>44</v>
       </c>
       <c r="H241">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="I241">
         <v>468</v>
       </c>
       <c r="J241" s="1">
-        <v>0.43590000000000001</v>
+        <v>0.46789999999999998</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B242" s="2">
         <v>2026</v>
@@ -8439,7 +8439,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B243" s="2">
         <v>2026</v>
@@ -8460,18 +8460,18 @@
         <v>90</v>
       </c>
       <c r="H243">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="I243">
         <v>1080</v>
       </c>
       <c r="J243" s="1">
-        <v>0.42309999999999998</v>
+        <v>0.4713</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B244" s="2">
         <v>2026</v>
@@ -8492,18 +8492,18 @@
         <v>27</v>
       </c>
       <c r="H244">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I244">
         <v>192</v>
       </c>
       <c r="J244" s="1">
-        <v>0.42709999999999998</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B245" s="2">
         <v>2026</v>
@@ -8524,18 +8524,18 @@
         <v>121</v>
       </c>
       <c r="H245">
-        <v>597</v>
+        <v>654</v>
       </c>
       <c r="I245">
         <v>1428</v>
       </c>
       <c r="J245" s="1">
-        <v>0.41810000000000003</v>
+        <v>0.45800000000000002</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B246" s="2">
         <v>2026</v>
@@ -8567,7 +8567,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B247" s="2">
         <v>2026</v>
@@ -8588,18 +8588,18 @@
         <v>35</v>
       </c>
       <c r="H247">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="I247">
         <v>420</v>
       </c>
       <c r="J247" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4738</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B248" s="2">
         <v>2026</v>
@@ -8620,18 +8620,18 @@
         <v>228</v>
       </c>
       <c r="H248">
-        <v>1162</v>
+        <v>1351</v>
       </c>
       <c r="I248">
         <v>2784</v>
       </c>
       <c r="J248" s="1">
-        <v>0.41739999999999999</v>
+        <v>0.48530000000000001</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B249" s="2">
         <v>2026</v>
@@ -8652,18 +8652,18 @@
         <v>264</v>
       </c>
       <c r="H249">
-        <v>1792</v>
+        <v>2068</v>
       </c>
       <c r="I249">
         <v>4291</v>
       </c>
       <c r="J249" s="1">
-        <v>0.41760000000000003</v>
+        <v>0.4819</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B250" s="2">
         <v>2026</v>
@@ -8684,18 +8684,18 @@
         <v>33</v>
       </c>
       <c r="H250">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="I250">
         <v>384</v>
       </c>
       <c r="J250" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B251" s="2">
         <v>2026</v>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B252" s="2">
         <v>2026</v>
@@ -8748,18 +8748,18 @@
         <v>451</v>
       </c>
       <c r="H252">
-        <v>2224</v>
+        <v>2586</v>
       </c>
       <c r="I252">
         <v>5340</v>
       </c>
       <c r="J252" s="1">
-        <v>0.41649999999999998</v>
+        <v>0.48430000000000001</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B253" s="2">
         <v>2026</v>
@@ -8780,18 +8780,18 @@
         <v>66</v>
       </c>
       <c r="H253">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="I253">
         <v>792</v>
       </c>
       <c r="J253" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48110000000000003</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B254" s="2">
         <v>2026</v>
@@ -8812,18 +8812,18 @@
         <v>84</v>
       </c>
       <c r="H254">
-        <v>420</v>
+        <v>482</v>
       </c>
       <c r="I254">
         <v>1008</v>
       </c>
       <c r="J254" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47820000000000001</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B255" s="2">
         <v>2026</v>
@@ -8844,18 +8844,18 @@
         <v>23</v>
       </c>
       <c r="H255">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I255">
         <v>276</v>
       </c>
       <c r="J255" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46010000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B256" s="2">
         <v>2026</v>
@@ -8876,18 +8876,18 @@
         <v>14</v>
       </c>
       <c r="H256">
-        <v>2270</v>
+        <v>2612</v>
       </c>
       <c r="I256">
         <v>5110</v>
       </c>
       <c r="J256" s="1">
-        <v>0.44419999999999998</v>
+        <v>0.51119999999999999</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B257" s="2">
         <v>2026</v>
@@ -8908,18 +8908,18 @@
         <v>11</v>
       </c>
       <c r="H257">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I257">
         <v>44</v>
       </c>
       <c r="J257" s="1">
-        <v>0.4773</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B258" s="2">
         <v>2026</v>
@@ -8940,18 +8940,18 @@
         <v>11</v>
       </c>
       <c r="H258">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I258">
         <v>11</v>
       </c>
       <c r="J258" s="1">
-        <v>0.72729999999999995</v>
+        <v>0.81820000000000004</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B259" s="2">
         <v>2026</v>
@@ -8972,18 +8972,18 @@
         <v>34</v>
       </c>
       <c r="H259">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I259">
         <v>136</v>
       </c>
       <c r="J259" s="1">
-        <v>0.48530000000000001</v>
+        <v>0.49259999999999998</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B260" s="2">
         <v>2026</v>
@@ -9015,7 +9015,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B261" s="2">
         <v>2026</v>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B262" s="2">
         <v>2026</v>
@@ -9079,7 +9079,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B263" s="2">
         <v>2026</v>
@@ -9100,18 +9100,18 @@
         <v>33</v>
       </c>
       <c r="H263">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="I263">
         <v>396</v>
       </c>
       <c r="J263" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47470000000000001</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B264" s="2">
         <v>2026</v>
@@ -9132,18 +9132,18 @@
         <v>23</v>
       </c>
       <c r="H264">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I264">
         <v>276</v>
       </c>
       <c r="J264" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46010000000000001</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B265" s="2">
         <v>2026</v>
@@ -9164,18 +9164,18 @@
         <v>79</v>
       </c>
       <c r="H265">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="I265">
         <v>948</v>
       </c>
       <c r="J265" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47889999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B266" s="2">
         <v>2026</v>
@@ -9196,18 +9196,18 @@
         <v>276</v>
       </c>
       <c r="H266">
-        <v>2472</v>
+        <v>2712</v>
       </c>
       <c r="I266">
         <v>5904</v>
       </c>
       <c r="J266" s="1">
-        <v>0.41870000000000002</v>
+        <v>0.45929999999999999</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B267" s="2">
         <v>2026</v>
@@ -9228,18 +9228,18 @@
         <v>21</v>
       </c>
       <c r="H267">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="I267">
         <v>264</v>
       </c>
       <c r="J267" s="1">
-        <v>0.41289999999999999</v>
+        <v>0.48110000000000003</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B268" s="2">
         <v>2026</v>
@@ -9271,7 +9271,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B269" s="2">
         <v>2026</v>
@@ -9292,18 +9292,18 @@
         <v>74</v>
       </c>
       <c r="H269">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="I269">
         <v>888</v>
       </c>
       <c r="J269" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46510000000000001</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B270" s="2">
         <v>2026</v>
@@ -9324,18 +9324,18 @@
         <v>160</v>
       </c>
       <c r="H270">
-        <v>789</v>
+        <v>954</v>
       </c>
       <c r="I270">
         <v>1920</v>
       </c>
       <c r="J270" s="1">
-        <v>0.41089999999999999</v>
+        <v>0.49690000000000001</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B271" s="2">
         <v>2026</v>
@@ -9356,18 +9356,18 @@
         <v>82</v>
       </c>
       <c r="H271">
-        <v>813</v>
+        <v>947</v>
       </c>
       <c r="I271">
         <v>1968</v>
       </c>
       <c r="J271" s="1">
-        <v>0.41310000000000002</v>
+        <v>0.48120000000000002</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B272" s="2">
         <v>2026</v>
@@ -9388,18 +9388,18 @@
         <v>227</v>
       </c>
       <c r="H272">
-        <v>1126</v>
+        <v>1309</v>
       </c>
       <c r="I272">
         <v>2724</v>
       </c>
       <c r="J272" s="1">
-        <v>0.41339999999999999</v>
+        <v>0.48049999999999998</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A273" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B273" s="2">
         <v>2026</v>
@@ -9420,18 +9420,18 @@
         <v>172</v>
       </c>
       <c r="H273">
-        <v>1703</v>
+        <v>1918</v>
       </c>
       <c r="I273">
         <v>4128</v>
       </c>
       <c r="J273" s="1">
-        <v>0.41249999999999998</v>
+        <v>0.46460000000000001</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A274" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B274" s="2">
         <v>2026</v>
@@ -9452,18 +9452,18 @@
         <v>3</v>
       </c>
       <c r="H274">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I274">
         <v>36</v>
       </c>
       <c r="J274" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A275" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B275" s="2">
         <v>2026</v>
@@ -9484,18 +9484,18 @@
         <v>110</v>
       </c>
       <c r="H275">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="I275">
         <v>1320</v>
       </c>
       <c r="J275" s="1">
-        <v>0.41210000000000002</v>
+        <v>0.44769999999999999</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A276" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B276" s="2">
         <v>2026</v>
@@ -9516,18 +9516,18 @@
         <v>311</v>
       </c>
       <c r="H276">
-        <v>1542</v>
+        <v>1703</v>
       </c>
       <c r="I276">
         <v>3732</v>
       </c>
       <c r="J276" s="1">
-        <v>0.41320000000000001</v>
+        <v>0.45629999999999998</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A277" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B277" s="2">
         <v>2026</v>
@@ -9548,18 +9548,18 @@
         <v>286</v>
       </c>
       <c r="H277">
-        <v>1440</v>
+        <v>1515</v>
       </c>
       <c r="I277">
         <v>3432</v>
       </c>
       <c r="J277" s="1">
-        <v>0.41959999999999997</v>
+        <v>0.44140000000000001</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A278" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B278" s="2">
         <v>2026</v>
@@ -9580,18 +9580,18 @@
         <v>12</v>
       </c>
       <c r="H278">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I278">
         <v>144</v>
       </c>
       <c r="J278" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A279" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B279" s="2">
         <v>2026</v>
@@ -9612,18 +9612,18 @@
         <v>85</v>
       </c>
       <c r="H279">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="I279">
         <v>1020</v>
       </c>
       <c r="J279" s="1">
-        <v>0.38329999999999997</v>
+        <v>0.44219999999999998</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A280" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B280" s="2">
         <v>2026</v>
@@ -9644,18 +9644,18 @@
         <v>44</v>
       </c>
       <c r="H280">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="I280">
         <v>528</v>
       </c>
       <c r="J280" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A281" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B281" s="2">
         <v>2026</v>
@@ -9676,18 +9676,18 @@
         <v>47</v>
       </c>
       <c r="H281">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="I281">
         <v>564</v>
       </c>
       <c r="J281" s="1">
-        <v>0.41839999999999999</v>
+        <v>0.48759999999999998</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A282" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B282" s="2">
         <v>2026</v>
@@ -9708,18 +9708,18 @@
         <v>17</v>
       </c>
       <c r="H282">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I282">
         <v>204</v>
       </c>
       <c r="J282" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49020000000000002</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A283" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B283" s="2">
         <v>2026</v>
@@ -9740,18 +9740,18 @@
         <v>16</v>
       </c>
       <c r="H283">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="I283">
         <v>384</v>
       </c>
       <c r="J283" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47920000000000001</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A284" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B284" s="2">
         <v>2026</v>
@@ -9772,18 +9772,18 @@
         <v>91</v>
       </c>
       <c r="H284">
-        <v>454</v>
+        <v>489</v>
       </c>
       <c r="I284">
         <v>1092</v>
       </c>
       <c r="J284" s="1">
-        <v>0.4158</v>
+        <v>0.44779999999999998</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A285" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B285" s="2">
         <v>2026</v>
@@ -9804,18 +9804,18 @@
         <v>48</v>
       </c>
       <c r="H285">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="I285">
         <v>564</v>
       </c>
       <c r="J285" s="1">
-        <v>0.41839999999999999</v>
+        <v>0.47339999999999999</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A286" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B286" s="2">
         <v>2026</v>
@@ -9836,18 +9836,18 @@
         <v>16</v>
       </c>
       <c r="H286">
-        <v>2340</v>
+        <v>2544</v>
       </c>
       <c r="I286">
         <v>5842</v>
       </c>
       <c r="J286" s="1">
-        <v>0.40050000000000002</v>
+        <v>0.4355</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A287" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B287" s="2">
         <v>2026</v>
@@ -9879,7 +9879,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A288" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B288" s="2">
         <v>2026</v>
@@ -9911,7 +9911,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A289" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B289" s="2">
         <v>2026</v>
@@ -9932,18 +9932,18 @@
         <v>44</v>
       </c>
       <c r="H289">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I289">
         <v>180</v>
       </c>
       <c r="J289" s="1">
-        <v>0.4556</v>
+        <v>0.5111</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A290" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B290" s="2">
         <v>2026</v>
@@ -9975,7 +9975,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A291" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B291" s="2">
         <v>2026</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A292" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B292" s="2">
         <v>2026</v>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A293" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B293" s="2">
         <v>2026</v>
@@ -10060,18 +10060,18 @@
         <v>228</v>
       </c>
       <c r="H293">
-        <v>1126</v>
+        <v>1260</v>
       </c>
       <c r="I293">
         <v>2736</v>
       </c>
       <c r="J293" s="1">
-        <v>0.41149999999999998</v>
+        <v>0.46050000000000002</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A294" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B294" s="2">
         <v>2026</v>
@@ -10092,18 +10092,18 @@
         <v>24</v>
       </c>
       <c r="H294">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="I294">
         <v>300</v>
       </c>
       <c r="J294" s="1">
-        <v>0.38669999999999999</v>
+        <v>0.45329999999999998</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A295" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B295" s="2">
         <v>2026</v>
@@ -10124,18 +10124,18 @@
         <v>185</v>
       </c>
       <c r="H295">
-        <v>929</v>
+        <v>985</v>
       </c>
       <c r="I295">
         <v>2196</v>
       </c>
       <c r="J295" s="1">
-        <v>0.42299999999999999</v>
+        <v>0.44850000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A296" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B296" s="2">
         <v>2026</v>
@@ -10156,18 +10156,18 @@
         <v>87</v>
       </c>
       <c r="H296">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="I296">
         <v>1044</v>
       </c>
       <c r="J296" s="1">
-        <v>0.41089999999999999</v>
+        <v>0.46839999999999998</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A297" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B297" s="2">
         <v>2026</v>
@@ -10188,18 +10188,18 @@
         <v>96</v>
       </c>
       <c r="H297">
-        <v>960</v>
+        <v>1133</v>
       </c>
       <c r="I297">
         <v>2304</v>
       </c>
       <c r="J297" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49180000000000001</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A298" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B298" s="2">
         <v>2026</v>
@@ -10220,18 +10220,18 @@
         <v>17</v>
       </c>
       <c r="H298">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I298">
         <v>204</v>
       </c>
       <c r="J298" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.49020000000000002</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A299" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B299" s="2">
         <v>2026</v>
@@ -10252,18 +10252,18 @@
         <v>109</v>
       </c>
       <c r="H299">
-        <v>545</v>
+        <v>637</v>
       </c>
       <c r="I299">
         <v>1308</v>
       </c>
       <c r="J299" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48699999999999999</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A300" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B300" s="2">
         <v>2026</v>
@@ -10284,18 +10284,18 @@
         <v>8</v>
       </c>
       <c r="H300">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I300">
         <v>96</v>
       </c>
       <c r="J300" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.45829999999999999</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A301" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B301" s="2">
         <v>2026</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A302" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B302" s="2">
         <v>2026</v>
@@ -10348,18 +10348,18 @@
         <v>5</v>
       </c>
       <c r="H302">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I302">
         <v>120</v>
       </c>
       <c r="J302" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A303" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B303" s="2">
         <v>2026</v>
@@ -10380,18 +10380,18 @@
         <v>17</v>
       </c>
       <c r="H303">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I303">
         <v>204</v>
       </c>
       <c r="J303" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48530000000000001</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A304" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B304" s="2">
         <v>2026</v>
@@ -10412,18 +10412,18 @@
         <v>7</v>
       </c>
       <c r="H304">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I304">
         <v>84</v>
       </c>
       <c r="J304" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A305" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B305" s="2">
         <v>2026</v>
@@ -10444,18 +10444,18 @@
         <v>200</v>
       </c>
       <c r="H305">
-        <v>1000</v>
+        <v>1162</v>
       </c>
       <c r="I305">
         <v>2400</v>
       </c>
       <c r="J305" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48420000000000002</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A306" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B306" s="2">
         <v>2026</v>
@@ -10476,18 +10476,18 @@
         <v>14</v>
       </c>
       <c r="H306">
-        <v>2114</v>
+        <v>2324</v>
       </c>
       <c r="I306">
         <v>5110</v>
       </c>
       <c r="J306" s="1">
-        <v>0.41370000000000001</v>
+        <v>0.45479999999999998</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A307" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B307" s="2">
         <v>2026</v>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A308" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B308" s="2">
         <v>2026</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A309" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B309" s="2">
         <v>2026</v>
@@ -10583,7 +10583,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A310" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B310" s="2">
         <v>2026</v>
@@ -10615,7 +10615,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A311" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B311" s="2">
         <v>2026</v>
@@ -10636,18 +10636,18 @@
         <v>10</v>
       </c>
       <c r="H311">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I311">
         <v>120</v>
       </c>
       <c r="J311" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A312" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B312" s="2">
         <v>2026</v>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A313" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B313" s="2">
         <v>2026</v>
@@ -10700,18 +10700,18 @@
         <v>39</v>
       </c>
       <c r="H313">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="I313">
         <v>468</v>
       </c>
       <c r="J313" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A314" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B314" s="2">
         <v>2026</v>
@@ -10732,18 +10732,18 @@
         <v>778</v>
       </c>
       <c r="H314">
-        <v>3890</v>
+        <v>4391</v>
       </c>
       <c r="I314">
         <v>9336</v>
       </c>
       <c r="J314" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4703</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A315" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B315" s="2">
         <v>2026</v>
@@ -10764,18 +10764,18 @@
         <v>392</v>
       </c>
       <c r="H315">
-        <v>3933</v>
+        <v>4572</v>
       </c>
       <c r="I315">
         <v>9408</v>
       </c>
       <c r="J315" s="1">
-        <v>0.41799999999999998</v>
+        <v>0.48599999999999999</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A316" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B316" s="2">
         <v>2026</v>
@@ -10796,18 +10796,18 @@
         <v>7</v>
       </c>
       <c r="H316">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I316">
         <v>84</v>
       </c>
       <c r="J316" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A317" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B317" s="2">
         <v>2026</v>
@@ -10828,18 +10828,18 @@
         <v>9</v>
       </c>
       <c r="H317">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I317">
         <v>108</v>
       </c>
       <c r="J317" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.45369999999999999</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A318" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B318" s="2">
         <v>2026</v>
@@ -10860,18 +10860,18 @@
         <v>145</v>
       </c>
       <c r="H318">
-        <v>725</v>
+        <v>826</v>
       </c>
       <c r="I318">
         <v>1740</v>
       </c>
       <c r="J318" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47470000000000001</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A319" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B319" s="2">
         <v>2026</v>
@@ -10892,18 +10892,18 @@
         <v>925</v>
       </c>
       <c r="H319">
-        <v>4625</v>
+        <v>5181</v>
       </c>
       <c r="I319">
         <v>11100</v>
       </c>
       <c r="J319" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.46679999999999999</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A320" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B320" s="2">
         <v>2026</v>
@@ -10924,18 +10924,18 @@
         <v>45</v>
       </c>
       <c r="H320">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="I320">
         <v>540</v>
       </c>
       <c r="J320" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4556</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B321" s="2">
         <v>2026</v>
@@ -10956,18 +10956,18 @@
         <v>24</v>
       </c>
       <c r="H321">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="I321">
         <v>576</v>
       </c>
       <c r="J321" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B322" s="2">
         <v>2026</v>
@@ -10988,18 +10988,18 @@
         <v>25</v>
       </c>
       <c r="H322">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="I322">
         <v>300</v>
       </c>
       <c r="J322" s="1">
-        <v>0.42670000000000002</v>
+        <v>0.48670000000000002</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B323" s="2">
         <v>2026</v>
@@ -11020,18 +11020,18 @@
         <v>25</v>
       </c>
       <c r="H323">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="I323">
         <v>420</v>
       </c>
       <c r="J323" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48099999999999998</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B324" s="2">
         <v>2026</v>
@@ -11052,18 +11052,18 @@
         <v>4</v>
       </c>
       <c r="H324">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I324">
         <v>48</v>
       </c>
       <c r="J324" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B325" s="2">
         <v>2026</v>
@@ -11084,18 +11084,18 @@
         <v>16</v>
       </c>
       <c r="H325">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I325">
         <v>192</v>
       </c>
       <c r="J325" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B326" s="2">
         <v>2026</v>
@@ -11116,18 +11116,18 @@
         <v>4</v>
       </c>
       <c r="H326">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I326">
         <v>48</v>
       </c>
       <c r="J326" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.45829999999999999</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A327" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B327" s="2">
         <v>2026</v>
@@ -11148,18 +11148,18 @@
         <v>105</v>
       </c>
       <c r="H327">
-        <v>14398</v>
+        <v>16440</v>
       </c>
       <c r="I327">
         <v>38325</v>
       </c>
       <c r="J327" s="1">
-        <v>0.37569999999999998</v>
+        <v>0.42899999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A328" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B328" s="2">
         <v>2026</v>
@@ -11180,18 +11180,18 @@
         <v>65</v>
       </c>
       <c r="H328">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I328">
         <v>260</v>
       </c>
       <c r="J328" s="1">
-        <v>0.43459999999999999</v>
+        <v>0.49230000000000002</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A329" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B329" s="2">
         <v>2026</v>
@@ -11223,7 +11223,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A330" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B330" s="2">
         <v>2026</v>
@@ -11255,7 +11255,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A331" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B331" s="2">
         <v>2026</v>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A332" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B332" s="2">
         <v>2026</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A333" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B333" s="2">
         <v>2026</v>
@@ -11351,7 +11351,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A334" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B334" s="2">
         <v>2026</v>
@@ -11372,18 +11372,18 @@
         <v>33</v>
       </c>
       <c r="H334">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="I334">
         <v>396</v>
       </c>
       <c r="J334" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48230000000000001</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A335" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B335" s="2">
         <v>2026</v>
@@ -11404,18 +11404,18 @@
         <v>11</v>
       </c>
       <c r="H335">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I335">
         <v>132</v>
       </c>
       <c r="J335" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48480000000000001</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A336" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B336" s="2">
         <v>2026</v>
@@ -11436,18 +11436,18 @@
         <v>23</v>
       </c>
       <c r="H336">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="I336">
         <v>276</v>
       </c>
       <c r="J336" s="1">
-        <v>0.42749999999999999</v>
+        <v>0.49280000000000002</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A337" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B337" s="2">
         <v>2026</v>
@@ -11468,18 +11468,18 @@
         <v>3536</v>
       </c>
       <c r="H337">
-        <v>17680</v>
+        <v>20676</v>
       </c>
       <c r="I337">
         <v>42432</v>
       </c>
       <c r="J337" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48730000000000001</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A338" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B338" s="2">
         <v>2026</v>
@@ -11500,18 +11500,18 @@
         <v>277</v>
       </c>
       <c r="H338">
-        <v>2783</v>
+        <v>3160</v>
       </c>
       <c r="I338">
         <v>6648</v>
       </c>
       <c r="J338" s="1">
-        <v>0.41860000000000003</v>
+        <v>0.4753</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A339" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B339" s="2">
         <v>2026</v>
@@ -11532,18 +11532,18 @@
         <v>129</v>
       </c>
       <c r="H339">
-        <v>649</v>
+        <v>751</v>
       </c>
       <c r="I339">
         <v>1548</v>
       </c>
       <c r="J339" s="1">
-        <v>0.41930000000000001</v>
+        <v>0.48509999999999998</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A340" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B340" s="2">
         <v>2026</v>
@@ -11564,18 +11564,18 @@
         <v>553</v>
       </c>
       <c r="H340">
-        <v>2800</v>
+        <v>3127</v>
       </c>
       <c r="I340">
         <v>6636</v>
       </c>
       <c r="J340" s="1">
-        <v>0.4219</v>
+        <v>0.47120000000000001</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A341" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B341" s="2">
         <v>2026</v>
@@ -11596,18 +11596,18 @@
         <v>315</v>
       </c>
       <c r="H341">
-        <v>1576</v>
+        <v>1761</v>
       </c>
       <c r="I341">
         <v>3780</v>
       </c>
       <c r="J341" s="1">
-        <v>0.41689999999999999</v>
+        <v>0.46589999999999998</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A342" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B342" s="2">
         <v>2026</v>
@@ -11628,18 +11628,18 @@
         <v>20</v>
       </c>
       <c r="H342">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="I342">
         <v>240</v>
       </c>
       <c r="J342" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.48330000000000001</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A343" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B343" s="2">
         <v>2026</v>
@@ -11660,18 +11660,18 @@
         <v>19</v>
       </c>
       <c r="H343">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="I343">
         <v>228</v>
       </c>
       <c r="J343" s="1">
-        <v>0.42109999999999997</v>
+        <v>0.47810000000000002</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A344" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B344" s="2">
         <v>2026</v>
@@ -11692,18 +11692,18 @@
         <v>19</v>
       </c>
       <c r="H344">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="I344">
         <v>456</v>
       </c>
       <c r="J344" s="1">
-        <v>0.40129999999999999</v>
+        <v>0.44740000000000002</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A345" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B345" s="2">
         <v>2026</v>
@@ -11724,18 +11724,18 @@
         <v>86</v>
       </c>
       <c r="H345">
-        <v>429</v>
+        <v>498</v>
       </c>
       <c r="I345">
         <v>1032</v>
       </c>
       <c r="J345" s="1">
-        <v>0.41570000000000001</v>
+        <v>0.48259999999999997</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A346" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B346" s="2">
         <v>2026</v>
@@ -11756,18 +11756,18 @@
         <v>2</v>
       </c>
       <c r="H346">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I346">
         <v>24</v>
       </c>
       <c r="J346" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A347" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B347" s="2">
         <v>2026</v>
@@ -11788,18 +11788,18 @@
         <v>32</v>
       </c>
       <c r="H347">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="I347">
         <v>384</v>
       </c>
       <c r="J347" s="1">
-        <v>0.40889999999999999</v>
+        <v>0.46350000000000002</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A348" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B348" s="2">
         <v>2026</v>
@@ -11820,18 +11820,18 @@
         <v>615</v>
       </c>
       <c r="H348">
-        <v>3080</v>
+        <v>3541</v>
       </c>
       <c r="I348">
         <v>7380</v>
       </c>
       <c r="J348" s="1">
-        <v>0.4173</v>
+        <v>0.4798</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A349" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B349" s="2">
         <v>2026</v>
@@ -11849,21 +11849,21 @@
         <v>76</v>
       </c>
       <c r="G349">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="H349">
-        <v>7804</v>
+        <v>8010</v>
       </c>
       <c r="I349">
-        <v>17695</v>
+        <v>17472</v>
       </c>
       <c r="J349" s="1">
-        <v>0.441</v>
+        <v>0.45839999999999997</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A350" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B350" s="2">
         <v>2026</v>
@@ -11881,21 +11881,21 @@
         <v>27</v>
       </c>
       <c r="G350">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="H350">
         <v>313</v>
       </c>
       <c r="I350">
-        <v>700</v>
+        <v>204</v>
       </c>
       <c r="J350" s="1">
-        <v>0.4471</v>
+        <v>1.5343</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A351" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B351" s="2">
         <v>2026</v>
@@ -11913,21 +11913,21 @@
         <v>34</v>
       </c>
       <c r="G351">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="H351">
         <v>178</v>
       </c>
       <c r="I351">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="J351" s="1">
-        <v>1.0170999999999999</v>
+        <v>3.4902000000000002</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A352" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B352" s="2">
         <v>2026</v>
@@ -11959,7 +11959,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A353" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B353" s="2">
         <v>2026</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A354" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B354" s="2">
         <v>2026</v>
@@ -12012,18 +12012,18 @@
         <v>13</v>
       </c>
       <c r="H354">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I354">
         <v>26</v>
       </c>
       <c r="J354" s="1">
-        <v>0.46150000000000002</v>
+        <v>0.53849999999999998</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B355" s="2">
         <v>2026</v>
@@ -12044,18 +12044,18 @@
         <v>50</v>
       </c>
       <c r="H355">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="I355">
         <v>600</v>
       </c>
       <c r="J355" s="1">
-        <v>0.41670000000000001</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B356" s="2">
         <v>2026</v>
@@ -12076,18 +12076,18 @@
         <v>48</v>
       </c>
       <c r="H356">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="I356">
         <v>576</v>
       </c>
       <c r="J356" s="1">
-        <v>0.41320000000000001</v>
+        <v>0.48959999999999998</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B357" s="2">
         <v>2026</v>
@@ -12108,18 +12108,18 @@
         <v>17</v>
       </c>
       <c r="H357">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I357">
         <v>204</v>
       </c>
       <c r="J357" s="1">
-        <v>0.4118</v>
+        <v>0.45100000000000001</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B358" s="2">
         <v>2026</v>
@@ -12140,18 +12140,18 @@
         <v>62</v>
       </c>
       <c r="H358">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="I358">
         <v>744</v>
       </c>
       <c r="J358" s="1">
-        <v>0.40589999999999998</v>
+        <v>0.46910000000000002</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="3">
-        <v>46173</v>
+        <v>46195</v>
       </c>
       <c r="B359" s="2">
         <v>2026</v>
@@ -12163,27 +12163,55 @@
         <v>22</v>
       </c>
       <c r="E359" t="s">
+        <v>88</v>
+      </c>
+      <c r="F359" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G359">
+        <v>29</v>
+      </c>
+      <c r="H359">
+        <v>40</v>
+      </c>
+      <c r="I359">
+        <v>348</v>
+      </c>
+      <c r="J359" s="1">
+        <v>0.1149</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A360" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B360" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E360" t="s">
         <v>89</v>
       </c>
-      <c r="F359" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G359">
+      <c r="F360" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G360">
         <v>25</v>
       </c>
-      <c r="H359">
-        <v>129</v>
-      </c>
-      <c r="I359">
+      <c r="H360">
+        <v>146</v>
+      </c>
+      <c r="I360">
         <v>300</v>
       </c>
-      <c r="J359" s="1">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A360" s="3"/>
-      <c r="J360" s="1"/>
+      <c r="J360" s="1">
+        <v>0.48670000000000002</v>
+      </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="3"/>

--- a/data/Rekakapitulasi-Perawatan.xlsx
+++ b/data/Rekakapitulasi-Perawatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\6. Jun\KP\Perawatan Peralatan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFDAFA7-C6A6-4A16-993F-F585C1EABC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FBB706-276E-4B48-8E3F-FCA3D7D9FD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{89E2D6B6-1DCD-4189-A113-A83F3B882A03}"/>
   </bookViews>
@@ -727,7 +727,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="2">
         <v>2026</v>
@@ -748,18 +748,18 @@
         <v>59</v>
       </c>
       <c r="H2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="I2">
         <v>1416</v>
       </c>
       <c r="J2" s="1">
-        <v>0.48309999999999997</v>
+        <v>0.49790000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -812,18 +812,18 @@
         <v>59</v>
       </c>
       <c r="H4">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I4">
         <v>708</v>
       </c>
       <c r="J4" s="1">
-        <v>0.49009999999999998</v>
+        <v>0.50139999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B5" s="2">
         <v>2026</v>
@@ -844,18 +844,18 @@
         <v>398</v>
       </c>
       <c r="H5">
-        <v>2261</v>
+        <v>2370</v>
       </c>
       <c r="I5">
         <v>4776</v>
       </c>
       <c r="J5" s="1">
-        <v>0.47339999999999999</v>
+        <v>0.49619999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -876,18 +876,18 @@
         <v>398</v>
       </c>
       <c r="H6">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="I6">
         <v>398</v>
       </c>
       <c r="J6" s="1">
-        <v>0.6482</v>
+        <v>0.71109999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -908,18 +908,18 @@
         <v>64</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7">
         <v>128</v>
       </c>
       <c r="J7" s="1">
-        <v>0.49220000000000003</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -940,18 +940,18 @@
         <v>61</v>
       </c>
       <c r="H8">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I8">
         <v>244</v>
       </c>
       <c r="J8" s="1">
-        <v>0.48359999999999997</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -972,18 +972,18 @@
         <v>59</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I9">
         <v>59</v>
       </c>
       <c r="J9" s="1">
-        <v>0.76270000000000004</v>
+        <v>0.81359999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -1004,18 +1004,18 @@
         <v>161</v>
       </c>
       <c r="H10">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I10">
         <v>161</v>
       </c>
       <c r="J10" s="1">
-        <v>0.35399999999999998</v>
+        <v>0.37269999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1036,18 +1036,18 @@
         <v>265</v>
       </c>
       <c r="H11">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I11">
         <v>265</v>
       </c>
       <c r="J11" s="1">
-        <v>0.34720000000000001</v>
+        <v>0.36230000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1068,18 +1068,18 @@
         <v>72</v>
       </c>
       <c r="H12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I12">
         <v>72</v>
       </c>
       <c r="J12" s="1">
-        <v>0.47220000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1100,18 +1100,18 @@
         <v>289</v>
       </c>
       <c r="H13">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I13">
         <v>289</v>
       </c>
       <c r="J13" s="1">
-        <v>0.4083</v>
+        <v>0.4602</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1132,18 +1132,18 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
       <c r="J14" s="1">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1164,18 +1164,18 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <v>60</v>
       </c>
       <c r="J15" s="1">
-        <v>0.48330000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1196,18 +1196,18 @@
         <v>395</v>
       </c>
       <c r="H16">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="I16">
         <v>395</v>
       </c>
       <c r="J16" s="1">
-        <v>0.68610000000000004</v>
+        <v>0.75190000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1228,18 +1228,18 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I17">
         <v>400</v>
       </c>
       <c r="J17" s="1">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1260,18 +1260,18 @@
         <v>245</v>
       </c>
       <c r="H18">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I18">
         <v>245</v>
       </c>
       <c r="J18" s="1">
-        <v>0.47760000000000002</v>
+        <v>0.51429999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1292,18 +1292,18 @@
         <v>69</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I19">
         <v>276</v>
       </c>
       <c r="J19" s="1">
-        <v>0.45650000000000002</v>
+        <v>0.4783</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1324,18 +1324,18 @@
         <v>61</v>
       </c>
       <c r="H20">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20">
         <v>61</v>
       </c>
       <c r="J20" s="1">
-        <v>0.39340000000000003</v>
+        <v>0.42620000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1388,18 +1388,18 @@
         <v>691280</v>
       </c>
       <c r="H22">
-        <v>3995932</v>
+        <v>4149381</v>
       </c>
       <c r="I22">
         <v>8295360</v>
       </c>
       <c r="J22" s="1">
-        <v>0.48170000000000002</v>
+        <v>0.50019999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
@@ -1420,18 +1420,18 @@
         <v>689046</v>
       </c>
       <c r="H23">
-        <v>634235.30000000005</v>
+        <v>681815.3</v>
       </c>
       <c r="I23">
         <v>1378092</v>
       </c>
       <c r="J23" s="1">
-        <v>0.4602</v>
+        <v>0.49480000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
@@ -1452,18 +1452,18 @@
         <v>647</v>
       </c>
       <c r="H24">
-        <v>7408</v>
+        <v>7800</v>
       </c>
       <c r="I24">
         <v>15528</v>
       </c>
       <c r="J24" s="1">
-        <v>0.47710000000000002</v>
+        <v>0.50229999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
@@ -1484,18 +1484,18 @@
         <v>691280</v>
       </c>
       <c r="H25">
-        <v>1353557</v>
+        <v>1372516</v>
       </c>
       <c r="I25">
         <v>2765120</v>
       </c>
       <c r="J25" s="1">
-        <v>0.48949999999999999</v>
+        <v>0.49640000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
@@ -1516,18 +1516,18 @@
         <v>691280</v>
       </c>
       <c r="H26">
-        <v>433791</v>
+        <v>445361</v>
       </c>
       <c r="I26">
         <v>691280</v>
       </c>
       <c r="J26" s="1">
-        <v>0.62749999999999995</v>
+        <v>0.64429999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
@@ -1548,18 +1548,18 @@
         <v>346</v>
       </c>
       <c r="H27">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="I27">
         <v>1384</v>
       </c>
       <c r="J27" s="1">
-        <v>0.47760000000000002</v>
+        <v>0.49349999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
@@ -1580,18 +1580,18 @@
         <v>501</v>
       </c>
       <c r="H28">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="I28">
         <v>501</v>
       </c>
       <c r="J28" s="1">
-        <v>0.61480000000000001</v>
+        <v>0.66269999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
@@ -1609,21 +1609,21 @@
         <v>28</v>
       </c>
       <c r="G29">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="H29">
-        <v>1037</v>
+        <v>1104</v>
       </c>
       <c r="I29">
-        <v>2218</v>
+        <v>2210</v>
       </c>
       <c r="J29" s="1">
-        <v>0.46750000000000003</v>
+        <v>0.4995</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
@@ -1641,21 +1641,21 @@
         <v>34</v>
       </c>
       <c r="G30">
-        <v>649</v>
+        <v>652</v>
       </c>
     